--- a/assets/excel/IPCse - Series históricas.xlsx
+++ b/assets/excel/IPCse - Series históricas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iaral\Dropbox\IPC seasonal adjustment\IPCse\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A642022-764F-437F-992E-19F49E1A244C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91FC60AB-622B-4ADA-B77A-AD8ACF259F74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{A81B6F3A-9175-42CA-B78F-287A4E3C6249}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{A81B6F3A-9175-42CA-B78F-287A4E3C6249}"/>
   </bookViews>
   <sheets>
     <sheet name="Índices" sheetId="1" r:id="rId1"/>
@@ -203,9 +203,6 @@
 Tasa de Inflación Mensual por Quintiles</t>
   </si>
   <si>
-    <t>Ago.</t>
-  </si>
-  <si>
     <t>Sep.</t>
   </si>
   <si>
@@ -219,6 +216,9 @@
   </si>
   <si>
     <t>Ene.</t>
+  </si>
+  <si>
+    <t>Feb.</t>
   </si>
 </sst>
 </file>
@@ -1287,7 +1287,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA821952-0137-4F39-844C-15CA99AC928E}">
-  <dimension ref="B1:V114"/>
+  <dimension ref="B1:V115"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="15.5703125" defaultRowHeight="18" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="4" customWidth="1"/>
@@ -8504,69 +8504,134 @@
         <v>9950.2065999999995</v>
       </c>
     </row>
-    <row r="114" spans="2:22" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B114" s="14">
+    <row r="114" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B114" s="13">
         <v>46023</v>
       </c>
-      <c r="C114" s="18">
+      <c r="C114" s="15">
         <v>10447.616599999999</v>
       </c>
-      <c r="D114" s="19">
+      <c r="D114" s="16">
         <v>10427.264499999999</v>
       </c>
-      <c r="E114" s="19">
+      <c r="E114" s="16">
         <v>10394.1335</v>
       </c>
-      <c r="F114" s="19">
+      <c r="F114" s="16">
         <v>10445.439399999999</v>
       </c>
-      <c r="G114" s="19">
+      <c r="G114" s="16">
         <v>10299.0033</v>
       </c>
-      <c r="H114" s="19">
+      <c r="H114" s="16">
         <v>10565.299800000001</v>
       </c>
-      <c r="I114" s="20">
+      <c r="I114" s="17">
         <v>10571.6165</v>
       </c>
-      <c r="J114" s="19">
+      <c r="J114" s="16">
         <v>11182.2269</v>
       </c>
-      <c r="K114" s="19">
+      <c r="K114" s="16">
         <v>7522.57</v>
       </c>
-      <c r="L114" s="19">
+      <c r="L114" s="16">
         <v>7915.9506000000001</v>
       </c>
-      <c r="M114" s="19">
+      <c r="M114" s="16">
         <v>10917.5939</v>
       </c>
-      <c r="N114" s="19">
+      <c r="N114" s="16">
         <v>8591.4308999999994</v>
       </c>
-      <c r="O114" s="19">
+      <c r="O114" s="16">
         <v>11608.8086</v>
       </c>
-      <c r="P114" s="19">
+      <c r="P114" s="16">
         <v>10925.223400000001</v>
       </c>
-      <c r="Q114" s="19">
+      <c r="Q114" s="16">
         <v>9535.8953000000001</v>
       </c>
-      <c r="R114" s="19">
+      <c r="R114" s="16">
         <v>9214.2831000000006</v>
       </c>
-      <c r="S114" s="19">
+      <c r="S114" s="16">
         <v>10219.718699999999</v>
       </c>
-      <c r="T114" s="19">
+      <c r="T114" s="16">
         <v>12834.644700000001</v>
       </c>
-      <c r="U114" s="20">
+      <c r="U114" s="17">
         <v>10147.018700000001</v>
       </c>
-      <c r="V114" s="18">
+      <c r="V114" s="15">
         <v>10201.693499999999</v>
+      </c>
+    </row>
+    <row r="115" spans="2:22" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B115" s="14">
+        <v>46054</v>
+      </c>
+      <c r="C115" s="18">
+        <v>10713.0087</v>
+      </c>
+      <c r="D115" s="19">
+        <v>10665.4244</v>
+      </c>
+      <c r="E115" s="19">
+        <v>10677.3019</v>
+      </c>
+      <c r="F115" s="19">
+        <v>10763.225200000001</v>
+      </c>
+      <c r="G115" s="19">
+        <v>10597.746800000001</v>
+      </c>
+      <c r="H115" s="19">
+        <v>10872.1333</v>
+      </c>
+      <c r="I115" s="20">
+        <v>10849.270699999999</v>
+      </c>
+      <c r="J115" s="19">
+        <v>11408.62</v>
+      </c>
+      <c r="K115" s="19">
+        <v>7548.8959999999997</v>
+      </c>
+      <c r="L115" s="19">
+        <v>8032.5016999999998</v>
+      </c>
+      <c r="M115" s="19">
+        <v>11658.648999999999</v>
+      </c>
+      <c r="N115" s="19">
+        <v>8811.7546000000002</v>
+      </c>
+      <c r="O115" s="19">
+        <v>11895.636399999999</v>
+      </c>
+      <c r="P115" s="19">
+        <v>11141.320400000001</v>
+      </c>
+      <c r="Q115" s="19">
+        <v>9435.1581000000006</v>
+      </c>
+      <c r="R115" s="19">
+        <v>9430.3948999999993</v>
+      </c>
+      <c r="S115" s="19">
+        <v>10355.4599</v>
+      </c>
+      <c r="T115" s="19">
+        <v>13210.944100000001</v>
+      </c>
+      <c r="U115" s="20">
+        <v>10479.518099999999</v>
+      </c>
+      <c r="V115" s="18">
+        <v>10427.577499999999</v>
       </c>
     </row>
   </sheetData>
@@ -8582,7 +8647,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED968B30-91AE-4BCD-9838-818BA334E48C}">
-  <dimension ref="B1:V114"/>
+  <dimension ref="B1:V115"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="15.5703125" defaultRowHeight="18" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="4" customWidth="1"/>
@@ -8744,27 +8809,35 @@
         <v>42736</v>
       </c>
       <c r="C6" s="15">
+        <f>ROUND(100*(Índices!C6/Índices!C5-1),4)</f>
         <v>1.7487999999999999</v>
       </c>
       <c r="D6" s="16">
+        <f>ROUND(100*(Índices!D6/Índices!D5-1),4)</f>
         <v>1.5026999999999999</v>
       </c>
       <c r="E6" s="16">
+        <f>ROUND(100*(Índices!E6/Índices!E5-1),4)</f>
         <v>1.8845000000000001</v>
       </c>
       <c r="F6" s="16">
+        <f>ROUND(100*(Índices!F6/Índices!F5-1),4)</f>
         <v>1.7318</v>
       </c>
       <c r="G6" s="16">
+        <f>ROUND(100*(Índices!G6/Índices!G5-1),4)</f>
         <v>1.7968999999999999</v>
       </c>
       <c r="H6" s="16">
+        <f>ROUND(100*(Índices!H6/Índices!H5-1),4)</f>
         <v>1.8922000000000001</v>
       </c>
       <c r="I6" s="17">
+        <f>ROUND(100*(Índices!I6/Índices!I5-1),4)</f>
         <v>2.9377</v>
       </c>
       <c r="J6" s="16">
+        <f>ROUND(100*(Índices!J6/Índices!J5-1),4)</f>
         <v>0.86929999999999996</v>
       </c>
       <c r="K6" s="16">
@@ -8809,27 +8882,35 @@
         <v>42767</v>
       </c>
       <c r="C7" s="15">
+        <f>ROUND(100*(Índices!C7/Índices!C6-1),4)</f>
         <v>2.2298</v>
       </c>
       <c r="D7" s="16">
+        <f>ROUND(100*(Índices!D7/Índices!D6-1),4)</f>
         <v>2.7776999999999998</v>
       </c>
       <c r="E7" s="16">
+        <f>ROUND(100*(Índices!E7/Índices!E6-1),4)</f>
         <v>1.802</v>
       </c>
       <c r="F7" s="16">
+        <f>ROUND(100*(Índices!F7/Índices!F6-1),4)</f>
         <v>2.1490999999999998</v>
       </c>
       <c r="G7" s="16">
+        <f>ROUND(100*(Índices!G7/Índices!G6-1),4)</f>
         <v>1.9001999999999999</v>
       </c>
       <c r="H7" s="16">
+        <f>ROUND(100*(Índices!H7/Índices!H6-1),4)</f>
         <v>1.4670000000000001</v>
       </c>
       <c r="I7" s="17">
+        <f>ROUND(100*(Índices!I7/Índices!I6-1),4)</f>
         <v>2.0699000000000001</v>
       </c>
       <c r="J7" s="16">
+        <f>ROUND(100*(Índices!J7/Índices!J6-1),4)</f>
         <v>1.3761000000000001</v>
       </c>
       <c r="K7" s="16">
@@ -8874,27 +8955,35 @@
         <v>42795</v>
       </c>
       <c r="C8" s="15">
+        <f>ROUND(100*(Índices!C8/Índices!C7-1),4)</f>
         <v>1.7052</v>
       </c>
       <c r="D8" s="16">
+        <f>ROUND(100*(Índices!D8/Índices!D7-1),4)</f>
         <v>1.514</v>
       </c>
       <c r="E8" s="16">
+        <f>ROUND(100*(Índices!E8/Índices!E7-1),4)</f>
         <v>1.5681</v>
       </c>
       <c r="F8" s="16">
+        <f>ROUND(100*(Índices!F8/Índices!F7-1),4)</f>
         <v>2.4689000000000001</v>
       </c>
       <c r="G8" s="16">
+        <f>ROUND(100*(Índices!G8/Índices!G7-1),4)</f>
         <v>2.0184000000000002</v>
       </c>
       <c r="H8" s="16">
+        <f>ROUND(100*(Índices!H8/Índices!H7-1),4)</f>
         <v>1.9470000000000001</v>
       </c>
       <c r="I8" s="17">
+        <f>ROUND(100*(Índices!I8/Índices!I7-1),4)</f>
         <v>1.4957</v>
       </c>
       <c r="J8" s="16">
+        <f>ROUND(100*(Índices!J8/Índices!J7-1),4)</f>
         <v>1.8279000000000001</v>
       </c>
       <c r="K8" s="16">
@@ -8939,27 +9028,35 @@
         <v>42826</v>
       </c>
       <c r="C9" s="15">
+        <f>ROUND(100*(Índices!C9/Índices!C8-1),4)</f>
         <v>2.6654</v>
       </c>
       <c r="D9" s="16">
+        <f>ROUND(100*(Índices!D9/Índices!D8-1),4)</f>
         <v>2.6957</v>
       </c>
       <c r="E9" s="16">
+        <f>ROUND(100*(Índices!E9/Índices!E8-1),4)</f>
         <v>2.6231</v>
       </c>
       <c r="F9" s="16">
+        <f>ROUND(100*(Índices!F9/Índices!F8-1),4)</f>
         <v>2.5550999999999999</v>
       </c>
       <c r="G9" s="16">
+        <f>ROUND(100*(Índices!G9/Índices!G8-1),4)</f>
         <v>2.4539</v>
       </c>
       <c r="H9" s="16">
+        <f>ROUND(100*(Índices!H9/Índices!H8-1),4)</f>
         <v>3.2035999999999998</v>
       </c>
       <c r="I9" s="17">
+        <f>ROUND(100*(Índices!I9/Índices!I8-1),4)</f>
         <v>2.0581999999999998</v>
       </c>
       <c r="J9" s="16">
+        <f>ROUND(100*(Índices!J9/Índices!J8-1),4)</f>
         <v>2.5916000000000001</v>
       </c>
       <c r="K9" s="16">
@@ -9004,27 +9101,35 @@
         <v>42856</v>
       </c>
       <c r="C10" s="15">
+        <f>ROUND(100*(Índices!C10/Índices!C9-1),4)</f>
         <v>1.7382</v>
       </c>
       <c r="D10" s="16">
+        <f>ROUND(100*(Índices!D10/Índices!D9-1),4)</f>
         <v>1.6472</v>
       </c>
       <c r="E10" s="16">
+        <f>ROUND(100*(Índices!E10/Índices!E9-1),4)</f>
         <v>1.6981999999999999</v>
       </c>
       <c r="F10" s="16">
+        <f>ROUND(100*(Índices!F10/Índices!F9-1),4)</f>
         <v>1.9121999999999999</v>
       </c>
       <c r="G10" s="16">
+        <f>ROUND(100*(Índices!G10/Índices!G9-1),4)</f>
         <v>2.2059000000000002</v>
       </c>
       <c r="H10" s="16">
+        <f>ROUND(100*(Índices!H10/Índices!H9-1),4)</f>
         <v>2.0747</v>
       </c>
       <c r="I10" s="17">
+        <f>ROUND(100*(Índices!I10/Índices!I9-1),4)</f>
         <v>1.8593</v>
       </c>
       <c r="J10" s="16">
+        <f>ROUND(100*(Índices!J10/Índices!J9-1),4)</f>
         <v>2.1341999999999999</v>
       </c>
       <c r="K10" s="16">
@@ -9069,27 +9174,35 @@
         <v>42887</v>
       </c>
       <c r="C11" s="15">
+        <f>ROUND(100*(Índices!C11/Índices!C10-1),4)</f>
         <v>1.2983</v>
       </c>
       <c r="D11" s="16">
+        <f>ROUND(100*(Índices!D11/Índices!D10-1),4)</f>
         <v>1.4381999999999999</v>
       </c>
       <c r="E11" s="16">
+        <f>ROUND(100*(Índices!E11/Índices!E10-1),4)</f>
         <v>1.1860999999999999</v>
       </c>
       <c r="F11" s="16">
+        <f>ROUND(100*(Índices!F11/Índices!F10-1),4)</f>
         <v>1.1023000000000001</v>
       </c>
       <c r="G11" s="16">
+        <f>ROUND(100*(Índices!G11/Índices!G10-1),4)</f>
         <v>1.6447000000000001</v>
       </c>
       <c r="H11" s="16">
+        <f>ROUND(100*(Índices!H11/Índices!H10-1),4)</f>
         <v>1.0723</v>
       </c>
       <c r="I11" s="17">
+        <f>ROUND(100*(Índices!I11/Índices!I10-1),4)</f>
         <v>1.1475</v>
       </c>
       <c r="J11" s="16">
+        <f>ROUND(100*(Índices!J11/Índices!J10-1),4)</f>
         <v>1.2533000000000001</v>
       </c>
       <c r="K11" s="16">
@@ -9134,27 +9247,35 @@
         <v>42917</v>
       </c>
       <c r="C12" s="15">
+        <f>ROUND(100*(Índices!C12/Índices!C11-1),4)</f>
         <v>2.0444</v>
       </c>
       <c r="D12" s="16">
+        <f>ROUND(100*(Índices!D12/Índices!D11-1),4)</f>
         <v>1.9338</v>
       </c>
       <c r="E12" s="16">
+        <f>ROUND(100*(Índices!E12/Índices!E11-1),4)</f>
         <v>2.4174000000000002</v>
       </c>
       <c r="F12" s="16">
+        <f>ROUND(100*(Índices!F12/Índices!F11-1),4)</f>
         <v>1.8596999999999999</v>
       </c>
       <c r="G12" s="16">
+        <f>ROUND(100*(Índices!G12/Índices!G11-1),4)</f>
         <v>1.6625000000000001</v>
       </c>
       <c r="H12" s="16">
+        <f>ROUND(100*(Índices!H12/Índices!H11-1),4)</f>
         <v>1.5895999999999999</v>
       </c>
       <c r="I12" s="17">
+        <f>ROUND(100*(Índices!I12/Índices!I11-1),4)</f>
         <v>1.6265000000000001</v>
       </c>
       <c r="J12" s="16">
+        <f>ROUND(100*(Índices!J12/Índices!J11-1),4)</f>
         <v>1.7292000000000001</v>
       </c>
       <c r="K12" s="16">
@@ -9199,27 +9320,35 @@
         <v>42948</v>
       </c>
       <c r="C13" s="15">
+        <f>ROUND(100*(Índices!C13/Índices!C12-1),4)</f>
         <v>1.4317</v>
       </c>
       <c r="D13" s="16">
+        <f>ROUND(100*(Índices!D13/Índices!D12-1),4)</f>
         <v>1.5065</v>
       </c>
       <c r="E13" s="16">
+        <f>ROUND(100*(Índices!E13/Índices!E12-1),4)</f>
         <v>1.4601</v>
       </c>
       <c r="F13" s="16">
+        <f>ROUND(100*(Índices!F13/Índices!F12-1),4)</f>
         <v>1.1950000000000001</v>
       </c>
       <c r="G13" s="16">
+        <f>ROUND(100*(Índices!G13/Índices!G12-1),4)</f>
         <v>0.98970000000000002</v>
       </c>
       <c r="H13" s="16">
+        <f>ROUND(100*(Índices!H13/Índices!H12-1),4)</f>
         <v>1.3681000000000001</v>
       </c>
       <c r="I13" s="17">
+        <f>ROUND(100*(Índices!I13/Índices!I12-1),4)</f>
         <v>1.4582999999999999</v>
       </c>
       <c r="J13" s="16">
+        <f>ROUND(100*(Índices!J13/Índices!J12-1),4)</f>
         <v>1.8512</v>
       </c>
       <c r="K13" s="16">
@@ -9264,27 +9393,35 @@
         <v>42979</v>
       </c>
       <c r="C14" s="15">
+        <f>ROUND(100*(Índices!C14/Índices!C13-1),4)</f>
         <v>1.1866000000000001</v>
       </c>
       <c r="D14" s="16">
+        <f>ROUND(100*(Índices!D14/Índices!D13-1),4)</f>
         <v>1.1162000000000001</v>
       </c>
       <c r="E14" s="16">
+        <f>ROUND(100*(Índices!E14/Índices!E13-1),4)</f>
         <v>1.3812</v>
       </c>
       <c r="F14" s="16">
+        <f>ROUND(100*(Índices!F14/Índices!F13-1),4)</f>
         <v>1.3387</v>
       </c>
       <c r="G14" s="16">
+        <f>ROUND(100*(Índices!G14/Índices!G13-1),4)</f>
         <v>0.61619999999999997</v>
       </c>
       <c r="H14" s="16">
+        <f>ROUND(100*(Índices!H14/Índices!H13-1),4)</f>
         <v>1.2394000000000001</v>
       </c>
       <c r="I14" s="17">
+        <f>ROUND(100*(Índices!I14/Índices!I13-1),4)</f>
         <v>0.73809999999999998</v>
       </c>
       <c r="J14" s="16">
+        <f>ROUND(100*(Índices!J14/Índices!J13-1),4)</f>
         <v>1.0415000000000001</v>
       </c>
       <c r="K14" s="16">
@@ -9329,27 +9466,35 @@
         <v>43009</v>
       </c>
       <c r="C15" s="15">
+        <f>ROUND(100*(Índices!C15/Índices!C14-1),4)</f>
         <v>1.2363999999999999</v>
       </c>
       <c r="D15" s="16">
+        <f>ROUND(100*(Índices!D15/Índices!D14-1),4)</f>
         <v>1.0093000000000001</v>
       </c>
       <c r="E15" s="16">
+        <f>ROUND(100*(Índices!E15/Índices!E14-1),4)</f>
         <v>1.4077999999999999</v>
       </c>
       <c r="F15" s="16">
+        <f>ROUND(100*(Índices!F15/Índices!F14-1),4)</f>
         <v>1.6025</v>
       </c>
       <c r="G15" s="16">
+        <f>ROUND(100*(Índices!G15/Índices!G14-1),4)</f>
         <v>1.1488</v>
       </c>
       <c r="H15" s="16">
+        <f>ROUND(100*(Índices!H15/Índices!H14-1),4)</f>
         <v>1.6121000000000001</v>
       </c>
       <c r="I15" s="17">
+        <f>ROUND(100*(Índices!I15/Índices!I14-1),4)</f>
         <v>1.3524</v>
       </c>
       <c r="J15" s="16">
+        <f>ROUND(100*(Índices!J15/Índices!J14-1),4)</f>
         <v>0.85899999999999999</v>
       </c>
       <c r="K15" s="16">
@@ -9394,27 +9539,35 @@
         <v>43040</v>
       </c>
       <c r="C16" s="15">
+        <f>ROUND(100*(Índices!C16/Índices!C15-1),4)</f>
         <v>1.6453</v>
       </c>
       <c r="D16" s="16">
+        <f>ROUND(100*(Índices!D16/Índices!D15-1),4)</f>
         <v>1.5267999999999999</v>
       </c>
       <c r="E16" s="16">
+        <f>ROUND(100*(Índices!E16/Índices!E15-1),4)</f>
         <v>1.7553000000000001</v>
       </c>
       <c r="F16" s="16">
+        <f>ROUND(100*(Índices!F16/Índices!F15-1),4)</f>
         <v>1.5357000000000001</v>
       </c>
       <c r="G16" s="16">
+        <f>ROUND(100*(Índices!G16/Índices!G15-1),4)</f>
         <v>1.7325999999999999</v>
       </c>
       <c r="H16" s="16">
+        <f>ROUND(100*(Índices!H16/Índices!H15-1),4)</f>
         <v>1.8363</v>
       </c>
       <c r="I16" s="17">
+        <f>ROUND(100*(Índices!I16/Índices!I15-1),4)</f>
         <v>1.5595000000000001</v>
       </c>
       <c r="J16" s="16">
+        <f>ROUND(100*(Índices!J16/Índices!J15-1),4)</f>
         <v>1.8842000000000001</v>
       </c>
       <c r="K16" s="16">
@@ -9459,27 +9612,35 @@
         <v>43070</v>
       </c>
       <c r="C17" s="15">
+        <f>ROUND(100*(Índices!C17/Índices!C16-1),4)</f>
         <v>3.4948999999999999</v>
       </c>
       <c r="D17" s="16">
+        <f>ROUND(100*(Índices!D17/Índices!D16-1),4)</f>
         <v>3.9373999999999998</v>
       </c>
       <c r="E17" s="16">
+        <f>ROUND(100*(Índices!E17/Índices!E16-1),4)</f>
         <v>3.3347000000000002</v>
       </c>
       <c r="F17" s="16">
+        <f>ROUND(100*(Índices!F17/Índices!F16-1),4)</f>
         <v>2.5430000000000001</v>
       </c>
       <c r="G17" s="16">
+        <f>ROUND(100*(Índices!G17/Índices!G16-1),4)</f>
         <v>2.1324000000000001</v>
       </c>
       <c r="H17" s="16">
+        <f>ROUND(100*(Índices!H17/Índices!H16-1),4)</f>
         <v>3.6840999999999999</v>
       </c>
       <c r="I17" s="17">
+        <f>ROUND(100*(Índices!I17/Índices!I16-1),4)</f>
         <v>3.0038999999999998</v>
       </c>
       <c r="J17" s="16">
+        <f>ROUND(100*(Índices!J17/Índices!J16-1),4)</f>
         <v>1.2654000000000001</v>
       </c>
       <c r="K17" s="16">
@@ -9524,27 +9685,35 @@
         <v>43101</v>
       </c>
       <c r="C18" s="15">
+        <f>ROUND(100*(Índices!C18/Índices!C17-1),4)</f>
         <v>1.9419</v>
       </c>
       <c r="D18" s="16">
+        <f>ROUND(100*(Índices!D18/Índices!D17-1),4)</f>
         <v>1.7645999999999999</v>
       </c>
       <c r="E18" s="16">
+        <f>ROUND(100*(Índices!E18/Índices!E17-1),4)</f>
         <v>1.9656</v>
       </c>
       <c r="F18" s="16">
+        <f>ROUND(100*(Índices!F18/Índices!F17-1),4)</f>
         <v>1.9914000000000001</v>
       </c>
       <c r="G18" s="16">
+        <f>ROUND(100*(Índices!G18/Índices!G17-1),4)</f>
         <v>2.1463000000000001</v>
       </c>
       <c r="H18" s="16">
+        <f>ROUND(100*(Índices!H18/Índices!H17-1),4)</f>
         <v>1.6739999999999999</v>
       </c>
       <c r="I18" s="17">
+        <f>ROUND(100*(Índices!I18/Índices!I17-1),4)</f>
         <v>2.931</v>
       </c>
       <c r="J18" s="16">
+        <f>ROUND(100*(Índices!J18/Índices!J17-1),4)</f>
         <v>1.6754</v>
       </c>
       <c r="K18" s="16">
@@ -9589,27 +9758,35 @@
         <v>43132</v>
       </c>
       <c r="C19" s="15">
+        <f>ROUND(100*(Índices!C19/Índices!C18-1),4)</f>
         <v>2.6078000000000001</v>
       </c>
       <c r="D19" s="16">
+        <f>ROUND(100*(Índices!D19/Índices!D18-1),4)</f>
         <v>2.8723000000000001</v>
       </c>
       <c r="E19" s="16">
+        <f>ROUND(100*(Índices!E19/Índices!E18-1),4)</f>
         <v>2.4308999999999998</v>
       </c>
       <c r="F19" s="16">
+        <f>ROUND(100*(Índices!F19/Índices!F18-1),4)</f>
         <v>2.1273</v>
       </c>
       <c r="G19" s="16">
+        <f>ROUND(100*(Índices!G19/Índices!G18-1),4)</f>
         <v>2.1684999999999999</v>
       </c>
       <c r="H19" s="16">
+        <f>ROUND(100*(Índices!H19/Índices!H18-1),4)</f>
         <v>2.5796999999999999</v>
       </c>
       <c r="I19" s="17">
+        <f>ROUND(100*(Índices!I19/Índices!I18-1),4)</f>
         <v>2.3912</v>
       </c>
       <c r="J19" s="16">
+        <f>ROUND(100*(Índices!J19/Índices!J18-1),4)</f>
         <v>1.7171000000000001</v>
       </c>
       <c r="K19" s="16">
@@ -9654,27 +9831,35 @@
         <v>43160</v>
       </c>
       <c r="C20" s="15">
+        <f>ROUND(100*(Índices!C20/Índices!C19-1),4)</f>
         <v>1.6079000000000001</v>
       </c>
       <c r="D20" s="16">
+        <f>ROUND(100*(Índices!D20/Índices!D19-1),4)</f>
         <v>1.6061000000000001</v>
       </c>
       <c r="E20" s="16">
+        <f>ROUND(100*(Índices!E20/Índices!E19-1),4)</f>
         <v>1.2943</v>
       </c>
       <c r="F20" s="16">
+        <f>ROUND(100*(Índices!F20/Índices!F19-1),4)</f>
         <v>2.3054999999999999</v>
       </c>
       <c r="G20" s="16">
+        <f>ROUND(100*(Índices!G20/Índices!G19-1),4)</f>
         <v>2.0044</v>
       </c>
       <c r="H20" s="16">
+        <f>ROUND(100*(Índices!H20/Índices!H19-1),4)</f>
         <v>1.4951000000000001</v>
       </c>
       <c r="I20" s="17">
+        <f>ROUND(100*(Índices!I20/Índices!I19-1),4)</f>
         <v>2.4847000000000001</v>
       </c>
       <c r="J20" s="16">
+        <f>ROUND(100*(Índices!J20/Índices!J19-1),4)</f>
         <v>1.3884000000000001</v>
       </c>
       <c r="K20" s="16">
@@ -9719,27 +9904,35 @@
         <v>43191</v>
       </c>
       <c r="C21" s="15">
+        <f>ROUND(100*(Índices!C21/Índices!C20-1),4)</f>
         <v>2.7519</v>
       </c>
       <c r="D21" s="16">
+        <f>ROUND(100*(Índices!D21/Índices!D20-1),4)</f>
         <v>2.6530999999999998</v>
       </c>
       <c r="E21" s="16">
+        <f>ROUND(100*(Índices!E21/Índices!E20-1),4)</f>
         <v>2.7963</v>
       </c>
       <c r="F21" s="16">
+        <f>ROUND(100*(Índices!F21/Índices!F20-1),4)</f>
         <v>2.7031000000000001</v>
       </c>
       <c r="G21" s="16">
+        <f>ROUND(100*(Índices!G21/Índices!G20-1),4)</f>
         <v>2.8563000000000001</v>
       </c>
       <c r="H21" s="16">
+        <f>ROUND(100*(Índices!H21/Índices!H20-1),4)</f>
         <v>3.2381000000000002</v>
       </c>
       <c r="I21" s="17">
+        <f>ROUND(100*(Índices!I21/Índices!I20-1),4)</f>
         <v>2.7568999999999999</v>
       </c>
       <c r="J21" s="16">
+        <f>ROUND(100*(Índices!J21/Índices!J20-1),4)</f>
         <v>1.5042</v>
       </c>
       <c r="K21" s="16">
@@ -9784,27 +9977,35 @@
         <v>43221</v>
       </c>
       <c r="C22" s="15">
+        <f>ROUND(100*(Índices!C22/Índices!C21-1),4)</f>
         <v>2.4020000000000001</v>
       </c>
       <c r="D22" s="16">
+        <f>ROUND(100*(Índices!D22/Índices!D21-1),4)</f>
         <v>2.2768999999999999</v>
       </c>
       <c r="E22" s="16">
+        <f>ROUND(100*(Índices!E22/Índices!E21-1),4)</f>
         <v>2.4367000000000001</v>
       </c>
       <c r="F22" s="16">
+        <f>ROUND(100*(Índices!F22/Índices!F21-1),4)</f>
         <v>2.6894999999999998</v>
       </c>
       <c r="G22" s="16">
+        <f>ROUND(100*(Índices!G22/Índices!G21-1),4)</f>
         <v>2.8407</v>
       </c>
       <c r="H22" s="16">
+        <f>ROUND(100*(Índices!H22/Índices!H21-1),4)</f>
         <v>2.1633</v>
       </c>
       <c r="I22" s="17">
+        <f>ROUND(100*(Índices!I22/Índices!I21-1),4)</f>
         <v>2.1753</v>
       </c>
       <c r="J22" s="16">
+        <f>ROUND(100*(Índices!J22/Índices!J21-1),4)</f>
         <v>4.1135000000000002</v>
       </c>
       <c r="K22" s="16">
@@ -9849,27 +10050,35 @@
         <v>43252</v>
       </c>
       <c r="C23" s="15">
+        <f>ROUND(100*(Índices!C23/Índices!C22-1),4)</f>
         <v>3.8269000000000002</v>
       </c>
       <c r="D23" s="16">
+        <f>ROUND(100*(Índices!D23/Índices!D22-1),4)</f>
         <v>3.9824000000000002</v>
       </c>
       <c r="E23" s="16">
+        <f>ROUND(100*(Índices!E23/Índices!E22-1),4)</f>
         <v>3.9041999999999999</v>
       </c>
       <c r="F23" s="16">
+        <f>ROUND(100*(Índices!F23/Índices!F22-1),4)</f>
         <v>3.5783</v>
       </c>
       <c r="G23" s="16">
+        <f>ROUND(100*(Índices!G23/Índices!G22-1),4)</f>
         <v>3.3959999999999999</v>
       </c>
       <c r="H23" s="16">
+        <f>ROUND(100*(Índices!H23/Índices!H22-1),4)</f>
         <v>3.7269000000000001</v>
       </c>
       <c r="I23" s="17">
+        <f>ROUND(100*(Índices!I23/Índices!I22-1),4)</f>
         <v>3.3691</v>
       </c>
       <c r="J23" s="16">
+        <f>ROUND(100*(Índices!J23/Índices!J22-1),4)</f>
         <v>5.5880999999999998</v>
       </c>
       <c r="K23" s="16">
@@ -9914,27 +10123,35 @@
         <v>43282</v>
       </c>
       <c r="C24" s="15">
+        <f>ROUND(100*(Índices!C24/Índices!C23-1),4)</f>
         <v>3.4085000000000001</v>
       </c>
       <c r="D24" s="16">
+        <f>ROUND(100*(Índices!D24/Índices!D23-1),4)</f>
         <v>3.0062000000000002</v>
       </c>
       <c r="E24" s="16">
+        <f>ROUND(100*(Índices!E24/Índices!E23-1),4)</f>
         <v>3.7423000000000002</v>
       </c>
       <c r="F24" s="16">
+        <f>ROUND(100*(Índices!F24/Índices!F23-1),4)</f>
         <v>3.8546999999999998</v>
       </c>
       <c r="G24" s="16">
+        <f>ROUND(100*(Índices!G24/Índices!G23-1),4)</f>
         <v>3.7696999999999998</v>
       </c>
       <c r="H24" s="16">
+        <f>ROUND(100*(Índices!H24/Índices!H23-1),4)</f>
         <v>3.8086000000000002</v>
       </c>
       <c r="I24" s="17">
+        <f>ROUND(100*(Índices!I24/Índices!I23-1),4)</f>
         <v>3.2789000000000001</v>
       </c>
       <c r="J24" s="16">
+        <f>ROUND(100*(Índices!J24/Índices!J23-1),4)</f>
         <v>4.5726000000000004</v>
       </c>
       <c r="K24" s="16">
@@ -9979,27 +10196,35 @@
         <v>43313</v>
       </c>
       <c r="C25" s="15">
+        <f>ROUND(100*(Índices!C25/Índices!C24-1),4)</f>
         <v>3.8580000000000001</v>
       </c>
       <c r="D25" s="16">
+        <f>ROUND(100*(Índices!D25/Índices!D24-1),4)</f>
         <v>4.0613000000000001</v>
       </c>
       <c r="E25" s="16">
+        <f>ROUND(100*(Índices!E25/Índices!E24-1),4)</f>
         <v>3.8553000000000002</v>
       </c>
       <c r="F25" s="16">
+        <f>ROUND(100*(Índices!F25/Índices!F24-1),4)</f>
         <v>3.8873000000000002</v>
       </c>
       <c r="G25" s="16">
+        <f>ROUND(100*(Índices!G25/Índices!G24-1),4)</f>
         <v>3.8239000000000001</v>
       </c>
       <c r="H25" s="16">
+        <f>ROUND(100*(Índices!H25/Índices!H24-1),4)</f>
         <v>3.3936000000000002</v>
       </c>
       <c r="I25" s="17">
+        <f>ROUND(100*(Índices!I25/Índices!I24-1),4)</f>
         <v>3.4047999999999998</v>
       </c>
       <c r="J25" s="16">
+        <f>ROUND(100*(Índices!J25/Índices!J24-1),4)</f>
         <v>3.7928999999999999</v>
       </c>
       <c r="K25" s="16">
@@ -10044,27 +10269,35 @@
         <v>43344</v>
       </c>
       <c r="C26" s="15">
+        <f>ROUND(100*(Índices!C26/Índices!C25-1),4)</f>
         <v>5.8846999999999996</v>
       </c>
       <c r="D26" s="16">
+        <f>ROUND(100*(Índices!D26/Índices!D25-1),4)</f>
         <v>5.7710999999999997</v>
       </c>
       <c r="E26" s="16">
+        <f>ROUND(100*(Índices!E26/Índices!E25-1),4)</f>
         <v>5.8414999999999999</v>
       </c>
       <c r="F26" s="16">
+        <f>ROUND(100*(Índices!F26/Índices!F25-1),4)</f>
         <v>5.5682999999999998</v>
       </c>
       <c r="G26" s="16">
+        <f>ROUND(100*(Índices!G26/Índices!G25-1),4)</f>
         <v>6.6554000000000002</v>
       </c>
       <c r="H26" s="16">
+        <f>ROUND(100*(Índices!H26/Índices!H25-1),4)</f>
         <v>6.3659999999999997</v>
       </c>
       <c r="I26" s="17">
+        <f>ROUND(100*(Índices!I26/Índices!I25-1),4)</f>
         <v>6.0266000000000002</v>
       </c>
       <c r="J26" s="16">
+        <f>ROUND(100*(Índices!J26/Índices!J25-1),4)</f>
         <v>6.2320000000000002</v>
       </c>
       <c r="K26" s="16">
@@ -10109,27 +10342,35 @@
         <v>43374</v>
       </c>
       <c r="C27" s="15">
+        <f>ROUND(100*(Índices!C27/Índices!C26-1),4)</f>
         <v>5.1303000000000001</v>
       </c>
       <c r="D27" s="16">
+        <f>ROUND(100*(Índices!D27/Índices!D26-1),4)</f>
         <v>4.7542999999999997</v>
       </c>
       <c r="E27" s="16">
+        <f>ROUND(100*(Índices!E27/Índices!E26-1),4)</f>
         <v>5.5141</v>
       </c>
       <c r="F27" s="16">
+        <f>ROUND(100*(Índices!F27/Índices!F26-1),4)</f>
         <v>5.0587</v>
       </c>
       <c r="G27" s="16">
+        <f>ROUND(100*(Índices!G27/Índices!G26-1),4)</f>
         <v>4.5179999999999998</v>
       </c>
       <c r="H27" s="16">
+        <f>ROUND(100*(Índices!H27/Índices!H26-1),4)</f>
         <v>5.8524000000000003</v>
       </c>
       <c r="I27" s="17">
+        <f>ROUND(100*(Índices!I27/Índices!I26-1),4)</f>
         <v>5.4950999999999999</v>
       </c>
       <c r="J27" s="16">
+        <f>ROUND(100*(Índices!J27/Índices!J26-1),4)</f>
         <v>5.1913999999999998</v>
       </c>
       <c r="K27" s="16">
@@ -10174,27 +10415,35 @@
         <v>43405</v>
       </c>
       <c r="C28" s="15">
+        <f>ROUND(100*(Índices!C28/Índices!C27-1),4)</f>
         <v>3.4581</v>
       </c>
       <c r="D28" s="16">
+        <f>ROUND(100*(Índices!D28/Índices!D27-1),4)</f>
         <v>3.2763</v>
       </c>
       <c r="E28" s="16">
+        <f>ROUND(100*(Índices!E28/Índices!E27-1),4)</f>
         <v>3.4359999999999999</v>
       </c>
       <c r="F28" s="16">
+        <f>ROUND(100*(Índices!F28/Índices!F27-1),4)</f>
         <v>3.5707</v>
       </c>
       <c r="G28" s="16">
+        <f>ROUND(100*(Índices!G28/Índices!G27-1),4)</f>
         <v>3.2448999999999999</v>
       </c>
       <c r="H28" s="16">
+        <f>ROUND(100*(Índices!H28/Índices!H27-1),4)</f>
         <v>3.9365999999999999</v>
       </c>
       <c r="I28" s="17">
+        <f>ROUND(100*(Índices!I28/Índices!I27-1),4)</f>
         <v>4.3178000000000001</v>
       </c>
       <c r="J28" s="16">
+        <f>ROUND(100*(Índices!J28/Índices!J27-1),4)</f>
         <v>4.1722000000000001</v>
       </c>
       <c r="K28" s="16">
@@ -10239,27 +10488,35 @@
         <v>43435</v>
       </c>
       <c r="C29" s="15">
+        <f>ROUND(100*(Índices!C29/Índices!C28-1),4)</f>
         <v>2.8531</v>
       </c>
       <c r="D29" s="16">
+        <f>ROUND(100*(Índices!D29/Índices!D28-1),4)</f>
         <v>3.2841</v>
       </c>
       <c r="E29" s="16">
+        <f>ROUND(100*(Índices!E29/Índices!E28-1),4)</f>
         <v>2.4883000000000002</v>
       </c>
       <c r="F29" s="16">
+        <f>ROUND(100*(Índices!F29/Índices!F28-1),4)</f>
         <v>2.4540000000000002</v>
       </c>
       <c r="G29" s="16">
+        <f>ROUND(100*(Índices!G29/Índices!G28-1),4)</f>
         <v>2.3973</v>
       </c>
       <c r="H29" s="16">
+        <f>ROUND(100*(Índices!H29/Índices!H28-1),4)</f>
         <v>2.7896999999999998</v>
       </c>
       <c r="I29" s="17">
+        <f>ROUND(100*(Índices!I29/Índices!I28-1),4)</f>
         <v>3.0670000000000002</v>
       </c>
       <c r="J29" s="16">
+        <f>ROUND(100*(Índices!J29/Índices!J28-1),4)</f>
         <v>2.2281</v>
       </c>
       <c r="K29" s="16">
@@ -10304,27 +10561,35 @@
         <v>43466</v>
       </c>
       <c r="C30" s="15">
+        <f>ROUND(100*(Índices!C30/Índices!C29-1),4)</f>
         <v>3.0928</v>
       </c>
       <c r="D30" s="16">
+        <f>ROUND(100*(Índices!D30/Índices!D29-1),4)</f>
         <v>3.0110000000000001</v>
       </c>
       <c r="E30" s="16">
+        <f>ROUND(100*(Índices!E30/Índices!E29-1),4)</f>
         <v>2.9376000000000002</v>
       </c>
       <c r="F30" s="16">
+        <f>ROUND(100*(Índices!F30/Índices!F29-1),4)</f>
         <v>3.2831999999999999</v>
       </c>
       <c r="G30" s="16">
+        <f>ROUND(100*(Índices!G30/Índices!G29-1),4)</f>
         <v>3.6076999999999999</v>
       </c>
       <c r="H30" s="16">
+        <f>ROUND(100*(Índices!H30/Índices!H29-1),4)</f>
         <v>3.0973999999999999</v>
       </c>
       <c r="I30" s="17">
+        <f>ROUND(100*(Índices!I30/Índices!I29-1),4)</f>
         <v>3.4205999999999999</v>
       </c>
       <c r="J30" s="16">
+        <f>ROUND(100*(Índices!J30/Índices!J29-1),4)</f>
         <v>2.9780000000000002</v>
       </c>
       <c r="K30" s="16">
@@ -10369,27 +10634,35 @@
         <v>43497</v>
       </c>
       <c r="C31" s="15">
+        <f>ROUND(100*(Índices!C31/Índices!C30-1),4)</f>
         <v>3.9001999999999999</v>
       </c>
       <c r="D31" s="16">
+        <f>ROUND(100*(Índices!D31/Índices!D30-1),4)</f>
         <v>4.0902000000000003</v>
       </c>
       <c r="E31" s="16">
+        <f>ROUND(100*(Índices!E31/Índices!E30-1),4)</f>
         <v>3.6560999999999999</v>
       </c>
       <c r="F31" s="16">
+        <f>ROUND(100*(Índices!F31/Índices!F30-1),4)</f>
         <v>4.2812999999999999</v>
       </c>
       <c r="G31" s="16">
+        <f>ROUND(100*(Índices!G31/Índices!G30-1),4)</f>
         <v>4.5891999999999999</v>
       </c>
       <c r="H31" s="16">
+        <f>ROUND(100*(Índices!H31/Índices!H30-1),4)</f>
         <v>3.7109000000000001</v>
       </c>
       <c r="I31" s="17">
+        <f>ROUND(100*(Índices!I31/Índices!I30-1),4)</f>
         <v>3.2921</v>
       </c>
       <c r="J31" s="16">
+        <f>ROUND(100*(Índices!J31/Índices!J30-1),4)</f>
         <v>5.2058999999999997</v>
       </c>
       <c r="K31" s="16">
@@ -10434,27 +10707,35 @@
         <v>43525</v>
       </c>
       <c r="C32" s="15">
+        <f>ROUND(100*(Índices!C32/Índices!C31-1),4)</f>
         <v>3.9302000000000001</v>
       </c>
       <c r="D32" s="16">
+        <f>ROUND(100*(Índices!D32/Índices!D31-1),4)</f>
         <v>3.9203999999999999</v>
       </c>
       <c r="E32" s="16">
+        <f>ROUND(100*(Índices!E32/Índices!E31-1),4)</f>
         <v>3.8559000000000001</v>
       </c>
       <c r="F32" s="16">
+        <f>ROUND(100*(Índices!F32/Índices!F31-1),4)</f>
         <v>4.0631000000000004</v>
       </c>
       <c r="G32" s="16">
+        <f>ROUND(100*(Índices!G32/Índices!G31-1),4)</f>
         <v>4.7443</v>
       </c>
       <c r="H32" s="16">
+        <f>ROUND(100*(Índices!H32/Índices!H31-1),4)</f>
         <v>3.8138000000000001</v>
       </c>
       <c r="I32" s="17">
+        <f>ROUND(100*(Índices!I32/Índices!I31-1),4)</f>
         <v>3.7122999999999999</v>
       </c>
       <c r="J32" s="16">
+        <f>ROUND(100*(Índices!J32/Índices!J31-1),4)</f>
         <v>5.0096999999999996</v>
       </c>
       <c r="K32" s="16">
@@ -10499,27 +10780,35 @@
         <v>43556</v>
       </c>
       <c r="C33" s="15">
+        <f>ROUND(100*(Índices!C33/Índices!C32-1),4)</f>
         <v>3.4590000000000001</v>
       </c>
       <c r="D33" s="16">
+        <f>ROUND(100*(Índices!D33/Índices!D32-1),4)</f>
         <v>3.3155000000000001</v>
       </c>
       <c r="E33" s="16">
+        <f>ROUND(100*(Índices!E33/Índices!E32-1),4)</f>
         <v>3.6294</v>
       </c>
       <c r="F33" s="16">
+        <f>ROUND(100*(Índices!F33/Índices!F32-1),4)</f>
         <v>3.5257999999999998</v>
       </c>
       <c r="G33" s="16">
+        <f>ROUND(100*(Índices!G33/Índices!G32-1),4)</f>
         <v>3.6775000000000002</v>
       </c>
       <c r="H33" s="16">
+        <f>ROUND(100*(Índices!H33/Índices!H32-1),4)</f>
         <v>3.2496</v>
       </c>
       <c r="I33" s="17">
+        <f>ROUND(100*(Índices!I33/Índices!I32-1),4)</f>
         <v>3.5853999999999999</v>
       </c>
       <c r="J33" s="16">
+        <f>ROUND(100*(Índices!J33/Índices!J32-1),4)</f>
         <v>2.8319999999999999</v>
       </c>
       <c r="K33" s="16">
@@ -10564,27 +10853,35 @@
         <v>43586</v>
       </c>
       <c r="C34" s="15">
+        <f>ROUND(100*(Índices!C34/Índices!C33-1),4)</f>
         <v>3.3877000000000002</v>
       </c>
       <c r="D34" s="16">
+        <f>ROUND(100*(Índices!D34/Índices!D33-1),4)</f>
         <v>3.3801000000000001</v>
       </c>
       <c r="E34" s="16">
+        <f>ROUND(100*(Índices!E34/Índices!E33-1),4)</f>
         <v>3.2025999999999999</v>
       </c>
       <c r="F34" s="16">
+        <f>ROUND(100*(Índices!F34/Índices!F33-1),4)</f>
         <v>4.2708000000000004</v>
       </c>
       <c r="G34" s="16">
+        <f>ROUND(100*(Índices!G34/Índices!G33-1),4)</f>
         <v>3.0979999999999999</v>
       </c>
       <c r="H34" s="16">
+        <f>ROUND(100*(Índices!H34/Índices!H33-1),4)</f>
         <v>3.2305000000000001</v>
       </c>
       <c r="I34" s="17">
+        <f>ROUND(100*(Índices!I34/Índices!I33-1),4)</f>
         <v>3.6476000000000002</v>
       </c>
       <c r="J34" s="16">
+        <f>ROUND(100*(Índices!J34/Índices!J33-1),4)</f>
         <v>3.2585000000000002</v>
       </c>
       <c r="K34" s="16">
@@ -10629,27 +10926,35 @@
         <v>43617</v>
       </c>
       <c r="C35" s="15">
+        <f>ROUND(100*(Índices!C35/Índices!C34-1),4)</f>
         <v>2.8654000000000002</v>
       </c>
       <c r="D35" s="16">
+        <f>ROUND(100*(Índices!D35/Índices!D34-1),4)</f>
         <v>2.6873999999999998</v>
       </c>
       <c r="E35" s="16">
+        <f>ROUND(100*(Índices!E35/Índices!E34-1),4)</f>
         <v>3.0230000000000001</v>
       </c>
       <c r="F35" s="16">
+        <f>ROUND(100*(Índices!F35/Índices!F34-1),4)</f>
         <v>3.0447000000000002</v>
       </c>
       <c r="G35" s="16">
+        <f>ROUND(100*(Índices!G35/Índices!G34-1),4)</f>
         <v>3.2442000000000002</v>
       </c>
       <c r="H35" s="16">
+        <f>ROUND(100*(Índices!H35/Índices!H34-1),4)</f>
         <v>2.7240000000000002</v>
       </c>
       <c r="I35" s="17">
+        <f>ROUND(100*(Índices!I35/Índices!I34-1),4)</f>
         <v>2.8702000000000001</v>
       </c>
       <c r="J35" s="16">
+        <f>ROUND(100*(Índices!J35/Índices!J34-1),4)</f>
         <v>3.0324</v>
       </c>
       <c r="K35" s="16">
@@ -10694,27 +10999,35 @@
         <v>43647</v>
       </c>
       <c r="C36" s="15">
+        <f>ROUND(100*(Índices!C36/Índices!C35-1),4)</f>
         <v>2.4794999999999998</v>
       </c>
       <c r="D36" s="16">
+        <f>ROUND(100*(Índices!D36/Índices!D35-1),4)</f>
         <v>2.3357999999999999</v>
       </c>
       <c r="E36" s="16">
+        <f>ROUND(100*(Índices!E36/Índices!E35-1),4)</f>
         <v>2.6086</v>
       </c>
       <c r="F36" s="16">
+        <f>ROUND(100*(Índices!F36/Índices!F35-1),4)</f>
         <v>2.3628</v>
       </c>
       <c r="G36" s="16">
+        <f>ROUND(100*(Índices!G36/Índices!G35-1),4)</f>
         <v>2.1501000000000001</v>
       </c>
       <c r="H36" s="16">
+        <f>ROUND(100*(Índices!H36/Índices!H35-1),4)</f>
         <v>2.9468000000000001</v>
       </c>
       <c r="I36" s="17">
+        <f>ROUND(100*(Índices!I36/Índices!I35-1),4)</f>
         <v>2.5545</v>
       </c>
       <c r="J36" s="16">
+        <f>ROUND(100*(Índices!J36/Índices!J35-1),4)</f>
         <v>2.8140000000000001</v>
       </c>
       <c r="K36" s="16">
@@ -10759,27 +11072,35 @@
         <v>43678</v>
       </c>
       <c r="C37" s="15">
+        <f>ROUND(100*(Índices!C37/Índices!C36-1),4)</f>
         <v>3.9325999999999999</v>
       </c>
       <c r="D37" s="16">
+        <f>ROUND(100*(Índices!D37/Índices!D36-1),4)</f>
         <v>3.8304999999999998</v>
       </c>
       <c r="E37" s="16">
+        <f>ROUND(100*(Índices!E37/Índices!E36-1),4)</f>
         <v>3.9510999999999998</v>
       </c>
       <c r="F37" s="16">
+        <f>ROUND(100*(Índices!F37/Índices!F36-1),4)</f>
         <v>4.0313999999999997</v>
       </c>
       <c r="G37" s="16">
+        <f>ROUND(100*(Índices!G37/Índices!G36-1),4)</f>
         <v>4.2765000000000004</v>
       </c>
       <c r="H37" s="16">
+        <f>ROUND(100*(Índices!H37/Índices!H36-1),4)</f>
         <v>4.3518999999999997</v>
       </c>
       <c r="I37" s="17">
+        <f>ROUND(100*(Índices!I37/Índices!I36-1),4)</f>
         <v>3.9556</v>
       </c>
       <c r="J37" s="16">
+        <f>ROUND(100*(Índices!J37/Índices!J36-1),4)</f>
         <v>4.3106999999999998</v>
       </c>
       <c r="K37" s="16">
@@ -10824,27 +11145,35 @@
         <v>43709</v>
       </c>
       <c r="C38" s="15">
+        <f>ROUND(100*(Índices!C38/Índices!C37-1),4)</f>
         <v>5.2901999999999996</v>
       </c>
       <c r="D38" s="16">
+        <f>ROUND(100*(Índices!D38/Índices!D37-1),4)</f>
         <v>5.0342000000000002</v>
       </c>
       <c r="E38" s="16">
+        <f>ROUND(100*(Índices!E38/Índices!E37-1),4)</f>
         <v>5.5945</v>
       </c>
       <c r="F38" s="16">
+        <f>ROUND(100*(Índices!F38/Índices!F37-1),4)</f>
         <v>5.4627999999999997</v>
       </c>
       <c r="G38" s="16">
+        <f>ROUND(100*(Índices!G38/Índices!G37-1),4)</f>
         <v>5.5879000000000003</v>
       </c>
       <c r="H38" s="16">
+        <f>ROUND(100*(Índices!H38/Índices!H37-1),4)</f>
         <v>5.3902000000000001</v>
       </c>
       <c r="I38" s="17">
+        <f>ROUND(100*(Índices!I38/Índices!I37-1),4)</f>
         <v>4.7605000000000004</v>
       </c>
       <c r="J38" s="16">
+        <f>ROUND(100*(Índices!J38/Índices!J37-1),4)</f>
         <v>4.9607000000000001</v>
       </c>
       <c r="K38" s="16">
@@ -10889,27 +11218,35 @@
         <v>43739</v>
       </c>
       <c r="C39" s="15">
+        <f>ROUND(100*(Índices!C39/Índices!C38-1),4)</f>
         <v>3.0234000000000001</v>
       </c>
       <c r="D39" s="16">
+        <f>ROUND(100*(Índices!D39/Índices!D38-1),4)</f>
         <v>2.8837999999999999</v>
       </c>
       <c r="E39" s="16">
+        <f>ROUND(100*(Índices!E39/Índices!E38-1),4)</f>
         <v>3.1879</v>
       </c>
       <c r="F39" s="16">
+        <f>ROUND(100*(Índices!F39/Índices!F38-1),4)</f>
         <v>2.6373000000000002</v>
       </c>
       <c r="G39" s="16">
+        <f>ROUND(100*(Índices!G39/Índices!G38-1),4)</f>
         <v>2.9539</v>
       </c>
       <c r="H39" s="16">
+        <f>ROUND(100*(Índices!H39/Índices!H38-1),4)</f>
         <v>3.6503999999999999</v>
       </c>
       <c r="I39" s="17">
+        <f>ROUND(100*(Índices!I39/Índices!I38-1),4)</f>
         <v>2.9135</v>
       </c>
       <c r="J39" s="16">
+        <f>ROUND(100*(Índices!J39/Índices!J38-1),4)</f>
         <v>1.7974000000000001</v>
       </c>
       <c r="K39" s="16">
@@ -10954,27 +11291,35 @@
         <v>43770</v>
       </c>
       <c r="C40" s="15">
+        <f>ROUND(100*(Índices!C40/Índices!C39-1),4)</f>
         <v>4.5861999999999998</v>
       </c>
       <c r="D40" s="16">
+        <f>ROUND(100*(Índices!D40/Índices!D39-1),4)</f>
         <v>4.5166000000000004</v>
       </c>
       <c r="E40" s="16">
+        <f>ROUND(100*(Índices!E40/Índices!E39-1),4)</f>
         <v>4.6612999999999998</v>
       </c>
       <c r="F40" s="16">
+        <f>ROUND(100*(Índices!F40/Índices!F39-1),4)</f>
         <v>4.1668000000000003</v>
       </c>
       <c r="G40" s="16">
+        <f>ROUND(100*(Índices!G40/Índices!G39-1),4)</f>
         <v>4.5317999999999996</v>
       </c>
       <c r="H40" s="16">
+        <f>ROUND(100*(Índices!H40/Índices!H39-1),4)</f>
         <v>4.8036000000000003</v>
       </c>
       <c r="I40" s="17">
+        <f>ROUND(100*(Índices!I40/Índices!I39-1),4)</f>
         <v>4.7164999999999999</v>
       </c>
       <c r="J40" s="16">
+        <f>ROUND(100*(Índices!J40/Índices!J39-1),4)</f>
         <v>6.1368</v>
       </c>
       <c r="K40" s="16">
@@ -11019,27 +11364,35 @@
         <v>43800</v>
       </c>
       <c r="C41" s="15">
+        <f>ROUND(100*(Índices!C41/Índices!C40-1),4)</f>
         <v>3.9769000000000001</v>
       </c>
       <c r="D41" s="16">
+        <f>ROUND(100*(Índices!D41/Índices!D40-1),4)</f>
         <v>4.2182000000000004</v>
       </c>
       <c r="E41" s="16">
+        <f>ROUND(100*(Índices!E41/Índices!E40-1),4)</f>
         <v>3.7789999999999999</v>
       </c>
       <c r="F41" s="16">
+        <f>ROUND(100*(Índices!F41/Índices!F40-1),4)</f>
         <v>3.8388</v>
       </c>
       <c r="G41" s="16">
+        <f>ROUND(100*(Índices!G41/Índices!G40-1),4)</f>
         <v>3.8841000000000001</v>
       </c>
       <c r="H41" s="16">
+        <f>ROUND(100*(Índices!H41/Índices!H40-1),4)</f>
         <v>3.5047999999999999</v>
       </c>
       <c r="I41" s="17">
+        <f>ROUND(100*(Índices!I41/Índices!I40-1),4)</f>
         <v>4.5637999999999996</v>
       </c>
       <c r="J41" s="16">
+        <f>ROUND(100*(Índices!J41/Índices!J40-1),4)</f>
         <v>3.5411999999999999</v>
       </c>
       <c r="K41" s="16">
@@ -11084,27 +11437,35 @@
         <v>43831</v>
       </c>
       <c r="C42" s="15">
+        <f>ROUND(100*(Índices!C42/Índices!C41-1),4)</f>
         <v>2.2280000000000002</v>
       </c>
       <c r="D42" s="16">
+        <f>ROUND(100*(Índices!D42/Índices!D41-1),4)</f>
         <v>2.0232000000000001</v>
       </c>
       <c r="E42" s="16">
+        <f>ROUND(100*(Índices!E42/Índices!E41-1),4)</f>
         <v>2.3287</v>
       </c>
       <c r="F42" s="16">
+        <f>ROUND(100*(Índices!F42/Índices!F41-1),4)</f>
         <v>2.1896</v>
       </c>
       <c r="G42" s="16">
+        <f>ROUND(100*(Índices!G42/Índices!G41-1),4)</f>
         <v>2.8690000000000002</v>
       </c>
       <c r="H42" s="16">
+        <f>ROUND(100*(Índices!H42/Índices!H41-1),4)</f>
         <v>2.2625999999999999</v>
       </c>
       <c r="I42" s="17">
+        <f>ROUND(100*(Índices!I42/Índices!I41-1),4)</f>
         <v>2.5571999999999999</v>
       </c>
       <c r="J42" s="16">
+        <f>ROUND(100*(Índices!J42/Índices!J41-1),4)</f>
         <v>3.4584000000000001</v>
       </c>
       <c r="K42" s="16">
@@ -11149,27 +11510,35 @@
         <v>43862</v>
       </c>
       <c r="C43" s="15">
+        <f>ROUND(100*(Índices!C43/Índices!C42-1),4)</f>
         <v>1.7683</v>
       </c>
       <c r="D43" s="16">
+        <f>ROUND(100*(Índices!D43/Índices!D42-1),4)</f>
         <v>1.5924</v>
       </c>
       <c r="E43" s="16">
+        <f>ROUND(100*(Índices!E43/Índices!E42-1),4)</f>
         <v>2.0789</v>
       </c>
       <c r="F43" s="16">
+        <f>ROUND(100*(Índices!F43/Índices!F42-1),4)</f>
         <v>1.5785</v>
       </c>
       <c r="G43" s="16">
+        <f>ROUND(100*(Índices!G43/Índices!G42-1),4)</f>
         <v>2.0390999999999999</v>
       </c>
       <c r="H43" s="16">
+        <f>ROUND(100*(Índices!H43/Índices!H42-1),4)</f>
         <v>1.9298</v>
       </c>
       <c r="I43" s="17">
+        <f>ROUND(100*(Índices!I43/Índices!I42-1),4)</f>
         <v>1.5442</v>
       </c>
       <c r="J43" s="16">
+        <f>ROUND(100*(Índices!J43/Índices!J42-1),4)</f>
         <v>1.3803000000000001</v>
       </c>
       <c r="K43" s="16">
@@ -11214,27 +11583,35 @@
         <v>43891</v>
       </c>
       <c r="C44" s="15">
+        <f>ROUND(100*(Índices!C44/Índices!C43-1),4)</f>
         <v>2.3370000000000002</v>
       </c>
       <c r="D44" s="16">
+        <f>ROUND(100*(Índices!D44/Índices!D43-1),4)</f>
         <v>2.4424000000000001</v>
       </c>
       <c r="E44" s="16">
+        <f>ROUND(100*(Índices!E44/Índices!E43-1),4)</f>
         <v>2.1958000000000002</v>
       </c>
       <c r="F44" s="16">
+        <f>ROUND(100*(Índices!F44/Índices!F43-1),4)</f>
         <v>2.9359999999999999</v>
       </c>
       <c r="G44" s="16">
+        <f>ROUND(100*(Índices!G44/Índices!G43-1),4)</f>
         <v>3.0186000000000002</v>
       </c>
       <c r="H44" s="16">
+        <f>ROUND(100*(Índices!H44/Índices!H43-1),4)</f>
         <v>2.3582999999999998</v>
       </c>
       <c r="I44" s="17">
+        <f>ROUND(100*(Índices!I44/Índices!I43-1),4)</f>
         <v>1.9314</v>
       </c>
       <c r="J44" s="16">
+        <f>ROUND(100*(Índices!J44/Índices!J43-1),4)</f>
         <v>2.6791</v>
       </c>
       <c r="K44" s="16">
@@ -11279,27 +11656,35 @@
         <v>43922</v>
       </c>
       <c r="C45" s="15">
+        <f>ROUND(100*(Índices!C45/Índices!C44-1),4)</f>
         <v>1.496</v>
       </c>
       <c r="D45" s="16">
+        <f>ROUND(100*(Índices!D45/Índices!D44-1),4)</f>
         <v>1.4045000000000001</v>
       </c>
       <c r="E45" s="16">
+        <f>ROUND(100*(Índices!E45/Índices!E44-1),4)</f>
         <v>1.4470000000000001</v>
       </c>
       <c r="F45" s="16">
+        <f>ROUND(100*(Índices!F45/Índices!F44-1),4)</f>
         <v>2.4521999999999999</v>
       </c>
       <c r="G45" s="16">
+        <f>ROUND(100*(Índices!G45/Índices!G44-1),4)</f>
         <v>2.2141999999999999</v>
       </c>
       <c r="H45" s="16">
+        <f>ROUND(100*(Índices!H45/Índices!H44-1),4)</f>
         <v>1.3103</v>
       </c>
       <c r="I45" s="17">
+        <f>ROUND(100*(Índices!I45/Índices!I44-1),4)</f>
         <v>0.877</v>
       </c>
       <c r="J45" s="16">
+        <f>ROUND(100*(Índices!J45/Índices!J44-1),4)</f>
         <v>3.4689000000000001</v>
       </c>
       <c r="K45" s="16">
@@ -11344,27 +11729,35 @@
         <v>43952</v>
       </c>
       <c r="C46" s="15">
+        <f>ROUND(100*(Índices!C46/Índices!C45-1),4)</f>
         <v>2.0554000000000001</v>
       </c>
       <c r="D46" s="16">
+        <f>ROUND(100*(Índices!D46/Índices!D45-1),4)</f>
         <v>1.9876</v>
       </c>
       <c r="E46" s="16">
+        <f>ROUND(100*(Índices!E46/Índices!E45-1),4)</f>
         <v>2.0160999999999998</v>
       </c>
       <c r="F46" s="16">
+        <f>ROUND(100*(Índices!F46/Índices!F45-1),4)</f>
         <v>2.1709000000000001</v>
       </c>
       <c r="G46" s="16">
+        <f>ROUND(100*(Índices!G46/Índices!G45-1),4)</f>
         <v>2.1964000000000001</v>
       </c>
       <c r="H46" s="16">
+        <f>ROUND(100*(Índices!H46/Índices!H45-1),4)</f>
         <v>1.9224000000000001</v>
       </c>
       <c r="I46" s="17">
+        <f>ROUND(100*(Índices!I46/Índices!I45-1),4)</f>
         <v>1.9875</v>
       </c>
       <c r="J46" s="16">
+        <f>ROUND(100*(Índices!J46/Índices!J45-1),4)</f>
         <v>1.9629000000000001</v>
       </c>
       <c r="K46" s="16">
@@ -11409,27 +11802,35 @@
         <v>43983</v>
       </c>
       <c r="C47" s="15">
+        <f>ROUND(100*(Índices!C47/Índices!C46-1),4)</f>
         <v>2.8418000000000001</v>
       </c>
       <c r="D47" s="16">
+        <f>ROUND(100*(Índices!D47/Índices!D46-1),4)</f>
         <v>2.6749000000000001</v>
       </c>
       <c r="E47" s="16">
+        <f>ROUND(100*(Índices!E47/Índices!E46-1),4)</f>
         <v>3.0762</v>
       </c>
       <c r="F47" s="16">
+        <f>ROUND(100*(Índices!F47/Índices!F46-1),4)</f>
         <v>2.8222</v>
       </c>
       <c r="G47" s="16">
+        <f>ROUND(100*(Índices!G47/Índices!G46-1),4)</f>
         <v>3.1057000000000001</v>
       </c>
       <c r="H47" s="16">
+        <f>ROUND(100*(Índices!H47/Índices!H46-1),4)</f>
         <v>2.8921000000000001</v>
       </c>
       <c r="I47" s="17">
+        <f>ROUND(100*(Índices!I47/Índices!I46-1),4)</f>
         <v>2.3856000000000002</v>
       </c>
       <c r="J47" s="16">
+        <f>ROUND(100*(Índices!J47/Índices!J46-1),4)</f>
         <v>2.8458999999999999</v>
       </c>
       <c r="K47" s="16">
@@ -11474,27 +11875,35 @@
         <v>44013</v>
       </c>
       <c r="C48" s="15">
+        <f>ROUND(100*(Índices!C48/Índices!C47-1),4)</f>
         <v>2.6543999999999999</v>
       </c>
       <c r="D48" s="16">
+        <f>ROUND(100*(Índices!D48/Índices!D47-1),4)</f>
         <v>2.2793000000000001</v>
       </c>
       <c r="E48" s="16">
+        <f>ROUND(100*(Índices!E48/Índices!E47-1),4)</f>
         <v>2.9249000000000001</v>
       </c>
       <c r="F48" s="16">
+        <f>ROUND(100*(Índices!F48/Índices!F47-1),4)</f>
         <v>2.9277000000000002</v>
       </c>
       <c r="G48" s="16">
+        <f>ROUND(100*(Índices!G48/Índices!G47-1),4)</f>
         <v>2.9569999999999999</v>
       </c>
       <c r="H48" s="16">
+        <f>ROUND(100*(Índices!H48/Índices!H47-1),4)</f>
         <v>2.9131999999999998</v>
       </c>
       <c r="I48" s="17">
+        <f>ROUND(100*(Índices!I48/Índices!I47-1),4)</f>
         <v>3.1099000000000001</v>
       </c>
       <c r="J48" s="16">
+        <f>ROUND(100*(Índices!J48/Índices!J47-1),4)</f>
         <v>2.9039999999999999</v>
       </c>
       <c r="K48" s="16">
@@ -11539,27 +11948,35 @@
         <v>44044</v>
       </c>
       <c r="C49" s="15">
+        <f>ROUND(100*(Índices!C49/Índices!C48-1),4)</f>
         <v>2.8231000000000002</v>
       </c>
       <c r="D49" s="16">
+        <f>ROUND(100*(Índices!D49/Índices!D48-1),4)</f>
         <v>2.9561000000000002</v>
       </c>
       <c r="E49" s="16">
+        <f>ROUND(100*(Índices!E49/Índices!E48-1),4)</f>
         <v>2.7557</v>
       </c>
       <c r="F49" s="16">
+        <f>ROUND(100*(Índices!F49/Índices!F48-1),4)</f>
         <v>2.4119999999999999</v>
       </c>
       <c r="G49" s="16">
+        <f>ROUND(100*(Índices!G49/Índices!G48-1),4)</f>
         <v>2.2496</v>
       </c>
       <c r="H49" s="16">
+        <f>ROUND(100*(Índices!H49/Índices!H48-1),4)</f>
         <v>2.7789000000000001</v>
       </c>
       <c r="I49" s="17">
+        <f>ROUND(100*(Índices!I49/Índices!I48-1),4)</f>
         <v>2.9567000000000001</v>
       </c>
       <c r="J49" s="16">
+        <f>ROUND(100*(Índices!J49/Índices!J48-1),4)</f>
         <v>3.5625</v>
       </c>
       <c r="K49" s="16">
@@ -11604,27 +12021,35 @@
         <v>44075</v>
       </c>
       <c r="C50" s="15">
+        <f>ROUND(100*(Índices!C50/Índices!C49-1),4)</f>
         <v>2.4977999999999998</v>
       </c>
       <c r="D50" s="16">
+        <f>ROUND(100*(Índices!D50/Índices!D49-1),4)</f>
         <v>2.3054999999999999</v>
       </c>
       <c r="E50" s="16">
+        <f>ROUND(100*(Índices!E50/Índices!E49-1),4)</f>
         <v>2.6692999999999998</v>
       </c>
       <c r="F50" s="16">
+        <f>ROUND(100*(Índices!F50/Índices!F49-1),4)</f>
         <v>2.1032000000000002</v>
       </c>
       <c r="G50" s="16">
+        <f>ROUND(100*(Índices!G50/Índices!G49-1),4)</f>
         <v>3.0682</v>
       </c>
       <c r="H50" s="16">
+        <f>ROUND(100*(Índices!H50/Índices!H49-1),4)</f>
         <v>3.2134</v>
       </c>
       <c r="I50" s="17">
+        <f>ROUND(100*(Índices!I50/Índices!I49-1),4)</f>
         <v>2.0876000000000001</v>
       </c>
       <c r="J50" s="16">
+        <f>ROUND(100*(Índices!J50/Índices!J49-1),4)</f>
         <v>2.6497000000000002</v>
       </c>
       <c r="K50" s="16">
@@ -11669,27 +12094,35 @@
         <v>44105</v>
       </c>
       <c r="C51" s="15">
+        <f>ROUND(100*(Índices!C51/Índices!C50-1),4)</f>
         <v>3.75</v>
       </c>
       <c r="D51" s="16">
+        <f>ROUND(100*(Índices!D51/Índices!D50-1),4)</f>
         <v>3.524</v>
       </c>
       <c r="E51" s="16">
+        <f>ROUND(100*(Índices!E51/Índices!E50-1),4)</f>
         <v>3.9628999999999999</v>
       </c>
       <c r="F51" s="16">
+        <f>ROUND(100*(Índices!F51/Índices!F50-1),4)</f>
         <v>4.1780999999999997</v>
       </c>
       <c r="G51" s="16">
+        <f>ROUND(100*(Índices!G51/Índices!G50-1),4)</f>
         <v>3.7679999999999998</v>
       </c>
       <c r="H51" s="16">
+        <f>ROUND(100*(Índices!H51/Índices!H50-1),4)</f>
         <v>3.8763999999999998</v>
       </c>
       <c r="I51" s="17">
+        <f>ROUND(100*(Índices!I51/Índices!I50-1),4)</f>
         <v>3.5455999999999999</v>
       </c>
       <c r="J51" s="16">
+        <f>ROUND(100*(Índices!J51/Índices!J50-1),4)</f>
         <v>4.7573999999999996</v>
       </c>
       <c r="K51" s="16">
@@ -11734,27 +12167,35 @@
         <v>44136</v>
       </c>
       <c r="C52" s="15">
+        <f>ROUND(100*(Índices!C52/Índices!C51-1),4)</f>
         <v>3.3448000000000002</v>
       </c>
       <c r="D52" s="16">
+        <f>ROUND(100*(Índices!D52/Índices!D51-1),4)</f>
         <v>3.3083999999999998</v>
       </c>
       <c r="E52" s="16">
+        <f>ROUND(100*(Índices!E52/Índices!E51-1),4)</f>
         <v>3.4144999999999999</v>
       </c>
       <c r="F52" s="16">
+        <f>ROUND(100*(Índices!F52/Índices!F51-1),4)</f>
         <v>3.37</v>
       </c>
       <c r="G52" s="16">
+        <f>ROUND(100*(Índices!G52/Índices!G51-1),4)</f>
         <v>3.8317999999999999</v>
       </c>
       <c r="H52" s="16">
+        <f>ROUND(100*(Índices!H52/Índices!H51-1),4)</f>
         <v>3.3452000000000002</v>
       </c>
       <c r="I52" s="17">
+        <f>ROUND(100*(Índices!I52/Índices!I51-1),4)</f>
         <v>2.9845999999999999</v>
       </c>
       <c r="J52" s="16">
+        <f>ROUND(100*(Índices!J52/Índices!J51-1),4)</f>
         <v>3.1743999999999999</v>
       </c>
       <c r="K52" s="16">
@@ -11799,27 +12240,35 @@
         <v>44166</v>
       </c>
       <c r="C53" s="15">
+        <f>ROUND(100*(Índices!C53/Índices!C52-1),4)</f>
         <v>3.6869999999999998</v>
       </c>
       <c r="D53" s="16">
+        <f>ROUND(100*(Índices!D53/Índices!D52-1),4)</f>
         <v>3.6013000000000002</v>
       </c>
       <c r="E53" s="16">
+        <f>ROUND(100*(Índices!E53/Índices!E52-1),4)</f>
         <v>3.9241000000000001</v>
       </c>
       <c r="F53" s="16">
+        <f>ROUND(100*(Índices!F53/Índices!F52-1),4)</f>
         <v>3.8593000000000002</v>
       </c>
       <c r="G53" s="16">
+        <f>ROUND(100*(Índices!G53/Índices!G52-1),4)</f>
         <v>4.5679999999999996</v>
       </c>
       <c r="H53" s="16">
+        <f>ROUND(100*(Índices!H53/Índices!H52-1),4)</f>
         <v>3.9415</v>
       </c>
       <c r="I53" s="17">
+        <f>ROUND(100*(Índices!I53/Índices!I52-1),4)</f>
         <v>2.8504</v>
       </c>
       <c r="J53" s="16">
+        <f>ROUND(100*(Índices!J53/Índices!J52-1),4)</f>
         <v>3.3010999999999999</v>
       </c>
       <c r="K53" s="16">
@@ -11864,27 +12313,35 @@
         <v>44197</v>
       </c>
       <c r="C54" s="15">
+        <f>ROUND(100*(Índices!C54/Índices!C53-1),4)</f>
         <v>3.7511999999999999</v>
       </c>
       <c r="D54" s="16">
+        <f>ROUND(100*(Índices!D54/Índices!D53-1),4)</f>
         <v>3.1156000000000001</v>
       </c>
       <c r="E54" s="16">
+        <f>ROUND(100*(Índices!E54/Índices!E53-1),4)</f>
         <v>4.2582000000000004</v>
       </c>
       <c r="F54" s="16">
+        <f>ROUND(100*(Índices!F54/Índices!F53-1),4)</f>
         <v>5.0228000000000002</v>
       </c>
       <c r="G54" s="16">
+        <f>ROUND(100*(Índices!G54/Índices!G53-1),4)</f>
         <v>3.9354</v>
       </c>
       <c r="H54" s="16">
+        <f>ROUND(100*(Índices!H54/Índices!H53-1),4)</f>
         <v>3.9756999999999998</v>
       </c>
       <c r="I54" s="17">
+        <f>ROUND(100*(Índices!I54/Índices!I53-1),4)</f>
         <v>3.6859999999999999</v>
       </c>
       <c r="J54" s="16">
+        <f>ROUND(100*(Índices!J54/Índices!J53-1),4)</f>
         <v>3.1067999999999998</v>
       </c>
       <c r="K54" s="16">
@@ -11929,27 +12386,35 @@
         <v>44228</v>
       </c>
       <c r="C55" s="15">
+        <f>ROUND(100*(Índices!C55/Índices!C54-1),4)</f>
         <v>3.3384999999999998</v>
       </c>
       <c r="D55" s="16">
+        <f>ROUND(100*(Índices!D55/Índices!D54-1),4)</f>
         <v>3.3525</v>
       </c>
       <c r="E55" s="16">
+        <f>ROUND(100*(Índices!E55/Índices!E54-1),4)</f>
         <v>3.2749999999999999</v>
       </c>
       <c r="F55" s="16">
+        <f>ROUND(100*(Índices!F55/Índices!F54-1),4)</f>
         <v>3.0339999999999998</v>
       </c>
       <c r="G55" s="16">
+        <f>ROUND(100*(Índices!G55/Índices!G54-1),4)</f>
         <v>3.6095999999999999</v>
       </c>
       <c r="H55" s="16">
+        <f>ROUND(100*(Índices!H55/Índices!H54-1),4)</f>
         <v>3.6917</v>
       </c>
       <c r="I55" s="17">
+        <f>ROUND(100*(Índices!I55/Índices!I54-1),4)</f>
         <v>3.5825999999999998</v>
       </c>
       <c r="J55" s="16">
+        <f>ROUND(100*(Índices!J55/Índices!J54-1),4)</f>
         <v>2.5257000000000001</v>
       </c>
       <c r="K55" s="16">
@@ -11994,27 +12459,35 @@
         <v>44256</v>
       </c>
       <c r="C56" s="15">
+        <f>ROUND(100*(Índices!C56/Índices!C55-1),4)</f>
         <v>3.8342999999999998</v>
       </c>
       <c r="D56" s="16">
+        <f>ROUND(100*(Índices!D56/Índices!D55-1),4)</f>
         <v>3.9268000000000001</v>
       </c>
       <c r="E56" s="16">
+        <f>ROUND(100*(Índices!E56/Índices!E55-1),4)</f>
         <v>3.9251</v>
       </c>
       <c r="F56" s="16">
+        <f>ROUND(100*(Índices!F56/Índices!F55-1),4)</f>
         <v>3.3468</v>
       </c>
       <c r="G56" s="16">
+        <f>ROUND(100*(Índices!G56/Índices!G55-1),4)</f>
         <v>2.9036</v>
       </c>
       <c r="H56" s="16">
+        <f>ROUND(100*(Índices!H56/Índices!H55-1),4)</f>
         <v>3.5632999999999999</v>
       </c>
       <c r="I56" s="17">
+        <f>ROUND(100*(Índices!I56/Índices!I55-1),4)</f>
         <v>3.4079000000000002</v>
       </c>
       <c r="J56" s="16">
+        <f>ROUND(100*(Índices!J56/Índices!J55-1),4)</f>
         <v>3.3283999999999998</v>
       </c>
       <c r="K56" s="16">
@@ -12059,27 +12532,35 @@
         <v>44287</v>
       </c>
       <c r="C57" s="15">
+        <f>ROUND(100*(Índices!C57/Índices!C56-1),4)</f>
         <v>4.0395000000000003</v>
       </c>
       <c r="D57" s="16">
+        <f>ROUND(100*(Índices!D57/Índices!D56-1),4)</f>
         <v>4.0541999999999998</v>
       </c>
       <c r="E57" s="16">
+        <f>ROUND(100*(Índices!E57/Índices!E56-1),4)</f>
         <v>3.8996</v>
       </c>
       <c r="F57" s="16">
+        <f>ROUND(100*(Índices!F57/Índices!F56-1),4)</f>
         <v>3.7890999999999999</v>
       </c>
       <c r="G57" s="16">
+        <f>ROUND(100*(Índices!G57/Índices!G56-1),4)</f>
         <v>4.1538000000000004</v>
       </c>
       <c r="H57" s="16">
+        <f>ROUND(100*(Índices!H57/Índices!H56-1),4)</f>
         <v>4.1901000000000002</v>
       </c>
       <c r="I57" s="17">
+        <f>ROUND(100*(Índices!I57/Índices!I56-1),4)</f>
         <v>5.0145</v>
       </c>
       <c r="J57" s="16">
+        <f>ROUND(100*(Índices!J57/Índices!J56-1),4)</f>
         <v>4.6199000000000003</v>
       </c>
       <c r="K57" s="16">
@@ -12124,27 +12605,35 @@
         <v>44317</v>
       </c>
       <c r="C58" s="15">
+        <f>ROUND(100*(Índices!C58/Índices!C57-1),4)</f>
         <v>3.7856000000000001</v>
       </c>
       <c r="D58" s="16">
+        <f>ROUND(100*(Índices!D58/Índices!D57-1),4)</f>
         <v>3.8923999999999999</v>
       </c>
       <c r="E58" s="16">
+        <f>ROUND(100*(Índices!E58/Índices!E57-1),4)</f>
         <v>3.7099000000000002</v>
       </c>
       <c r="F58" s="16">
+        <f>ROUND(100*(Índices!F58/Índices!F57-1),4)</f>
         <v>3.7862</v>
       </c>
       <c r="G58" s="16">
+        <f>ROUND(100*(Índices!G58/Índices!G57-1),4)</f>
         <v>3.7738999999999998</v>
       </c>
       <c r="H58" s="16">
+        <f>ROUND(100*(Índices!H58/Índices!H57-1),4)</f>
         <v>4.2176999999999998</v>
       </c>
       <c r="I58" s="17">
+        <f>ROUND(100*(Índices!I58/Índices!I57-1),4)</f>
         <v>3.8965999999999998</v>
       </c>
       <c r="J58" s="16">
+        <f>ROUND(100*(Índices!J58/Índices!J57-1),4)</f>
         <v>4.4200999999999997</v>
       </c>
       <c r="K58" s="16">
@@ -12189,27 +12678,35 @@
         <v>44348</v>
       </c>
       <c r="C59" s="15">
+        <f>ROUND(100*(Índices!C59/Índices!C58-1),4)</f>
         <v>3.8508</v>
       </c>
       <c r="D59" s="16">
+        <f>ROUND(100*(Índices!D59/Índices!D58-1),4)</f>
         <v>3.7336999999999998</v>
       </c>
       <c r="E59" s="16">
+        <f>ROUND(100*(Índices!E59/Índices!E58-1),4)</f>
         <v>3.8494999999999999</v>
       </c>
       <c r="F59" s="16">
+        <f>ROUND(100*(Índices!F59/Índices!F58-1),4)</f>
         <v>3.9451999999999998</v>
       </c>
       <c r="G59" s="16">
+        <f>ROUND(100*(Índices!G59/Índices!G58-1),4)</f>
         <v>3.7031000000000001</v>
       </c>
       <c r="H59" s="16">
+        <f>ROUND(100*(Índices!H59/Índices!H58-1),4)</f>
         <v>4.1261000000000001</v>
       </c>
       <c r="I59" s="17">
+        <f>ROUND(100*(Índices!I59/Índices!I58-1),4)</f>
         <v>3.9258000000000002</v>
       </c>
       <c r="J59" s="16">
+        <f>ROUND(100*(Índices!J59/Índices!J58-1),4)</f>
         <v>5.0846999999999998</v>
       </c>
       <c r="K59" s="16">
@@ -12254,27 +12751,35 @@
         <v>44378</v>
       </c>
       <c r="C60" s="15">
+        <f>ROUND(100*(Índices!C60/Índices!C59-1),4)</f>
         <v>3.7370999999999999</v>
       </c>
       <c r="D60" s="16">
+        <f>ROUND(100*(Índices!D60/Índices!D59-1),4)</f>
         <v>3.7692999999999999</v>
       </c>
       <c r="E60" s="16">
+        <f>ROUND(100*(Índices!E60/Índices!E59-1),4)</f>
         <v>3.6958000000000002</v>
       </c>
       <c r="F60" s="16">
+        <f>ROUND(100*(Índices!F60/Índices!F59-1),4)</f>
         <v>3.8290999999999999</v>
       </c>
       <c r="G60" s="16">
+        <f>ROUND(100*(Índices!G60/Índices!G59-1),4)</f>
         <v>3.7284999999999999</v>
       </c>
       <c r="H60" s="16">
+        <f>ROUND(100*(Índices!H60/Índices!H59-1),4)</f>
         <v>3.8357999999999999</v>
       </c>
       <c r="I60" s="17">
+        <f>ROUND(100*(Índices!I60/Índices!I59-1),4)</f>
         <v>3.7241</v>
       </c>
       <c r="J60" s="16">
+        <f>ROUND(100*(Índices!J60/Índices!J59-1),4)</f>
         <v>5.0617000000000001</v>
       </c>
       <c r="K60" s="16">
@@ -12319,27 +12824,35 @@
         <v>44409</v>
       </c>
       <c r="C61" s="15">
+        <f>ROUND(100*(Índices!C61/Índices!C60-1),4)</f>
         <v>2.5573999999999999</v>
       </c>
       <c r="D61" s="16">
+        <f>ROUND(100*(Índices!D61/Índices!D60-1),4)</f>
         <v>2.7629999999999999</v>
       </c>
       <c r="E61" s="16">
+        <f>ROUND(100*(Índices!E61/Índices!E60-1),4)</f>
         <v>2.3639999999999999</v>
       </c>
       <c r="F61" s="16">
+        <f>ROUND(100*(Índices!F61/Índices!F60-1),4)</f>
         <v>2.2159</v>
       </c>
       <c r="G61" s="16">
+        <f>ROUND(100*(Índices!G61/Índices!G60-1),4)</f>
         <v>2.6432000000000002</v>
       </c>
       <c r="H61" s="16">
+        <f>ROUND(100*(Índices!H61/Índices!H60-1),4)</f>
         <v>1.8532999999999999</v>
       </c>
       <c r="I61" s="17">
+        <f>ROUND(100*(Índices!I61/Índices!I60-1),4)</f>
         <v>3.4432</v>
       </c>
       <c r="J61" s="16">
+        <f>ROUND(100*(Índices!J61/Índices!J60-1),4)</f>
         <v>1.5766</v>
       </c>
       <c r="K61" s="16">
@@ -12384,27 +12897,35 @@
         <v>44440</v>
       </c>
       <c r="C62" s="15">
+        <f>ROUND(100*(Índices!C62/Índices!C61-1),4)</f>
         <v>3.1688999999999998</v>
       </c>
       <c r="D62" s="16">
+        <f>ROUND(100*(Índices!D62/Índices!D61-1),4)</f>
         <v>3.3551000000000002</v>
       </c>
       <c r="E62" s="16">
+        <f>ROUND(100*(Índices!E62/Índices!E61-1),4)</f>
         <v>3.1385000000000001</v>
       </c>
       <c r="F62" s="16">
+        <f>ROUND(100*(Índices!F62/Índices!F61-1),4)</f>
         <v>2.9893999999999998</v>
       </c>
       <c r="G62" s="16">
+        <f>ROUND(100*(Índices!G62/Índices!G61-1),4)</f>
         <v>2.4857</v>
       </c>
       <c r="H62" s="16">
+        <f>ROUND(100*(Índices!H62/Índices!H61-1),4)</f>
         <v>2.5257999999999998</v>
       </c>
       <c r="I62" s="17">
+        <f>ROUND(100*(Índices!I62/Índices!I61-1),4)</f>
         <v>3.5697999999999999</v>
       </c>
       <c r="J62" s="16">
+        <f>ROUND(100*(Índices!J62/Índices!J61-1),4)</f>
         <v>2.6423999999999999</v>
       </c>
       <c r="K62" s="16">
@@ -12449,27 +12970,35 @@
         <v>44470</v>
       </c>
       <c r="C63" s="15">
+        <f>ROUND(100*(Índices!C63/Índices!C62-1),4)</f>
         <v>3.5230999999999999</v>
       </c>
       <c r="D63" s="16">
+        <f>ROUND(100*(Índices!D63/Índices!D62-1),4)</f>
         <v>3.7549000000000001</v>
       </c>
       <c r="E63" s="16">
+        <f>ROUND(100*(Índices!E63/Índices!E62-1),4)</f>
         <v>3.3873000000000002</v>
       </c>
       <c r="F63" s="16">
+        <f>ROUND(100*(Índices!F63/Índices!F62-1),4)</f>
         <v>3.3323999999999998</v>
       </c>
       <c r="G63" s="16">
+        <f>ROUND(100*(Índices!G63/Índices!G62-1),4)</f>
         <v>3.5</v>
       </c>
       <c r="H63" s="16">
+        <f>ROUND(100*(Índices!H63/Índices!H62-1),4)</f>
         <v>3.3306</v>
       </c>
       <c r="I63" s="17">
+        <f>ROUND(100*(Índices!I63/Índices!I62-1),4)</f>
         <v>2.9535999999999998</v>
       </c>
       <c r="J63" s="16">
+        <f>ROUND(100*(Índices!J63/Índices!J62-1),4)</f>
         <v>3.4016000000000002</v>
       </c>
       <c r="K63" s="16">
@@ -12514,27 +13043,35 @@
         <v>44501</v>
       </c>
       <c r="C64" s="15">
+        <f>ROUND(100*(Índices!C64/Índices!C63-1),4)</f>
         <v>2.7570999999999999</v>
       </c>
       <c r="D64" s="16">
+        <f>ROUND(100*(Índices!D64/Índices!D63-1),4)</f>
         <v>2.6482999999999999</v>
       </c>
       <c r="E64" s="16">
+        <f>ROUND(100*(Índices!E64/Índices!E63-1),4)</f>
         <v>2.8475000000000001</v>
       </c>
       <c r="F64" s="16">
+        <f>ROUND(100*(Índices!F64/Índices!F63-1),4)</f>
         <v>2.9559000000000002</v>
       </c>
       <c r="G64" s="16">
+        <f>ROUND(100*(Índices!G64/Índices!G63-1),4)</f>
         <v>3.1343000000000001</v>
       </c>
       <c r="H64" s="16">
+        <f>ROUND(100*(Índices!H64/Índices!H63-1),4)</f>
         <v>2.8700999999999999</v>
       </c>
       <c r="I64" s="17">
+        <f>ROUND(100*(Índices!I64/Índices!I63-1),4)</f>
         <v>2.2692999999999999</v>
       </c>
       <c r="J64" s="16">
+        <f>ROUND(100*(Índices!J64/Índices!J63-1),4)</f>
         <v>2.5701999999999998</v>
       </c>
       <c r="K64" s="16">
@@ -12579,27 +13116,35 @@
         <v>44531</v>
       </c>
       <c r="C65" s="15">
+        <f>ROUND(100*(Índices!C65/Índices!C64-1),4)</f>
         <v>3.5710999999999999</v>
       </c>
       <c r="D65" s="16">
+        <f>ROUND(100*(Índices!D65/Índices!D64-1),4)</f>
         <v>3.9289999999999998</v>
       </c>
       <c r="E65" s="16">
+        <f>ROUND(100*(Índices!E65/Índices!E64-1),4)</f>
         <v>3.2650000000000001</v>
       </c>
       <c r="F65" s="16">
+        <f>ROUND(100*(Índices!F65/Índices!F64-1),4)</f>
         <v>3.5705</v>
       </c>
       <c r="G65" s="16">
+        <f>ROUND(100*(Índices!G65/Índices!G64-1),4)</f>
         <v>3.4285000000000001</v>
       </c>
       <c r="H65" s="16">
+        <f>ROUND(100*(Índices!H65/Índices!H64-1),4)</f>
         <v>3.5558000000000001</v>
       </c>
       <c r="I65" s="17">
+        <f>ROUND(100*(Índices!I65/Índices!I64-1),4)</f>
         <v>2.9363000000000001</v>
       </c>
       <c r="J65" s="16">
+        <f>ROUND(100*(Índices!J65/Índices!J64-1),4)</f>
         <v>3.2065000000000001</v>
       </c>
       <c r="K65" s="16">
@@ -12644,27 +13189,35 @@
         <v>44562</v>
       </c>
       <c r="C66" s="15">
+        <f>ROUND(100*(Índices!C66/Índices!C65-1),4)</f>
         <v>3.5985</v>
       </c>
       <c r="D66" s="16">
+        <f>ROUND(100*(Índices!D66/Índices!D65-1),4)</f>
         <v>3.7831999999999999</v>
       </c>
       <c r="E66" s="16">
+        <f>ROUND(100*(Índices!E66/Índices!E65-1),4)</f>
         <v>3.4647000000000001</v>
       </c>
       <c r="F66" s="16">
+        <f>ROUND(100*(Índices!F66/Índices!F65-1),4)</f>
         <v>3.5672999999999999</v>
       </c>
       <c r="G66" s="16">
+        <f>ROUND(100*(Índices!G66/Índices!G65-1),4)</f>
         <v>3.0621999999999998</v>
       </c>
       <c r="H66" s="16">
+        <f>ROUND(100*(Índices!H66/Índices!H65-1),4)</f>
         <v>3.5646</v>
       </c>
       <c r="I66" s="17">
+        <f>ROUND(100*(Índices!I66/Índices!I65-1),4)</f>
         <v>3.1833</v>
       </c>
       <c r="J66" s="16">
+        <f>ROUND(100*(Índices!J66/Índices!J65-1),4)</f>
         <v>3.2206000000000001</v>
       </c>
       <c r="K66" s="16">
@@ -12709,27 +13262,35 @@
         <v>44593</v>
       </c>
       <c r="C67" s="15">
+        <f>ROUND(100*(Índices!C67/Índices!C66-1),4)</f>
         <v>4.4962</v>
       </c>
       <c r="D67" s="16">
+        <f>ROUND(100*(Índices!D67/Índices!D66-1),4)</f>
         <v>4.2904999999999998</v>
       </c>
       <c r="E67" s="16">
+        <f>ROUND(100*(Índices!E67/Índices!E66-1),4)</f>
         <v>4.5098000000000003</v>
       </c>
       <c r="F67" s="16">
+        <f>ROUND(100*(Índices!F67/Índices!F66-1),4)</f>
         <v>4.5692000000000004</v>
       </c>
       <c r="G67" s="16">
+        <f>ROUND(100*(Índices!G67/Índices!G66-1),4)</f>
         <v>4.7759</v>
       </c>
       <c r="H67" s="16">
+        <f>ROUND(100*(Índices!H67/Índices!H66-1),4)</f>
         <v>4.9763000000000002</v>
       </c>
       <c r="I67" s="17">
+        <f>ROUND(100*(Índices!I67/Índices!I66-1),4)</f>
         <v>4.5456000000000003</v>
       </c>
       <c r="J67" s="16">
+        <f>ROUND(100*(Índices!J67/Índices!J66-1),4)</f>
         <v>6.1284000000000001</v>
       </c>
       <c r="K67" s="16">
@@ -12774,27 +13335,35 @@
         <v>44621</v>
       </c>
       <c r="C68" s="15">
+        <f>ROUND(100*(Índices!C68/Índices!C67-1),4)</f>
         <v>5.5423</v>
       </c>
       <c r="D68" s="16">
+        <f>ROUND(100*(Índices!D68/Índices!D67-1),4)</f>
         <v>5.2352999999999996</v>
       </c>
       <c r="E68" s="16">
+        <f>ROUND(100*(Índices!E68/Índices!E67-1),4)</f>
         <v>5.6013000000000002</v>
       </c>
       <c r="F68" s="16">
+        <f>ROUND(100*(Índices!F68/Índices!F67-1),4)</f>
         <v>5.8468999999999998</v>
       </c>
       <c r="G68" s="16">
+        <f>ROUND(100*(Índices!G68/Índices!G67-1),4)</f>
         <v>6.8284000000000002</v>
       </c>
       <c r="H68" s="16">
+        <f>ROUND(100*(Índices!H68/Índices!H67-1),4)</f>
         <v>5.9512999999999998</v>
       </c>
       <c r="I68" s="17">
+        <f>ROUND(100*(Índices!I68/Índices!I67-1),4)</f>
         <v>6.7369000000000003</v>
       </c>
       <c r="J68" s="16">
+        <f>ROUND(100*(Índices!J68/Índices!J67-1),4)</f>
         <v>5.9473000000000003</v>
       </c>
       <c r="K68" s="16">
@@ -12839,27 +13408,35 @@
         <v>44652</v>
       </c>
       <c r="C69" s="15">
+        <f>ROUND(100*(Índices!C69/Índices!C68-1),4)</f>
         <v>5.9547999999999996</v>
       </c>
       <c r="D69" s="16">
+        <f>ROUND(100*(Índices!D69/Índices!D68-1),4)</f>
         <v>6.0625999999999998</v>
       </c>
       <c r="E69" s="16">
+        <f>ROUND(100*(Índices!E69/Índices!E68-1),4)</f>
         <v>5.7770000000000001</v>
       </c>
       <c r="F69" s="16">
+        <f>ROUND(100*(Índices!F69/Índices!F68-1),4)</f>
         <v>6.0824999999999996</v>
       </c>
       <c r="G69" s="16">
+        <f>ROUND(100*(Índices!G69/Índices!G68-1),4)</f>
         <v>5.9619999999999997</v>
       </c>
       <c r="H69" s="16">
+        <f>ROUND(100*(Índices!H69/Índices!H68-1),4)</f>
         <v>5.8596000000000004</v>
       </c>
       <c r="I69" s="17">
+        <f>ROUND(100*(Índices!I69/Índices!I68-1),4)</f>
         <v>6.1215999999999999</v>
       </c>
       <c r="J69" s="16">
+        <f>ROUND(100*(Índices!J69/Índices!J68-1),4)</f>
         <v>6.1672000000000002</v>
       </c>
       <c r="K69" s="16">
@@ -12904,27 +13481,35 @@
         <v>44682</v>
       </c>
       <c r="C70" s="15">
+        <f>ROUND(100*(Índices!C70/Índices!C69-1),4)</f>
         <v>5.6184000000000003</v>
       </c>
       <c r="D70" s="16">
+        <f>ROUND(100*(Índices!D70/Índices!D69-1),4)</f>
         <v>5.3296000000000001</v>
       </c>
       <c r="E70" s="16">
+        <f>ROUND(100*(Índices!E70/Índices!E69-1),4)</f>
         <v>5.7821999999999996</v>
       </c>
       <c r="F70" s="16">
+        <f>ROUND(100*(Índices!F70/Índices!F69-1),4)</f>
         <v>6.1651999999999996</v>
       </c>
       <c r="G70" s="16">
+        <f>ROUND(100*(Índices!G70/Índices!G69-1),4)</f>
         <v>5.9718999999999998</v>
       </c>
       <c r="H70" s="16">
+        <f>ROUND(100*(Índices!H70/Índices!H69-1),4)</f>
         <v>5.8391999999999999</v>
       </c>
       <c r="I70" s="17">
+        <f>ROUND(100*(Índices!I70/Índices!I69-1),4)</f>
         <v>5.26</v>
       </c>
       <c r="J70" s="16">
+        <f>ROUND(100*(Índices!J70/Índices!J69-1),4)</f>
         <v>5.7431999999999999</v>
       </c>
       <c r="K70" s="16">
@@ -12969,27 +13554,35 @@
         <v>44713</v>
       </c>
       <c r="C71" s="15">
+        <f>ROUND(100*(Índices!C71/Índices!C70-1),4)</f>
         <v>6.0377999999999998</v>
       </c>
       <c r="D71" s="16">
+        <f>ROUND(100*(Índices!D71/Índices!D70-1),4)</f>
         <v>6.2378</v>
       </c>
       <c r="E71" s="16">
+        <f>ROUND(100*(Índices!E71/Índices!E70-1),4)</f>
         <v>5.8604000000000003</v>
       </c>
       <c r="F71" s="16">
+        <f>ROUND(100*(Índices!F71/Índices!F70-1),4)</f>
         <v>5.9821999999999997</v>
       </c>
       <c r="G71" s="16">
+        <f>ROUND(100*(Índices!G71/Índices!G70-1),4)</f>
         <v>5.8426999999999998</v>
       </c>
       <c r="H71" s="16">
+        <f>ROUND(100*(Índices!H71/Índices!H70-1),4)</f>
         <v>5.9158999999999997</v>
       </c>
       <c r="I71" s="17">
+        <f>ROUND(100*(Índices!I71/Índices!I70-1),4)</f>
         <v>5.5928000000000004</v>
       </c>
       <c r="J71" s="16">
+        <f>ROUND(100*(Índices!J71/Índices!J70-1),4)</f>
         <v>6.4846000000000004</v>
       </c>
       <c r="K71" s="16">
@@ -13034,27 +13627,35 @@
         <v>44743</v>
       </c>
       <c r="C72" s="15">
+        <f>ROUND(100*(Índices!C72/Índices!C71-1),4)</f>
         <v>8.1999999999999993</v>
       </c>
       <c r="D72" s="16">
+        <f>ROUND(100*(Índices!D72/Índices!D71-1),4)</f>
         <v>8.1683000000000003</v>
       </c>
       <c r="E72" s="16">
+        <f>ROUND(100*(Índices!E72/Índices!E71-1),4)</f>
         <v>8.4308999999999994</v>
       </c>
       <c r="F72" s="16">
+        <f>ROUND(100*(Índices!F72/Índices!F71-1),4)</f>
         <v>7.8813000000000004</v>
       </c>
       <c r="G72" s="16">
+        <f>ROUND(100*(Índices!G72/Índices!G71-1),4)</f>
         <v>8.1944999999999997</v>
       </c>
       <c r="H72" s="16">
+        <f>ROUND(100*(Índices!H72/Índices!H71-1),4)</f>
         <v>8.0350999999999999</v>
       </c>
       <c r="I72" s="17">
+        <f>ROUND(100*(Índices!I72/Índices!I71-1),4)</f>
         <v>8.4328000000000003</v>
       </c>
       <c r="J72" s="16">
+        <f>ROUND(100*(Índices!J72/Índices!J71-1),4)</f>
         <v>7.7127999999999997</v>
       </c>
       <c r="K72" s="16">
@@ -13099,27 +13700,35 @@
         <v>44774</v>
       </c>
       <c r="C73" s="15">
+        <f>ROUND(100*(Índices!C73/Índices!C72-1),4)</f>
         <v>7.1026999999999996</v>
       </c>
       <c r="D73" s="16">
+        <f>ROUND(100*(Índices!D73/Índices!D72-1),4)</f>
         <v>7.1374000000000004</v>
       </c>
       <c r="E73" s="16">
+        <f>ROUND(100*(Índices!E73/Índices!E72-1),4)</f>
         <v>7.0563000000000002</v>
       </c>
       <c r="F73" s="16">
+        <f>ROUND(100*(Índices!F73/Índices!F72-1),4)</f>
         <v>7.4732000000000003</v>
       </c>
       <c r="G73" s="16">
+        <f>ROUND(100*(Índices!G73/Índices!G72-1),4)</f>
         <v>7.5396000000000001</v>
       </c>
       <c r="H73" s="16">
+        <f>ROUND(100*(Índices!H73/Índices!H72-1),4)</f>
         <v>6.5382999999999996</v>
       </c>
       <c r="I73" s="17">
+        <f>ROUND(100*(Índices!I73/Índices!I72-1),4)</f>
         <v>6.4634</v>
       </c>
       <c r="J73" s="16">
+        <f>ROUND(100*(Índices!J73/Índices!J72-1),4)</f>
         <v>7.1933999999999996</v>
       </c>
       <c r="K73" s="16">
@@ -13164,27 +13773,35 @@
         <v>44805</v>
       </c>
       <c r="C74" s="15">
+        <f>ROUND(100*(Índices!C74/Índices!C73-1),4)</f>
         <v>5.7778</v>
       </c>
       <c r="D74" s="16">
+        <f>ROUND(100*(Índices!D74/Índices!D73-1),4)</f>
         <v>5.4924999999999997</v>
       </c>
       <c r="E74" s="16">
+        <f>ROUND(100*(Índices!E74/Índices!E73-1),4)</f>
         <v>5.9278000000000004</v>
       </c>
       <c r="F74" s="16">
+        <f>ROUND(100*(Índices!F74/Índices!F73-1),4)</f>
         <v>5.7850000000000001</v>
       </c>
       <c r="G74" s="16">
+        <f>ROUND(100*(Índices!G74/Índices!G73-1),4)</f>
         <v>6.4797000000000002</v>
       </c>
       <c r="H74" s="16">
+        <f>ROUND(100*(Índices!H74/Índices!H73-1),4)</f>
         <v>5.7042000000000002</v>
       </c>
       <c r="I74" s="17">
+        <f>ROUND(100*(Índices!I74/Índices!I73-1),4)</f>
         <v>5.9688999999999997</v>
       </c>
       <c r="J74" s="16">
+        <f>ROUND(100*(Índices!J74/Índices!J73-1),4)</f>
         <v>6.4233000000000002</v>
       </c>
       <c r="K74" s="16">
@@ -13229,27 +13846,35 @@
         <v>44835</v>
       </c>
       <c r="C75" s="15">
+        <f>ROUND(100*(Índices!C75/Índices!C74-1),4)</f>
         <v>6.3478000000000003</v>
       </c>
       <c r="D75" s="16">
+        <f>ROUND(100*(Índices!D75/Índices!D74-1),4)</f>
         <v>6.5435999999999996</v>
       </c>
       <c r="E75" s="16">
+        <f>ROUND(100*(Índices!E75/Índices!E74-1),4)</f>
         <v>6.1266999999999996</v>
       </c>
       <c r="F75" s="16">
+        <f>ROUND(100*(Índices!F75/Índices!F74-1),4)</f>
         <v>6.4040999999999997</v>
       </c>
       <c r="G75" s="16">
+        <f>ROUND(100*(Índices!G75/Índices!G74-1),4)</f>
         <v>6.1501999999999999</v>
       </c>
       <c r="H75" s="16">
+        <f>ROUND(100*(Índices!H75/Índices!H74-1),4)</f>
         <v>6.2367999999999997</v>
       </c>
       <c r="I75" s="17">
+        <f>ROUND(100*(Índices!I75/Índices!I74-1),4)</f>
         <v>6.7008999999999999</v>
       </c>
       <c r="J75" s="16">
+        <f>ROUND(100*(Índices!J75/Índices!J74-1),4)</f>
         <v>6.1540999999999997</v>
       </c>
       <c r="K75" s="16">
@@ -13294,27 +13919,35 @@
         <v>44866</v>
       </c>
       <c r="C76" s="15">
+        <f>ROUND(100*(Índices!C76/Índices!C75-1),4)</f>
         <v>5.1672000000000002</v>
       </c>
       <c r="D76" s="16">
+        <f>ROUND(100*(Índices!D76/Índices!D75-1),4)</f>
         <v>5.4345999999999997</v>
       </c>
       <c r="E76" s="16">
+        <f>ROUND(100*(Índices!E76/Índices!E75-1),4)</f>
         <v>5.0023</v>
       </c>
       <c r="F76" s="16">
+        <f>ROUND(100*(Índices!F76/Índices!F75-1),4)</f>
         <v>4.8808999999999996</v>
       </c>
       <c r="G76" s="16">
+        <f>ROUND(100*(Índices!G76/Índices!G75-1),4)</f>
         <v>4.6874000000000002</v>
       </c>
       <c r="H76" s="16">
+        <f>ROUND(100*(Índices!H76/Índices!H75-1),4)</f>
         <v>5.1704999999999997</v>
       </c>
       <c r="I76" s="17">
+        <f>ROUND(100*(Índices!I76/Índices!I75-1),4)</f>
         <v>5.0004</v>
       </c>
       <c r="J76" s="16">
+        <f>ROUND(100*(Índices!J76/Índices!J75-1),4)</f>
         <v>3.9645999999999999</v>
       </c>
       <c r="K76" s="16">
@@ -13359,27 +13992,35 @@
         <v>44896</v>
       </c>
       <c r="C77" s="15">
+        <f>ROUND(100*(Índices!C77/Índices!C76-1),4)</f>
         <v>4.8902999999999999</v>
       </c>
       <c r="D77" s="16">
+        <f>ROUND(100*(Índices!D77/Índices!D76-1),4)</f>
         <v>5.2004999999999999</v>
       </c>
       <c r="E77" s="16">
+        <f>ROUND(100*(Índices!E77/Índices!E76-1),4)</f>
         <v>4.8014000000000001</v>
       </c>
       <c r="F77" s="16">
+        <f>ROUND(100*(Índices!F77/Índices!F76-1),4)</f>
         <v>4.1490999999999998</v>
       </c>
       <c r="G77" s="16">
+        <f>ROUND(100*(Índices!G77/Índices!G76-1),4)</f>
         <v>3.7934000000000001</v>
       </c>
       <c r="H77" s="16">
+        <f>ROUND(100*(Índices!H77/Índices!H76-1),4)</f>
         <v>4.6268000000000002</v>
       </c>
       <c r="I77" s="17">
+        <f>ROUND(100*(Índices!I77/Índices!I76-1),4)</f>
         <v>4.3968999999999996</v>
       </c>
       <c r="J77" s="16">
+        <f>ROUND(100*(Índices!J77/Índices!J76-1),4)</f>
         <v>3.6168</v>
       </c>
       <c r="K77" s="16">
@@ -13424,27 +14065,35 @@
         <v>44927</v>
       </c>
       <c r="C78" s="15">
+        <f>ROUND(100*(Índices!C78/Índices!C77-1),4)</f>
         <v>5.7138999999999998</v>
       </c>
       <c r="D78" s="16">
+        <f>ROUND(100*(Índices!D78/Índices!D77-1),4)</f>
         <v>5.7967000000000004</v>
       </c>
       <c r="E78" s="16">
+        <f>ROUND(100*(Índices!E78/Índices!E77-1),4)</f>
         <v>5.6573000000000002</v>
       </c>
       <c r="F78" s="16">
+        <f>ROUND(100*(Índices!F78/Índices!F77-1),4)</f>
         <v>5.8897000000000004</v>
       </c>
       <c r="G78" s="16">
+        <f>ROUND(100*(Índices!G78/Índices!G77-1),4)</f>
         <v>5.2648000000000001</v>
       </c>
       <c r="H78" s="16">
+        <f>ROUND(100*(Índices!H78/Índices!H77-1),4)</f>
         <v>5.8543000000000003</v>
       </c>
       <c r="I78" s="17">
+        <f>ROUND(100*(Índices!I78/Índices!I77-1),4)</f>
         <v>5.4778000000000002</v>
       </c>
       <c r="J78" s="16">
+        <f>ROUND(100*(Índices!J78/Índices!J77-1),4)</f>
         <v>5.0232999999999999</v>
       </c>
       <c r="K78" s="16">
@@ -13489,27 +14138,35 @@
         <v>44958</v>
       </c>
       <c r="C79" s="15">
+        <f>ROUND(100*(Índices!C79/Índices!C78-1),4)</f>
         <v>6.3708999999999998</v>
       </c>
       <c r="D79" s="16">
+        <f>ROUND(100*(Índices!D79/Índices!D78-1),4)</f>
         <v>6.3978000000000002</v>
       </c>
       <c r="E79" s="16">
+        <f>ROUND(100*(Índices!E79/Índices!E78-1),4)</f>
         <v>6.1902999999999997</v>
       </c>
       <c r="F79" s="16">
+        <f>ROUND(100*(Índices!F79/Índices!F78-1),4)</f>
         <v>6.9429999999999996</v>
       </c>
       <c r="G79" s="16">
+        <f>ROUND(100*(Índices!G79/Índices!G78-1),4)</f>
         <v>7.5970000000000004</v>
       </c>
       <c r="H79" s="16">
+        <f>ROUND(100*(Índices!H79/Índices!H78-1),4)</f>
         <v>6.2602000000000002</v>
       </c>
       <c r="I79" s="17">
+        <f>ROUND(100*(Índices!I79/Índices!I78-1),4)</f>
         <v>5.4192999999999998</v>
       </c>
       <c r="J79" s="16">
+        <f>ROUND(100*(Índices!J79/Índices!J78-1),4)</f>
         <v>8.4095999999999993</v>
       </c>
       <c r="K79" s="16">
@@ -13554,27 +14211,35 @@
         <v>44986</v>
       </c>
       <c r="C80" s="15">
+        <f>ROUND(100*(Índices!C80/Índices!C79-1),4)</f>
         <v>6.4751000000000003</v>
       </c>
       <c r="D80" s="16">
+        <f>ROUND(100*(Índices!D80/Índices!D79-1),4)</f>
         <v>6.2666000000000004</v>
       </c>
       <c r="E80" s="16">
+        <f>ROUND(100*(Índices!E80/Índices!E79-1),4)</f>
         <v>6.7304000000000004</v>
       </c>
       <c r="F80" s="16">
+        <f>ROUND(100*(Índices!F80/Índices!F79-1),4)</f>
         <v>6.4870999999999999</v>
       </c>
       <c r="G80" s="16">
+        <f>ROUND(100*(Índices!G80/Índices!G79-1),4)</f>
         <v>5.8754999999999997</v>
       </c>
       <c r="H80" s="16">
+        <f>ROUND(100*(Índices!H80/Índices!H79-1),4)</f>
         <v>6.9764999999999997</v>
       </c>
       <c r="I80" s="17">
+        <f>ROUND(100*(Índices!I80/Índices!I79-1),4)</f>
         <v>6.2561999999999998</v>
       </c>
       <c r="J80" s="16">
+        <f>ROUND(100*(Índices!J80/Índices!J79-1),4)</f>
         <v>8.0272000000000006</v>
       </c>
       <c r="K80" s="16">
@@ -13619,27 +14284,35 @@
         <v>45017</v>
       </c>
       <c r="C81" s="15">
+        <f>ROUND(100*(Índices!C81/Índices!C80-1),4)</f>
         <v>8.2483000000000004</v>
       </c>
       <c r="D81" s="16">
+        <f>ROUND(100*(Índices!D81/Índices!D80-1),4)</f>
         <v>8.3714999999999993</v>
       </c>
       <c r="E81" s="16">
+        <f>ROUND(100*(Índices!E81/Índices!E80-1),4)</f>
         <v>8.4100999999999999</v>
       </c>
       <c r="F81" s="16">
+        <f>ROUND(100*(Índices!F81/Índices!F80-1),4)</f>
         <v>7.3125999999999998</v>
       </c>
       <c r="G81" s="16">
+        <f>ROUND(100*(Índices!G81/Índices!G80-1),4)</f>
         <v>8.1957000000000004</v>
       </c>
       <c r="H81" s="16">
+        <f>ROUND(100*(Índices!H81/Índices!H80-1),4)</f>
         <v>7.1997</v>
       </c>
       <c r="I81" s="17">
+        <f>ROUND(100*(Índices!I81/Índices!I80-1),4)</f>
         <v>8.3209999999999997</v>
       </c>
       <c r="J81" s="16">
+        <f>ROUND(100*(Índices!J81/Índices!J80-1),4)</f>
         <v>10.4635</v>
       </c>
       <c r="K81" s="16">
@@ -13684,27 +14357,35 @@
         <v>45047</v>
       </c>
       <c r="C82" s="15">
+        <f>ROUND(100*(Índices!C82/Índices!C81-1),4)</f>
         <v>8.3346999999999998</v>
       </c>
       <c r="D82" s="16">
+        <f>ROUND(100*(Índices!D82/Índices!D81-1),4)</f>
         <v>8.5404999999999998</v>
       </c>
       <c r="E82" s="16">
+        <f>ROUND(100*(Índices!E82/Índices!E81-1),4)</f>
         <v>8.1757000000000009</v>
       </c>
       <c r="F82" s="16">
+        <f>ROUND(100*(Índices!F82/Índices!F81-1),4)</f>
         <v>8.6220999999999997</v>
       </c>
       <c r="G82" s="16">
+        <f>ROUND(100*(Índices!G82/Índices!G81-1),4)</f>
         <v>8.0921000000000003</v>
       </c>
       <c r="H82" s="16">
+        <f>ROUND(100*(Índices!H82/Índices!H81-1),4)</f>
         <v>8.1209000000000007</v>
       </c>
       <c r="I82" s="17">
+        <f>ROUND(100*(Índices!I82/Índices!I81-1),4)</f>
         <v>7.6727999999999996</v>
       </c>
       <c r="J82" s="16">
+        <f>ROUND(100*(Índices!J82/Índices!J81-1),4)</f>
         <v>7.1569000000000003</v>
       </c>
       <c r="K82" s="16">
@@ -13749,27 +14430,35 @@
         <v>45078</v>
       </c>
       <c r="C83" s="15">
+        <f>ROUND(100*(Índices!C83/Índices!C82-1),4)</f>
         <v>6.7567000000000004</v>
       </c>
       <c r="D83" s="16">
+        <f>ROUND(100*(Índices!D83/Índices!D82-1),4)</f>
         <v>6.6811999999999996</v>
       </c>
       <c r="E83" s="16">
+        <f>ROUND(100*(Índices!E83/Índices!E82-1),4)</f>
         <v>6.6997</v>
       </c>
       <c r="F83" s="16">
+        <f>ROUND(100*(Índices!F83/Índices!F82-1),4)</f>
         <v>7.4223999999999997</v>
       </c>
       <c r="G83" s="16">
+        <f>ROUND(100*(Índices!G83/Índices!G82-1),4)</f>
         <v>7.5454999999999997</v>
       </c>
       <c r="H83" s="16">
+        <f>ROUND(100*(Índices!H83/Índices!H82-1),4)</f>
         <v>5.9603000000000002</v>
       </c>
       <c r="I83" s="17">
+        <f>ROUND(100*(Índices!I83/Índices!I82-1),4)</f>
         <v>7.3167</v>
       </c>
       <c r="J83" s="16">
+        <f>ROUND(100*(Índices!J83/Índices!J82-1),4)</f>
         <v>6.0064000000000002</v>
       </c>
       <c r="K83" s="16">
@@ -13814,27 +14503,35 @@
         <v>45108</v>
       </c>
       <c r="C84" s="15">
+        <f>ROUND(100*(Índices!C84/Índices!C83-1),4)</f>
         <v>7.2511000000000001</v>
       </c>
       <c r="D84" s="16">
+        <f>ROUND(100*(Índices!D84/Índices!D83-1),4)</f>
         <v>7.0724</v>
       </c>
       <c r="E84" s="16">
+        <f>ROUND(100*(Índices!E84/Índices!E83-1),4)</f>
         <v>7.3869999999999996</v>
       </c>
       <c r="F84" s="16">
+        <f>ROUND(100*(Índices!F84/Índices!F83-1),4)</f>
         <v>7.2103000000000002</v>
       </c>
       <c r="G84" s="16">
+        <f>ROUND(100*(Índices!G84/Índices!G83-1),4)</f>
         <v>6.9543999999999997</v>
       </c>
       <c r="H84" s="16">
+        <f>ROUND(100*(Índices!H84/Índices!H83-1),4)</f>
         <v>7.0311000000000003</v>
       </c>
       <c r="I84" s="17">
+        <f>ROUND(100*(Índices!I84/Índices!I83-1),4)</f>
         <v>8.2101000000000006</v>
       </c>
       <c r="J84" s="16">
+        <f>ROUND(100*(Índices!J84/Índices!J83-1),4)</f>
         <v>7.4528999999999996</v>
       </c>
       <c r="K84" s="16">
@@ -13879,27 +14576,35 @@
         <v>45139</v>
       </c>
       <c r="C85" s="15">
+        <f>ROUND(100*(Índices!C85/Índices!C84-1),4)</f>
         <v>12.5465</v>
       </c>
       <c r="D85" s="16">
+        <f>ROUND(100*(Índices!D85/Índices!D84-1),4)</f>
         <v>12.4893</v>
       </c>
       <c r="E85" s="16">
+        <f>ROUND(100*(Índices!E85/Índices!E84-1),4)</f>
         <v>12.4476</v>
       </c>
       <c r="F85" s="16">
+        <f>ROUND(100*(Índices!F85/Índices!F84-1),4)</f>
         <v>13.588200000000001</v>
       </c>
       <c r="G85" s="16">
+        <f>ROUND(100*(Índices!G85/Índices!G84-1),4)</f>
         <v>14.1374</v>
       </c>
       <c r="H85" s="16">
+        <f>ROUND(100*(Índices!H85/Índices!H84-1),4)</f>
         <v>12.4016</v>
       </c>
       <c r="I85" s="17">
+        <f>ROUND(100*(Índices!I85/Índices!I84-1),4)</f>
         <v>12.156499999999999</v>
       </c>
       <c r="J85" s="16">
+        <f>ROUND(100*(Índices!J85/Índices!J84-1),4)</f>
         <v>15.696999999999999</v>
       </c>
       <c r="K85" s="16">
@@ -13944,27 +14649,35 @@
         <v>45170</v>
       </c>
       <c r="C86" s="15">
+        <f>ROUND(100*(Índices!C86/Índices!C85-1),4)</f>
         <v>12.3087</v>
       </c>
       <c r="D86" s="16">
+        <f>ROUND(100*(Índices!D86/Índices!D85-1),4)</f>
         <v>11.621499999999999</v>
       </c>
       <c r="E86" s="16">
+        <f>ROUND(100*(Índices!E86/Índices!E85-1),4)</f>
         <v>12.7159</v>
       </c>
       <c r="F86" s="16">
+        <f>ROUND(100*(Índices!F86/Índices!F85-1),4)</f>
         <v>12.855</v>
       </c>
       <c r="G86" s="16">
+        <f>ROUND(100*(Índices!G86/Índices!G85-1),4)</f>
         <v>12.589499999999999</v>
       </c>
       <c r="H86" s="16">
+        <f>ROUND(100*(Índices!H86/Índices!H85-1),4)</f>
         <v>13.3567</v>
       </c>
       <c r="I86" s="17">
+        <f>ROUND(100*(Índices!I86/Índices!I85-1),4)</f>
         <v>13.8345</v>
       </c>
       <c r="J86" s="16">
+        <f>ROUND(100*(Índices!J86/Índices!J85-1),4)</f>
         <v>14.0038</v>
       </c>
       <c r="K86" s="16">
@@ -14009,27 +14722,35 @@
         <v>45200</v>
       </c>
       <c r="C87" s="15">
+        <f>ROUND(100*(Índices!C87/Índices!C86-1),4)</f>
         <v>8.3603000000000005</v>
       </c>
       <c r="D87" s="16">
+        <f>ROUND(100*(Índices!D87/Índices!D86-1),4)</f>
         <v>8.6327999999999996</v>
       </c>
       <c r="E87" s="16">
+        <f>ROUND(100*(Índices!E87/Índices!E86-1),4)</f>
         <v>8.3033999999999999</v>
       </c>
       <c r="F87" s="16">
+        <f>ROUND(100*(Índices!F87/Índices!F86-1),4)</f>
         <v>7.8254000000000001</v>
       </c>
       <c r="G87" s="16">
+        <f>ROUND(100*(Índices!G87/Índices!G86-1),4)</f>
         <v>7.3289999999999997</v>
       </c>
       <c r="H87" s="16">
+        <f>ROUND(100*(Índices!H87/Índices!H86-1),4)</f>
         <v>7.6685999999999996</v>
       </c>
       <c r="I87" s="17">
+        <f>ROUND(100*(Índices!I87/Índices!I86-1),4)</f>
         <v>8.2833000000000006</v>
       </c>
       <c r="J87" s="16">
+        <f>ROUND(100*(Índices!J87/Índices!J86-1),4)</f>
         <v>7.6951000000000001</v>
       </c>
       <c r="K87" s="16">
@@ -14074,27 +14795,35 @@
         <v>45231</v>
       </c>
       <c r="C88" s="15">
+        <f>ROUND(100*(Índices!C88/Índices!C87-1),4)</f>
         <v>13.129899999999999</v>
       </c>
       <c r="D88" s="16">
+        <f>ROUND(100*(Índices!D88/Índices!D87-1),4)</f>
         <v>13.379899999999999</v>
       </c>
       <c r="E88" s="16">
+        <f>ROUND(100*(Índices!E88/Índices!E87-1),4)</f>
         <v>13.1092</v>
       </c>
       <c r="F88" s="16">
+        <f>ROUND(100*(Índices!F88/Índices!F87-1),4)</f>
         <v>12.2143</v>
       </c>
       <c r="G88" s="16">
+        <f>ROUND(100*(Índices!G88/Índices!G87-1),4)</f>
         <v>13.0075</v>
       </c>
       <c r="H88" s="16">
+        <f>ROUND(100*(Índices!H88/Índices!H87-1),4)</f>
         <v>13.0411</v>
       </c>
       <c r="I88" s="17">
+        <f>ROUND(100*(Índices!I88/Índices!I87-1),4)</f>
         <v>12.0562</v>
       </c>
       <c r="J88" s="16">
+        <f>ROUND(100*(Índices!J88/Índices!J87-1),4)</f>
         <v>16.177499999999998</v>
       </c>
       <c r="K88" s="16">
@@ -14139,27 +14868,35 @@
         <v>45261</v>
       </c>
       <c r="C89" s="15">
+        <f>ROUND(100*(Índices!C89/Índices!C88-1),4)</f>
         <v>25.1052</v>
       </c>
       <c r="D89" s="16">
+        <f>ROUND(100*(Índices!D89/Índices!D88-1),4)</f>
         <v>24.853000000000002</v>
       </c>
       <c r="E89" s="16">
+        <f>ROUND(100*(Índices!E89/Índices!E88-1),4)</f>
         <v>25.2593</v>
       </c>
       <c r="F89" s="16">
+        <f>ROUND(100*(Índices!F89/Índices!F88-1),4)</f>
         <v>24.5413</v>
       </c>
       <c r="G89" s="16">
+        <f>ROUND(100*(Índices!G89/Índices!G88-1),4)</f>
         <v>27.0931</v>
       </c>
       <c r="H89" s="16">
+        <f>ROUND(100*(Índices!H89/Índices!H88-1),4)</f>
         <v>25.3459</v>
       </c>
       <c r="I89" s="17">
+        <f>ROUND(100*(Índices!I89/Índices!I88-1),4)</f>
         <v>24.1111</v>
       </c>
       <c r="J89" s="16">
+        <f>ROUND(100*(Índices!J89/Índices!J88-1),4)</f>
         <v>28.386500000000002</v>
       </c>
       <c r="K89" s="16">
@@ -14204,27 +14941,35 @@
         <v>45292</v>
       </c>
       <c r="C90" s="15">
+        <f>ROUND(100*(Índices!C90/Índices!C89-1),4)</f>
         <v>20.102599999999999</v>
       </c>
       <c r="D90" s="16">
+        <f>ROUND(100*(Índices!D90/Índices!D89-1),4)</f>
         <v>19.119199999999999</v>
       </c>
       <c r="E90" s="16">
+        <f>ROUND(100*(Índices!E90/Índices!E89-1),4)</f>
         <v>20.552600000000002</v>
       </c>
       <c r="F90" s="16">
+        <f>ROUND(100*(Índices!F90/Índices!F89-1),4)</f>
         <v>21.0487</v>
       </c>
       <c r="G90" s="16">
+        <f>ROUND(100*(Índices!G90/Índices!G89-1),4)</f>
         <v>18.954499999999999</v>
       </c>
       <c r="H90" s="16">
+        <f>ROUND(100*(Índices!H90/Índices!H89-1),4)</f>
         <v>21.577000000000002</v>
       </c>
       <c r="I90" s="17">
+        <f>ROUND(100*(Índices!I90/Índices!I89-1),4)</f>
         <v>23.6282</v>
       </c>
       <c r="J90" s="16">
+        <f>ROUND(100*(Índices!J90/Índices!J89-1),4)</f>
         <v>18.4206</v>
       </c>
       <c r="K90" s="16">
@@ -14269,27 +15014,35 @@
         <v>45323</v>
       </c>
       <c r="C91" s="15">
+        <f>ROUND(100*(Índices!C91/Índices!C90-1),4)</f>
         <v>12.8597</v>
       </c>
       <c r="D91" s="16">
+        <f>ROUND(100*(Índices!D91/Índices!D90-1),4)</f>
         <v>14.5756</v>
       </c>
       <c r="E91" s="16">
+        <f>ROUND(100*(Índices!E91/Índices!E90-1),4)</f>
         <v>11.6212</v>
       </c>
       <c r="F91" s="16">
+        <f>ROUND(100*(Índices!F91/Índices!F90-1),4)</f>
         <v>11.190300000000001</v>
       </c>
       <c r="G91" s="16">
+        <f>ROUND(100*(Índices!G91/Índices!G90-1),4)</f>
         <v>10.7203</v>
       </c>
       <c r="H91" s="16">
+        <f>ROUND(100*(Índices!H91/Índices!H90-1),4)</f>
         <v>12.9598</v>
       </c>
       <c r="I91" s="17">
+        <f>ROUND(100*(Índices!I91/Índices!I90-1),4)</f>
         <v>10.9194</v>
       </c>
       <c r="J91" s="16">
+        <f>ROUND(100*(Índices!J91/Índices!J90-1),4)</f>
         <v>10.5022</v>
       </c>
       <c r="K91" s="16">
@@ -14334,27 +15087,35 @@
         <v>45352</v>
       </c>
       <c r="C92" s="15">
+        <f>ROUND(100*(Índices!C92/Índices!C91-1),4)</f>
         <v>9.9530999999999992</v>
       </c>
       <c r="D92" s="16">
+        <f>ROUND(100*(Índices!D92/Índices!D91-1),4)</f>
         <v>10.083600000000001</v>
       </c>
       <c r="E92" s="16">
+        <f>ROUND(100*(Índices!E92/Índices!E91-1),4)</f>
         <v>10.299899999999999</v>
       </c>
       <c r="F92" s="16">
+        <f>ROUND(100*(Índices!F92/Índices!F91-1),4)</f>
         <v>8.0082000000000004</v>
       </c>
       <c r="G92" s="16">
+        <f>ROUND(100*(Índices!G92/Índices!G91-1),4)</f>
         <v>10.0375</v>
       </c>
       <c r="H92" s="16">
+        <f>ROUND(100*(Índices!H92/Índices!H91-1),4)</f>
         <v>8.4779999999999998</v>
       </c>
       <c r="I92" s="17">
+        <f>ROUND(100*(Índices!I92/Índices!I91-1),4)</f>
         <v>9.8508999999999993</v>
       </c>
       <c r="J92" s="16">
+        <f>ROUND(100*(Índices!J92/Índices!J91-1),4)</f>
         <v>9.2150999999999996</v>
       </c>
       <c r="K92" s="16">
@@ -14399,27 +15160,35 @@
         <v>45383</v>
       </c>
       <c r="C93" s="15">
+        <f>ROUND(100*(Índices!C93/Índices!C92-1),4)</f>
         <v>8.6994000000000007</v>
       </c>
       <c r="D93" s="16">
+        <f>ROUND(100*(Índices!D93/Índices!D92-1),4)</f>
         <v>9.0898000000000003</v>
       </c>
       <c r="E93" s="16">
+        <f>ROUND(100*(Índices!E93/Índices!E92-1),4)</f>
         <v>8.7280999999999995</v>
       </c>
       <c r="F93" s="16">
+        <f>ROUND(100*(Índices!F93/Índices!F92-1),4)</f>
         <v>8.7790999999999997</v>
       </c>
       <c r="G93" s="16">
+        <f>ROUND(100*(Índices!G93/Índices!G92-1),4)</f>
         <v>6.1692999999999998</v>
       </c>
       <c r="H93" s="16">
+        <f>ROUND(100*(Índices!H93/Índices!H92-1),4)</f>
         <v>8.1791999999999998</v>
       </c>
       <c r="I93" s="17">
+        <f>ROUND(100*(Índices!I93/Índices!I92-1),4)</f>
         <v>8.6582000000000008</v>
       </c>
       <c r="J93" s="16">
+        <f>ROUND(100*(Índices!J93/Índices!J92-1),4)</f>
         <v>6.3246000000000002</v>
       </c>
       <c r="K93" s="16">
@@ -14464,27 +15233,35 @@
         <v>45413</v>
       </c>
       <c r="C94" s="15">
+        <f>ROUND(100*(Índices!C94/Índices!C93-1),4)</f>
         <v>4.6734999999999998</v>
       </c>
       <c r="D94" s="16">
+        <f>ROUND(100*(Índices!D94/Índices!D93-1),4)</f>
         <v>4.7962999999999996</v>
       </c>
       <c r="E94" s="16">
+        <f>ROUND(100*(Índices!E94/Índices!E93-1),4)</f>
         <v>4.4550999999999998</v>
       </c>
       <c r="F94" s="16">
+        <f>ROUND(100*(Índices!F94/Índices!F93-1),4)</f>
         <v>4.7828999999999997</v>
       </c>
       <c r="G94" s="16">
+        <f>ROUND(100*(Índices!G94/Índices!G93-1),4)</f>
         <v>4.49</v>
       </c>
       <c r="H94" s="16">
+        <f>ROUND(100*(Índices!H94/Índices!H93-1),4)</f>
         <v>4.8803999999999998</v>
       </c>
       <c r="I94" s="17">
+        <f>ROUND(100*(Índices!I94/Índices!I93-1),4)</f>
         <v>4.9057000000000004</v>
       </c>
       <c r="J94" s="16">
+        <f>ROUND(100*(Índices!J94/Índices!J93-1),4)</f>
         <v>6.1848999999999998</v>
       </c>
       <c r="K94" s="16">
@@ -14529,27 +15306,35 @@
         <v>45444</v>
       </c>
       <c r="C95" s="15">
+        <f>ROUND(100*(Índices!C95/Índices!C94-1),4)</f>
         <v>5.3903999999999996</v>
       </c>
       <c r="D95" s="16">
+        <f>ROUND(100*(Índices!D95/Índices!D94-1),4)</f>
         <v>5.2119999999999997</v>
       </c>
       <c r="E95" s="16">
+        <f>ROUND(100*(Índices!E95/Índices!E94-1),4)</f>
         <v>5.5685000000000002</v>
       </c>
       <c r="F95" s="16">
+        <f>ROUND(100*(Índices!F95/Índices!F94-1),4)</f>
         <v>5.5609999999999999</v>
       </c>
       <c r="G95" s="16">
+        <f>ROUND(100*(Índices!G95/Índices!G94-1),4)</f>
         <v>5.2556000000000003</v>
       </c>
       <c r="H95" s="16">
+        <f>ROUND(100*(Índices!H95/Índices!H94-1),4)</f>
         <v>5.7375999999999996</v>
       </c>
       <c r="I95" s="17">
+        <f>ROUND(100*(Índices!I95/Índices!I94-1),4)</f>
         <v>5.4981999999999998</v>
       </c>
       <c r="J95" s="16">
+        <f>ROUND(100*(Índices!J95/Índices!J94-1),4)</f>
         <v>4.8456999999999999</v>
       </c>
       <c r="K95" s="16">
@@ -14594,27 +15379,35 @@
         <v>45474</v>
       </c>
       <c r="C96" s="15">
+        <f>ROUND(100*(Índices!C96/Índices!C95-1),4)</f>
         <v>4.9076000000000004</v>
       </c>
       <c r="D96" s="16">
+        <f>ROUND(100*(Índices!D96/Índices!D95-1),4)</f>
         <v>4.8810000000000002</v>
       </c>
       <c r="E96" s="16">
+        <f>ROUND(100*(Índices!E96/Índices!E95-1),4)</f>
         <v>4.8445999999999998</v>
       </c>
       <c r="F96" s="16">
+        <f>ROUND(100*(Índices!F96/Índices!F95-1),4)</f>
         <v>4.6638999999999999</v>
       </c>
       <c r="G96" s="16">
+        <f>ROUND(100*(Índices!G96/Índices!G95-1),4)</f>
         <v>5.2553999999999998</v>
       </c>
       <c r="H96" s="16">
+        <f>ROUND(100*(Índices!H96/Índices!H95-1),4)</f>
         <v>5.2979000000000003</v>
       </c>
       <c r="I96" s="17">
+        <f>ROUND(100*(Índices!I96/Índices!I95-1),4)</f>
         <v>4.5862999999999996</v>
       </c>
       <c r="J96" s="16">
+        <f>ROUND(100*(Índices!J96/Índices!J95-1),4)</f>
         <v>4.8535000000000004</v>
       </c>
       <c r="K96" s="16">
@@ -14659,27 +15452,35 @@
         <v>45505</v>
       </c>
       <c r="C97" s="15">
+        <f>ROUND(100*(Índices!C97/Índices!C96-1),4)</f>
         <v>4.3365</v>
       </c>
       <c r="D97" s="16">
+        <f>ROUND(100*(Índices!D97/Índices!D96-1),4)</f>
         <v>4.3756000000000004</v>
       </c>
       <c r="E97" s="16">
+        <f>ROUND(100*(Índices!E97/Índices!E96-1),4)</f>
         <v>4.1182999999999996</v>
       </c>
       <c r="F97" s="16">
+        <f>ROUND(100*(Índices!F97/Índices!F96-1),4)</f>
         <v>5.0030999999999999</v>
       </c>
       <c r="G97" s="16">
+        <f>ROUND(100*(Índices!G97/Índices!G96-1),4)</f>
         <v>4.3318000000000003</v>
       </c>
       <c r="H97" s="16">
+        <f>ROUND(100*(Índices!H97/Índices!H96-1),4)</f>
         <v>4.5582000000000003</v>
       </c>
       <c r="I97" s="17">
+        <f>ROUND(100*(Índices!I97/Índices!I96-1),4)</f>
         <v>4.6135000000000002</v>
       </c>
       <c r="J97" s="16">
+        <f>ROUND(100*(Índices!J97/Índices!J96-1),4)</f>
         <v>3.7239</v>
       </c>
       <c r="K97" s="16">
@@ -14724,27 +15525,35 @@
         <v>45536</v>
       </c>
       <c r="C98" s="15">
+        <f>ROUND(100*(Índices!C98/Índices!C97-1),4)</f>
         <v>3.1389999999999998</v>
       </c>
       <c r="D98" s="16">
+        <f>ROUND(100*(Índices!D98/Índices!D97-1),4)</f>
         <v>3.3033999999999999</v>
       </c>
       <c r="E98" s="16">
+        <f>ROUND(100*(Índices!E98/Índices!E97-1),4)</f>
         <v>2.9279999999999999</v>
       </c>
       <c r="F98" s="16">
+        <f>ROUND(100*(Índices!F98/Índices!F97-1),4)</f>
         <v>3.2031000000000001</v>
       </c>
       <c r="G98" s="16">
+        <f>ROUND(100*(Índices!G98/Índices!G97-1),4)</f>
         <v>2.9741</v>
       </c>
       <c r="H98" s="16">
+        <f>ROUND(100*(Índices!H98/Índices!H97-1),4)</f>
         <v>2.8317999999999999</v>
       </c>
       <c r="I98" s="17">
+        <f>ROUND(100*(Índices!I98/Índices!I97-1),4)</f>
         <v>3.577</v>
       </c>
       <c r="J98" s="16">
+        <f>ROUND(100*(Índices!J98/Índices!J97-1),4)</f>
         <v>1.9977</v>
       </c>
       <c r="K98" s="16">
@@ -14789,27 +15598,35 @@
         <v>45566</v>
       </c>
       <c r="C99" s="15">
+        <f>ROUND(100*(Índices!C99/Índices!C98-1),4)</f>
         <v>2.7323</v>
       </c>
       <c r="D99" s="16">
+        <f>ROUND(100*(Índices!D99/Índices!D98-1),4)</f>
         <v>2.8340000000000001</v>
       </c>
       <c r="E99" s="16">
+        <f>ROUND(100*(Índices!E99/Índices!E98-1),4)</f>
         <v>2.5617999999999999</v>
       </c>
       <c r="F99" s="16">
+        <f>ROUND(100*(Índices!F99/Índices!F98-1),4)</f>
         <v>2.6528</v>
       </c>
       <c r="G99" s="16">
+        <f>ROUND(100*(Índices!G99/Índices!G98-1),4)</f>
         <v>2.5358999999999998</v>
       </c>
       <c r="H99" s="16">
+        <f>ROUND(100*(Índices!H99/Índices!H98-1),4)</f>
         <v>2.5167999999999999</v>
       </c>
       <c r="I99" s="17">
+        <f>ROUND(100*(Índices!I99/Índices!I98-1),4)</f>
         <v>3.3525</v>
       </c>
       <c r="J99" s="16">
+        <f>ROUND(100*(Índices!J99/Índices!J98-1),4)</f>
         <v>1.1819999999999999</v>
       </c>
       <c r="K99" s="16">
@@ -14854,27 +15671,35 @@
         <v>45597</v>
       </c>
       <c r="C100" s="15">
+        <f>ROUND(100*(Índices!C100/Índices!C99-1),4)</f>
         <v>2.6701999999999999</v>
       </c>
       <c r="D100" s="16">
+        <f>ROUND(100*(Índices!D100/Índices!D99-1),4)</f>
         <v>2.9550000000000001</v>
       </c>
       <c r="E100" s="16">
+        <f>ROUND(100*(Índices!E100/Índices!E99-1),4)</f>
         <v>2.3813</v>
       </c>
       <c r="F100" s="16">
+        <f>ROUND(100*(Índices!F100/Índices!F99-1),4)</f>
         <v>2.2646999999999999</v>
       </c>
       <c r="G100" s="16">
+        <f>ROUND(100*(Índices!G100/Índices!G99-1),4)</f>
         <v>1.9154</v>
       </c>
       <c r="H100" s="16">
+        <f>ROUND(100*(Índices!H100/Índices!H99-1),4)</f>
         <v>2.3681999999999999</v>
       </c>
       <c r="I100" s="17">
+        <f>ROUND(100*(Índices!I100/Índices!I99-1),4)</f>
         <v>3.3948</v>
       </c>
       <c r="J100" s="16">
+        <f>ROUND(100*(Índices!J100/Índices!J99-1),4)</f>
         <v>1.3479000000000001</v>
       </c>
       <c r="K100" s="16">
@@ -14919,27 +15744,35 @@
         <v>45627</v>
       </c>
       <c r="C101" s="15">
+        <f>ROUND(100*(Índices!C101/Índices!C100-1),4)</f>
         <v>2.4199000000000002</v>
       </c>
       <c r="D101" s="16">
+        <f>ROUND(100*(Índices!D101/Índices!D100-1),4)</f>
         <v>2.7218</v>
       </c>
       <c r="E101" s="16">
+        <f>ROUND(100*(Índices!E101/Índices!E100-1),4)</f>
         <v>2.1652999999999998</v>
       </c>
       <c r="F101" s="16">
+        <f>ROUND(100*(Índices!F101/Índices!F100-1),4)</f>
         <v>2.2046000000000001</v>
       </c>
       <c r="G101" s="16">
+        <f>ROUND(100*(Índices!G101/Índices!G100-1),4)</f>
         <v>2.0464000000000002</v>
       </c>
       <c r="H101" s="16">
+        <f>ROUND(100*(Índices!H101/Índices!H100-1),4)</f>
         <v>1.9162999999999999</v>
       </c>
       <c r="I101" s="17">
+        <f>ROUND(100*(Índices!I101/Índices!I100-1),4)</f>
         <v>2.5442999999999998</v>
       </c>
       <c r="J101" s="16">
+        <f>ROUND(100*(Índices!J101/Índices!J100-1),4)</f>
         <v>1.1963999999999999</v>
       </c>
       <c r="K101" s="16">
@@ -14984,27 +15817,35 @@
         <v>45658</v>
       </c>
       <c r="C102" s="15">
+        <f>ROUND(100*(Índices!C102/Índices!C101-1),4)</f>
         <v>1.7890999999999999</v>
       </c>
       <c r="D102" s="16">
+        <f>ROUND(100*(Índices!D102/Índices!D101-1),4)</f>
         <v>1.6497999999999999</v>
       </c>
       <c r="E102" s="16">
+        <f>ROUND(100*(Índices!E102/Índices!E101-1),4)</f>
         <v>1.8462000000000001</v>
       </c>
       <c r="F102" s="16">
+        <f>ROUND(100*(Índices!F102/Índices!F101-1),4)</f>
         <v>2.1183000000000001</v>
       </c>
       <c r="G102" s="16">
+        <f>ROUND(100*(Índices!G102/Índices!G101-1),4)</f>
         <v>2.0373000000000001</v>
       </c>
       <c r="H102" s="16">
+        <f>ROUND(100*(Índices!H102/Índices!H101-1),4)</f>
         <v>1.3928</v>
       </c>
       <c r="I102" s="17">
+        <f>ROUND(100*(Índices!I102/Índices!I101-1),4)</f>
         <v>2.0954000000000002</v>
       </c>
       <c r="J102" s="16">
+        <f>ROUND(100*(Índices!J102/Índices!J101-1),4)</f>
         <v>0.18099999999999999</v>
       </c>
       <c r="K102" s="16">
@@ -15049,27 +15890,35 @@
         <v>45689</v>
       </c>
       <c r="C103" s="15">
+        <f>ROUND(100*(Índices!C103/Índices!C102-1),4)</f>
         <v>2.0952999999999999</v>
       </c>
       <c r="D103" s="16">
+        <f>ROUND(100*(Índices!D103/Índices!D102-1),4)</f>
         <v>1.9340999999999999</v>
       </c>
       <c r="E103" s="16">
+        <f>ROUND(100*(Índices!E103/Índices!E102-1),4)</f>
         <v>2.2473000000000001</v>
       </c>
       <c r="F103" s="16">
+        <f>ROUND(100*(Índices!F103/Índices!F102-1),4)</f>
         <v>2.1251000000000002</v>
       </c>
       <c r="G103" s="16">
+        <f>ROUND(100*(Índices!G103/Índices!G102-1),4)</f>
         <v>1.7230000000000001</v>
       </c>
       <c r="H103" s="16">
+        <f>ROUND(100*(Índices!H103/Índices!H102-1),4)</f>
         <v>2.1833999999999998</v>
       </c>
       <c r="I103" s="17">
+        <f>ROUND(100*(Índices!I103/Índices!I102-1),4)</f>
         <v>2.8611</v>
       </c>
       <c r="J103" s="16">
+        <f>ROUND(100*(Índices!J103/Índices!J102-1),4)</f>
         <v>1.9495</v>
       </c>
       <c r="K103" s="16">
@@ -15114,27 +15963,35 @@
         <v>45717</v>
       </c>
       <c r="C104" s="15">
+        <f>ROUND(100*(Índices!C104/Índices!C103-1),4)</f>
         <v>2.6402000000000001</v>
       </c>
       <c r="D104" s="16">
+        <f>ROUND(100*(Índices!D104/Índices!D103-1),4)</f>
         <v>2.4683999999999999</v>
       </c>
       <c r="E104" s="16">
+        <f>ROUND(100*(Índices!E104/Índices!E103-1),4)</f>
         <v>2.6495000000000002</v>
       </c>
       <c r="F104" s="16">
+        <f>ROUND(100*(Índices!F104/Índices!F103-1),4)</f>
         <v>3.4302999999999999</v>
       </c>
       <c r="G104" s="16">
+        <f>ROUND(100*(Índices!G104/Índices!G103-1),4)</f>
         <v>2.7581000000000002</v>
       </c>
       <c r="H104" s="16">
+        <f>ROUND(100*(Índices!H104/Índices!H103-1),4)</f>
         <v>2.6716000000000002</v>
       </c>
       <c r="I104" s="17">
+        <f>ROUND(100*(Índices!I104/Índices!I103-1),4)</f>
         <v>2.5583999999999998</v>
       </c>
       <c r="J104" s="16">
+        <f>ROUND(100*(Índices!J104/Índices!J103-1),4)</f>
         <v>4.6249000000000002</v>
       </c>
       <c r="K104" s="16">
@@ -15179,27 +16036,35 @@
         <v>45748</v>
       </c>
       <c r="C105" s="15">
+        <f>ROUND(100*(Índices!C105/Índices!C104-1),4)</f>
         <v>2.6669999999999998</v>
       </c>
       <c r="D105" s="16">
+        <f>ROUND(100*(Índices!D105/Índices!D104-1),4)</f>
         <v>2.6114999999999999</v>
       </c>
       <c r="E105" s="16">
+        <f>ROUND(100*(Índices!E105/Índices!E104-1),4)</f>
         <v>2.7566000000000002</v>
       </c>
       <c r="F105" s="16">
+        <f>ROUND(100*(Índices!F105/Índices!F104-1),4)</f>
         <v>2.5194999999999999</v>
       </c>
       <c r="G105" s="16">
+        <f>ROUND(100*(Índices!G105/Índices!G104-1),4)</f>
         <v>2.5179</v>
       </c>
       <c r="H105" s="16">
+        <f>ROUND(100*(Índices!H105/Índices!H104-1),4)</f>
         <v>2.8338000000000001</v>
       </c>
       <c r="I105" s="17">
+        <f>ROUND(100*(Índices!I105/Índices!I104-1),4)</f>
         <v>2.8186</v>
       </c>
       <c r="J105" s="16">
+        <f>ROUND(100*(Índices!J105/Índices!J104-1),4)</f>
         <v>3.2475000000000001</v>
       </c>
       <c r="K105" s="16">
@@ -15244,27 +16109,35 @@
         <v>45778</v>
       </c>
       <c r="C106" s="15">
+        <f>ROUND(100*(Índices!C106/Índices!C105-1),4)</f>
         <v>1.9560999999999999</v>
       </c>
       <c r="D106" s="16">
+        <f>ROUND(100*(Índices!D106/Índices!D105-1),4)</f>
         <v>1.9722</v>
       </c>
       <c r="E106" s="16">
+        <f>ROUND(100*(Índices!E106/Índices!E105-1),4)</f>
         <v>1.9734</v>
       </c>
       <c r="F106" s="16">
+        <f>ROUND(100*(Índices!F106/Índices!F105-1),4)</f>
         <v>1.8351999999999999</v>
       </c>
       <c r="G106" s="16">
+        <f>ROUND(100*(Índices!G106/Índices!G105-1),4)</f>
         <v>2.0009000000000001</v>
       </c>
       <c r="H106" s="16">
+        <f>ROUND(100*(Índices!H106/Índices!H105-1),4)</f>
         <v>2.2170000000000001</v>
       </c>
       <c r="I106" s="17">
+        <f>ROUND(100*(Índices!I106/Índices!I105-1),4)</f>
         <v>1.8691</v>
       </c>
       <c r="J106" s="16">
+        <f>ROUND(100*(Índices!J106/Índices!J105-1),4)</f>
         <v>1.7863</v>
       </c>
       <c r="K106" s="16">
@@ -15309,27 +16182,35 @@
         <v>45809</v>
       </c>
       <c r="C107" s="15">
+        <f>ROUND(100*(Índices!C107/Índices!C106-1),4)</f>
         <v>2.4007000000000001</v>
       </c>
       <c r="D107" s="16">
+        <f>ROUND(100*(Índices!D107/Índices!D106-1),4)</f>
         <v>2.8344999999999998</v>
       </c>
       <c r="E107" s="16">
+        <f>ROUND(100*(Índices!E107/Índices!E106-1),4)</f>
         <v>2.1021000000000001</v>
       </c>
       <c r="F107" s="16">
+        <f>ROUND(100*(Índices!F107/Índices!F106-1),4)</f>
         <v>1.9479</v>
       </c>
       <c r="G107" s="16">
+        <f>ROUND(100*(Índices!G107/Índices!G106-1),4)</f>
         <v>1.8838999999999999</v>
       </c>
       <c r="H107" s="16">
+        <f>ROUND(100*(Índices!H107/Índices!H106-1),4)</f>
         <v>1.6333</v>
       </c>
       <c r="I107" s="17">
+        <f>ROUND(100*(Índices!I107/Índices!I106-1),4)</f>
         <v>2.3504</v>
       </c>
       <c r="J107" s="16">
+        <f>ROUND(100*(Índices!J107/Índices!J106-1),4)</f>
         <v>2.3601999999999999</v>
       </c>
       <c r="K107" s="16">
@@ -15374,27 +16255,35 @@
         <v>45839</v>
       </c>
       <c r="C108" s="15">
+        <f>ROUND(100*(Índices!C108/Índices!C107-1),4)</f>
         <v>2.726</v>
       </c>
       <c r="D108" s="16">
+        <f>ROUND(100*(Índices!D108/Índices!D107-1),4)</f>
         <v>2.6816</v>
       </c>
       <c r="E108" s="16">
+        <f>ROUND(100*(Índices!E108/Índices!E107-1),4)</f>
         <v>2.8755999999999999</v>
       </c>
       <c r="F108" s="16">
+        <f>ROUND(100*(Índices!F108/Índices!F107-1),4)</f>
         <v>2.7092999999999998</v>
       </c>
       <c r="G108" s="16">
+        <f>ROUND(100*(Índices!G108/Índices!G107-1),4)</f>
         <v>2.3117000000000001</v>
       </c>
       <c r="H108" s="16">
+        <f>ROUND(100*(Índices!H108/Índices!H107-1),4)</f>
         <v>2.5226000000000002</v>
       </c>
       <c r="I108" s="17">
+        <f>ROUND(100*(Índices!I108/Índices!I107-1),4)</f>
         <v>2.5705</v>
       </c>
       <c r="J108" s="16">
+        <f>ROUND(100*(Índices!J108/Índices!J107-1),4)</f>
         <v>3.5238999999999998</v>
       </c>
       <c r="K108" s="16">
@@ -15439,27 +16328,35 @@
         <v>45870</v>
       </c>
       <c r="C109" s="15">
+        <f>ROUND(100*(Índices!C109/Índices!C108-1),4)</f>
         <v>2.1013000000000002</v>
       </c>
       <c r="D109" s="16">
+        <f>ROUND(100*(Índices!D109/Índices!D108-1),4)</f>
         <v>2.1259000000000001</v>
       </c>
       <c r="E109" s="16">
+        <f>ROUND(100*(Índices!E109/Índices!E108-1),4)</f>
         <v>2.0718000000000001</v>
       </c>
       <c r="F109" s="16">
+        <f>ROUND(100*(Índices!F109/Índices!F108-1),4)</f>
         <v>1.9440999999999999</v>
       </c>
       <c r="G109" s="16">
+        <f>ROUND(100*(Índices!G109/Índices!G108-1),4)</f>
         <v>1.6539999999999999</v>
       </c>
       <c r="H109" s="16">
+        <f>ROUND(100*(Índices!H109/Índices!H108-1),4)</f>
         <v>2.1442000000000001</v>
       </c>
       <c r="I109" s="17">
+        <f>ROUND(100*(Índices!I109/Índices!I108-1),4)</f>
         <v>1.9371</v>
       </c>
       <c r="J109" s="16">
+        <f>ROUND(100*(Índices!J109/Índices!J108-1),4)</f>
         <v>1.4757</v>
       </c>
       <c r="K109" s="16">
@@ -15504,27 +16401,35 @@
         <v>45901</v>
       </c>
       <c r="C110" s="15">
+        <f>ROUND(100*(Índices!C110/Índices!C109-1),4)</f>
         <v>1.8013999999999999</v>
       </c>
       <c r="D110" s="16">
+        <f>ROUND(100*(Índices!D110/Índices!D109-1),4)</f>
         <v>1.7339</v>
       </c>
       <c r="E110" s="16">
+        <f>ROUND(100*(Índices!E110/Índices!E109-1),4)</f>
         <v>1.7568999999999999</v>
       </c>
       <c r="F110" s="16">
+        <f>ROUND(100*(Índices!F110/Índices!F109-1),4)</f>
         <v>2.0485000000000002</v>
       </c>
       <c r="G110" s="16">
+        <f>ROUND(100*(Índices!G110/Índices!G109-1),4)</f>
         <v>1.5421</v>
       </c>
       <c r="H110" s="16">
+        <f>ROUND(100*(Índices!H110/Índices!H109-1),4)</f>
         <v>2.0384000000000002</v>
       </c>
       <c r="I110" s="17">
+        <f>ROUND(100*(Índices!I110/Índices!I109-1),4)</f>
         <v>2.2927</v>
       </c>
       <c r="J110" s="16">
+        <f>ROUND(100*(Índices!J110/Índices!J109-1),4)</f>
         <v>1.5581</v>
       </c>
       <c r="K110" s="16">
@@ -15569,27 +16474,35 @@
         <v>45931</v>
       </c>
       <c r="C111" s="15">
+        <f>ROUND(100*(Índices!C111/Índices!C110-1),4)</f>
         <v>2.3969999999999998</v>
       </c>
       <c r="D111" s="16">
+        <f>ROUND(100*(Índices!D111/Índices!D110-1),4)</f>
         <v>2.4363999999999999</v>
       </c>
       <c r="E111" s="16">
+        <f>ROUND(100*(Índices!E111/Índices!E110-1),4)</f>
         <v>2.3344</v>
       </c>
       <c r="F111" s="16">
+        <f>ROUND(100*(Índices!F111/Índices!F110-1),4)</f>
         <v>2.2738999999999998</v>
       </c>
       <c r="G111" s="16">
+        <f>ROUND(100*(Índices!G111/Índices!G110-1),4)</f>
         <v>2.1981999999999999</v>
       </c>
       <c r="H111" s="16">
+        <f>ROUND(100*(Índices!H111/Índices!H110-1),4)</f>
         <v>2.6499000000000001</v>
       </c>
       <c r="I111" s="17">
+        <f>ROUND(100*(Índices!I111/Índices!I110-1),4)</f>
         <v>2.5768</v>
       </c>
       <c r="J111" s="16">
+        <f>ROUND(100*(Índices!J111/Índices!J110-1),4)</f>
         <v>2.2686999999999999</v>
       </c>
       <c r="K111" s="16">
@@ -15634,27 +16547,35 @@
         <v>45962</v>
       </c>
       <c r="C112" s="15">
+        <f>ROUND(100*(Índices!C112/Índices!C111-1),4)</f>
         <v>2.7004999999999999</v>
       </c>
       <c r="D112" s="16">
+        <f>ROUND(100*(Índices!D112/Índices!D111-1),4)</f>
         <v>2.8277000000000001</v>
       </c>
       <c r="E112" s="16">
+        <f>ROUND(100*(Índices!E112/Índices!E111-1),4)</f>
         <v>2.5508999999999999</v>
       </c>
       <c r="F112" s="16">
+        <f>ROUND(100*(Índices!F112/Índices!F111-1),4)</f>
         <v>2.6806999999999999</v>
       </c>
       <c r="G112" s="16">
+        <f>ROUND(100*(Índices!G112/Índices!G111-1),4)</f>
         <v>2.5632000000000001</v>
       </c>
       <c r="H112" s="16">
+        <f>ROUND(100*(Índices!H112/Índices!H111-1),4)</f>
         <v>3.0586000000000002</v>
       </c>
       <c r="I112" s="17">
+        <f>ROUND(100*(Índices!I112/Índices!I111-1),4)</f>
         <v>2.4605999999999999</v>
       </c>
       <c r="J112" s="16">
+        <f>ROUND(100*(Índices!J112/Índices!J111-1),4)</f>
         <v>3.2688999999999999</v>
       </c>
       <c r="K112" s="16">
@@ -15699,27 +16620,35 @@
         <v>45992</v>
       </c>
       <c r="C113" s="15">
+        <f>ROUND(100*(Índices!C113/Índices!C112-1),4)</f>
         <v>2.5646</v>
       </c>
       <c r="D113" s="16">
+        <f>ROUND(100*(Índices!D113/Índices!D112-1),4)</f>
         <v>2.6457000000000002</v>
       </c>
       <c r="E113" s="16">
+        <f>ROUND(100*(Índices!E113/Índices!E112-1),4)</f>
         <v>2.5547</v>
       </c>
       <c r="F113" s="16">
+        <f>ROUND(100*(Índices!F113/Índices!F112-1),4)</f>
         <v>2.1278999999999999</v>
       </c>
       <c r="G113" s="16">
+        <f>ROUND(100*(Índices!G113/Índices!G112-1),4)</f>
         <v>2.4977</v>
       </c>
       <c r="H113" s="16">
+        <f>ROUND(100*(Índices!H113/Índices!H112-1),4)</f>
         <v>2.5573999999999999</v>
       </c>
       <c r="I113" s="17">
+        <f>ROUND(100*(Índices!I113/Índices!I112-1),4)</f>
         <v>2.5169000000000001</v>
       </c>
       <c r="J113" s="16">
+        <f>ROUND(100*(Índices!J113/Índices!J112-1),4)</f>
         <v>2.1086999999999998</v>
       </c>
       <c r="K113" s="16">
@@ -15759,69 +16688,150 @@
         <v>2.1663999999999999</v>
       </c>
     </row>
-    <row r="114" spans="2:22" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B114" s="48">
+    <row r="114" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B114" s="13">
         <v>46023</v>
       </c>
-      <c r="C114" s="18">
+      <c r="C114" s="15">
+        <f>ROUND(100*(Índices!C114/Índices!C113-1),4)</f>
         <v>2.4319999999999999</v>
       </c>
-      <c r="D114" s="19">
+      <c r="D114" s="16">
+        <f>ROUND(100*(Índices!D114/Índices!D113-1),4)</f>
         <v>2.3557000000000001</v>
       </c>
-      <c r="E114" s="19">
+      <c r="E114" s="16">
+        <f>ROUND(100*(Índices!E114/Índices!E113-1),4)</f>
         <v>2.3969</v>
       </c>
-      <c r="F114" s="19">
+      <c r="F114" s="16">
+        <f>ROUND(100*(Índices!F114/Índices!F113-1),4)</f>
         <v>2.3860999999999999</v>
       </c>
-      <c r="G114" s="19">
+      <c r="G114" s="16">
+        <f>ROUND(100*(Índices!G114/Índices!G113-1),4)</f>
         <v>3.3418999999999999</v>
       </c>
-      <c r="H114" s="19">
+      <c r="H114" s="16">
+        <f>ROUND(100*(Índices!H114/Índices!H113-1),4)</f>
         <v>2.3765999999999998</v>
       </c>
-      <c r="I114" s="20">
+      <c r="I114" s="17">
+        <f>ROUND(100*(Índices!I114/Índices!I113-1),4)</f>
         <v>2.4904000000000002</v>
       </c>
-      <c r="J114" s="19">
+      <c r="J114" s="16">
+        <f>ROUND(100*(Índices!J114/Índices!J113-1),4)</f>
         <v>2.9632000000000001</v>
       </c>
-      <c r="K114" s="19">
+      <c r="K114" s="16">
         <v>0.09</v>
       </c>
-      <c r="L114" s="19">
+      <c r="L114" s="16">
         <v>1.1326000000000001</v>
       </c>
-      <c r="M114" s="19">
+      <c r="M114" s="16">
         <v>3.0529000000000002</v>
       </c>
-      <c r="N114" s="19">
+      <c r="N114" s="16">
         <v>1.8302</v>
       </c>
-      <c r="O114" s="19">
+      <c r="O114" s="16">
         <v>2.3418000000000001</v>
       </c>
-      <c r="P114" s="19">
+      <c r="P114" s="16">
         <v>1.8548</v>
       </c>
-      <c r="Q114" s="19">
+      <c r="Q114" s="16">
         <v>-1.0443</v>
       </c>
-      <c r="R114" s="19">
+      <c r="R114" s="16">
         <v>1.0244</v>
       </c>
-      <c r="S114" s="19">
+      <c r="S114" s="16">
         <v>5.1432000000000002</v>
       </c>
-      <c r="T114" s="19">
+      <c r="T114" s="16">
         <v>3.9603000000000002</v>
       </c>
-      <c r="U114" s="20">
+      <c r="U114" s="17">
         <v>2.7301000000000002</v>
       </c>
-      <c r="V114" s="18">
+      <c r="V114" s="15">
         <v>2.5274999999999999</v>
+      </c>
+    </row>
+    <row r="115" spans="2:22" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B115" s="48">
+        <v>46054</v>
+      </c>
+      <c r="C115" s="18">
+        <f>ROUND(100*(Índices!C115/Índices!C114-1),4)</f>
+        <v>2.5402</v>
+      </c>
+      <c r="D115" s="19">
+        <f>ROUND(100*(Índices!D115/Índices!D114-1),4)</f>
+        <v>2.2839999999999998</v>
+      </c>
+      <c r="E115" s="19">
+        <f>ROUND(100*(Índices!E115/Índices!E114-1),4)</f>
+        <v>2.7242999999999999</v>
+      </c>
+      <c r="F115" s="19">
+        <f>ROUND(100*(Índices!F115/Índices!F114-1),4)</f>
+        <v>3.0423</v>
+      </c>
+      <c r="G115" s="19">
+        <f>ROUND(100*(Índices!G115/Índices!G114-1),4)</f>
+        <v>2.9007000000000001</v>
+      </c>
+      <c r="H115" s="19">
+        <f>ROUND(100*(Índices!H115/Índices!H114-1),4)</f>
+        <v>2.9041999999999999</v>
+      </c>
+      <c r="I115" s="20">
+        <f>ROUND(100*(Índices!I115/Índices!I114-1),4)</f>
+        <v>2.6263999999999998</v>
+      </c>
+      <c r="J115" s="19">
+        <f>ROUND(100*(Índices!J115/Índices!J114-1),4)</f>
+        <v>2.0246</v>
+      </c>
+      <c r="K115" s="19">
+        <v>0.35</v>
+      </c>
+      <c r="L115" s="19">
+        <v>1.4723999999999999</v>
+      </c>
+      <c r="M115" s="19">
+        <v>6.7877000000000001</v>
+      </c>
+      <c r="N115" s="19">
+        <v>2.5644999999999998</v>
+      </c>
+      <c r="O115" s="19">
+        <v>2.4708000000000001</v>
+      </c>
+      <c r="P115" s="19">
+        <v>1.978</v>
+      </c>
+      <c r="Q115" s="19">
+        <v>-1.0564</v>
+      </c>
+      <c r="R115" s="19">
+        <v>2.3454000000000002</v>
+      </c>
+      <c r="S115" s="19">
+        <v>1.3282</v>
+      </c>
+      <c r="T115" s="19">
+        <v>2.9319000000000002</v>
+      </c>
+      <c r="U115" s="20">
+        <v>3.2768000000000002</v>
+      </c>
+      <c r="V115" s="18">
+        <v>2.2141999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -15890,7 +16900,7 @@
       <c r="H4" s="70"/>
       <c r="I4" s="23" t="str">
         <f>+_xlfn.CONCAT(H5, " ", C4, "/", H5, " ", C4-1)</f>
-        <v>Ene. 2024/Ene. 2023</v>
+        <v>Feb. 2024/Feb. 2023</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.25">
@@ -15920,25 +16930,25 @@
         <v>18</v>
       </c>
       <c r="C6" s="27">
-        <v>2.1013000000000002</v>
+        <v>1.8013999999999999</v>
       </c>
       <c r="D6" s="27">
-        <v>1.8013999999999999</v>
+        <v>2.3969999999999998</v>
       </c>
       <c r="E6" s="27">
-        <v>2.3969999999999998</v>
+        <v>2.7004999999999999</v>
       </c>
       <c r="F6" s="27">
-        <v>2.7004999999999999</v>
+        <v>2.5646</v>
       </c>
       <c r="G6" s="27">
-        <v>2.5646</v>
+        <v>2.4319999999999999</v>
       </c>
       <c r="H6" s="27">
-        <v>2.4319999999999999</v>
+        <v>2.5402</v>
       </c>
       <c r="I6" s="28">
-        <v>32.411799999999999</v>
+        <v>33.051499999999997</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -15958,25 +16968,25 @@
         <v>19</v>
       </c>
       <c r="C8" s="32">
-        <v>2.1259000000000001</v>
+        <v>1.7339</v>
       </c>
       <c r="D8" s="32">
-        <v>1.7339</v>
+        <v>2.4363999999999999</v>
       </c>
       <c r="E8" s="32">
-        <v>2.4363999999999999</v>
+        <v>2.8277000000000001</v>
       </c>
       <c r="F8" s="32">
-        <v>2.8277000000000001</v>
+        <v>2.6457000000000002</v>
       </c>
       <c r="G8" s="32">
-        <v>2.6457000000000002</v>
+        <v>2.3557000000000001</v>
       </c>
       <c r="H8" s="32">
-        <v>2.3557000000000001</v>
+        <v>2.2839999999999998</v>
       </c>
       <c r="I8" s="33">
-        <v>32.697899999999997</v>
+        <v>33.192500000000003</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.25">
@@ -15984,25 +16994,25 @@
         <v>2</v>
       </c>
       <c r="C9" s="32">
-        <v>2.0718000000000001</v>
+        <v>1.7568999999999999</v>
       </c>
       <c r="D9" s="32">
-        <v>1.7568999999999999</v>
+        <v>2.3344</v>
       </c>
       <c r="E9" s="32">
-        <v>2.3344</v>
+        <v>2.5508999999999999</v>
       </c>
       <c r="F9" s="32">
-        <v>2.5508999999999999</v>
+        <v>2.5547</v>
       </c>
       <c r="G9" s="32">
-        <v>2.5547</v>
+        <v>2.3969</v>
       </c>
       <c r="H9" s="32">
-        <v>2.3969</v>
+        <v>2.7242999999999999</v>
       </c>
       <c r="I9" s="33">
-        <v>32.191099999999999</v>
+        <v>32.850999999999999</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.25">
@@ -16010,25 +17020,25 @@
         <v>3</v>
       </c>
       <c r="C10" s="32">
-        <v>1.9440999999999999</v>
+        <v>2.0485000000000002</v>
       </c>
       <c r="D10" s="32">
-        <v>2.0485000000000002</v>
+        <v>2.2738999999999998</v>
       </c>
       <c r="E10" s="32">
-        <v>2.2738999999999998</v>
+        <v>2.6806999999999999</v>
       </c>
       <c r="F10" s="32">
-        <v>2.6806999999999999</v>
+        <v>2.1278999999999999</v>
       </c>
       <c r="G10" s="32">
-        <v>2.1278999999999999</v>
+        <v>2.3860999999999999</v>
       </c>
       <c r="H10" s="32">
-        <v>2.3860999999999999</v>
+        <v>3.0423</v>
       </c>
       <c r="I10" s="33">
-        <v>31.7638</v>
+        <v>33.005099999999999</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.25">
@@ -16036,25 +17046,25 @@
         <v>4</v>
       </c>
       <c r="C11" s="32">
-        <v>1.6539999999999999</v>
+        <v>1.5421</v>
       </c>
       <c r="D11" s="32">
-        <v>1.5421</v>
+        <v>2.1981999999999999</v>
       </c>
       <c r="E11" s="32">
-        <v>2.1981999999999999</v>
+        <v>2.5632000000000001</v>
       </c>
       <c r="F11" s="32">
-        <v>2.5632000000000001</v>
+        <v>2.4977</v>
       </c>
       <c r="G11" s="32">
-        <v>2.4977</v>
+        <v>3.3418999999999999</v>
       </c>
       <c r="H11" s="32">
-        <v>3.3418999999999999</v>
+        <v>2.9007000000000001</v>
       </c>
       <c r="I11" s="33">
-        <v>30.540600000000001</v>
+        <v>32.127299999999998</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.25">
@@ -16062,25 +17072,25 @@
         <v>5</v>
       </c>
       <c r="C12" s="32">
-        <v>2.1442000000000001</v>
+        <v>2.0384000000000002</v>
       </c>
       <c r="D12" s="32">
-        <v>2.0384000000000002</v>
+        <v>2.6499000000000001</v>
       </c>
       <c r="E12" s="32">
-        <v>2.6499000000000001</v>
+        <v>3.0586000000000002</v>
       </c>
       <c r="F12" s="32">
-        <v>3.0586000000000002</v>
+        <v>2.5573999999999999</v>
       </c>
       <c r="G12" s="32">
-        <v>2.5573999999999999</v>
+        <v>2.3765999999999998</v>
       </c>
       <c r="H12" s="32">
-        <v>2.3765999999999998</v>
+        <v>2.9041999999999999</v>
       </c>
       <c r="I12" s="33">
-        <v>32.987099999999998</v>
+        <v>33.9422</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.25">
@@ -16088,25 +17098,25 @@
         <v>6</v>
       </c>
       <c r="C13" s="32">
-        <v>1.9371</v>
+        <v>2.2927</v>
       </c>
       <c r="D13" s="32">
-        <v>2.2927</v>
+        <v>2.5768</v>
       </c>
       <c r="E13" s="32">
-        <v>2.5768</v>
+        <v>2.4605999999999999</v>
       </c>
       <c r="F13" s="32">
-        <v>2.4605999999999999</v>
+        <v>2.5169000000000001</v>
       </c>
       <c r="G13" s="32">
-        <v>2.5169000000000001</v>
+        <v>2.4904000000000002</v>
       </c>
       <c r="H13" s="32">
-        <v>2.4904000000000002</v>
+        <v>2.6263999999999998</v>
       </c>
       <c r="I13" s="33">
-        <v>33.418399999999998</v>
+        <v>33.123399999999997</v>
       </c>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.25">
@@ -16136,25 +17146,25 @@
         <v>20</v>
       </c>
       <c r="C16" s="32">
-        <v>1.4757</v>
+        <v>1.5581</v>
       </c>
       <c r="D16" s="32">
-        <v>1.5581</v>
+        <v>2.2686999999999999</v>
       </c>
       <c r="E16" s="32">
-        <v>2.2686999999999999</v>
+        <v>3.2688999999999999</v>
       </c>
       <c r="F16" s="32">
-        <v>3.2688999999999999</v>
+        <v>2.1086999999999998</v>
       </c>
       <c r="G16" s="32">
-        <v>2.1086999999999998</v>
+        <v>2.9632000000000001</v>
       </c>
       <c r="H16" s="32">
-        <v>2.9632000000000001</v>
+        <v>2.0246</v>
       </c>
       <c r="I16" s="33">
-        <v>35.914000000000001</v>
+        <v>36.017899999999997</v>
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.25">
@@ -16162,25 +17172,25 @@
         <v>21</v>
       </c>
       <c r="C17" s="32">
-        <v>4.444</v>
+        <v>0.53410000000000002</v>
       </c>
       <c r="D17" s="32">
-        <v>0.53410000000000002</v>
+        <v>2.6392000000000002</v>
       </c>
       <c r="E17" s="32">
-        <v>2.6392000000000002</v>
+        <v>0.33200000000000002</v>
       </c>
       <c r="F17" s="32">
-        <v>0.33200000000000002</v>
+        <v>2.4317000000000002</v>
       </c>
       <c r="G17" s="32">
-        <v>2.4317000000000002</v>
+        <v>0.09</v>
       </c>
       <c r="H17" s="32">
-        <v>0.09</v>
+        <v>0.35</v>
       </c>
       <c r="I17" s="33">
-        <v>24.13</v>
+        <v>23.2895</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.25">
@@ -16188,25 +17198,25 @@
         <v>22</v>
       </c>
       <c r="C18" s="32">
-        <v>0.62190000000000001</v>
+        <v>-1.3429</v>
       </c>
       <c r="D18" s="32">
-        <v>-1.3429</v>
+        <v>1.7358</v>
       </c>
       <c r="E18" s="32">
-        <v>1.7358</v>
+        <v>1.3657999999999999</v>
       </c>
       <c r="F18" s="32">
-        <v>1.3657999999999999</v>
+        <v>0.55920000000000003</v>
       </c>
       <c r="G18" s="32">
-        <v>0.55920000000000003</v>
+        <v>1.1326000000000001</v>
       </c>
       <c r="H18" s="32">
-        <v>1.1326000000000001</v>
+        <v>1.4723999999999999</v>
       </c>
       <c r="I18" s="33">
-        <v>15.5503</v>
+        <v>15.055400000000001</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.25">
@@ -16214,25 +17224,25 @@
         <v>23</v>
       </c>
       <c r="C19" s="32">
-        <v>2.6928000000000001</v>
+        <v>3.1423999999999999</v>
       </c>
       <c r="D19" s="32">
-        <v>3.1423999999999999</v>
+        <v>2.8279999999999998</v>
       </c>
       <c r="E19" s="32">
-        <v>2.8279999999999998</v>
+        <v>3.4380000000000002</v>
       </c>
       <c r="F19" s="32">
-        <v>3.4380000000000002</v>
+        <v>3.3896000000000002</v>
       </c>
       <c r="G19" s="32">
-        <v>3.3896000000000002</v>
+        <v>3.0529000000000002</v>
       </c>
       <c r="H19" s="32">
-        <v>3.0529000000000002</v>
+        <v>6.7877000000000001</v>
       </c>
       <c r="I19" s="33">
-        <v>40.242100000000001</v>
+        <v>44.299599999999998</v>
       </c>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.25">
@@ -16240,25 +17250,25 @@
         <v>24</v>
       </c>
       <c r="C20" s="32">
-        <v>0.93520000000000003</v>
+        <v>2.2124999999999999</v>
       </c>
       <c r="D20" s="32">
-        <v>2.2124999999999999</v>
+        <v>1.6339999999999999</v>
       </c>
       <c r="E20" s="32">
-        <v>1.6339999999999999</v>
+        <v>1.119</v>
       </c>
       <c r="F20" s="32">
-        <v>1.119</v>
+        <v>2.0001000000000002</v>
       </c>
       <c r="G20" s="32">
-        <v>2.0001000000000002</v>
+        <v>1.8302</v>
       </c>
       <c r="H20" s="32">
-        <v>1.8302</v>
+        <v>2.5644999999999998</v>
       </c>
       <c r="I20" s="33">
-        <v>19.526299999999999</v>
+        <v>21.360299999999999</v>
       </c>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.25">
@@ -16266,25 +17276,25 @@
         <v>25</v>
       </c>
       <c r="C21" s="32">
-        <v>1.7205999999999999</v>
+        <v>2.2858999999999998</v>
       </c>
       <c r="D21" s="32">
-        <v>2.2858999999999998</v>
+        <v>1.8307</v>
       </c>
       <c r="E21" s="32">
-        <v>1.8307</v>
+        <v>2.3965000000000001</v>
       </c>
       <c r="F21" s="32">
-        <v>2.3965000000000001</v>
+        <v>2.0903999999999998</v>
       </c>
       <c r="G21" s="32">
-        <v>2.0903999999999998</v>
+        <v>2.3418000000000001</v>
       </c>
       <c r="H21" s="32">
-        <v>2.3418000000000001</v>
+        <v>2.4708000000000001</v>
       </c>
       <c r="I21" s="33">
-        <v>28.1751</v>
+        <v>28.6935</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.25">
@@ -16292,25 +17302,25 @@
         <v>26</v>
       </c>
       <c r="C22" s="32">
-        <v>3.5581</v>
+        <v>2.9731000000000001</v>
       </c>
       <c r="D22" s="32">
-        <v>2.9731000000000001</v>
+        <v>3.4594999999999998</v>
       </c>
       <c r="E22" s="32">
-        <v>3.4594999999999998</v>
+        <v>3.0304000000000002</v>
       </c>
       <c r="F22" s="32">
-        <v>3.0304000000000002</v>
+        <v>3.9982000000000002</v>
       </c>
       <c r="G22" s="32">
-        <v>3.9982000000000002</v>
+        <v>1.8548</v>
       </c>
       <c r="H22" s="32">
-        <v>1.8548</v>
+        <v>1.978</v>
       </c>
       <c r="I22" s="33">
-        <v>32.750599999999999</v>
+        <v>33.074800000000003</v>
       </c>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.25">
@@ -16318,25 +17328,25 @@
         <v>27</v>
       </c>
       <c r="C23" s="32">
-        <v>4.6970999999999998</v>
+        <v>3.4643000000000002</v>
       </c>
       <c r="D23" s="32">
-        <v>3.4643000000000002</v>
+        <v>2.7322000000000002</v>
       </c>
       <c r="E23" s="32">
-        <v>2.7322000000000002</v>
+        <v>3.0445000000000002</v>
       </c>
       <c r="F23" s="32">
-        <v>3.0445000000000002</v>
+        <v>3.0379999999999998</v>
       </c>
       <c r="G23" s="32">
-        <v>3.0379999999999998</v>
+        <v>-1.0443</v>
       </c>
       <c r="H23" s="32">
-        <v>-1.0443</v>
+        <v>-1.0564</v>
       </c>
       <c r="I23" s="33">
-        <v>36.656500000000001</v>
+        <v>36.066200000000002</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.25">
@@ -16344,25 +17354,25 @@
         <v>28</v>
       </c>
       <c r="C24" s="32">
-        <v>0.53080000000000005</v>
+        <v>1.3376999999999999</v>
       </c>
       <c r="D24" s="32">
-        <v>1.3376999999999999</v>
+        <v>1.6108</v>
       </c>
       <c r="E24" s="32">
-        <v>1.6108</v>
+        <v>2.4485000000000001</v>
       </c>
       <c r="F24" s="32">
-        <v>2.4485000000000001</v>
+        <v>2.5417000000000001</v>
       </c>
       <c r="G24" s="32">
-        <v>2.5417000000000001</v>
+        <v>1.0244</v>
       </c>
       <c r="H24" s="32">
-        <v>1.0244</v>
+        <v>2.3454000000000002</v>
       </c>
       <c r="I24" s="33">
-        <v>28.648199999999999</v>
+        <v>27.917100000000001</v>
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.25">
@@ -16370,25 +17380,25 @@
         <v>29</v>
       </c>
       <c r="C25" s="32">
-        <v>2.9026999999999998</v>
+        <v>5.7842000000000002</v>
       </c>
       <c r="D25" s="32">
-        <v>5.7842000000000002</v>
+        <v>5.7397999999999998</v>
       </c>
       <c r="E25" s="32">
-        <v>5.7397999999999998</v>
+        <v>4.8711000000000002</v>
       </c>
       <c r="F25" s="32">
-        <v>4.8711000000000002</v>
+        <v>4.8147000000000002</v>
       </c>
       <c r="G25" s="32">
-        <v>4.8147000000000002</v>
+        <v>5.1432000000000002</v>
       </c>
       <c r="H25" s="32">
-        <v>5.1432000000000002</v>
+        <v>1.3282</v>
       </c>
       <c r="I25" s="33">
-        <v>52.400599999999997</v>
+        <v>50.653799999999997</v>
       </c>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.25">
@@ -16396,25 +17406,25 @@
         <v>30</v>
       </c>
       <c r="C26" s="32">
-        <v>3.4422000000000001</v>
+        <v>1.2056</v>
       </c>
       <c r="D26" s="32">
-        <v>1.2056</v>
+        <v>2.2783000000000002</v>
       </c>
       <c r="E26" s="32">
-        <v>2.2783000000000002</v>
+        <v>2.4801000000000002</v>
       </c>
       <c r="F26" s="32">
-        <v>2.4801000000000002</v>
+        <v>3.0933000000000002</v>
       </c>
       <c r="G26" s="32">
-        <v>3.0933000000000002</v>
+        <v>3.9603000000000002</v>
       </c>
       <c r="H26" s="32">
-        <v>3.9603000000000002</v>
+        <v>2.9319000000000002</v>
       </c>
       <c r="I26" s="33">
-        <v>40.627000000000002</v>
+        <v>41.646900000000002</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.25">
@@ -16422,25 +17432,25 @@
         <v>31</v>
       </c>
       <c r="C27" s="32">
-        <v>2.2492999999999999</v>
+        <v>2.1455000000000002</v>
       </c>
       <c r="D27" s="32">
-        <v>2.1455000000000002</v>
+        <v>2.4439000000000002</v>
       </c>
       <c r="E27" s="32">
-        <v>2.4439000000000002</v>
+        <v>2.5068000000000001</v>
       </c>
       <c r="F27" s="32">
-        <v>2.5068000000000001</v>
+        <v>2.6438000000000001</v>
       </c>
       <c r="G27" s="32">
-        <v>2.6438000000000001</v>
+        <v>2.7301000000000002</v>
       </c>
       <c r="H27" s="32">
-        <v>2.7301000000000002</v>
+        <v>3.2768000000000002</v>
       </c>
       <c r="I27" s="33">
-        <v>33.232300000000002</v>
+        <v>33.683700000000002</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.25">
@@ -16470,25 +17480,25 @@
         <v>33</v>
       </c>
       <c r="C30" s="32">
-        <v>1.6693</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="D30" s="32">
-        <v>1.1499999999999999</v>
+        <v>2.1185999999999998</v>
       </c>
       <c r="E30" s="32">
-        <v>2.1185999999999998</v>
+        <v>2.4952000000000001</v>
       </c>
       <c r="F30" s="32">
-        <v>2.4952000000000001</v>
+        <v>2.1663999999999999</v>
       </c>
       <c r="G30" s="32">
-        <v>2.1663999999999999</v>
+        <v>2.5274999999999999</v>
       </c>
       <c r="H30" s="32">
-        <v>2.5274999999999999</v>
+        <v>2.2141999999999999</v>
       </c>
       <c r="I30" s="33">
-        <v>30.9482</v>
+        <v>31.275099999999998</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.25">
@@ -16496,25 +17506,25 @@
         <v>19</v>
       </c>
       <c r="C31" s="32">
-        <v>1.7341</v>
+        <v>1.0967</v>
       </c>
       <c r="D31" s="32">
-        <v>1.0967</v>
+        <v>2.2909999999999999</v>
       </c>
       <c r="E31" s="32">
-        <v>2.2909999999999999</v>
+        <v>2.6549999999999998</v>
       </c>
       <c r="F31" s="32">
-        <v>2.6549999999999998</v>
+        <v>2.1663999999999999</v>
       </c>
       <c r="G31" s="32">
-        <v>2.1663999999999999</v>
+        <v>2.7825000000000002</v>
       </c>
       <c r="H31" s="32">
-        <v>2.7825000000000002</v>
+        <v>1.8584000000000001</v>
       </c>
       <c r="I31" s="33">
-        <v>32.015000000000001</v>
+        <v>32.087800000000001</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.25">
@@ -16522,25 +17532,25 @@
         <v>2</v>
       </c>
       <c r="C32" s="32">
-        <v>1.7455000000000001</v>
+        <v>1.1006</v>
       </c>
       <c r="D32" s="32">
-        <v>1.1006</v>
+        <v>1.9105000000000001</v>
       </c>
       <c r="E32" s="32">
-        <v>1.9105000000000001</v>
+        <v>2.3687999999999998</v>
       </c>
       <c r="F32" s="32">
-        <v>2.3687999999999998</v>
+        <v>2.2696999999999998</v>
       </c>
       <c r="G32" s="32">
-        <v>2.2696999999999998</v>
+        <v>2.3115999999999999</v>
       </c>
       <c r="H32" s="32">
-        <v>2.3115999999999999</v>
+        <v>2.6072000000000002</v>
       </c>
       <c r="I32" s="33">
-        <v>30.963100000000001</v>
+        <v>31.500299999999999</v>
       </c>
     </row>
     <row r="33" spans="2:9" x14ac:dyDescent="0.25">
@@ -16548,25 +17558,25 @@
         <v>3</v>
       </c>
       <c r="C33" s="32">
-        <v>1.4332</v>
+        <v>1.4411</v>
       </c>
       <c r="D33" s="32">
-        <v>1.4411</v>
+        <v>2.2098</v>
       </c>
       <c r="E33" s="32">
-        <v>2.2098</v>
+        <v>2.5064000000000002</v>
       </c>
       <c r="F33" s="32">
-        <v>2.5064000000000002</v>
+        <v>1.6786000000000001</v>
       </c>
       <c r="G33" s="32">
-        <v>1.6786000000000001</v>
+        <v>2.3090000000000002</v>
       </c>
       <c r="H33" s="32">
-        <v>2.3090000000000002</v>
+        <v>2.4470000000000001</v>
       </c>
       <c r="I33" s="33">
-        <v>30.595300000000002</v>
+        <v>31.083100000000002</v>
       </c>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.25">
@@ -16574,25 +17584,25 @@
         <v>4</v>
       </c>
       <c r="C34" s="32">
-        <v>1.1435</v>
+        <v>1.0519000000000001</v>
       </c>
       <c r="D34" s="32">
-        <v>1.0519000000000001</v>
+        <v>1.9383999999999999</v>
       </c>
       <c r="E34" s="32">
-        <v>1.9383999999999999</v>
+        <v>2.4870000000000001</v>
       </c>
       <c r="F34" s="32">
-        <v>2.4870000000000001</v>
+        <v>2.2094</v>
       </c>
       <c r="G34" s="32">
-        <v>2.2094</v>
+        <v>2.9220999999999999</v>
       </c>
       <c r="H34" s="32">
-        <v>2.9220999999999999</v>
+        <v>3.2063000000000001</v>
       </c>
       <c r="I34" s="33">
-        <v>29.502199999999998</v>
+        <v>31.628699999999998</v>
       </c>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.25">
@@ -16600,25 +17610,25 @@
         <v>5</v>
       </c>
       <c r="C35" s="32">
-        <v>1.7746999999999999</v>
+        <v>1.5072000000000001</v>
       </c>
       <c r="D35" s="32">
-        <v>1.5072000000000001</v>
+        <v>2.2623000000000002</v>
       </c>
       <c r="E35" s="32">
-        <v>2.2623000000000002</v>
+        <v>2.6513</v>
       </c>
       <c r="F35" s="32">
-        <v>2.6513</v>
+        <v>2.3127</v>
       </c>
       <c r="G35" s="32">
-        <v>2.3127</v>
+        <v>2.0385</v>
       </c>
       <c r="H35" s="32">
-        <v>2.0385</v>
+        <v>2.1634000000000002</v>
       </c>
       <c r="I35" s="33">
-        <v>26.5276</v>
+        <v>27.292000000000002</v>
       </c>
     </row>
     <row r="36" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -16626,25 +17636,25 @@
         <v>6</v>
       </c>
       <c r="C36" s="35">
-        <v>1.1681999999999999</v>
+        <v>1.3167</v>
       </c>
       <c r="D36" s="35">
-        <v>1.3167</v>
+        <v>1.8217000000000001</v>
       </c>
       <c r="E36" s="35">
-        <v>1.8217000000000001</v>
+        <v>1.6400999999999999</v>
       </c>
       <c r="F36" s="35">
-        <v>1.6400999999999999</v>
+        <v>1.9037999999999999</v>
       </c>
       <c r="G36" s="35">
-        <v>1.9037999999999999</v>
+        <v>2.0792000000000002</v>
       </c>
       <c r="H36" s="35">
-        <v>2.0792000000000002</v>
+        <v>1.623</v>
       </c>
       <c r="I36" s="36">
-        <v>27.064699999999998</v>
+        <v>25.946999999999999</v>
       </c>
     </row>
     <row r="37" spans="2:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16758,25 +17768,25 @@
         <v>37</v>
       </c>
       <c r="C5" s="41">
-        <v>2.3557000000000001</v>
+        <v>2.2839999999999998</v>
       </c>
       <c r="D5" s="41">
-        <v>2.3969</v>
+        <v>2.7242999999999999</v>
       </c>
       <c r="E5" s="41">
-        <v>2.3860999999999999</v>
+        <v>3.0423</v>
       </c>
       <c r="F5" s="41">
-        <v>3.3418999999999999</v>
+        <v>2.9007000000000001</v>
       </c>
       <c r="G5" s="41">
-        <v>2.3765999999999998</v>
+        <v>2.9041999999999999</v>
       </c>
       <c r="H5" s="41">
-        <v>2.4904000000000002</v>
+        <v>2.6263999999999998</v>
       </c>
       <c r="I5" s="42">
-        <v>2.4319999999999999</v>
+        <v>2.5402</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.25">
@@ -16784,25 +17794,25 @@
         <v>20</v>
       </c>
       <c r="C6" s="32">
-        <v>0.83120000000000005</v>
+        <v>0.36120000000000002</v>
       </c>
       <c r="D6" s="32">
-        <v>0.82769999999999999</v>
+        <v>0.73899999999999999</v>
       </c>
       <c r="E6" s="32">
-        <v>0.89610000000000001</v>
+        <v>0.96399999999999997</v>
       </c>
       <c r="F6" s="32">
-        <v>1.2378</v>
+        <v>1.4200999999999999</v>
       </c>
       <c r="G6" s="32">
-        <v>0.82289999999999996</v>
+        <v>0.85929999999999995</v>
       </c>
       <c r="H6" s="32">
-        <v>0.62909999999999999</v>
+        <v>0.44009999999999999</v>
       </c>
       <c r="I6" s="33">
-        <v>0.84309999999999996</v>
+        <v>0.60899999999999999</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.25">
@@ -16810,25 +17820,25 @@
         <v>21</v>
       </c>
       <c r="C7" s="32">
-        <v>-6.0000000000000001E-3</v>
+        <v>2.9999999999999997E-4</v>
       </c>
       <c r="D7" s="32">
+        <v>1.8599999999999998E-2</v>
+      </c>
+      <c r="E7" s="32">
+        <v>-4.0000000000000002E-4</v>
+      </c>
+      <c r="F7" s="32">
+        <v>4.1799999999999997E-2</v>
+      </c>
+      <c r="G7" s="32">
+        <v>1.44E-2</v>
+      </c>
+      <c r="H7" s="32">
+        <v>7.6E-3</v>
+      </c>
+      <c r="I7" s="33">
         <v>9.4000000000000004E-3</v>
-      </c>
-      <c r="E7" s="32">
-        <v>3.3999999999999998E-3</v>
-      </c>
-      <c r="F7" s="32">
-        <v>2.1700000000000001E-2</v>
-      </c>
-      <c r="G7" s="32">
-        <v>1.4500000000000001E-2</v>
-      </c>
-      <c r="H7" s="32">
-        <v>7.4999999999999997E-3</v>
-      </c>
-      <c r="I7" s="33">
-        <v>2.8E-3</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.25">
@@ -16836,25 +17846,25 @@
         <v>22</v>
       </c>
       <c r="C8" s="32">
-        <v>5.62E-2</v>
+        <v>9.1499999999999998E-2</v>
       </c>
       <c r="D8" s="32">
-        <v>0.106</v>
+        <v>0.1258</v>
       </c>
       <c r="E8" s="32">
-        <v>0.1268</v>
+        <v>0.14330000000000001</v>
       </c>
       <c r="F8" s="32">
-        <v>0.2041</v>
+        <v>0.1598</v>
       </c>
       <c r="G8" s="32">
-        <v>7.5499999999999998E-2</v>
+        <v>7.9500000000000001E-2</v>
       </c>
       <c r="H8" s="32">
-        <v>0.1258</v>
+        <v>0.1305</v>
       </c>
       <c r="I8" s="33">
-        <v>8.8900000000000007E-2</v>
+        <v>0.1111</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.25">
@@ -16862,25 +17872,25 @@
         <v>23</v>
       </c>
       <c r="C9" s="32">
-        <v>0.2114</v>
+        <v>0.60470000000000002</v>
       </c>
       <c r="D9" s="32">
-        <v>0.28539999999999999</v>
+        <v>0.57650000000000001</v>
       </c>
       <c r="E9" s="32">
-        <v>0.25219999999999998</v>
+        <v>0.85260000000000002</v>
       </c>
       <c r="F9" s="32">
-        <v>0.97209999999999996</v>
+        <v>0.37269999999999998</v>
       </c>
       <c r="G9" s="32">
-        <v>0.1928</v>
+        <v>1.115</v>
       </c>
       <c r="H9" s="32">
-        <v>0.56430000000000002</v>
+        <v>1.2051000000000001</v>
       </c>
       <c r="I9" s="33">
-        <v>0.28899999999999998</v>
+        <v>0.65549999999999997</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.25">
@@ -16888,25 +17898,25 @@
         <v>24</v>
       </c>
       <c r="C10" s="32">
-        <v>7.85E-2</v>
+        <v>0.15890000000000001</v>
       </c>
       <c r="D10" s="32">
-        <v>0.11409999999999999</v>
+        <v>0.1061</v>
       </c>
       <c r="E10" s="32">
-        <v>0.1019</v>
+        <v>0.1293</v>
       </c>
       <c r="F10" s="32">
-        <v>9.2999999999999999E-2</v>
+        <v>0.1696</v>
       </c>
       <c r="G10" s="32">
-        <v>0.1134</v>
+        <v>0.10349999999999999</v>
       </c>
       <c r="H10" s="32">
-        <v>0.11550000000000001</v>
+        <v>0.1145</v>
       </c>
       <c r="I10" s="33">
-        <v>9.64E-2</v>
+        <v>0.13439999999999999</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.25">
@@ -16914,25 +17924,25 @@
         <v>25</v>
       </c>
       <c r="C11" s="32">
-        <v>0.20280000000000001</v>
+        <v>0.2099</v>
       </c>
       <c r="D11" s="32">
-        <v>0.2351</v>
+        <v>0.248</v>
       </c>
       <c r="E11" s="32">
-        <v>0.18820000000000001</v>
+        <v>0.1686</v>
       </c>
       <c r="F11" s="32">
-        <v>0.1363</v>
+        <v>0.1464</v>
       </c>
       <c r="G11" s="32">
-        <v>0.19570000000000001</v>
+        <v>0.21640000000000001</v>
       </c>
       <c r="H11" s="32">
-        <v>0.1482</v>
+        <v>0.2009</v>
       </c>
       <c r="I11" s="33">
-        <v>0.20699999999999999</v>
+        <v>0.2172</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.25">
@@ -16940,25 +17950,25 @@
         <v>26</v>
       </c>
       <c r="C12" s="32">
-        <v>0.1444</v>
+        <v>0.2261</v>
       </c>
       <c r="D12" s="32">
-        <v>0.221</v>
+        <v>0.21579999999999999</v>
       </c>
       <c r="E12" s="32">
-        <v>0.21909999999999999</v>
+        <v>0.31030000000000002</v>
       </c>
       <c r="F12" s="32">
-        <v>0.2016</v>
+        <v>0.28060000000000002</v>
       </c>
       <c r="G12" s="32">
-        <v>0.59109999999999996</v>
+        <v>0.10829999999999999</v>
       </c>
       <c r="H12" s="32">
-        <v>0.41949999999999998</v>
+        <v>0.18340000000000001</v>
       </c>
       <c r="I12" s="33">
-        <v>0.21410000000000001</v>
+        <v>0.2228</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.25">
@@ -16966,25 +17976,25 @@
         <v>27</v>
       </c>
       <c r="C13" s="32">
-        <v>-5.3499999999999999E-2</v>
+        <v>-2.93E-2</v>
       </c>
       <c r="D13" s="32">
-        <v>1.0699999999999999E-2</v>
+        <v>-3.7100000000000001E-2</v>
       </c>
       <c r="E13" s="32">
-        <v>-7.6399999999999996E-2</v>
+        <v>1.2800000000000001E-2</v>
       </c>
       <c r="F13" s="32">
-        <v>7.1000000000000004E-3</v>
+        <v>-2.4299999999999999E-2</v>
       </c>
       <c r="G13" s="32">
-        <v>-1.2699999999999999E-2</v>
+        <v>-2.4400000000000002E-2</v>
       </c>
       <c r="H13" s="32">
-        <v>-3.1899999999999998E-2</v>
+        <v>-2.3E-3</v>
       </c>
       <c r="I13" s="33">
-        <v>-2.7300000000000001E-2</v>
+        <v>-2.7400000000000001E-2</v>
       </c>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.25">
@@ -16992,25 +18002,25 @@
         <v>28</v>
       </c>
       <c r="C14" s="32">
-        <v>7.0999999999999994E-2</v>
+        <v>9.1700000000000004E-2</v>
       </c>
       <c r="D14" s="32">
-        <v>1.6199999999999999E-2</v>
+        <v>0.27800000000000002</v>
       </c>
       <c r="E14" s="32">
-        <v>0.12909999999999999</v>
+        <v>1.4800000000000001E-2</v>
       </c>
       <c r="F14" s="32">
-        <v>9.4100000000000003E-2</v>
+        <v>0.18029999999999999</v>
       </c>
       <c r="G14" s="32">
-        <v>0.14399999999999999</v>
+        <v>6.3799999999999996E-2</v>
       </c>
       <c r="H14" s="32">
-        <v>0.14960000000000001</v>
+        <v>7.6899999999999996E-2</v>
       </c>
       <c r="I14" s="33">
-        <v>6.4699999999999994E-2</v>
+        <v>0.152</v>
       </c>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.25">
@@ -17018,25 +18028,25 @@
         <v>29</v>
       </c>
       <c r="C15" s="32">
-        <v>9.5799999999999996E-2</v>
+        <v>9.5699999999999993E-2</v>
       </c>
       <c r="D15" s="32">
-        <v>0.1065</v>
+        <v>-1.24E-2</v>
       </c>
       <c r="E15" s="32">
-        <v>0.1908</v>
+        <v>-9.1999999999999998E-3</v>
       </c>
       <c r="F15" s="32">
-        <v>3.1800000000000002E-2</v>
+        <v>-5.2699999999999997E-2</v>
       </c>
       <c r="G15" s="32">
-        <v>0.106</v>
+        <v>0.10979999999999999</v>
       </c>
       <c r="H15" s="32">
-        <v>0.1082</v>
+        <v>4.2599999999999999E-2</v>
       </c>
       <c r="I15" s="33">
-        <v>0.1042</v>
+        <v>4.3099999999999999E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.25">
@@ -17044,25 +18054,25 @@
         <v>30</v>
       </c>
       <c r="C16" s="32">
-        <v>0.62239999999999995</v>
+        <v>0.34939999999999999</v>
       </c>
       <c r="D16" s="32">
-        <v>0.376</v>
+        <v>0.35289999999999999</v>
       </c>
       <c r="E16" s="32">
-        <v>0.2999</v>
+        <v>0.37030000000000002</v>
       </c>
       <c r="F16" s="32">
-        <v>0.25669999999999998</v>
+        <v>0.1295</v>
       </c>
       <c r="G16" s="32">
-        <v>6.7999999999999996E-3</v>
+        <v>0.14829999999999999</v>
       </c>
       <c r="H16" s="32">
-        <v>0.17599999999999999</v>
+        <v>0.14760000000000001</v>
       </c>
       <c r="I16" s="33">
-        <v>0.44719999999999999</v>
+        <v>0.32250000000000001</v>
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.25">
@@ -17070,22 +18080,22 @@
         <v>31</v>
       </c>
       <c r="C17" s="32">
-        <v>0.10150000000000001</v>
+        <v>0.12379999999999999</v>
       </c>
       <c r="D17" s="32">
-        <v>8.8900000000000007E-2</v>
+        <v>0.113</v>
       </c>
       <c r="E17" s="32">
-        <v>5.5E-2</v>
+        <v>8.5999999999999993E-2</v>
       </c>
       <c r="F17" s="32">
-        <v>8.5500000000000007E-2</v>
+        <v>7.6899999999999996E-2</v>
       </c>
       <c r="G17" s="32">
-        <v>0.12659999999999999</v>
+        <v>0.1103</v>
       </c>
       <c r="H17" s="32">
-        <v>7.8600000000000003E-2</v>
+        <v>7.9600000000000004E-2</v>
       </c>
       <c r="I17" s="33">
         <v>0.08</v>
@@ -17118,25 +18128,25 @@
         <v>37</v>
       </c>
       <c r="C20" s="41">
-        <v>32.697899999999997</v>
+        <v>33.192500000000003</v>
       </c>
       <c r="D20" s="41">
-        <v>32.191099999999999</v>
+        <v>32.850999999999999</v>
       </c>
       <c r="E20" s="41">
-        <v>31.7638</v>
+        <v>33.005099999999999</v>
       </c>
       <c r="F20" s="41">
-        <v>30.540600000000001</v>
+        <v>32.127299999999998</v>
       </c>
       <c r="G20" s="41">
-        <v>32.987099999999998</v>
+        <v>33.9422</v>
       </c>
       <c r="H20" s="41">
-        <v>33.418399999999998</v>
+        <v>33.123399999999997</v>
       </c>
       <c r="I20" s="42">
-        <v>32.411799999999999</v>
+        <v>33.051499999999997</v>
       </c>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.25">
@@ -17144,25 +18154,25 @@
         <v>20</v>
       </c>
       <c r="C21" s="32">
-        <v>9.1907999999999994</v>
+        <v>9.2178000000000004</v>
       </c>
       <c r="D21" s="32">
-        <v>10.622400000000001</v>
+        <v>10.8096</v>
       </c>
       <c r="E21" s="32">
-        <v>12.5618</v>
+        <v>12.9297</v>
       </c>
       <c r="F21" s="32">
-        <v>12.8995</v>
+        <v>13.858599999999999</v>
       </c>
       <c r="G21" s="32">
-        <v>11.186400000000001</v>
+        <v>11.466200000000001</v>
       </c>
       <c r="H21" s="32">
-        <v>8.6745000000000001</v>
+        <v>8.0873000000000008</v>
       </c>
       <c r="I21" s="33">
-        <v>10.1592</v>
+        <v>10.291499999999999</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.25">
@@ -17170,25 +18180,25 @@
         <v>21</v>
       </c>
       <c r="C22" s="32">
-        <v>0.62639999999999996</v>
+        <v>0.60070000000000001</v>
       </c>
       <c r="D22" s="32">
-        <v>0.72150000000000003</v>
+        <v>0.68010000000000004</v>
       </c>
       <c r="E22" s="32">
-        <v>0.54990000000000006</v>
+        <v>0.51039999999999996</v>
       </c>
       <c r="F22" s="32">
-        <v>0.55430000000000001</v>
+        <v>0.5958</v>
       </c>
       <c r="G22" s="32">
-        <v>0.62839999999999996</v>
+        <v>0.60289999999999999</v>
       </c>
       <c r="H22" s="32">
-        <v>0.73719999999999997</v>
+        <v>0.69750000000000001</v>
       </c>
       <c r="I22" s="33">
-        <v>0.65559999999999996</v>
+        <v>0.62590000000000001</v>
       </c>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.25">
@@ -17196,25 +18206,25 @@
         <v>22</v>
       </c>
       <c r="C23" s="32">
-        <v>1.2072000000000001</v>
+        <v>1.1172</v>
       </c>
       <c r="D23" s="32">
-        <v>1.2927999999999999</v>
+        <v>1.2209000000000001</v>
       </c>
       <c r="E23" s="32">
-        <v>1.7210000000000001</v>
+        <v>1.6615</v>
       </c>
       <c r="F23" s="32">
-        <v>1.3218000000000001</v>
+        <v>1.3461000000000001</v>
       </c>
       <c r="G23" s="32">
-        <v>1.391</v>
+        <v>1.4410000000000001</v>
       </c>
       <c r="H23" s="32">
-        <v>1.9545999999999999</v>
+        <v>2.04</v>
       </c>
       <c r="I23" s="33">
-        <v>1.3206</v>
+        <v>1.2594000000000001</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.25">
@@ -17222,25 +18232,25 @@
         <v>23</v>
       </c>
       <c r="C24" s="32">
-        <v>3.6453000000000002</v>
+        <v>4.0495000000000001</v>
       </c>
       <c r="D24" s="32">
-        <v>3.4834000000000001</v>
+        <v>3.8138999999999998</v>
       </c>
       <c r="E24" s="32">
-        <v>3.0975999999999999</v>
+        <v>3.875</v>
       </c>
       <c r="F24" s="32">
-        <v>4.1970999999999998</v>
+        <v>4.3304</v>
       </c>
       <c r="G24" s="32">
-        <v>3.9096000000000002</v>
+        <v>4.7001999999999997</v>
       </c>
       <c r="H24" s="32">
-        <v>6.4852999999999996</v>
+        <v>7.0789999999999997</v>
       </c>
       <c r="I24" s="33">
-        <v>3.7206000000000001</v>
+        <v>4.1417999999999999</v>
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.25">
@@ -17248,25 +18258,25 @@
         <v>24</v>
       </c>
       <c r="C25" s="32">
-        <v>1.1876</v>
+        <v>1.2996000000000001</v>
       </c>
       <c r="D25" s="32">
-        <v>1.0942000000000001</v>
+        <v>1.1700999999999999</v>
       </c>
       <c r="E25" s="32">
-        <v>1.0084</v>
+        <v>1.0939000000000001</v>
       </c>
       <c r="F25" s="32">
-        <v>0.90629999999999999</v>
+        <v>1.0307999999999999</v>
       </c>
       <c r="G25" s="32">
-        <v>1.161</v>
+        <v>1.2005999999999999</v>
       </c>
       <c r="H25" s="32">
-        <v>1.2658</v>
+        <v>1.2750999999999999</v>
       </c>
       <c r="I25" s="33">
-        <v>1.1328</v>
+        <v>1.2228000000000001</v>
       </c>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.25">
@@ -17274,25 +18284,25 @@
         <v>25</v>
       </c>
       <c r="C26" s="32">
-        <v>2.6983999999999999</v>
+        <v>2.7320000000000002</v>
       </c>
       <c r="D26" s="32">
-        <v>2.7921999999999998</v>
+        <v>2.8292000000000002</v>
       </c>
       <c r="E26" s="32">
-        <v>2.1398999999999999</v>
+        <v>2.1701000000000001</v>
       </c>
       <c r="F26" s="32">
-        <v>1.6891</v>
+        <v>1.7154</v>
       </c>
       <c r="G26" s="32">
-        <v>2.3751000000000002</v>
+        <v>2.4068000000000001</v>
       </c>
       <c r="H26" s="32">
-        <v>1.7497</v>
+        <v>1.8359000000000001</v>
       </c>
       <c r="I26" s="33">
-        <v>2.5863999999999998</v>
+        <v>2.6230000000000002</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.25">
@@ -17300,25 +18310,25 @@
         <v>26</v>
       </c>
       <c r="C27" s="32">
-        <v>3.8652000000000002</v>
+        <v>3.8978999999999999</v>
       </c>
       <c r="D27" s="32">
-        <v>3.5585</v>
+        <v>3.5384000000000002</v>
       </c>
       <c r="E27" s="32">
-        <v>2.8256999999999999</v>
+        <v>2.9449999999999998</v>
       </c>
       <c r="F27" s="32">
-        <v>2.9948000000000001</v>
+        <v>3.1053999999999999</v>
       </c>
       <c r="G27" s="32">
-        <v>4.7141999999999999</v>
+        <v>4.5557999999999996</v>
       </c>
       <c r="H27" s="32">
-        <v>5.6851000000000003</v>
+        <v>5.5776000000000003</v>
       </c>
       <c r="I27" s="33">
-        <v>3.7766999999999999</v>
+        <v>3.7845</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.25">
@@ -17326,25 +18336,25 @@
         <v>27</v>
       </c>
       <c r="C28" s="32">
-        <v>0.99819999999999998</v>
+        <v>0.98660000000000003</v>
       </c>
       <c r="D28" s="32">
-        <v>0.88329999999999997</v>
+        <v>0.86939999999999995</v>
       </c>
       <c r="E28" s="32">
-        <v>0.82040000000000002</v>
+        <v>0.80010000000000003</v>
       </c>
       <c r="F28" s="32">
-        <v>0.83089999999999997</v>
+        <v>0.81510000000000005</v>
       </c>
       <c r="G28" s="32">
-        <v>0.72450000000000003</v>
+        <v>0.69920000000000004</v>
       </c>
       <c r="H28" s="32">
-        <v>0.9304</v>
+        <v>0.87590000000000001</v>
       </c>
       <c r="I28" s="33">
-        <v>0.92190000000000005</v>
+        <v>0.90600000000000003</v>
       </c>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.25">
@@ -17352,25 +18362,25 @@
         <v>28</v>
       </c>
       <c r="C29" s="32">
-        <v>1.9414</v>
+        <v>1.8306</v>
       </c>
       <c r="D29" s="32">
-        <v>2.1025</v>
+        <v>2.1438000000000001</v>
       </c>
       <c r="E29" s="32">
-        <v>1.4013</v>
+        <v>1.3217000000000001</v>
       </c>
       <c r="F29" s="32">
-        <v>1.3604000000000001</v>
+        <v>1.4739</v>
       </c>
       <c r="G29" s="32">
-        <v>1.6197999999999999</v>
+        <v>1.5828</v>
       </c>
       <c r="H29" s="32">
-        <v>1.5246</v>
+        <v>1.4729000000000001</v>
       </c>
       <c r="I29" s="33">
-        <v>1.8974</v>
+        <v>1.8573999999999999</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.25">
@@ -17378,25 +18388,25 @@
         <v>29</v>
       </c>
       <c r="C30" s="32">
-        <v>1.0577000000000001</v>
+        <v>1.038</v>
       </c>
       <c r="D30" s="32">
-        <v>0.61809999999999998</v>
+        <v>0.58940000000000003</v>
       </c>
       <c r="E30" s="32">
-        <v>1.2345999999999999</v>
+        <v>1.2060999999999999</v>
       </c>
       <c r="F30" s="32">
-        <v>0.52390000000000003</v>
+        <v>0.439</v>
       </c>
       <c r="G30" s="32">
-        <v>0.82240000000000002</v>
+        <v>0.84040000000000004</v>
       </c>
       <c r="H30" s="32">
-        <v>1.0306999999999999</v>
+        <v>0.97819999999999996</v>
       </c>
       <c r="I30" s="33">
-        <v>0.88200000000000001</v>
+        <v>0.85619999999999996</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.25">
@@ -17404,25 +18414,25 @@
         <v>30</v>
       </c>
       <c r="C31" s="32">
-        <v>5.0145999999999997</v>
+        <v>5.1292</v>
       </c>
       <c r="D31" s="32">
-        <v>3.9617</v>
+        <v>4.0964999999999998</v>
       </c>
       <c r="E31" s="32">
-        <v>3.5228999999999999</v>
+        <v>3.6065999999999998</v>
       </c>
       <c r="F31" s="32">
-        <v>2.3359999999999999</v>
+        <v>2.4902000000000002</v>
       </c>
       <c r="G31" s="32">
-        <v>3.2555000000000001</v>
+        <v>3.2376999999999998</v>
       </c>
       <c r="H31" s="32">
-        <v>2.4003999999999999</v>
+        <v>2.2553999999999998</v>
       </c>
       <c r="I31" s="33">
-        <v>4.2206000000000001</v>
+        <v>4.3230000000000004</v>
       </c>
     </row>
     <row r="32" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -17430,25 +18440,25 @@
         <v>31</v>
       </c>
       <c r="C32" s="35">
-        <v>1.2644</v>
+        <v>1.2925</v>
       </c>
       <c r="D32" s="35">
-        <v>1.0593999999999999</v>
+        <v>1.0886</v>
       </c>
       <c r="E32" s="35">
-        <v>0.88060000000000005</v>
+        <v>0.8851</v>
       </c>
       <c r="F32" s="35">
-        <v>0.92600000000000005</v>
+        <v>0.92589999999999995</v>
       </c>
       <c r="G32" s="35">
-        <v>1.1995</v>
+        <v>1.2087000000000001</v>
       </c>
       <c r="H32" s="35">
-        <v>0.9819</v>
+        <v>0.95069999999999999</v>
       </c>
       <c r="I32" s="36">
-        <v>1.1364000000000001</v>
+        <v>1.1583000000000001</v>
       </c>
     </row>
     <row r="33" spans="2:9" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">

--- a/assets/excel/IPCse - Series históricas.xlsx
+++ b/assets/excel/IPCse - Series históricas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iaral\Dropbox\IPC seasonal adjustment\IPCse\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91FC60AB-622B-4ADA-B77A-AD8ACF259F74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{42D2DCA1-30D2-40BC-8862-5E464150D88B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{A81B6F3A-9175-42CA-B78F-287A4E3C6249}"/>
   </bookViews>
@@ -203,9 +203,6 @@
 Tasa de Inflación Mensual por Quintiles</t>
   </si>
   <si>
-    <t>Sep.</t>
-  </si>
-  <si>
     <t>Oct.</t>
   </si>
   <si>
@@ -219,6 +216,9 @@
   </si>
   <si>
     <t>Feb.</t>
+  </si>
+  <si>
+    <t>Mar.</t>
   </si>
 </sst>
 </file>
@@ -1287,7 +1287,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA821952-0137-4F39-844C-15CA99AC928E}">
-  <dimension ref="B1:V115"/>
+  <dimension ref="B1:V116"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="15.5703125" defaultRowHeight="18" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="4" customWidth="1"/>
@@ -8569,69 +8569,134 @@
         <v>10201.693499999999</v>
       </c>
     </row>
-    <row r="115" spans="2:22" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B115" s="14">
+    <row r="115" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B115" s="13">
         <v>46054</v>
       </c>
-      <c r="C115" s="18">
+      <c r="C115" s="15">
         <v>10713.0087</v>
       </c>
-      <c r="D115" s="19">
+      <c r="D115" s="16">
         <v>10665.4244</v>
       </c>
-      <c r="E115" s="19">
+      <c r="E115" s="16">
         <v>10677.3019</v>
       </c>
-      <c r="F115" s="19">
+      <c r="F115" s="16">
         <v>10763.225200000001</v>
       </c>
-      <c r="G115" s="19">
+      <c r="G115" s="16">
         <v>10597.746800000001</v>
       </c>
-      <c r="H115" s="19">
+      <c r="H115" s="16">
         <v>10872.1333</v>
       </c>
-      <c r="I115" s="20">
+      <c r="I115" s="17">
         <v>10849.270699999999</v>
       </c>
-      <c r="J115" s="19">
+      <c r="J115" s="16">
         <v>11408.62</v>
       </c>
-      <c r="K115" s="19">
+      <c r="K115" s="16">
         <v>7548.8959999999997</v>
       </c>
-      <c r="L115" s="19">
+      <c r="L115" s="16">
         <v>8032.5016999999998</v>
       </c>
-      <c r="M115" s="19">
+      <c r="M115" s="16">
         <v>11658.648999999999</v>
       </c>
-      <c r="N115" s="19">
+      <c r="N115" s="16">
         <v>8811.7546000000002</v>
       </c>
-      <c r="O115" s="19">
+      <c r="O115" s="16">
         <v>11895.636399999999</v>
       </c>
-      <c r="P115" s="19">
+      <c r="P115" s="16">
         <v>11141.320400000001</v>
       </c>
-      <c r="Q115" s="19">
+      <c r="Q115" s="16">
         <v>9435.1581000000006</v>
       </c>
-      <c r="R115" s="19">
+      <c r="R115" s="16">
         <v>9430.3948999999993</v>
       </c>
-      <c r="S115" s="19">
+      <c r="S115" s="16">
         <v>10355.4599</v>
       </c>
-      <c r="T115" s="19">
+      <c r="T115" s="16">
         <v>13210.944100000001</v>
       </c>
-      <c r="U115" s="20">
+      <c r="U115" s="17">
         <v>10479.518099999999</v>
       </c>
-      <c r="V115" s="18">
+      <c r="V115" s="15">
         <v>10427.577499999999</v>
+      </c>
+    </row>
+    <row r="116" spans="2:22" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B116" s="14">
+        <v>46082</v>
+      </c>
+      <c r="C116" s="18">
+        <v>10956.1021</v>
+      </c>
+      <c r="D116" s="19">
+        <v>10887.980100000001</v>
+      </c>
+      <c r="E116" s="19">
+        <v>10925.5167</v>
+      </c>
+      <c r="F116" s="19">
+        <v>11076.978800000001</v>
+      </c>
+      <c r="G116" s="19">
+        <v>10996.589400000001</v>
+      </c>
+      <c r="H116" s="19">
+        <v>11122.317300000001</v>
+      </c>
+      <c r="I116" s="20">
+        <v>11026.3896</v>
+      </c>
+      <c r="J116" s="19">
+        <v>11648.402700000001</v>
+      </c>
+      <c r="K116" s="19">
+        <v>7618.9602000000004</v>
+      </c>
+      <c r="L116" s="19">
+        <v>8000.4431000000004</v>
+      </c>
+      <c r="M116" s="19">
+        <v>12092.325999999999</v>
+      </c>
+      <c r="N116" s="19">
+        <v>8925.5949999999993</v>
+      </c>
+      <c r="O116" s="19">
+        <v>12210.1445</v>
+      </c>
+      <c r="P116" s="19">
+        <v>11598.991900000001</v>
+      </c>
+      <c r="Q116" s="19">
+        <v>9747.6638000000003</v>
+      </c>
+      <c r="R116" s="19">
+        <v>9766.2255999999998</v>
+      </c>
+      <c r="S116" s="19">
+        <v>9304.0820999999996</v>
+      </c>
+      <c r="T116" s="19">
+        <v>13663.4095</v>
+      </c>
+      <c r="U116" s="20">
+        <v>10656.376200000001</v>
+      </c>
+      <c r="V116" s="18">
+        <v>10645.208000000001</v>
       </c>
     </row>
   </sheetData>
@@ -8647,7 +8712,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED968B30-91AE-4BCD-9838-818BA334E48C}">
-  <dimension ref="B1:V115"/>
+  <dimension ref="B1:V116"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="15.5703125" defaultRowHeight="18" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="4" customWidth="1"/>
@@ -8841,39 +8906,51 @@
         <v>0.86929999999999996</v>
       </c>
       <c r="K6" s="16">
+        <f>ROUND(100*(Índices!K6/Índices!K5-1),4)</f>
         <v>0.50229999999999997</v>
       </c>
       <c r="L6" s="16">
+        <f>ROUND(100*(Índices!L6/Índices!L5-1),4)</f>
         <v>1.8717999999999999</v>
       </c>
       <c r="M6" s="16">
+        <f>ROUND(100*(Índices!M6/Índices!M5-1),4)</f>
         <v>1.5481</v>
       </c>
       <c r="N6" s="16">
+        <f>ROUND(100*(Índices!N6/Índices!N5-1),4)</f>
         <v>1.4705999999999999</v>
       </c>
       <c r="O6" s="16">
+        <f>ROUND(100*(Índices!O6/Índices!O5-1),4)</f>
         <v>2.3879000000000001</v>
       </c>
       <c r="P6" s="16">
+        <f>ROUND(100*(Índices!P6/Índices!P5-1),4)</f>
         <v>2.0838999999999999</v>
       </c>
       <c r="Q6" s="16">
+        <f>ROUND(100*(Índices!Q6/Índices!Q5-1),4)</f>
         <v>2.3902000000000001</v>
       </c>
       <c r="R6" s="16">
+        <f>ROUND(100*(Índices!R6/Índices!R5-1),4)</f>
         <v>2.5834999999999999</v>
       </c>
       <c r="S6" s="16">
+        <f>ROUND(100*(Índices!S6/Índices!S5-1),4)</f>
         <v>2.6265000000000001</v>
       </c>
       <c r="T6" s="16">
+        <f>ROUND(100*(Índices!T6/Índices!T5-1),4)</f>
         <v>2.9868000000000001</v>
       </c>
       <c r="U6" s="17">
+        <f>ROUND(100*(Índices!U6/Índices!U5-1),4)</f>
         <v>1.9661999999999999</v>
       </c>
       <c r="V6" s="15">
+        <f>ROUND(100*(Índices!V6/Índices!V5-1),4)</f>
         <v>1.6071</v>
       </c>
     </row>
@@ -8914,39 +8991,51 @@
         <v>1.3761000000000001</v>
       </c>
       <c r="K7" s="16">
+        <f>ROUND(100*(Índices!K7/Índices!K6-1),4)</f>
         <v>4.6935000000000002</v>
       </c>
       <c r="L7" s="16">
+        <f>ROUND(100*(Índices!L7/Índices!L6-1),4)</f>
         <v>1.8668</v>
       </c>
       <c r="M7" s="16">
+        <f>ROUND(100*(Índices!M7/Índices!M6-1),4)</f>
         <v>5.2967000000000004</v>
       </c>
       <c r="N7" s="16">
+        <f>ROUND(100*(Índices!N7/Índices!N6-1),4)</f>
         <v>0.90939999999999999</v>
       </c>
       <c r="O7" s="16">
+        <f>ROUND(100*(Índices!O7/Índices!O6-1),4)</f>
         <v>2.6901999999999999</v>
       </c>
       <c r="P7" s="16">
+        <f>ROUND(100*(Índices!P7/Índices!P6-1),4)</f>
         <v>1.8837999999999999</v>
       </c>
       <c r="Q7" s="16">
+        <f>ROUND(100*(Índices!Q7/Índices!Q6-1),4)</f>
         <v>3.6934</v>
       </c>
       <c r="R7" s="16">
+        <f>ROUND(100*(Índices!R7/Índices!R6-1),4)</f>
         <v>1.4674</v>
       </c>
       <c r="S7" s="16">
+        <f>ROUND(100*(Índices!S7/Índices!S6-1),4)</f>
         <v>4.335</v>
       </c>
       <c r="T7" s="16">
+        <f>ROUND(100*(Índices!T7/Índices!T6-1),4)</f>
         <v>1.7111000000000001</v>
       </c>
       <c r="U7" s="17">
+        <f>ROUND(100*(Índices!U7/Índices!U6-1),4)</f>
         <v>1.8775999999999999</v>
       </c>
       <c r="V7" s="15">
+        <f>ROUND(100*(Índices!V7/Índices!V6-1),4)</f>
         <v>1.6587000000000001</v>
       </c>
     </row>
@@ -8987,39 +9076,51 @@
         <v>1.8279000000000001</v>
       </c>
       <c r="K8" s="16">
+        <f>ROUND(100*(Índices!K8/Índices!K7-1),4)</f>
         <v>1.6578999999999999</v>
       </c>
       <c r="L8" s="16">
+        <f>ROUND(100*(Índices!L8/Índices!L7-1),4)</f>
         <v>1.1292</v>
       </c>
       <c r="M8" s="16">
+        <f>ROUND(100*(Índices!M8/Índices!M7-1),4)</f>
         <v>3.6665999999999999</v>
       </c>
       <c r="N8" s="16">
+        <f>ROUND(100*(Índices!N8/Índices!N7-1),4)</f>
         <v>0.77759999999999996</v>
       </c>
       <c r="O8" s="16">
+        <f>ROUND(100*(Índices!O8/Índices!O7-1),4)</f>
         <v>1.9854000000000001</v>
       </c>
       <c r="P8" s="16">
+        <f>ROUND(100*(Índices!P8/Índices!P7-1),4)</f>
         <v>1.1793</v>
       </c>
       <c r="Q8" s="16">
+        <f>ROUND(100*(Índices!Q8/Índices!Q7-1),4)</f>
         <v>3.2494000000000001</v>
       </c>
       <c r="R8" s="16">
+        <f>ROUND(100*(Índices!R8/Índices!R7-1),4)</f>
         <v>2.2909999999999999</v>
       </c>
       <c r="S8" s="16">
+        <f>ROUND(100*(Índices!S8/Índices!S7-1),4)</f>
         <v>-2.3403999999999998</v>
       </c>
       <c r="T8" s="16">
+        <f>ROUND(100*(Índices!T8/Índices!T7-1),4)</f>
         <v>1.0108999999999999</v>
       </c>
       <c r="U8" s="17">
+        <f>ROUND(100*(Índices!U8/Índices!U7-1),4)</f>
         <v>1.8391999999999999</v>
       </c>
       <c r="V8" s="15">
+        <f>ROUND(100*(Índices!V8/Índices!V7-1),4)</f>
         <v>1.5406</v>
       </c>
     </row>
@@ -9060,39 +9161,51 @@
         <v>2.5916000000000001</v>
       </c>
       <c r="K9" s="16">
+        <f>ROUND(100*(Índices!K9/Índices!K8-1),4)</f>
         <v>3.1263999999999998</v>
       </c>
       <c r="L9" s="16">
+        <f>ROUND(100*(Índices!L9/Índices!L8-1),4)</f>
         <v>2.3744000000000001</v>
       </c>
       <c r="M9" s="16">
+        <f>ROUND(100*(Índices!M9/Índices!M8-1),4)</f>
         <v>5.9916999999999998</v>
       </c>
       <c r="N9" s="16">
+        <f>ROUND(100*(Índices!N9/Índices!N8-1),4)</f>
         <v>1.4933000000000001</v>
       </c>
       <c r="O9" s="16">
+        <f>ROUND(100*(Índices!O9/Índices!O8-1),4)</f>
         <v>1.7967</v>
       </c>
       <c r="P9" s="16">
+        <f>ROUND(100*(Índices!P9/Índices!P8-1),4)</f>
         <v>0.62170000000000003</v>
       </c>
       <c r="Q9" s="16">
+        <f>ROUND(100*(Índices!Q9/Índices!Q8-1),4)</f>
         <v>7.1840000000000002</v>
       </c>
       <c r="R9" s="16">
+        <f>ROUND(100*(Índices!R9/Índices!R8-1),4)</f>
         <v>2.6154000000000002</v>
       </c>
       <c r="S9" s="16">
+        <f>ROUND(100*(Índices!S9/Índices!S8-1),4)</f>
         <v>4.3068999999999997</v>
       </c>
       <c r="T9" s="16">
+        <f>ROUND(100*(Índices!T9/Índices!T8-1),4)</f>
         <v>1.9072</v>
       </c>
       <c r="U9" s="17">
+        <f>ROUND(100*(Índices!U9/Índices!U8-1),4)</f>
         <v>1.8447</v>
       </c>
       <c r="V9" s="15">
+        <f>ROUND(100*(Índices!V9/Índices!V8-1),4)</f>
         <v>2.3517000000000001</v>
       </c>
     </row>
@@ -9133,39 +9246,51 @@
         <v>2.1341999999999999</v>
       </c>
       <c r="K10" s="16">
+        <f>ROUND(100*(Índices!K10/Índices!K9-1),4)</f>
         <v>2.2545999999999999</v>
       </c>
       <c r="L10" s="16">
+        <f>ROUND(100*(Índices!L10/Índices!L9-1),4)</f>
         <v>1.7161999999999999</v>
       </c>
       <c r="M10" s="16">
+        <f>ROUND(100*(Índices!M10/Índices!M9-1),4)</f>
         <v>1.7934000000000001</v>
       </c>
       <c r="N10" s="16">
+        <f>ROUND(100*(Índices!N10/Índices!N9-1),4)</f>
         <v>2.8679999999999999</v>
       </c>
       <c r="O10" s="16">
+        <f>ROUND(100*(Índices!O10/Índices!O9-1),4)</f>
         <v>1.5297000000000001</v>
       </c>
       <c r="P10" s="16">
+        <f>ROUND(100*(Índices!P10/Índices!P9-1),4)</f>
         <v>0.93159999999999998</v>
       </c>
       <c r="Q10" s="16">
+        <f>ROUND(100*(Índices!Q10/Índices!Q9-1),4)</f>
         <v>0.75219999999999998</v>
       </c>
       <c r="R10" s="16">
+        <f>ROUND(100*(Índices!R10/Índices!R9-1),4)</f>
         <v>1.089</v>
       </c>
       <c r="S10" s="16">
+        <f>ROUND(100*(Índices!S10/Índices!S9-1),4)</f>
         <v>2.5304000000000002</v>
       </c>
       <c r="T10" s="16">
+        <f>ROUND(100*(Índices!T10/Índices!T9-1),4)</f>
         <v>1.4910000000000001</v>
       </c>
       <c r="U10" s="17">
+        <f>ROUND(100*(Índices!U10/Índices!U9-1),4)</f>
         <v>1.3640000000000001</v>
       </c>
       <c r="V10" s="15">
+        <f>ROUND(100*(Índices!V10/Índices!V9-1),4)</f>
         <v>1.8993</v>
       </c>
     </row>
@@ -9206,39 +9331,51 @@
         <v>1.2533000000000001</v>
       </c>
       <c r="K11" s="16">
+        <f>ROUND(100*(Índices!K11/Índices!K10-1),4)</f>
         <v>0.93969999999999998</v>
       </c>
       <c r="L11" s="16">
+        <f>ROUND(100*(Índices!L11/Índices!L10-1),4)</f>
         <v>0.95750000000000002</v>
       </c>
       <c r="M11" s="16">
+        <f>ROUND(100*(Índices!M11/Índices!M10-1),4)</f>
         <v>1.7366999999999999</v>
       </c>
       <c r="N11" s="16">
+        <f>ROUND(100*(Índices!N11/Índices!N10-1),4)</f>
         <v>1.0780000000000001</v>
       </c>
       <c r="O11" s="16">
+        <f>ROUND(100*(Índices!O11/Índices!O10-1),4)</f>
         <v>1.4726999999999999</v>
       </c>
       <c r="P11" s="16">
+        <f>ROUND(100*(Índices!P11/Índices!P10-1),4)</f>
         <v>0.69630000000000003</v>
       </c>
       <c r="Q11" s="16">
+        <f>ROUND(100*(Índices!Q11/Índices!Q10-1),4)</f>
         <v>1.2334000000000001</v>
       </c>
       <c r="R11" s="16">
+        <f>ROUND(100*(Índices!R11/Índices!R10-1),4)</f>
         <v>2.0760000000000001</v>
       </c>
       <c r="S11" s="16">
+        <f>ROUND(100*(Índices!S11/Índices!S10-1),4)</f>
         <v>2.2387000000000001</v>
       </c>
       <c r="T11" s="16">
+        <f>ROUND(100*(Índices!T11/Índices!T10-1),4)</f>
         <v>1.2934000000000001</v>
       </c>
       <c r="U11" s="17">
+        <f>ROUND(100*(Índices!U11/Índices!U10-1),4)</f>
         <v>1.2994000000000001</v>
       </c>
       <c r="V11" s="15">
+        <f>ROUND(100*(Índices!V11/Índices!V10-1),4)</f>
         <v>1.2845</v>
       </c>
     </row>
@@ -9279,39 +9416,51 @@
         <v>1.7292000000000001</v>
       </c>
       <c r="K12" s="16">
+        <f>ROUND(100*(Índices!K12/Índices!K11-1),4)</f>
         <v>3.1669</v>
       </c>
       <c r="L12" s="16">
+        <f>ROUND(100*(Índices!L12/Índices!L11-1),4)</f>
         <v>0.89039999999999997</v>
       </c>
       <c r="M12" s="16">
+        <f>ROUND(100*(Índices!M12/Índices!M11-1),4)</f>
         <v>1.9917</v>
       </c>
       <c r="N12" s="16">
+        <f>ROUND(100*(Índices!N12/Índices!N11-1),4)</f>
         <v>1.8418000000000001</v>
       </c>
       <c r="O12" s="16">
+        <f>ROUND(100*(Índices!O12/Índices!O11-1),4)</f>
         <v>3.3252999999999999</v>
       </c>
       <c r="P12" s="16">
+        <f>ROUND(100*(Índices!P12/Índices!P11-1),4)</f>
         <v>2.1753</v>
       </c>
       <c r="Q12" s="16">
+        <f>ROUND(100*(Índices!Q12/Índices!Q11-1),4)</f>
         <v>1.7094</v>
       </c>
       <c r="R12" s="16">
+        <f>ROUND(100*(Índices!R12/Índices!R11-1),4)</f>
         <v>2.7905000000000002</v>
       </c>
       <c r="S12" s="16">
+        <f>ROUND(100*(Índices!S12/Índices!S11-1),4)</f>
         <v>1.8702000000000001</v>
       </c>
       <c r="T12" s="16">
+        <f>ROUND(100*(Índices!T12/Índices!T11-1),4)</f>
         <v>2.5055000000000001</v>
       </c>
       <c r="U12" s="17">
+        <f>ROUND(100*(Índices!U12/Índices!U11-1),4)</f>
         <v>1.36</v>
       </c>
       <c r="V12" s="15">
+        <f>ROUND(100*(Índices!V12/Índices!V11-1),4)</f>
         <v>1.8971</v>
       </c>
     </row>
@@ -9352,39 +9501,51 @@
         <v>1.8512</v>
       </c>
       <c r="K13" s="16">
+        <f>ROUND(100*(Índices!K13/Índices!K12-1),4)</f>
         <v>1.7755000000000001</v>
       </c>
       <c r="L13" s="16">
+        <f>ROUND(100*(Índices!L13/Índices!L12-1),4)</f>
         <v>6.8500000000000005E-2</v>
       </c>
       <c r="M13" s="16">
+        <f>ROUND(100*(Índices!M13/Índices!M12-1),4)</f>
         <v>2.1337000000000002</v>
       </c>
       <c r="N13" s="16">
+        <f>ROUND(100*(Índices!N13/Índices!N12-1),4)</f>
         <v>0.67069999999999996</v>
       </c>
       <c r="O13" s="16">
+        <f>ROUND(100*(Índices!O13/Índices!O12-1),4)</f>
         <v>2.4981</v>
       </c>
       <c r="P13" s="16">
+        <f>ROUND(100*(Índices!P13/Índices!P12-1),4)</f>
         <v>1.0873999999999999</v>
       </c>
       <c r="Q13" s="16">
+        <f>ROUND(100*(Índices!Q13/Índices!Q12-1),4)</f>
         <v>1.8106</v>
       </c>
       <c r="R13" s="16">
+        <f>ROUND(100*(Índices!R13/Índices!R12-1),4)</f>
         <v>0.81920000000000004</v>
       </c>
       <c r="S13" s="16">
+        <f>ROUND(100*(Índices!S13/Índices!S12-1),4)</f>
         <v>2.4093</v>
       </c>
       <c r="T13" s="16">
+        <f>ROUND(100*(Índices!T13/Índices!T12-1),4)</f>
         <v>0.75380000000000003</v>
       </c>
       <c r="U13" s="17">
+        <f>ROUND(100*(Índices!U13/Índices!U12-1),4)</f>
         <v>1.4476</v>
       </c>
       <c r="V13" s="15">
+        <f>ROUND(100*(Índices!V13/Índices!V12-1),4)</f>
         <v>1.1851</v>
       </c>
     </row>
@@ -9425,39 +9586,51 @@
         <v>1.0415000000000001</v>
       </c>
       <c r="K14" s="16">
+        <f>ROUND(100*(Índices!K14/Índices!K13-1),4)</f>
         <v>-0.90049999999999997</v>
       </c>
       <c r="L14" s="16">
+        <f>ROUND(100*(Índices!L14/Índices!L13-1),4)</f>
         <v>-0.12659999999999999</v>
       </c>
       <c r="M14" s="16">
+        <f>ROUND(100*(Índices!M14/Índices!M13-1),4)</f>
         <v>2.0291999999999999</v>
       </c>
       <c r="N14" s="16">
+        <f>ROUND(100*(Índices!N14/Índices!N13-1),4)</f>
         <v>0.36270000000000002</v>
       </c>
       <c r="O14" s="16">
+        <f>ROUND(100*(Índices!O14/Índices!O13-1),4)</f>
         <v>2.38</v>
       </c>
       <c r="P14" s="16">
+        <f>ROUND(100*(Índices!P14/Índices!P13-1),4)</f>
         <v>0.80279999999999996</v>
       </c>
       <c r="Q14" s="16">
+        <f>ROUND(100*(Índices!Q14/Índices!Q13-1),4)</f>
         <v>1.0123</v>
       </c>
       <c r="R14" s="16">
+        <f>ROUND(100*(Índices!R14/Índices!R13-1),4)</f>
         <v>1.5563</v>
       </c>
       <c r="S14" s="16">
+        <f>ROUND(100*(Índices!S14/Índices!S13-1),4)</f>
         <v>4.6139999999999999</v>
       </c>
       <c r="T14" s="16">
+        <f>ROUND(100*(Índices!T14/Índices!T13-1),4)</f>
         <v>1.4408000000000001</v>
       </c>
       <c r="U14" s="17">
+        <f>ROUND(100*(Índices!U14/Índices!U13-1),4)</f>
         <v>1.5919000000000001</v>
       </c>
       <c r="V14" s="15">
+        <f>ROUND(100*(Índices!V14/Índices!V13-1),4)</f>
         <v>0.83930000000000005</v>
       </c>
     </row>
@@ -9498,39 +9671,51 @@
         <v>0.85899999999999999</v>
       </c>
       <c r="K15" s="16">
+        <f>ROUND(100*(Índices!K15/Índices!K14-1),4)</f>
         <v>2.7696999999999998</v>
       </c>
       <c r="L15" s="16">
+        <f>ROUND(100*(Índices!L15/Índices!L14-1),4)</f>
         <v>0.99250000000000005</v>
       </c>
       <c r="M15" s="16">
+        <f>ROUND(100*(Índices!M15/Índices!M14-1),4)</f>
         <v>0.90549999999999997</v>
       </c>
       <c r="N15" s="16">
+        <f>ROUND(100*(Índices!N15/Índices!N14-1),4)</f>
         <v>0.32519999999999999</v>
       </c>
       <c r="O15" s="16">
+        <f>ROUND(100*(Índices!O15/Índices!O14-1),4)</f>
         <v>1.0527</v>
       </c>
       <c r="P15" s="16">
+        <f>ROUND(100*(Índices!P15/Índices!P14-1),4)</f>
         <v>1.2967</v>
       </c>
       <c r="Q15" s="16">
+        <f>ROUND(100*(Índices!Q15/Índices!Q14-1),4)</f>
         <v>5.2975000000000003</v>
       </c>
       <c r="R15" s="16">
+        <f>ROUND(100*(Índices!R15/Índices!R14-1),4)</f>
         <v>1.5078</v>
       </c>
       <c r="S15" s="16">
+        <f>ROUND(100*(Índices!S15/Índices!S14-1),4)</f>
         <v>1.4351</v>
       </c>
       <c r="T15" s="16">
+        <f>ROUND(100*(Índices!T15/Índices!T14-1),4)</f>
         <v>1.4362999999999999</v>
       </c>
       <c r="U15" s="17">
+        <f>ROUND(100*(Índices!U15/Índices!U14-1),4)</f>
         <v>1.3307</v>
       </c>
       <c r="V15" s="15">
+        <f>ROUND(100*(Índices!V15/Índices!V14-1),4)</f>
         <v>1.1243000000000001</v>
       </c>
     </row>
@@ -9571,39 +9756,51 @@
         <v>1.8842000000000001</v>
       </c>
       <c r="K16" s="16">
+        <f>ROUND(100*(Índices!K16/Índices!K15-1),4)</f>
         <v>0.49049999999999999</v>
       </c>
       <c r="L16" s="16">
+        <f>ROUND(100*(Índices!L16/Índices!L15-1),4)</f>
         <v>1.5711999999999999</v>
       </c>
       <c r="M16" s="16">
+        <f>ROUND(100*(Índices!M16/Índices!M15-1),4)</f>
         <v>1.2539</v>
       </c>
       <c r="N16" s="16">
+        <f>ROUND(100*(Índices!N16/Índices!N15-1),4)</f>
         <v>1.1100000000000001</v>
       </c>
       <c r="O16" s="16">
+        <f>ROUND(100*(Índices!O16/Índices!O15-1),4)</f>
         <v>1.3013999999999999</v>
       </c>
       <c r="P16" s="16">
+        <f>ROUND(100*(Índices!P16/Índices!P15-1),4)</f>
         <v>3.024</v>
       </c>
       <c r="Q16" s="16">
+        <f>ROUND(100*(Índices!Q16/Índices!Q15-1),4)</f>
         <v>0.93079999999999996</v>
       </c>
       <c r="R16" s="16">
+        <f>ROUND(100*(Índices!R16/Índices!R15-1),4)</f>
         <v>0.93320000000000003</v>
       </c>
       <c r="S16" s="16">
+        <f>ROUND(100*(Índices!S16/Índices!S15-1),4)</f>
         <v>2.0162</v>
       </c>
       <c r="T16" s="16">
+        <f>ROUND(100*(Índices!T16/Índices!T15-1),4)</f>
         <v>1.8843000000000001</v>
       </c>
       <c r="U16" s="17">
+        <f>ROUND(100*(Índices!U16/Índices!U15-1),4)</f>
         <v>1.1933</v>
       </c>
       <c r="V16" s="15">
+        <f>ROUND(100*(Índices!V16/Índices!V15-1),4)</f>
         <v>1.5330999999999999</v>
       </c>
     </row>
@@ -9644,39 +9841,51 @@
         <v>1.2654000000000001</v>
       </c>
       <c r="K17" s="16">
+        <f>ROUND(100*(Índices!K17/Índices!K16-1),4)</f>
         <v>1.0643</v>
       </c>
       <c r="L17" s="16">
+        <f>ROUND(100*(Índices!L17/Índices!L16-1),4)</f>
         <v>2.2522000000000002</v>
       </c>
       <c r="M17" s="16">
+        <f>ROUND(100*(Índices!M17/Índices!M16-1),4)</f>
         <v>17.804300000000001</v>
       </c>
       <c r="N17" s="16">
+        <f>ROUND(100*(Índices!N17/Índices!N16-1),4)</f>
         <v>3.3445999999999998</v>
       </c>
       <c r="O17" s="16">
+        <f>ROUND(100*(Índices!O17/Índices!O16-1),4)</f>
         <v>2.3912</v>
       </c>
       <c r="P17" s="16">
+        <f>ROUND(100*(Índices!P17/Índices!P16-1),4)</f>
         <v>3.2414999999999998</v>
       </c>
       <c r="Q17" s="16">
+        <f>ROUND(100*(Índices!Q17/Índices!Q16-1),4)</f>
         <v>0.69420000000000004</v>
       </c>
       <c r="R17" s="16">
+        <f>ROUND(100*(Índices!R17/Índices!R16-1),4)</f>
         <v>0.96350000000000002</v>
       </c>
       <c r="S17" s="16">
+        <f>ROUND(100*(Índices!S17/Índices!S16-1),4)</f>
         <v>1.8869</v>
       </c>
       <c r="T17" s="16">
+        <f>ROUND(100*(Índices!T17/Índices!T16-1),4)</f>
         <v>1.7698</v>
       </c>
       <c r="U17" s="17">
+        <f>ROUND(100*(Índices!U17/Índices!U16-1),4)</f>
         <v>1.1073999999999999</v>
       </c>
       <c r="V17" s="15">
+        <f>ROUND(100*(Índices!V17/Índices!V16-1),4)</f>
         <v>1.6093</v>
       </c>
     </row>
@@ -9717,39 +9926,51 @@
         <v>1.6754</v>
       </c>
       <c r="K18" s="16">
+        <f>ROUND(100*(Índices!K18/Índices!K17-1),4)</f>
         <v>1.9211</v>
       </c>
       <c r="L18" s="16">
+        <f>ROUND(100*(Índices!L18/Índices!L17-1),4)</f>
         <v>2.1074999999999999</v>
       </c>
       <c r="M18" s="16">
+        <f>ROUND(100*(Índices!M18/Índices!M17-1),4)</f>
         <v>1.1691</v>
       </c>
       <c r="N18" s="16">
+        <f>ROUND(100*(Índices!N18/Índices!N17-1),4)</f>
         <v>1.6467000000000001</v>
       </c>
       <c r="O18" s="16">
+        <f>ROUND(100*(Índices!O18/Índices!O17-1),4)</f>
         <v>1.7785</v>
       </c>
       <c r="P18" s="16">
+        <f>ROUND(100*(Índices!P18/Índices!P17-1),4)</f>
         <v>2.1682999999999999</v>
       </c>
       <c r="Q18" s="16">
+        <f>ROUND(100*(Índices!Q18/Índices!Q17-1),4)</f>
         <v>1.1515</v>
       </c>
       <c r="R18" s="16">
+        <f>ROUND(100*(Índices!R18/Índices!R17-1),4)</f>
         <v>2.8725999999999998</v>
       </c>
       <c r="S18" s="16">
+        <f>ROUND(100*(Índices!S18/Índices!S17-1),4)</f>
         <v>2.5886</v>
       </c>
       <c r="T18" s="16">
+        <f>ROUND(100*(Índices!T18/Índices!T17-1),4)</f>
         <v>2.8121999999999998</v>
       </c>
       <c r="U18" s="17">
+        <f>ROUND(100*(Índices!U18/Índices!U17-1),4)</f>
         <v>2.4632000000000001</v>
       </c>
       <c r="V18" s="15">
+        <f>ROUND(100*(Índices!V18/Índices!V17-1),4)</f>
         <v>2.0897000000000001</v>
       </c>
     </row>
@@ -9790,39 +10011,51 @@
         <v>1.7171000000000001</v>
       </c>
       <c r="K19" s="16">
+        <f>ROUND(100*(Índices!K19/Índices!K18-1),4)</f>
         <v>2.1985000000000001</v>
       </c>
       <c r="L19" s="16">
+        <f>ROUND(100*(Índices!L19/Índices!L18-1),4)</f>
         <v>1.4261999999999999</v>
       </c>
       <c r="M19" s="16">
+        <f>ROUND(100*(Índices!M19/Índices!M18-1),4)</f>
         <v>3.7362000000000002</v>
       </c>
       <c r="N19" s="16">
+        <f>ROUND(100*(Índices!N19/Índices!N18-1),4)</f>
         <v>2.1661000000000001</v>
       </c>
       <c r="O19" s="16">
+        <f>ROUND(100*(Índices!O19/Índices!O18-1),4)</f>
         <v>2.3616999999999999</v>
       </c>
       <c r="P19" s="16">
+        <f>ROUND(100*(Índices!P19/Índices!P18-1),4)</f>
         <v>4.4785000000000004</v>
       </c>
       <c r="Q19" s="16">
+        <f>ROUND(100*(Índices!Q19/Índices!Q18-1),4)</f>
         <v>8.7888000000000002</v>
       </c>
       <c r="R19" s="16">
+        <f>ROUND(100*(Índices!R19/Índices!R18-1),4)</f>
         <v>1.8742000000000001</v>
       </c>
       <c r="S19" s="16">
+        <f>ROUND(100*(Índices!S19/Índices!S18-1),4)</f>
         <v>3.1139999999999999</v>
       </c>
       <c r="T19" s="16">
+        <f>ROUND(100*(Índices!T19/Índices!T18-1),4)</f>
         <v>2.0703</v>
       </c>
       <c r="U19" s="17">
+        <f>ROUND(100*(Índices!U19/Índices!U18-1),4)</f>
         <v>1.7981</v>
       </c>
       <c r="V19" s="15">
+        <f>ROUND(100*(Índices!V19/Índices!V18-1),4)</f>
         <v>1.7984</v>
       </c>
     </row>
@@ -9863,39 +10096,51 @@
         <v>1.3884000000000001</v>
       </c>
       <c r="K20" s="16">
+        <f>ROUND(100*(Índices!K20/Índices!K19-1),4)</f>
         <v>0.30249999999999999</v>
       </c>
       <c r="L20" s="16">
+        <f>ROUND(100*(Índices!L20/Índices!L19-1),4)</f>
         <v>1.9258999999999999</v>
       </c>
       <c r="M20" s="16">
+        <f>ROUND(100*(Índices!M20/Índices!M19-1),4)</f>
         <v>0.54369999999999996</v>
       </c>
       <c r="N20" s="16">
+        <f>ROUND(100*(Índices!N20/Índices!N19-1),4)</f>
         <v>4.5092999999999996</v>
       </c>
       <c r="O20" s="16">
+        <f>ROUND(100*(Índices!O20/Índices!O19-1),4)</f>
         <v>1.3360000000000001</v>
       </c>
       <c r="P20" s="16">
+        <f>ROUND(100*(Índices!P20/Índices!P19-1),4)</f>
         <v>1.7958000000000001</v>
       </c>
       <c r="Q20" s="16">
+        <f>ROUND(100*(Índices!Q20/Índices!Q19-1),4)</f>
         <v>2.7772999999999999</v>
       </c>
       <c r="R20" s="16">
+        <f>ROUND(100*(Índices!R20/Índices!R19-1),4)</f>
         <v>1.7896000000000001</v>
       </c>
       <c r="S20" s="16">
+        <f>ROUND(100*(Índices!S20/Índices!S19-1),4)</f>
         <v>-0.1351</v>
       </c>
       <c r="T20" s="16">
+        <f>ROUND(100*(Índices!T20/Índices!T19-1),4)</f>
         <v>1.752</v>
       </c>
       <c r="U20" s="17">
+        <f>ROUND(100*(Índices!U20/Índices!U19-1),4)</f>
         <v>1.9016999999999999</v>
       </c>
       <c r="V20" s="15">
+        <f>ROUND(100*(Índices!V20/Índices!V19-1),4)</f>
         <v>1.8067</v>
       </c>
     </row>
@@ -9936,39 +10181,51 @@
         <v>1.5042</v>
       </c>
       <c r="K21" s="16">
+        <f>ROUND(100*(Índices!K21/Índices!K20-1),4)</f>
         <v>2.0865</v>
       </c>
       <c r="L21" s="16">
+        <f>ROUND(100*(Índices!L21/Índices!L20-1),4)</f>
         <v>1.974</v>
       </c>
       <c r="M21" s="16">
+        <f>ROUND(100*(Índices!M21/Índices!M20-1),4)</f>
         <v>8.0784000000000002</v>
       </c>
       <c r="N21" s="16">
+        <f>ROUND(100*(Índices!N21/Índices!N20-1),4)</f>
         <v>1.5851</v>
       </c>
       <c r="O21" s="16">
+        <f>ROUND(100*(Índices!O21/Índices!O20-1),4)</f>
         <v>1.7955000000000001</v>
       </c>
       <c r="P21" s="16">
+        <f>ROUND(100*(Índices!P21/Índices!P20-1),4)</f>
         <v>3.9805000000000001</v>
       </c>
       <c r="Q21" s="16">
+        <f>ROUND(100*(Índices!Q21/Índices!Q20-1),4)</f>
         <v>1.3804000000000001</v>
       </c>
       <c r="R21" s="16">
+        <f>ROUND(100*(Índices!R21/Índices!R20-1),4)</f>
         <v>1.9609000000000001</v>
       </c>
       <c r="S21" s="16">
+        <f>ROUND(100*(Índices!S21/Índices!S20-1),4)</f>
         <v>2.2267999999999999</v>
       </c>
       <c r="T21" s="16">
+        <f>ROUND(100*(Índices!T21/Índices!T20-1),4)</f>
         <v>2.2816000000000001</v>
       </c>
       <c r="U21" s="17">
+        <f>ROUND(100*(Índices!U21/Índices!U20-1),4)</f>
         <v>1.7461</v>
       </c>
       <c r="V21" s="15">
+        <f>ROUND(100*(Índices!V21/Índices!V20-1),4)</f>
         <v>1.8005</v>
       </c>
     </row>
@@ -10009,39 +10266,51 @@
         <v>4.1135000000000002</v>
       </c>
       <c r="K22" s="16">
+        <f>ROUND(100*(Índices!K22/Índices!K21-1),4)</f>
         <v>2.1745000000000001</v>
       </c>
       <c r="L22" s="16">
+        <f>ROUND(100*(Índices!L22/Índices!L21-1),4)</f>
         <v>1.944</v>
       </c>
       <c r="M22" s="16">
+        <f>ROUND(100*(Índices!M22/Índices!M21-1),4)</f>
         <v>-0.70469999999999999</v>
       </c>
       <c r="N22" s="16">
+        <f>ROUND(100*(Índices!N22/Índices!N21-1),4)</f>
         <v>2.3441999999999998</v>
       </c>
       <c r="O22" s="16">
+        <f>ROUND(100*(Índices!O22/Índices!O21-1),4)</f>
         <v>2.2029000000000001</v>
       </c>
       <c r="P22" s="16">
+        <f>ROUND(100*(Índices!P22/Índices!P21-1),4)</f>
         <v>1.9036999999999999</v>
       </c>
       <c r="Q22" s="16">
+        <f>ROUND(100*(Índices!Q22/Índices!Q21-1),4)</f>
         <v>4.4036</v>
       </c>
       <c r="R22" s="16">
+        <f>ROUND(100*(Índices!R22/Índices!R21-1),4)</f>
         <v>2.8159000000000001</v>
       </c>
       <c r="S22" s="16">
+        <f>ROUND(100*(Índices!S22/Índices!S21-1),4)</f>
         <v>1.7507999999999999</v>
       </c>
       <c r="T22" s="16">
+        <f>ROUND(100*(Índices!T22/Índices!T21-1),4)</f>
         <v>2.4327000000000001</v>
       </c>
       <c r="U22" s="17">
+        <f>ROUND(100*(Índices!U22/Índices!U21-1),4)</f>
         <v>2.0406</v>
       </c>
       <c r="V22" s="15">
+        <f>ROUND(100*(Índices!V22/Índices!V21-1),4)</f>
         <v>3.0171999999999999</v>
       </c>
     </row>
@@ -10082,39 +10351,51 @@
         <v>5.5880999999999998</v>
       </c>
       <c r="K23" s="16">
+        <f>ROUND(100*(Índices!K23/Índices!K22-1),4)</f>
         <v>1.1275999999999999</v>
       </c>
       <c r="L23" s="16">
+        <f>ROUND(100*(Índices!L23/Índices!L22-1),4)</f>
         <v>1.9531000000000001</v>
       </c>
       <c r="M23" s="16">
+        <f>ROUND(100*(Índices!M23/Índices!M22-1),4)</f>
         <v>2.597</v>
       </c>
       <c r="N23" s="16">
+        <f>ROUND(100*(Índices!N23/Índices!N22-1),4)</f>
         <v>3.7944</v>
       </c>
       <c r="O23" s="16">
+        <f>ROUND(100*(Índices!O23/Índices!O22-1),4)</f>
         <v>4.2937000000000003</v>
       </c>
       <c r="P23" s="16">
+        <f>ROUND(100*(Índices!P23/Índices!P22-1),4)</f>
         <v>5.9219999999999997</v>
       </c>
       <c r="Q23" s="16">
+        <f>ROUND(100*(Índices!Q23/Índices!Q22-1),4)</f>
         <v>0.38090000000000002</v>
       </c>
       <c r="R23" s="16">
+        <f>ROUND(100*(Índices!R23/Índices!R22-1),4)</f>
         <v>3.1398999999999999</v>
       </c>
       <c r="S23" s="16">
+        <f>ROUND(100*(Índices!S23/Índices!S22-1),4)</f>
         <v>2.4981</v>
       </c>
       <c r="T23" s="16">
+        <f>ROUND(100*(Índices!T23/Índices!T22-1),4)</f>
         <v>2.6791</v>
       </c>
       <c r="U23" s="17">
+        <f>ROUND(100*(Índices!U23/Índices!U22-1),4)</f>
         <v>3.1593</v>
       </c>
       <c r="V23" s="15">
+        <f>ROUND(100*(Índices!V23/Índices!V22-1),4)</f>
         <v>3.8776999999999999</v>
       </c>
     </row>
@@ -10155,39 +10436,51 @@
         <v>4.5726000000000004</v>
       </c>
       <c r="K24" s="16">
+        <f>ROUND(100*(Índices!K24/Índices!K23-1),4)</f>
         <v>2.8414000000000001</v>
       </c>
       <c r="L24" s="16">
+        <f>ROUND(100*(Índices!L24/Índices!L23-1),4)</f>
         <v>1.9656</v>
       </c>
       <c r="M24" s="16">
+        <f>ROUND(100*(Índices!M24/Índices!M23-1),4)</f>
         <v>1.0508</v>
       </c>
       <c r="N24" s="16">
+        <f>ROUND(100*(Índices!N24/Índices!N23-1),4)</f>
         <v>3.6059000000000001</v>
       </c>
       <c r="O24" s="16">
+        <f>ROUND(100*(Índices!O24/Índices!O23-1),4)</f>
         <v>2.8176000000000001</v>
       </c>
       <c r="P24" s="16">
+        <f>ROUND(100*(Índices!P24/Índices!P23-1),4)</f>
         <v>5.2266000000000004</v>
       </c>
       <c r="Q24" s="16">
+        <f>ROUND(100*(Índices!Q24/Índices!Q23-1),4)</f>
         <v>1.3478000000000001</v>
       </c>
       <c r="R24" s="16">
+        <f>ROUND(100*(Índices!R24/Índices!R23-1),4)</f>
         <v>4.3064</v>
       </c>
       <c r="S24" s="16">
+        <f>ROUND(100*(Índices!S24/Índices!S23-1),4)</f>
         <v>2.722</v>
       </c>
       <c r="T24" s="16">
+        <f>ROUND(100*(Índices!T24/Índices!T23-1),4)</f>
         <v>2.8081999999999998</v>
       </c>
       <c r="U24" s="17">
+        <f>ROUND(100*(Índices!U24/Índices!U23-1),4)</f>
         <v>3.9670999999999998</v>
       </c>
       <c r="V24" s="15">
+        <f>ROUND(100*(Índices!V24/Índices!V23-1),4)</f>
         <v>3.7290000000000001</v>
       </c>
     </row>
@@ -10228,39 +10521,51 @@
         <v>3.7928999999999999</v>
       </c>
       <c r="K25" s="16">
+        <f>ROUND(100*(Índices!K25/Índices!K24-1),4)</f>
         <v>1.7895000000000001</v>
       </c>
       <c r="L25" s="16">
+        <f>ROUND(100*(Índices!L25/Índices!L24-1),4)</f>
         <v>0.92759999999999998</v>
       </c>
       <c r="M25" s="16">
+        <f>ROUND(100*(Índices!M25/Índices!M24-1),4)</f>
         <v>6.0419999999999998</v>
       </c>
       <c r="N25" s="16">
+        <f>ROUND(100*(Índices!N25/Índices!N24-1),4)</f>
         <v>2.8460999999999999</v>
       </c>
       <c r="O25" s="16">
+        <f>ROUND(100*(Índices!O25/Índices!O24-1),4)</f>
         <v>4.0486000000000004</v>
       </c>
       <c r="P25" s="16">
+        <f>ROUND(100*(Índices!P25/Índices!P24-1),4)</f>
         <v>4.0677000000000003</v>
       </c>
       <c r="Q25" s="16">
+        <f>ROUND(100*(Índices!Q25/Índices!Q24-1),4)</f>
         <v>12.759</v>
       </c>
       <c r="R25" s="16">
+        <f>ROUND(100*(Índices!R25/Índices!R24-1),4)</f>
         <v>3.3771</v>
       </c>
       <c r="S25" s="16">
+        <f>ROUND(100*(Índices!S25/Índices!S24-1),4)</f>
         <v>2.3090000000000002</v>
       </c>
       <c r="T25" s="16">
+        <f>ROUND(100*(Índices!T25/Índices!T24-1),4)</f>
         <v>2.4628000000000001</v>
       </c>
       <c r="U25" s="17">
+        <f>ROUND(100*(Índices!U25/Índices!U24-1),4)</f>
         <v>4.7674000000000003</v>
       </c>
       <c r="V25" s="15">
+        <f>ROUND(100*(Índices!V25/Índices!V24-1),4)</f>
         <v>3.0457000000000001</v>
       </c>
     </row>
@@ -10301,39 +10606,51 @@
         <v>6.2320000000000002</v>
       </c>
       <c r="K26" s="16">
+        <f>ROUND(100*(Índices!K26/Índices!K25-1),4)</f>
         <v>2.7075</v>
       </c>
       <c r="L26" s="16">
+        <f>ROUND(100*(Índices!L26/Índices!L25-1),4)</f>
         <v>5.7488000000000001</v>
       </c>
       <c r="M26" s="16">
+        <f>ROUND(100*(Índices!M26/Índices!M25-1),4)</f>
         <v>2.3679999999999999</v>
       </c>
       <c r="N26" s="16">
+        <f>ROUND(100*(Índices!N26/Índices!N25-1),4)</f>
         <v>8.9994999999999994</v>
       </c>
       <c r="O26" s="16">
+        <f>ROUND(100*(Índices!O26/Índices!O25-1),4)</f>
         <v>4.4828999999999999</v>
       </c>
       <c r="P26" s="16">
+        <f>ROUND(100*(Índices!P26/Índices!P25-1),4)</f>
         <v>10.4033</v>
       </c>
       <c r="Q26" s="16">
+        <f>ROUND(100*(Índices!Q26/Índices!Q25-1),4)</f>
         <v>2.1206</v>
       </c>
       <c r="R26" s="16">
+        <f>ROUND(100*(Índices!R26/Índices!R25-1),4)</f>
         <v>5.7655000000000003</v>
       </c>
       <c r="S26" s="16">
+        <f>ROUND(100*(Índices!S26/Índices!S25-1),4)</f>
         <v>2.6518000000000002</v>
       </c>
       <c r="T26" s="16">
+        <f>ROUND(100*(Índices!T26/Índices!T25-1),4)</f>
         <v>5.7714999999999996</v>
       </c>
       <c r="U26" s="17">
+        <f>ROUND(100*(Índices!U26/Índices!U25-1),4)</f>
         <v>7.8433000000000002</v>
       </c>
       <c r="V26" s="15">
+        <f>ROUND(100*(Índices!V26/Índices!V25-1),4)</f>
         <v>6.2069000000000001</v>
       </c>
     </row>
@@ -10374,39 +10691,51 @@
         <v>5.1913999999999998</v>
       </c>
       <c r="K27" s="16">
+        <f>ROUND(100*(Índices!K27/Índices!K26-1),4)</f>
         <v>2.1421999999999999</v>
       </c>
       <c r="L27" s="16">
+        <f>ROUND(100*(Índices!L27/Índices!L26-1),4)</f>
         <v>3.9043999999999999</v>
       </c>
       <c r="M27" s="16">
+        <f>ROUND(100*(Índices!M27/Índices!M26-1),4)</f>
         <v>8.8673000000000002</v>
       </c>
       <c r="N27" s="16">
+        <f>ROUND(100*(Índices!N27/Índices!N26-1),4)</f>
         <v>3.9437000000000002</v>
       </c>
       <c r="O27" s="16">
+        <f>ROUND(100*(Índices!O27/Índices!O26-1),4)</f>
         <v>5.4348999999999998</v>
       </c>
       <c r="P27" s="16">
+        <f>ROUND(100*(Índices!P27/Índices!P26-1),4)</f>
         <v>7.6317000000000004</v>
       </c>
       <c r="Q27" s="16">
+        <f>ROUND(100*(Índices!Q27/Índices!Q26-1),4)</f>
         <v>0.66639999999999999</v>
       </c>
       <c r="R27" s="16">
+        <f>ROUND(100*(Índices!R27/Índices!R26-1),4)</f>
         <v>2.8984999999999999</v>
       </c>
       <c r="S27" s="16">
+        <f>ROUND(100*(Índices!S27/Índices!S26-1),4)</f>
         <v>2.7717999999999998</v>
       </c>
       <c r="T27" s="16">
+        <f>ROUND(100*(Índices!T27/Índices!T26-1),4)</f>
         <v>3.1259000000000001</v>
       </c>
       <c r="U27" s="17">
+        <f>ROUND(100*(Índices!U27/Índices!U26-1),4)</f>
         <v>6.1673999999999998</v>
       </c>
       <c r="V27" s="15">
+        <f>ROUND(100*(Índices!V27/Índices!V26-1),4)</f>
         <v>4.2497999999999996</v>
       </c>
     </row>
@@ -10447,39 +10776,51 @@
         <v>4.1722000000000001</v>
       </c>
       <c r="K28" s="16">
+        <f>ROUND(100*(Índices!K28/Índices!K27-1),4)</f>
         <v>4.0412999999999997</v>
       </c>
       <c r="L28" s="16">
+        <f>ROUND(100*(Índices!L28/Índices!L27-1),4)</f>
         <v>2.6147</v>
       </c>
       <c r="M28" s="16">
+        <f>ROUND(100*(Índices!M28/Índices!M27-1),4)</f>
         <v>2.1839</v>
       </c>
       <c r="N28" s="16">
+        <f>ROUND(100*(Índices!N28/Índices!N27-1),4)</f>
         <v>3.7765</v>
       </c>
       <c r="O28" s="16">
+        <f>ROUND(100*(Índices!O28/Índices!O27-1),4)</f>
         <v>5.6817000000000002</v>
       </c>
       <c r="P28" s="16">
+        <f>ROUND(100*(Índices!P28/Índices!P27-1),4)</f>
         <v>2.6642000000000001</v>
       </c>
       <c r="Q28" s="16">
+        <f>ROUND(100*(Índices!Q28/Índices!Q27-1),4)</f>
         <v>3.1354000000000002</v>
       </c>
       <c r="R28" s="16">
+        <f>ROUND(100*(Índices!R28/Índices!R27-1),4)</f>
         <v>3.0712999999999999</v>
       </c>
       <c r="S28" s="16">
+        <f>ROUND(100*(Índices!S28/Índices!S27-1),4)</f>
         <v>2.8401000000000001</v>
       </c>
       <c r="T28" s="16">
+        <f>ROUND(100*(Índices!T28/Índices!T27-1),4)</f>
         <v>2.6307</v>
       </c>
       <c r="U28" s="17">
+        <f>ROUND(100*(Índices!U28/Índices!U27-1),4)</f>
         <v>4.3593999999999999</v>
       </c>
       <c r="V28" s="15">
+        <f>ROUND(100*(Índices!V28/Índices!V27-1),4)</f>
         <v>3.6131000000000002</v>
       </c>
     </row>
@@ -10520,39 +10861,51 @@
         <v>2.2281</v>
       </c>
       <c r="K29" s="16">
+        <f>ROUND(100*(Índices!K29/Índices!K28-1),4)</f>
         <v>1.7428999999999999</v>
       </c>
       <c r="L29" s="16">
+        <f>ROUND(100*(Índices!L29/Índices!L28-1),4)</f>
         <v>2.5367000000000002</v>
       </c>
       <c r="M29" s="16">
+        <f>ROUND(100*(Índices!M29/Índices!M28-1),4)</f>
         <v>2.9171</v>
       </c>
       <c r="N29" s="16">
+        <f>ROUND(100*(Índices!N29/Índices!N28-1),4)</f>
         <v>2.2403</v>
       </c>
       <c r="O29" s="16">
+        <f>ROUND(100*(Índices!O29/Índices!O28-1),4)</f>
         <v>5.2541000000000002</v>
       </c>
       <c r="P29" s="16">
+        <f>ROUND(100*(Índices!P29/Índices!P28-1),4)</f>
         <v>2.3797999999999999</v>
       </c>
       <c r="Q29" s="16">
+        <f>ROUND(100*(Índices!Q29/Índices!Q28-1),4)</f>
         <v>6.6726999999999999</v>
       </c>
       <c r="R29" s="16">
+        <f>ROUND(100*(Índices!R29/Índices!R28-1),4)</f>
         <v>2.8138999999999998</v>
       </c>
       <c r="S29" s="16">
+        <f>ROUND(100*(Índices!S29/Índices!S28-1),4)</f>
         <v>3.0204</v>
       </c>
       <c r="T29" s="16">
+        <f>ROUND(100*(Índices!T29/Índices!T28-1),4)</f>
         <v>2.6236000000000002</v>
       </c>
       <c r="U29" s="17">
+        <f>ROUND(100*(Índices!U29/Índices!U28-1),4)</f>
         <v>3.4365000000000001</v>
       </c>
       <c r="V29" s="15">
+        <f>ROUND(100*(Índices!V29/Índices!V28-1),4)</f>
         <v>2.423</v>
       </c>
     </row>
@@ -10593,39 +10946,51 @@
         <v>2.9780000000000002</v>
       </c>
       <c r="K30" s="16">
+        <f>ROUND(100*(Índices!K30/Índices!K29-1),4)</f>
         <v>3.1905999999999999</v>
       </c>
       <c r="L30" s="16">
+        <f>ROUND(100*(Índices!L30/Índices!L29-1),4)</f>
         <v>2.3508</v>
       </c>
       <c r="M30" s="16">
+        <f>ROUND(100*(Índices!M30/Índices!M29-1),4)</f>
         <v>3.1783000000000001</v>
       </c>
       <c r="N30" s="16">
+        <f>ROUND(100*(Índices!N30/Índices!N29-1),4)</f>
         <v>3.3378000000000001</v>
       </c>
       <c r="O30" s="16">
+        <f>ROUND(100*(Índices!O30/Índices!O29-1),4)</f>
         <v>2.9489999999999998</v>
       </c>
       <c r="P30" s="16">
+        <f>ROUND(100*(Índices!P30/Índices!P29-1),4)</f>
         <v>2.4487999999999999</v>
       </c>
       <c r="Q30" s="16">
+        <f>ROUND(100*(Índices!Q30/Índices!Q29-1),4)</f>
         <v>6.5342000000000002</v>
       </c>
       <c r="R30" s="16">
+        <f>ROUND(100*(Índices!R30/Índices!R29-1),4)</f>
         <v>2.9297</v>
       </c>
       <c r="S30" s="16">
+        <f>ROUND(100*(Índices!S30/Índices!S29-1),4)</f>
         <v>2.7490999999999999</v>
       </c>
       <c r="T30" s="16">
+        <f>ROUND(100*(Índices!T30/Índices!T29-1),4)</f>
         <v>3.6095999999999999</v>
       </c>
       <c r="U30" s="17">
+        <f>ROUND(100*(Índices!U30/Índices!U29-1),4)</f>
         <v>3.6778</v>
       </c>
       <c r="V30" s="15">
+        <f>ROUND(100*(Índices!V30/Índices!V29-1),4)</f>
         <v>3.0381</v>
       </c>
     </row>
@@ -10666,39 +11031,51 @@
         <v>5.2058999999999997</v>
       </c>
       <c r="K31" s="16">
+        <f>ROUND(100*(Índices!K31/Índices!K30-1),4)</f>
         <v>2.9113000000000002</v>
       </c>
       <c r="L31" s="16">
+        <f>ROUND(100*(Índices!L31/Índices!L30-1),4)</f>
         <v>3.097</v>
       </c>
       <c r="M31" s="16">
+        <f>ROUND(100*(Índices!M31/Índices!M30-1),4)</f>
         <v>6.3657000000000004</v>
       </c>
       <c r="N31" s="16">
+        <f>ROUND(100*(Índices!N31/Índices!N30-1),4)</f>
         <v>3.1572</v>
       </c>
       <c r="O31" s="16">
+        <f>ROUND(100*(Índices!O31/Índices!O30-1),4)</f>
         <v>3.1886000000000001</v>
       </c>
       <c r="P31" s="16">
+        <f>ROUND(100*(Índices!P31/Índices!P30-1),4)</f>
         <v>2.1696</v>
       </c>
       <c r="Q31" s="16">
+        <f>ROUND(100*(Índices!Q31/Índices!Q30-1),4)</f>
         <v>0.90049999999999997</v>
       </c>
       <c r="R31" s="16">
+        <f>ROUND(100*(Índices!R31/Índices!R30-1),4)</f>
         <v>3.0922000000000001</v>
       </c>
       <c r="S31" s="16">
+        <f>ROUND(100*(Índices!S31/Índices!S30-1),4)</f>
         <v>2.8429000000000002</v>
       </c>
       <c r="T31" s="16">
+        <f>ROUND(100*(Índices!T31/Índices!T30-1),4)</f>
         <v>3.6137999999999999</v>
       </c>
       <c r="U31" s="17">
+        <f>ROUND(100*(Índices!U31/Índices!U30-1),4)</f>
         <v>3.1339000000000001</v>
       </c>
       <c r="V31" s="15">
+        <f>ROUND(100*(Índices!V31/Índices!V30-1),4)</f>
         <v>4.0686999999999998</v>
       </c>
     </row>
@@ -10739,39 +11116,51 @@
         <v>5.0096999999999996</v>
       </c>
       <c r="K32" s="16">
+        <f>ROUND(100*(Índices!K32/Índices!K31-1),4)</f>
         <v>3.5488</v>
       </c>
       <c r="L32" s="16">
+        <f>ROUND(100*(Índices!L32/Índices!L31-1),4)</f>
         <v>3.7799</v>
       </c>
       <c r="M32" s="16">
+        <f>ROUND(100*(Índices!M32/Índices!M31-1),4)</f>
         <v>2.7755000000000001</v>
       </c>
       <c r="N32" s="16">
+        <f>ROUND(100*(Índices!N32/Índices!N31-1),4)</f>
         <v>3.8338999999999999</v>
       </c>
       <c r="O32" s="16">
+        <f>ROUND(100*(Índices!O32/Índices!O31-1),4)</f>
         <v>3.2795000000000001</v>
       </c>
       <c r="P32" s="16">
+        <f>ROUND(100*(Índices!P32/Índices!P31-1),4)</f>
         <v>4.1666999999999996</v>
       </c>
       <c r="Q32" s="16">
+        <f>ROUND(100*(Índices!Q32/Índices!Q31-1),4)</f>
         <v>4.3867000000000003</v>
       </c>
       <c r="R32" s="16">
+        <f>ROUND(100*(Índices!R32/Índices!R31-1),4)</f>
         <v>2.5230000000000001</v>
       </c>
       <c r="S32" s="16">
+        <f>ROUND(100*(Índices!S32/Índices!S31-1),4)</f>
         <v>2.9028999999999998</v>
       </c>
       <c r="T32" s="16">
+        <f>ROUND(100*(Índices!T32/Índices!T31-1),4)</f>
         <v>4.3304</v>
       </c>
       <c r="U32" s="17">
+        <f>ROUND(100*(Índices!U32/Índices!U31-1),4)</f>
         <v>3.1204999999999998</v>
       </c>
       <c r="V32" s="15">
+        <f>ROUND(100*(Índices!V32/Índices!V31-1),4)</f>
         <v>4.1976000000000004</v>
       </c>
     </row>
@@ -10812,39 +11201,51 @@
         <v>2.8319999999999999</v>
       </c>
       <c r="K33" s="16">
+        <f>ROUND(100*(Índices!K33/Índices!K32-1),4)</f>
         <v>1.9020999999999999</v>
       </c>
       <c r="L33" s="16">
+        <f>ROUND(100*(Índices!L33/Índices!L32-1),4)</f>
         <v>4.1275000000000004</v>
       </c>
       <c r="M33" s="16">
+        <f>ROUND(100*(Índices!M33/Índices!M32-1),4)</f>
         <v>2.9188999999999998</v>
       </c>
       <c r="N33" s="16">
+        <f>ROUND(100*(Índices!N33/Índices!N32-1),4)</f>
         <v>4.8997000000000002</v>
       </c>
       <c r="O33" s="16">
+        <f>ROUND(100*(Índices!O33/Índices!O32-1),4)</f>
         <v>3.5154000000000001</v>
       </c>
       <c r="P33" s="16">
+        <f>ROUND(100*(Índices!P33/Índices!P32-1),4)</f>
         <v>4.3741000000000003</v>
       </c>
       <c r="Q33" s="16">
+        <f>ROUND(100*(Índices!Q33/Índices!Q32-1),4)</f>
         <v>3.8908999999999998</v>
       </c>
       <c r="R33" s="16">
+        <f>ROUND(100*(Índices!R33/Índices!R32-1),4)</f>
         <v>3.2827999999999999</v>
       </c>
       <c r="S33" s="16">
+        <f>ROUND(100*(Índices!S33/Índices!S32-1),4)</f>
         <v>2.9965000000000002</v>
       </c>
       <c r="T33" s="16">
+        <f>ROUND(100*(Índices!T33/Índices!T32-1),4)</f>
         <v>4.0696000000000003</v>
       </c>
       <c r="U33" s="17">
+        <f>ROUND(100*(Índices!U33/Índices!U32-1),4)</f>
         <v>3.0314000000000001</v>
       </c>
       <c r="V33" s="15">
+        <f>ROUND(100*(Índices!V33/Índices!V32-1),4)</f>
         <v>3.3864999999999998</v>
       </c>
     </row>
@@ -10885,39 +11286,51 @@
         <v>3.2585000000000002</v>
       </c>
       <c r="K34" s="16">
+        <f>ROUND(100*(Índices!K34/Índices!K33-1),4)</f>
         <v>2.7309999999999999</v>
       </c>
       <c r="L34" s="16">
+        <f>ROUND(100*(Índices!L34/Índices!L33-1),4)</f>
         <v>3.5198</v>
       </c>
       <c r="M34" s="16">
+        <f>ROUND(100*(Índices!M34/Índices!M33-1),4)</f>
         <v>4</v>
       </c>
       <c r="N34" s="16">
+        <f>ROUND(100*(Índices!N34/Índices!N33-1),4)</f>
         <v>3.3730000000000002</v>
       </c>
       <c r="O34" s="16">
+        <f>ROUND(100*(Índices!O34/Índices!O33-1),4)</f>
         <v>5.0635000000000003</v>
       </c>
       <c r="P34" s="16">
+        <f>ROUND(100*(Índices!P34/Índices!P33-1),4)</f>
         <v>3.5078</v>
       </c>
       <c r="Q34" s="16">
+        <f>ROUND(100*(Índices!Q34/Índices!Q33-1),4)</f>
         <v>2.4197000000000002</v>
       </c>
       <c r="R34" s="16">
+        <f>ROUND(100*(Índices!R34/Índices!R33-1),4)</f>
         <v>2.6149</v>
       </c>
       <c r="S34" s="16">
+        <f>ROUND(100*(Índices!S34/Índices!S33-1),4)</f>
         <v>4.1947000000000001</v>
       </c>
       <c r="T34" s="16">
+        <f>ROUND(100*(Índices!T34/Índices!T33-1),4)</f>
         <v>2.2440000000000002</v>
       </c>
       <c r="U34" s="17">
+        <f>ROUND(100*(Índices!U34/Índices!U33-1),4)</f>
         <v>2.8679999999999999</v>
       </c>
       <c r="V34" s="15">
+        <f>ROUND(100*(Índices!V34/Índices!V33-1),4)</f>
         <v>3.0464000000000002</v>
       </c>
     </row>
@@ -10958,39 +11371,51 @@
         <v>3.0324</v>
       </c>
       <c r="K35" s="16">
+        <f>ROUND(100*(Índices!K35/Índices!K34-1),4)</f>
         <v>2.8738000000000001</v>
       </c>
       <c r="L35" s="16">
+        <f>ROUND(100*(Índices!L35/Índices!L34-1),4)</f>
         <v>1.8683000000000001</v>
       </c>
       <c r="M35" s="16">
+        <f>ROUND(100*(Índices!M35/Índices!M34-1),4)</f>
         <v>2.7084999999999999</v>
       </c>
       <c r="N35" s="16">
+        <f>ROUND(100*(Índices!N35/Índices!N34-1),4)</f>
         <v>3.1353</v>
       </c>
       <c r="O35" s="16">
+        <f>ROUND(100*(Índices!O35/Índices!O34-1),4)</f>
         <v>3.5640999999999998</v>
       </c>
       <c r="P35" s="16">
+        <f>ROUND(100*(Índices!P35/Índices!P34-1),4)</f>
         <v>1.5529999999999999</v>
       </c>
       <c r="Q35" s="16">
+        <f>ROUND(100*(Índices!Q35/Índices!Q34-1),4)</f>
         <v>7.1497000000000002</v>
       </c>
       <c r="R35" s="16">
+        <f>ROUND(100*(Índices!R35/Índices!R34-1),4)</f>
         <v>3.5379</v>
       </c>
       <c r="S35" s="16">
+        <f>ROUND(100*(Índices!S35/Índices!S34-1),4)</f>
         <v>3.1695000000000002</v>
       </c>
       <c r="T35" s="16">
+        <f>ROUND(100*(Índices!T35/Índices!T34-1),4)</f>
         <v>2.5442</v>
       </c>
       <c r="U35" s="17">
+        <f>ROUND(100*(Índices!U35/Índices!U34-1),4)</f>
         <v>2.0996999999999999</v>
       </c>
       <c r="V35" s="15">
+        <f>ROUND(100*(Índices!V35/Índices!V34-1),4)</f>
         <v>2.8068</v>
       </c>
     </row>
@@ -11031,39 +11456,51 @@
         <v>2.8140000000000001</v>
       </c>
       <c r="K36" s="16">
+        <f>ROUND(100*(Índices!K36/Índices!K35-1),4)</f>
         <v>1.1634</v>
       </c>
       <c r="L36" s="16">
+        <f>ROUND(100*(Índices!L36/Índices!L35-1),4)</f>
         <v>2.3647999999999998</v>
       </c>
       <c r="M36" s="16">
+        <f>ROUND(100*(Índices!M36/Índices!M35-1),4)</f>
         <v>2.1815000000000002</v>
       </c>
       <c r="N36" s="16">
+        <f>ROUND(100*(Índices!N36/Índices!N35-1),4)</f>
         <v>1.9109</v>
       </c>
       <c r="O36" s="16">
+        <f>ROUND(100*(Índices!O36/Índices!O35-1),4)</f>
         <v>4.1151999999999997</v>
       </c>
       <c r="P36" s="16">
+        <f>ROUND(100*(Índices!P36/Índices!P35-1),4)</f>
         <v>1.1693</v>
       </c>
       <c r="Q36" s="16">
+        <f>ROUND(100*(Índices!Q36/Índices!Q35-1),4)</f>
         <v>0.83250000000000002</v>
       </c>
       <c r="R36" s="16">
+        <f>ROUND(100*(Índices!R36/Índices!R35-1),4)</f>
         <v>3.1495000000000002</v>
       </c>
       <c r="S36" s="16">
+        <f>ROUND(100*(Índices!S36/Índices!S35-1),4)</f>
         <v>2.8601999999999999</v>
       </c>
       <c r="T36" s="16">
+        <f>ROUND(100*(Índices!T36/Índices!T35-1),4)</f>
         <v>2.9062000000000001</v>
       </c>
       <c r="U36" s="17">
+        <f>ROUND(100*(Índices!U36/Índices!U35-1),4)</f>
         <v>2.7121</v>
       </c>
       <c r="V36" s="15">
+        <f>ROUND(100*(Índices!V36/Índices!V35-1),4)</f>
         <v>2.6156000000000001</v>
       </c>
     </row>
@@ -11104,39 +11541,51 @@
         <v>4.3106999999999998</v>
       </c>
       <c r="K37" s="16">
+        <f>ROUND(100*(Índices!K37/Índices!K36-1),4)</f>
         <v>4.7382</v>
       </c>
       <c r="L37" s="16">
+        <f>ROUND(100*(Índices!L37/Índices!L36-1),4)</f>
         <v>3.4828999999999999</v>
       </c>
       <c r="M37" s="16">
+        <f>ROUND(100*(Índices!M37/Índices!M36-1),4)</f>
         <v>2.1528</v>
       </c>
       <c r="N37" s="16">
+        <f>ROUND(100*(Índices!N37/Índices!N36-1),4)</f>
         <v>5.7979000000000003</v>
       </c>
       <c r="O37" s="16">
+        <f>ROUND(100*(Índices!O37/Índices!O36-1),4)</f>
         <v>5.1767000000000003</v>
       </c>
       <c r="P37" s="16">
+        <f>ROUND(100*(Índices!P37/Índices!P36-1),4)</f>
         <v>3.9525000000000001</v>
       </c>
       <c r="Q37" s="16">
+        <f>ROUND(100*(Índices!Q37/Índices!Q36-1),4)</f>
         <v>1.5553999999999999</v>
       </c>
       <c r="R37" s="16">
+        <f>ROUND(100*(Índices!R37/Índices!R36-1),4)</f>
         <v>4.0955000000000004</v>
       </c>
       <c r="S37" s="16">
+        <f>ROUND(100*(Índices!S37/Índices!S36-1),4)</f>
         <v>2.8633000000000002</v>
       </c>
       <c r="T37" s="16">
+        <f>ROUND(100*(Índices!T37/Índices!T36-1),4)</f>
         <v>3.6257000000000001</v>
       </c>
       <c r="U37" s="17">
+        <f>ROUND(100*(Índices!U37/Índices!U36-1),4)</f>
         <v>4.2965</v>
       </c>
       <c r="V37" s="15">
+        <f>ROUND(100*(Índices!V37/Índices!V36-1),4)</f>
         <v>4.2591999999999999</v>
       </c>
     </row>
@@ -11177,39 +11626,51 @@
         <v>4.9607000000000001</v>
       </c>
       <c r="K38" s="16">
+        <f>ROUND(100*(Índices!K38/Índices!K37-1),4)</f>
         <v>3.9011</v>
       </c>
       <c r="L38" s="16">
+        <f>ROUND(100*(Índices!L38/Índices!L37-1),4)</f>
         <v>5.8593999999999999</v>
       </c>
       <c r="M38" s="16">
+        <f>ROUND(100*(Índices!M38/Índices!M37-1),4)</f>
         <v>2.0114999999999998</v>
       </c>
       <c r="N38" s="16">
+        <f>ROUND(100*(Índices!N38/Índices!N37-1),4)</f>
         <v>6.7221000000000002</v>
       </c>
       <c r="O38" s="16">
+        <f>ROUND(100*(Índices!O38/Índices!O37-1),4)</f>
         <v>8.3053000000000008</v>
       </c>
       <c r="P38" s="16">
+        <f>ROUND(100*(Índices!P38/Índices!P37-1),4)</f>
         <v>4.7183000000000002</v>
       </c>
       <c r="Q38" s="16">
+        <f>ROUND(100*(Índices!Q38/Índices!Q37-1),4)</f>
         <v>6.7811000000000003</v>
       </c>
       <c r="R38" s="16">
+        <f>ROUND(100*(Índices!R38/Índices!R37-1),4)</f>
         <v>6.7510000000000003</v>
       </c>
       <c r="S38" s="16">
+        <f>ROUND(100*(Índices!S38/Índices!S37-1),4)</f>
         <v>2.2890000000000001</v>
       </c>
       <c r="T38" s="16">
+        <f>ROUND(100*(Índices!T38/Índices!T37-1),4)</f>
         <v>5.2911999999999999</v>
       </c>
       <c r="U38" s="17">
+        <f>ROUND(100*(Índices!U38/Índices!U37-1),4)</f>
         <v>8.1389999999999993</v>
       </c>
       <c r="V38" s="15">
+        <f>ROUND(100*(Índices!V38/Índices!V37-1),4)</f>
         <v>5.6048999999999998</v>
       </c>
     </row>
@@ -11250,39 +11711,51 @@
         <v>1.7974000000000001</v>
       </c>
       <c r="K39" s="16">
+        <f>ROUND(100*(Índices!K39/Índices!K38-1),4)</f>
         <v>6.0880000000000001</v>
       </c>
       <c r="L39" s="16">
+        <f>ROUND(100*(Índices!L39/Índices!L38-1),4)</f>
         <v>3.6206999999999998</v>
       </c>
       <c r="M39" s="16">
+        <f>ROUND(100*(Índices!M39/Índices!M38-1),4)</f>
         <v>1.8798999999999999</v>
       </c>
       <c r="N39" s="16">
+        <f>ROUND(100*(Índices!N39/Índices!N38-1),4)</f>
         <v>7.8771000000000004</v>
       </c>
       <c r="O39" s="16">
+        <f>ROUND(100*(Índices!O39/Índices!O38-1),4)</f>
         <v>4.6462000000000003</v>
       </c>
       <c r="P39" s="16">
+        <f>ROUND(100*(Índices!P39/Índices!P38-1),4)</f>
         <v>3.5344000000000002</v>
       </c>
       <c r="Q39" s="16">
+        <f>ROUND(100*(Índices!Q39/Índices!Q38-1),4)</f>
         <v>0.31890000000000002</v>
       </c>
       <c r="R39" s="16">
+        <f>ROUND(100*(Índices!R39/Índices!R38-1),4)</f>
         <v>2.0129999999999999</v>
       </c>
       <c r="S39" s="16">
+        <f>ROUND(100*(Índices!S39/Índices!S38-1),4)</f>
         <v>2.3412999999999999</v>
       </c>
       <c r="T39" s="16">
+        <f>ROUND(100*(Índices!T39/Índices!T38-1),4)</f>
         <v>2.5901999999999998</v>
       </c>
       <c r="U39" s="17">
+        <f>ROUND(100*(Índices!U39/Índices!U38-1),4)</f>
         <v>3.7923</v>
       </c>
       <c r="V39" s="15">
+        <f>ROUND(100*(Índices!V39/Índices!V38-1),4)</f>
         <v>3.0691999999999999</v>
       </c>
     </row>
@@ -11323,39 +11796,51 @@
         <v>6.1368</v>
       </c>
       <c r="K40" s="16">
+        <f>ROUND(100*(Índices!K40/Índices!K39-1),4)</f>
         <v>5.0702999999999996</v>
       </c>
       <c r="L40" s="16">
+        <f>ROUND(100*(Índices!L40/Índices!L39-1),4)</f>
         <v>4.9109999999999996</v>
       </c>
       <c r="M40" s="16">
+        <f>ROUND(100*(Índices!M40/Índices!M39-1),4)</f>
         <v>1.5163</v>
       </c>
       <c r="N40" s="16">
+        <f>ROUND(100*(Índices!N40/Índices!N39-1),4)</f>
         <v>0.81630000000000003</v>
       </c>
       <c r="O40" s="16">
+        <f>ROUND(100*(Índices!O40/Índices!O39-1),4)</f>
         <v>6.3221999999999996</v>
       </c>
       <c r="P40" s="16">
+        <f>ROUND(100*(Índices!P40/Índices!P39-1),4)</f>
         <v>4.6132</v>
       </c>
       <c r="Q40" s="16">
+        <f>ROUND(100*(Índices!Q40/Índices!Q39-1),4)</f>
         <v>7.3895999999999997</v>
       </c>
       <c r="R40" s="16">
+        <f>ROUND(100*(Índices!R40/Índices!R39-1),4)</f>
         <v>3.6429</v>
       </c>
       <c r="S40" s="16">
+        <f>ROUND(100*(Índices!S40/Índices!S39-1),4)</f>
         <v>6.2328999999999999</v>
       </c>
       <c r="T40" s="16">
+        <f>ROUND(100*(Índices!T40/Índices!T39-1),4)</f>
         <v>3.3515999999999999</v>
       </c>
       <c r="U40" s="17">
+        <f>ROUND(100*(Índices!U40/Índices!U39-1),4)</f>
         <v>4.843</v>
       </c>
       <c r="V40" s="15">
+        <f>ROUND(100*(Índices!V40/Índices!V39-1),4)</f>
         <v>4.6287000000000003</v>
       </c>
     </row>
@@ -11396,39 +11881,51 @@
         <v>3.5411999999999999</v>
       </c>
       <c r="K41" s="16">
+        <f>ROUND(100*(Índices!K41/Índices!K40-1),4)</f>
         <v>3.2179000000000002</v>
       </c>
       <c r="L41" s="16">
+        <f>ROUND(100*(Índices!L41/Índices!L40-1),4)</f>
         <v>3.7381000000000002</v>
       </c>
       <c r="M41" s="16">
+        <f>ROUND(100*(Índices!M41/Índices!M40-1),4)</f>
         <v>2.0966999999999998</v>
       </c>
       <c r="N41" s="16">
+        <f>ROUND(100*(Índices!N41/Índices!N40-1),4)</f>
         <v>5.6877000000000004</v>
       </c>
       <c r="O41" s="16">
+        <f>ROUND(100*(Índices!O41/Índices!O40-1),4)</f>
         <v>5.5849000000000002</v>
       </c>
       <c r="P41" s="16">
+        <f>ROUND(100*(Índices!P41/Índices!P40-1),4)</f>
         <v>4.9908999999999999</v>
       </c>
       <c r="Q41" s="16">
+        <f>ROUND(100*(Índices!Q41/Índices!Q40-1),4)</f>
         <v>8.7028999999999996</v>
       </c>
       <c r="R41" s="16">
+        <f>ROUND(100*(Índices!R41/Índices!R40-1),4)</f>
         <v>2.5788000000000002</v>
       </c>
       <c r="S41" s="16">
+        <f>ROUND(100*(Índices!S41/Índices!S40-1),4)</f>
         <v>4.0552000000000001</v>
       </c>
       <c r="T41" s="16">
+        <f>ROUND(100*(Índices!T41/Índices!T40-1),4)</f>
         <v>3.2509999999999999</v>
       </c>
       <c r="U41" s="17">
+        <f>ROUND(100*(Índices!U41/Índices!U40-1),4)</f>
         <v>3.6254</v>
       </c>
       <c r="V41" s="15">
+        <f>ROUND(100*(Índices!V41/Índices!V40-1),4)</f>
         <v>3.6472000000000002</v>
       </c>
     </row>
@@ -11469,39 +11966,51 @@
         <v>3.4584000000000001</v>
       </c>
       <c r="K42" s="16">
+        <f>ROUND(100*(Índices!K42/Índices!K41-1),4)</f>
         <v>3.8525</v>
       </c>
       <c r="L42" s="16">
+        <f>ROUND(100*(Índices!L42/Índices!L41-1),4)</f>
         <v>4.0072999999999999</v>
       </c>
       <c r="M42" s="16">
+        <f>ROUND(100*(Índices!M42/Índices!M41-1),4)</f>
         <v>0.6956</v>
       </c>
       <c r="N42" s="16">
+        <f>ROUND(100*(Índices!N42/Índices!N41-1),4)</f>
         <v>-0.75880000000000003</v>
       </c>
       <c r="O42" s="16">
+        <f>ROUND(100*(Índices!O42/Índices!O41-1),4)</f>
         <v>-1.9449000000000001</v>
       </c>
       <c r="P42" s="16">
+        <f>ROUND(100*(Índices!P42/Índices!P41-1),4)</f>
         <v>1.4922</v>
       </c>
       <c r="Q42" s="16">
+        <f>ROUND(100*(Índices!Q42/Índices!Q41-1),4)</f>
         <v>-0.93300000000000005</v>
       </c>
       <c r="R42" s="16">
+        <f>ROUND(100*(Índices!R42/Índices!R41-1),4)</f>
         <v>5.3032000000000004</v>
       </c>
       <c r="S42" s="16">
+        <f>ROUND(100*(Índices!S42/Índices!S41-1),4)</f>
         <v>3.2151000000000001</v>
       </c>
       <c r="T42" s="16">
+        <f>ROUND(100*(Índices!T42/Índices!T41-1),4)</f>
         <v>4.0389999999999997</v>
       </c>
       <c r="U42" s="17">
+        <f>ROUND(100*(Índices!U42/Índices!U41-1),4)</f>
         <v>3.2002000000000002</v>
       </c>
       <c r="V42" s="15">
+        <f>ROUND(100*(Índices!V42/Índices!V41-1),4)</f>
         <v>3.3772000000000002</v>
       </c>
     </row>
@@ -11542,39 +12051,51 @@
         <v>1.3803000000000001</v>
       </c>
       <c r="K43" s="16">
+        <f>ROUND(100*(Índices!K43/Índices!K42-1),4)</f>
         <v>1.0265</v>
       </c>
       <c r="L43" s="16">
+        <f>ROUND(100*(Índices!L43/Índices!L42-1),4)</f>
         <v>4.1547999999999998</v>
       </c>
       <c r="M43" s="16">
+        <f>ROUND(100*(Índices!M43/Índices!M42-1),4)</f>
         <v>0.58679999999999999</v>
       </c>
       <c r="N43" s="16">
+        <f>ROUND(100*(Índices!N43/Índices!N42-1),4)</f>
         <v>2.077</v>
       </c>
       <c r="O43" s="16">
+        <f>ROUND(100*(Índices!O43/Índices!O42-1),4)</f>
         <v>0.44619999999999999</v>
       </c>
       <c r="P43" s="16">
+        <f>ROUND(100*(Índices!P43/Índices!P42-1),4)</f>
         <v>1.6323000000000001</v>
       </c>
       <c r="Q43" s="16">
+        <f>ROUND(100*(Índices!Q43/Índices!Q42-1),4)</f>
         <v>0.88039999999999996</v>
       </c>
       <c r="R43" s="16">
+        <f>ROUND(100*(Índices!R43/Índices!R42-1),4)</f>
         <v>2.1966999999999999</v>
       </c>
       <c r="S43" s="16">
+        <f>ROUND(100*(Índices!S43/Índices!S42-1),4)</f>
         <v>3.5998000000000001</v>
       </c>
       <c r="T43" s="16">
+        <f>ROUND(100*(Índices!T43/Índices!T42-1),4)</f>
         <v>3.0243000000000002</v>
       </c>
       <c r="U43" s="17">
+        <f>ROUND(100*(Índices!U43/Índices!U42-1),4)</f>
         <v>2.4417</v>
       </c>
       <c r="V43" s="15">
+        <f>ROUND(100*(Índices!V43/Índices!V42-1),4)</f>
         <v>2.1797</v>
       </c>
     </row>
@@ -11615,39 +12136,51 @@
         <v>2.6791</v>
       </c>
       <c r="K44" s="16">
+        <f>ROUND(100*(Índices!K44/Índices!K43-1),4)</f>
         <v>1.651</v>
       </c>
       <c r="L44" s="16">
+        <f>ROUND(100*(Índices!L44/Índices!L43-1),4)</f>
         <v>1.35</v>
       </c>
       <c r="M44" s="16">
+        <f>ROUND(100*(Índices!M44/Índices!M43-1),4)</f>
         <v>1.3425</v>
       </c>
       <c r="N44" s="16">
+        <f>ROUND(100*(Índices!N44/Índices!N43-1),4)</f>
         <v>2.8959999999999999</v>
       </c>
       <c r="O44" s="16">
+        <f>ROUND(100*(Índices!O44/Índices!O43-1),4)</f>
         <v>2.6600999999999999</v>
       </c>
       <c r="P44" s="16">
+        <f>ROUND(100*(Índices!P44/Índices!P43-1),4)</f>
         <v>1.6072</v>
       </c>
       <c r="Q44" s="16">
+        <f>ROUND(100*(Índices!Q44/Índices!Q43-1),4)</f>
         <v>8.4859000000000009</v>
       </c>
       <c r="R44" s="16">
+        <f>ROUND(100*(Índices!R44/Índices!R43-1),4)</f>
         <v>2.4961000000000002</v>
       </c>
       <c r="S44" s="16">
+        <f>ROUND(100*(Índices!S44/Índices!S43-1),4)</f>
         <v>0.1265</v>
       </c>
       <c r="T44" s="16">
+        <f>ROUND(100*(Índices!T44/Índices!T43-1),4)</f>
         <v>2.1160999999999999</v>
       </c>
       <c r="U44" s="17">
+        <f>ROUND(100*(Índices!U44/Índices!U43-1),4)</f>
         <v>2.0390999999999999</v>
       </c>
       <c r="V44" s="15">
+        <f>ROUND(100*(Índices!V44/Índices!V43-1),4)</f>
         <v>2.3694000000000002</v>
       </c>
     </row>
@@ -11688,39 +12221,51 @@
         <v>3.4689000000000001</v>
       </c>
       <c r="K45" s="16">
+        <f>ROUND(100*(Índices!K45/Índices!K44-1),4)</f>
         <v>2.7561</v>
       </c>
       <c r="L45" s="16">
+        <f>ROUND(100*(Índices!L45/Índices!L44-1),4)</f>
         <v>-0.37940000000000002</v>
       </c>
       <c r="M45" s="16">
+        <f>ROUND(100*(Índices!M45/Índices!M44-1),4)</f>
         <v>-5.7999999999999996E-3</v>
       </c>
       <c r="N45" s="16">
+        <f>ROUND(100*(Índices!N45/Índices!N44-1),4)</f>
         <v>1.2309000000000001</v>
       </c>
       <c r="O45" s="16">
+        <f>ROUND(100*(Índices!O45/Índices!O44-1),4)</f>
         <v>1.1835</v>
       </c>
       <c r="P45" s="16">
+        <f>ROUND(100*(Índices!P45/Índices!P44-1),4)</f>
         <v>1.327</v>
       </c>
       <c r="Q45" s="16">
+        <f>ROUND(100*(Índices!Q45/Índices!Q44-1),4)</f>
         <v>-3.7113999999999998</v>
       </c>
       <c r="R45" s="16">
+        <f>ROUND(100*(Índices!R45/Índices!R44-1),4)</f>
         <v>2.3090999999999999</v>
       </c>
       <c r="S45" s="16">
+        <f>ROUND(100*(Índices!S45/Índices!S44-1),4)</f>
         <v>-0.23150000000000001</v>
       </c>
       <c r="T45" s="16">
+        <f>ROUND(100*(Índices!T45/Índices!T44-1),4)</f>
         <v>1.5172000000000001</v>
       </c>
       <c r="U45" s="17">
+        <f>ROUND(100*(Índices!U45/Índices!U44-1),4)</f>
         <v>0.1615</v>
       </c>
       <c r="V45" s="15">
+        <f>ROUND(100*(Índices!V45/Índices!V44-1),4)</f>
         <v>2.1497999999999999</v>
       </c>
     </row>
@@ -11761,39 +12306,51 @@
         <v>1.9629000000000001</v>
       </c>
       <c r="K46" s="16">
+        <f>ROUND(100*(Índices!K46/Índices!K45-1),4)</f>
         <v>0.73619999999999997</v>
       </c>
       <c r="L46" s="16">
+        <f>ROUND(100*(Índices!L46/Índices!L45-1),4)</f>
         <v>7.7942</v>
       </c>
       <c r="M46" s="16">
+        <f>ROUND(100*(Índices!M46/Índices!M45-1),4)</f>
         <v>0.1011</v>
       </c>
       <c r="N46" s="16">
+        <f>ROUND(100*(Índices!N46/Índices!N45-1),4)</f>
         <v>2.8296000000000001</v>
       </c>
       <c r="O46" s="16">
+        <f>ROUND(100*(Índices!O46/Índices!O45-1),4)</f>
         <v>1.0658000000000001</v>
       </c>
       <c r="P46" s="16">
+        <f>ROUND(100*(Índices!P46/Índices!P45-1),4)</f>
         <v>1.0724</v>
       </c>
       <c r="Q46" s="16">
+        <f>ROUND(100*(Índices!Q46/Índices!Q45-1),4)</f>
         <v>1.2891999999999999</v>
       </c>
       <c r="R46" s="16">
+        <f>ROUND(100*(Índices!R46/Índices!R45-1),4)</f>
         <v>2.4470999999999998</v>
       </c>
       <c r="S46" s="16">
+        <f>ROUND(100*(Índices!S46/Índices!S45-1),4)</f>
         <v>1.0087999999999999</v>
       </c>
       <c r="T46" s="16">
+        <f>ROUND(100*(Índices!T46/Índices!T45-1),4)</f>
         <v>1.6071</v>
       </c>
       <c r="U46" s="17">
+        <f>ROUND(100*(Índices!U46/Índices!U45-1),4)</f>
         <v>1.9246000000000001</v>
       </c>
       <c r="V46" s="15">
+        <f>ROUND(100*(Índices!V46/Índices!V45-1),4)</f>
         <v>2.7134999999999998</v>
       </c>
     </row>
@@ -11834,39 +12391,51 @@
         <v>2.8458999999999999</v>
       </c>
       <c r="K47" s="16">
+        <f>ROUND(100*(Índices!K47/Índices!K46-1),4)</f>
         <v>5.1829000000000001</v>
       </c>
       <c r="L47" s="16">
+        <f>ROUND(100*(Índices!L47/Índices!L46-1),4)</f>
         <v>6.9619999999999997</v>
       </c>
       <c r="M47" s="16">
+        <f>ROUND(100*(Índices!M47/Índices!M46-1),4)</f>
         <v>0.93140000000000001</v>
       </c>
       <c r="N47" s="16">
+        <f>ROUND(100*(Índices!N47/Índices!N46-1),4)</f>
         <v>4.0650000000000004</v>
       </c>
       <c r="O47" s="16">
+        <f>ROUND(100*(Índices!O47/Índices!O46-1),4)</f>
         <v>2.2443</v>
       </c>
       <c r="P47" s="16">
+        <f>ROUND(100*(Índices!P47/Índices!P46-1),4)</f>
         <v>1.8244</v>
       </c>
       <c r="Q47" s="16">
+        <f>ROUND(100*(Índices!Q47/Índices!Q46-1),4)</f>
         <v>0.1278</v>
       </c>
       <c r="R47" s="16">
+        <f>ROUND(100*(Índices!R47/Índices!R46-1),4)</f>
         <v>4.1772999999999998</v>
       </c>
       <c r="S47" s="16">
+        <f>ROUND(100*(Índices!S47/Índices!S46-1),4)</f>
         <v>1.8338000000000001</v>
       </c>
       <c r="T47" s="16">
+        <f>ROUND(100*(Índices!T47/Índices!T46-1),4)</f>
         <v>2.2886000000000002</v>
       </c>
       <c r="U47" s="17">
+        <f>ROUND(100*(Índices!U47/Índices!U46-1),4)</f>
         <v>0.32919999999999999</v>
       </c>
       <c r="V47" s="15">
+        <f>ROUND(100*(Índices!V47/Índices!V46-1),4)</f>
         <v>3.5611000000000002</v>
       </c>
     </row>
@@ -11907,39 +12476,51 @@
         <v>2.9039999999999999</v>
       </c>
       <c r="K48" s="16">
+        <f>ROUND(100*(Índices!K48/Índices!K47-1),4)</f>
         <v>1.9625999999999999</v>
       </c>
       <c r="L48" s="16">
+        <f>ROUND(100*(Índices!L48/Índices!L47-1),4)</f>
         <v>5.46</v>
       </c>
       <c r="M48" s="16">
+        <f>ROUND(100*(Índices!M48/Índices!M47-1),4)</f>
         <v>1.0526</v>
       </c>
       <c r="N48" s="16">
+        <f>ROUND(100*(Índices!N48/Índices!N47-1),4)</f>
         <v>3.8757000000000001</v>
       </c>
       <c r="O48" s="16">
+        <f>ROUND(100*(Índices!O48/Índices!O47-1),4)</f>
         <v>2.1762999999999999</v>
       </c>
       <c r="P48" s="16">
+        <f>ROUND(100*(Índices!P48/Índices!P47-1),4)</f>
         <v>1.8368</v>
       </c>
       <c r="Q48" s="16">
+        <f>ROUND(100*(Índices!Q48/Índices!Q47-1),4)</f>
         <v>1.8571</v>
       </c>
       <c r="R48" s="16">
+        <f>ROUND(100*(Índices!R48/Índices!R47-1),4)</f>
         <v>3.29</v>
       </c>
       <c r="S48" s="16">
+        <f>ROUND(100*(Índices!S48/Índices!S47-1),4)</f>
         <v>0.745</v>
       </c>
       <c r="T48" s="16">
+        <f>ROUND(100*(Índices!T48/Índices!T47-1),4)</f>
         <v>1.8917999999999999</v>
       </c>
       <c r="U48" s="17">
+        <f>ROUND(100*(Índices!U48/Índices!U47-1),4)</f>
         <v>2.3193999999999999</v>
       </c>
       <c r="V48" s="15">
+        <f>ROUND(100*(Índices!V48/Índices!V47-1),4)</f>
         <v>3.198</v>
       </c>
     </row>
@@ -11980,39 +12561,51 @@
         <v>3.5625</v>
       </c>
       <c r="K49" s="16">
+        <f>ROUND(100*(Índices!K49/Índices!K48-1),4)</f>
         <v>2.2751999999999999</v>
       </c>
       <c r="L49" s="16">
+        <f>ROUND(100*(Índices!L49/Índices!L48-1),4)</f>
         <v>2.1358999999999999</v>
       </c>
       <c r="M49" s="16">
+        <f>ROUND(100*(Índices!M49/Índices!M48-1),4)</f>
         <v>2.3214000000000001</v>
       </c>
       <c r="N49" s="16">
+        <f>ROUND(100*(Índices!N49/Índices!N48-1),4)</f>
         <v>3.4573999999999998</v>
       </c>
       <c r="O49" s="16">
+        <f>ROUND(100*(Índices!O49/Índices!O48-1),4)</f>
         <v>2.4026000000000001</v>
       </c>
       <c r="P49" s="16">
+        <f>ROUND(100*(Índices!P49/Índices!P48-1),4)</f>
         <v>2.8481000000000001</v>
       </c>
       <c r="Q49" s="16">
+        <f>ROUND(100*(Índices!Q49/Índices!Q48-1),4)</f>
         <v>1.9917</v>
       </c>
       <c r="R49" s="16">
+        <f>ROUND(100*(Índices!R49/Índices!R48-1),4)</f>
         <v>3.3087</v>
       </c>
       <c r="S49" s="16">
+        <f>ROUND(100*(Índices!S49/Índices!S48-1),4)</f>
         <v>0.92969999999999997</v>
       </c>
       <c r="T49" s="16">
+        <f>ROUND(100*(Índices!T49/Índices!T48-1),4)</f>
         <v>1.9008</v>
       </c>
       <c r="U49" s="17">
+        <f>ROUND(100*(Índices!U49/Índices!U48-1),4)</f>
         <v>3.3344</v>
       </c>
       <c r="V49" s="15">
+        <f>ROUND(100*(Índices!V49/Índices!V48-1),4)</f>
         <v>3.0295999999999998</v>
       </c>
     </row>
@@ -12053,39 +12646,51 @@
         <v>2.6497000000000002</v>
       </c>
       <c r="K50" s="16">
+        <f>ROUND(100*(Índices!K50/Índices!K49-1),4)</f>
         <v>3.1932999999999998</v>
       </c>
       <c r="L50" s="16">
+        <f>ROUND(100*(Índices!L50/Índices!L49-1),4)</f>
         <v>2.7355999999999998</v>
       </c>
       <c r="M50" s="16">
+        <f>ROUND(100*(Índices!M50/Índices!M49-1),4)</f>
         <v>1.5441</v>
       </c>
       <c r="N50" s="16">
+        <f>ROUND(100*(Índices!N50/Índices!N49-1),4)</f>
         <v>2.5857999999999999</v>
       </c>
       <c r="O50" s="16">
+        <f>ROUND(100*(Índices!O50/Índices!O49-1),4)</f>
         <v>3.4967000000000001</v>
       </c>
       <c r="P50" s="16">
+        <f>ROUND(100*(Índices!P50/Índices!P49-1),4)</f>
         <v>3.6034000000000002</v>
       </c>
       <c r="Q50" s="16">
+        <f>ROUND(100*(Índices!Q50/Índices!Q49-1),4)</f>
         <v>0.2918</v>
       </c>
       <c r="R50" s="16">
+        <f>ROUND(100*(Índices!R50/Índices!R49-1),4)</f>
         <v>1.8677999999999999</v>
       </c>
       <c r="S50" s="16">
+        <f>ROUND(100*(Índices!S50/Índices!S49-1),4)</f>
         <v>1.5620000000000001</v>
       </c>
       <c r="T50" s="16">
+        <f>ROUND(100*(Índices!T50/Índices!T49-1),4)</f>
         <v>1.8186</v>
       </c>
       <c r="U50" s="17">
+        <f>ROUND(100*(Índices!U50/Índices!U49-1),4)</f>
         <v>1.82</v>
       </c>
       <c r="V50" s="15">
+        <f>ROUND(100*(Índices!V50/Índices!V49-1),4)</f>
         <v>2.4451999999999998</v>
       </c>
     </row>
@@ -12126,39 +12731,51 @@
         <v>4.7573999999999996</v>
       </c>
       <c r="K51" s="16">
+        <f>ROUND(100*(Índices!K51/Índices!K50-1),4)</f>
         <v>2.1602000000000001</v>
       </c>
       <c r="L51" s="16">
+        <f>ROUND(100*(Índices!L51/Índices!L50-1),4)</f>
         <v>5.4043999999999999</v>
       </c>
       <c r="M51" s="16">
+        <f>ROUND(100*(Índices!M51/Índices!M50-1),4)</f>
         <v>2.3330000000000002</v>
       </c>
       <c r="N51" s="16">
+        <f>ROUND(100*(Índices!N51/Índices!N50-1),4)</f>
         <v>4.4888000000000003</v>
       </c>
       <c r="O51" s="16">
+        <f>ROUND(100*(Índices!O51/Índices!O50-1),4)</f>
         <v>3.0951</v>
       </c>
       <c r="P51" s="16">
+        <f>ROUND(100*(Índices!P51/Índices!P50-1),4)</f>
         <v>4.1612999999999998</v>
       </c>
       <c r="Q51" s="16">
+        <f>ROUND(100*(Índices!Q51/Índices!Q50-1),4)</f>
         <v>0.79849999999999999</v>
       </c>
       <c r="R51" s="16">
+        <f>ROUND(100*(Índices!R51/Índices!R50-1),4)</f>
         <v>2.5760999999999998</v>
       </c>
       <c r="S51" s="16">
+        <f>ROUND(100*(Índices!S51/Índices!S50-1),4)</f>
         <v>1.5724</v>
       </c>
       <c r="T51" s="16">
+        <f>ROUND(100*(Índices!T51/Índices!T50-1),4)</f>
         <v>3.4472</v>
       </c>
       <c r="U51" s="17">
+        <f>ROUND(100*(Índices!U51/Índices!U50-1),4)</f>
         <v>2.0971000000000002</v>
       </c>
       <c r="V51" s="15">
+        <f>ROUND(100*(Índices!V51/Índices!V50-1),4)</f>
         <v>4.1740000000000004</v>
       </c>
     </row>
@@ -12199,39 +12816,51 @@
         <v>3.1743999999999999</v>
       </c>
       <c r="K52" s="16">
+        <f>ROUND(100*(Índices!K52/Índices!K51-1),4)</f>
         <v>2.1356000000000002</v>
       </c>
       <c r="L52" s="16">
+        <f>ROUND(100*(Índices!L52/Índices!L51-1),4)</f>
         <v>4.3379000000000003</v>
       </c>
       <c r="M52" s="16">
+        <f>ROUND(100*(Índices!M52/Índices!M51-1),4)</f>
         <v>2.5240999999999998</v>
       </c>
       <c r="N52" s="16">
+        <f>ROUND(100*(Índices!N52/Índices!N51-1),4)</f>
         <v>3.9426000000000001</v>
       </c>
       <c r="O52" s="16">
+        <f>ROUND(100*(Índices!O52/Índices!O51-1),4)</f>
         <v>3.6714000000000002</v>
       </c>
       <c r="P52" s="16">
+        <f>ROUND(100*(Índices!P52/Índices!P51-1),4)</f>
         <v>3.6032999999999999</v>
       </c>
       <c r="Q52" s="16">
+        <f>ROUND(100*(Índices!Q52/Índices!Q51-1),4)</f>
         <v>-0.216</v>
       </c>
       <c r="R52" s="16">
+        <f>ROUND(100*(Índices!R52/Índices!R51-1),4)</f>
         <v>5.0902000000000003</v>
       </c>
       <c r="S52" s="16">
+        <f>ROUND(100*(Índices!S52/Índices!S51-1),4)</f>
         <v>2.4531000000000001</v>
       </c>
       <c r="T52" s="16">
+        <f>ROUND(100*(Índices!T52/Índices!T51-1),4)</f>
         <v>3.2582</v>
       </c>
       <c r="U52" s="17">
+        <f>ROUND(100*(Índices!U52/Índices!U51-1),4)</f>
         <v>2.645</v>
       </c>
       <c r="V52" s="15">
+        <f>ROUND(100*(Índices!V52/Índices!V51-1),4)</f>
         <v>3.5781999999999998</v>
       </c>
     </row>
@@ -12272,39 +12901,51 @@
         <v>3.3010999999999999</v>
       </c>
       <c r="K53" s="16">
+        <f>ROUND(100*(Índices!K53/Índices!K52-1),4)</f>
         <v>3.0038999999999998</v>
       </c>
       <c r="L53" s="16">
+        <f>ROUND(100*(Índices!L53/Índices!L52-1),4)</f>
         <v>4.2925000000000004</v>
       </c>
       <c r="M53" s="16">
+        <f>ROUND(100*(Índices!M53/Índices!M52-1),4)</f>
         <v>2.9033000000000002</v>
       </c>
       <c r="N53" s="16">
+        <f>ROUND(100*(Índices!N53/Índices!N52-1),4)</f>
         <v>2.3915999999999999</v>
       </c>
       <c r="O53" s="16">
+        <f>ROUND(100*(Índices!O53/Índices!O52-1),4)</f>
         <v>5.2335000000000003</v>
       </c>
       <c r="P53" s="16">
+        <f>ROUND(100*(Índices!P53/Índices!P52-1),4)</f>
         <v>4.8912000000000004</v>
       </c>
       <c r="Q53" s="16">
+        <f>ROUND(100*(Índices!Q53/Índices!Q52-1),4)</f>
         <v>-0.79239999999999999</v>
       </c>
       <c r="R53" s="16">
+        <f>ROUND(100*(Índices!R53/Índices!R52-1),4)</f>
         <v>5.2134999999999998</v>
       </c>
       <c r="S53" s="16">
+        <f>ROUND(100*(Índices!S53/Índices!S52-1),4)</f>
         <v>2.4651000000000001</v>
       </c>
       <c r="T53" s="16">
+        <f>ROUND(100*(Índices!T53/Índices!T52-1),4)</f>
         <v>4.5274000000000001</v>
       </c>
       <c r="U53" s="17">
+        <f>ROUND(100*(Índices!U53/Índices!U52-1),4)</f>
         <v>1.7331000000000001</v>
       </c>
       <c r="V53" s="15">
+        <f>ROUND(100*(Índices!V53/Índices!V52-1),4)</f>
         <v>3.6787999999999998</v>
       </c>
     </row>
@@ -12345,39 +12986,51 @@
         <v>3.1067999999999998</v>
       </c>
       <c r="K54" s="16">
+        <f>ROUND(100*(Índices!K54/Índices!K53-1),4)</f>
         <v>3.0394999999999999</v>
       </c>
       <c r="L54" s="16">
+        <f>ROUND(100*(Índices!L54/Índices!L53-1),4)</f>
         <v>4.4253999999999998</v>
       </c>
       <c r="M54" s="16">
+        <f>ROUND(100*(Índices!M54/Índices!M53-1),4)</f>
         <v>1.2412000000000001</v>
       </c>
       <c r="N54" s="16">
+        <f>ROUND(100*(Índices!N54/Índices!N53-1),4)</f>
         <v>2.9634</v>
       </c>
       <c r="O54" s="16">
+        <f>ROUND(100*(Índices!O54/Índices!O53-1),4)</f>
         <v>3.3925999999999998</v>
       </c>
       <c r="P54" s="16">
+        <f>ROUND(100*(Índices!P54/Índices!P53-1),4)</f>
         <v>4.6513999999999998</v>
       </c>
       <c r="Q54" s="16">
+        <f>ROUND(100*(Índices!Q54/Índices!Q53-1),4)</f>
         <v>11.3787</v>
       </c>
       <c r="R54" s="16">
+        <f>ROUND(100*(Índices!R54/Índices!R53-1),4)</f>
         <v>4.8205</v>
       </c>
       <c r="S54" s="16">
+        <f>ROUND(100*(Índices!S54/Índices!S53-1),4)</f>
         <v>3.6312000000000002</v>
       </c>
       <c r="T54" s="16">
+        <f>ROUND(100*(Índices!T54/Índices!T53-1),4)</f>
         <v>5.2268999999999997</v>
       </c>
       <c r="U54" s="17">
+        <f>ROUND(100*(Índices!U54/Índices!U53-1),4)</f>
         <v>2.0413999999999999</v>
       </c>
       <c r="V54" s="15">
+        <f>ROUND(100*(Índices!V54/Índices!V53-1),4)</f>
         <v>3.7155</v>
       </c>
     </row>
@@ -12418,39 +13071,51 @@
         <v>2.5257000000000001</v>
       </c>
       <c r="K55" s="16">
+        <f>ROUND(100*(Índices!K55/Índices!K54-1),4)</f>
         <v>3.3033000000000001</v>
       </c>
       <c r="L55" s="16">
+        <f>ROUND(100*(Índices!L55/Índices!L54-1),4)</f>
         <v>4.5031999999999996</v>
       </c>
       <c r="M55" s="16">
+        <f>ROUND(100*(Índices!M55/Índices!M54-1),4)</f>
         <v>2.0367000000000002</v>
       </c>
       <c r="N55" s="16">
+        <f>ROUND(100*(Índices!N55/Índices!N54-1),4)</f>
         <v>4.5579999999999998</v>
       </c>
       <c r="O55" s="16">
+        <f>ROUND(100*(Índices!O55/Índices!O54-1),4)</f>
         <v>3.4982000000000002</v>
       </c>
       <c r="P55" s="16">
+        <f>ROUND(100*(Índices!P55/Índices!P54-1),4)</f>
         <v>4.8215000000000003</v>
       </c>
       <c r="Q55" s="16">
+        <f>ROUND(100*(Índices!Q55/Índices!Q54-1),4)</f>
         <v>0.13730000000000001</v>
       </c>
       <c r="R55" s="16">
+        <f>ROUND(100*(Índices!R55/Índices!R54-1),4)</f>
         <v>2.2988</v>
       </c>
       <c r="S55" s="16">
+        <f>ROUND(100*(Índices!S55/Índices!S54-1),4)</f>
         <v>2.2025999999999999</v>
       </c>
       <c r="T55" s="16">
+        <f>ROUND(100*(Índices!T55/Índices!T54-1),4)</f>
         <v>5.3525999999999998</v>
       </c>
       <c r="U55" s="17">
+        <f>ROUND(100*(Índices!U55/Índices!U54-1),4)</f>
         <v>3.2269999999999999</v>
       </c>
       <c r="V55" s="15">
+        <f>ROUND(100*(Índices!V55/Índices!V54-1),4)</f>
         <v>3.4279999999999999</v>
       </c>
     </row>
@@ -12491,39 +13156,51 @@
         <v>3.3283999999999998</v>
       </c>
       <c r="K56" s="16">
+        <f>ROUND(100*(Índices!K56/Índices!K55-1),4)</f>
         <v>5.1683000000000003</v>
       </c>
       <c r="L56" s="16">
+        <f>ROUND(100*(Índices!L56/Índices!L55-1),4)</f>
         <v>7.2839999999999998</v>
       </c>
       <c r="M56" s="16">
+        <f>ROUND(100*(Índices!M56/Índices!M55-1),4)</f>
         <v>1.3351999999999999</v>
       </c>
       <c r="N56" s="16">
+        <f>ROUND(100*(Índices!N56/Índices!N55-1),4)</f>
         <v>3.1669999999999998</v>
       </c>
       <c r="O56" s="16">
+        <f>ROUND(100*(Índices!O56/Índices!O55-1),4)</f>
         <v>3.9872999999999998</v>
       </c>
       <c r="P56" s="16">
+        <f>ROUND(100*(Índices!P56/Índices!P55-1),4)</f>
         <v>4.1996000000000002</v>
       </c>
       <c r="Q56" s="16">
+        <f>ROUND(100*(Índices!Q56/Índices!Q55-1),4)</f>
         <v>0.2848</v>
       </c>
       <c r="R56" s="16">
+        <f>ROUND(100*(Índices!R56/Índices!R55-1),4)</f>
         <v>5.3433999999999999</v>
       </c>
       <c r="S56" s="16">
+        <f>ROUND(100*(Índices!S56/Índices!S55-1),4)</f>
         <v>7.9546000000000001</v>
       </c>
       <c r="T56" s="16">
+        <f>ROUND(100*(Índices!T56/Índices!T55-1),4)</f>
         <v>3.1078000000000001</v>
       </c>
       <c r="U56" s="17">
+        <f>ROUND(100*(Índices!U56/Índices!U55-1),4)</f>
         <v>2.2050000000000001</v>
       </c>
       <c r="V56" s="15">
+        <f>ROUND(100*(Índices!V56/Índices!V55-1),4)</f>
         <v>4.0498000000000003</v>
       </c>
     </row>
@@ -12564,39 +13241,51 @@
         <v>4.6199000000000003</v>
       </c>
       <c r="K57" s="16">
+        <f>ROUND(100*(Índices!K57/Índices!K56-1),4)</f>
         <v>4.9660000000000002</v>
       </c>
       <c r="L57" s="16">
+        <f>ROUND(100*(Índices!L57/Índices!L56-1),4)</f>
         <v>3.9117999999999999</v>
       </c>
       <c r="M57" s="16">
+        <f>ROUND(100*(Índices!M57/Índices!M56-1),4)</f>
         <v>3.4302000000000001</v>
       </c>
       <c r="N57" s="16">
+        <f>ROUND(100*(Índices!N57/Índices!N56-1),4)</f>
         <v>4.2946</v>
       </c>
       <c r="O57" s="16">
+        <f>ROUND(100*(Índices!O57/Índices!O56-1),4)</f>
         <v>3.7284999999999999</v>
       </c>
       <c r="P57" s="16">
+        <f>ROUND(100*(Índices!P57/Índices!P56-1),4)</f>
         <v>5.6657999999999999</v>
       </c>
       <c r="Q57" s="16">
+        <f>ROUND(100*(Índices!Q57/Índices!Q56-1),4)</f>
         <v>0.87119999999999997</v>
       </c>
       <c r="R57" s="16">
+        <f>ROUND(100*(Índices!R57/Índices!R56-1),4)</f>
         <v>1.4837</v>
       </c>
       <c r="S57" s="16">
+        <f>ROUND(100*(Índices!S57/Índices!S56-1),4)</f>
         <v>3.778</v>
       </c>
       <c r="T57" s="16">
+        <f>ROUND(100*(Índices!T57/Índices!T56-1),4)</f>
         <v>3.8839000000000001</v>
       </c>
       <c r="U57" s="17">
+        <f>ROUND(100*(Índices!U57/Índices!U56-1),4)</f>
         <v>3.6435</v>
       </c>
       <c r="V57" s="15">
+        <f>ROUND(100*(Índices!V57/Índices!V56-1),4)</f>
         <v>4.0016999999999996</v>
       </c>
     </row>
@@ -12637,39 +13326,51 @@
         <v>4.4200999999999997</v>
       </c>
       <c r="K58" s="16">
+        <f>ROUND(100*(Índices!K58/Índices!K57-1),4)</f>
         <v>2.2837000000000001</v>
       </c>
       <c r="L58" s="16">
+        <f>ROUND(100*(Índices!L58/Índices!L57-1),4)</f>
         <v>2.754</v>
       </c>
       <c r="M58" s="16">
+        <f>ROUND(100*(Índices!M58/Índices!M57-1),4)</f>
         <v>1.9985999999999999</v>
       </c>
       <c r="N58" s="16">
+        <f>ROUND(100*(Índices!N58/Índices!N57-1),4)</f>
         <v>2.3656000000000001</v>
       </c>
       <c r="O58" s="16">
+        <f>ROUND(100*(Índices!O58/Índices!O57-1),4)</f>
         <v>4.7465000000000002</v>
       </c>
       <c r="P58" s="16">
+        <f>ROUND(100*(Índices!P58/Índices!P57-1),4)</f>
         <v>5.9431000000000003</v>
       </c>
       <c r="Q58" s="16">
+        <f>ROUND(100*(Índices!Q58/Índices!Q57-1),4)</f>
         <v>1.8307</v>
       </c>
       <c r="R58" s="16">
+        <f>ROUND(100*(Índices!R58/Índices!R57-1),4)</f>
         <v>3.1080000000000001</v>
       </c>
       <c r="S58" s="16">
+        <f>ROUND(100*(Índices!S58/Índices!S57-1),4)</f>
         <v>3.5823</v>
       </c>
       <c r="T58" s="16">
+        <f>ROUND(100*(Índices!T58/Índices!T57-1),4)</f>
         <v>3.8119000000000001</v>
       </c>
       <c r="U58" s="17">
+        <f>ROUND(100*(Índices!U58/Índices!U57-1),4)</f>
         <v>2.9056000000000002</v>
       </c>
       <c r="V58" s="15">
+        <f>ROUND(100*(Índices!V58/Índices!V57-1),4)</f>
         <v>3.6198000000000001</v>
       </c>
     </row>
@@ -12710,39 +13411,51 @@
         <v>5.0846999999999998</v>
       </c>
       <c r="K59" s="16">
+        <f>ROUND(100*(Índices!K59/Índices!K58-1),4)</f>
         <v>6.9122000000000003</v>
       </c>
       <c r="L59" s="16">
+        <f>ROUND(100*(Índices!L59/Índices!L58-1),4)</f>
         <v>3.9704000000000002</v>
       </c>
       <c r="M59" s="16">
+        <f>ROUND(100*(Índices!M59/Índices!M58-1),4)</f>
         <v>2.5005000000000002</v>
       </c>
       <c r="N59" s="16">
+        <f>ROUND(100*(Índices!N59/Índices!N58-1),4)</f>
         <v>3.2332999999999998</v>
       </c>
       <c r="O59" s="16">
+        <f>ROUND(100*(Índices!O59/Índices!O58-1),4)</f>
         <v>3.2210999999999999</v>
       </c>
       <c r="P59" s="16">
+        <f>ROUND(100*(Índices!P59/Índices!P58-1),4)</f>
         <v>3.2591000000000001</v>
       </c>
       <c r="Q59" s="16">
+        <f>ROUND(100*(Índices!Q59/Índices!Q58-1),4)</f>
         <v>6.9465000000000003</v>
       </c>
       <c r="R59" s="16">
+        <f>ROUND(100*(Índices!R59/Índices!R58-1),4)</f>
         <v>2.2378999999999998</v>
       </c>
       <c r="S59" s="16">
+        <f>ROUND(100*(Índices!S59/Índices!S58-1),4)</f>
         <v>2.8997999999999999</v>
       </c>
       <c r="T59" s="16">
+        <f>ROUND(100*(Índices!T59/Índices!T58-1),4)</f>
         <v>3.1682000000000001</v>
       </c>
       <c r="U59" s="17">
+        <f>ROUND(100*(Índices!U59/Índices!U58-1),4)</f>
         <v>1.9655</v>
       </c>
       <c r="V59" s="15">
+        <f>ROUND(100*(Índices!V59/Índices!V58-1),4)</f>
         <v>4.0861999999999998</v>
       </c>
     </row>
@@ -12783,39 +13496,51 @@
         <v>5.0617000000000001</v>
       </c>
       <c r="K60" s="16">
+        <f>ROUND(100*(Índices!K60/Índices!K59-1),4)</f>
         <v>3.7071000000000001</v>
       </c>
       <c r="L60" s="16">
+        <f>ROUND(100*(Índices!L60/Índices!L59-1),4)</f>
         <v>3.5144000000000002</v>
       </c>
       <c r="M60" s="16">
+        <f>ROUND(100*(Índices!M60/Índices!M59-1),4)</f>
         <v>2.8473999999999999</v>
       </c>
       <c r="N60" s="16">
+        <f>ROUND(100*(Índices!N60/Índices!N59-1),4)</f>
         <v>2.7279</v>
       </c>
       <c r="O60" s="16">
+        <f>ROUND(100*(Índices!O60/Índices!O59-1),4)</f>
         <v>3.835</v>
       </c>
       <c r="P60" s="16">
+        <f>ROUND(100*(Índices!P60/Índices!P59-1),4)</f>
         <v>2.3123</v>
       </c>
       <c r="Q60" s="16">
+        <f>ROUND(100*(Índices!Q60/Índices!Q59-1),4)</f>
         <v>1.5045999999999999</v>
       </c>
       <c r="R60" s="16">
+        <f>ROUND(100*(Índices!R60/Índices!R59-1),4)</f>
         <v>3.0947</v>
       </c>
       <c r="S60" s="16">
+        <f>ROUND(100*(Índices!S60/Índices!S59-1),4)</f>
         <v>3.0514999999999999</v>
       </c>
       <c r="T60" s="16">
+        <f>ROUND(100*(Índices!T60/Índices!T59-1),4)</f>
         <v>4.7252999999999998</v>
       </c>
       <c r="U60" s="17">
+        <f>ROUND(100*(Índices!U60/Índices!U59-1),4)</f>
         <v>3.1937000000000002</v>
       </c>
       <c r="V60" s="15">
+        <f>ROUND(100*(Índices!V60/Índices!V59-1),4)</f>
         <v>4.2256</v>
       </c>
     </row>
@@ -12856,39 +13581,51 @@
         <v>1.5766</v>
       </c>
       <c r="K61" s="16">
+        <f>ROUND(100*(Índices!K61/Índices!K60-1),4)</f>
         <v>3.0005000000000002</v>
       </c>
       <c r="L61" s="16">
+        <f>ROUND(100*(Índices!L61/Índices!L60-1),4)</f>
         <v>3.323</v>
       </c>
       <c r="M61" s="16">
+        <f>ROUND(100*(Índices!M61/Índices!M60-1),4)</f>
         <v>1.0620000000000001</v>
       </c>
       <c r="N61" s="16">
+        <f>ROUND(100*(Índices!N61/Índices!N60-1),4)</f>
         <v>3.2749999999999999</v>
       </c>
       <c r="O61" s="16">
+        <f>ROUND(100*(Índices!O61/Índices!O60-1),4)</f>
         <v>4.1905000000000001</v>
       </c>
       <c r="P61" s="16">
+        <f>ROUND(100*(Índices!P61/Índices!P60-1),4)</f>
         <v>2.4519000000000002</v>
       </c>
       <c r="Q61" s="16">
+        <f>ROUND(100*(Índices!Q61/Índices!Q60-1),4)</f>
         <v>1.4073</v>
       </c>
       <c r="R61" s="16">
+        <f>ROUND(100*(Índices!R61/Índices!R60-1),4)</f>
         <v>3.7008000000000001</v>
       </c>
       <c r="S61" s="16">
+        <f>ROUND(100*(Índices!S61/Índices!S60-1),4)</f>
         <v>4.2756999999999996</v>
       </c>
       <c r="T61" s="16">
+        <f>ROUND(100*(Índices!T61/Índices!T60-1),4)</f>
         <v>2.9754999999999998</v>
       </c>
       <c r="U61" s="17">
+        <f>ROUND(100*(Índices!U61/Índices!U60-1),4)</f>
         <v>3.3048000000000002</v>
       </c>
       <c r="V61" s="15">
+        <f>ROUND(100*(Índices!V61/Índices!V60-1),4)</f>
         <v>2.5106000000000002</v>
       </c>
     </row>
@@ -12929,39 +13666,51 @@
         <v>2.6423999999999999</v>
       </c>
       <c r="K62" s="16">
+        <f>ROUND(100*(Índices!K62/Índices!K61-1),4)</f>
         <v>4.78</v>
       </c>
       <c r="L62" s="16">
+        <f>ROUND(100*(Índices!L62/Índices!L61-1),4)</f>
         <v>2.9081999999999999</v>
       </c>
       <c r="M62" s="16">
+        <f>ROUND(100*(Índices!M62/Índices!M61-1),4)</f>
         <v>1.9457</v>
       </c>
       <c r="N62" s="16">
+        <f>ROUND(100*(Índices!N62/Índices!N61-1),4)</f>
         <v>3.4849000000000001</v>
       </c>
       <c r="O62" s="16">
+        <f>ROUND(100*(Índices!O62/Índices!O61-1),4)</f>
         <v>4.3009000000000004</v>
       </c>
       <c r="P62" s="16">
+        <f>ROUND(100*(Índices!P62/Índices!P61-1),4)</f>
         <v>3.0255999999999998</v>
       </c>
       <c r="Q62" s="16">
+        <f>ROUND(100*(Índices!Q62/Índices!Q61-1),4)</f>
         <v>3.2406000000000001</v>
       </c>
       <c r="R62" s="16">
+        <f>ROUND(100*(Índices!R62/Índices!R61-1),4)</f>
         <v>3.7704</v>
       </c>
       <c r="S62" s="16">
+        <f>ROUND(100*(Índices!S62/Índices!S61-1),4)</f>
         <v>4.5210999999999997</v>
       </c>
       <c r="T62" s="16">
+        <f>ROUND(100*(Índices!T62/Índices!T61-1),4)</f>
         <v>4.1750999999999996</v>
       </c>
       <c r="U62" s="17">
+        <f>ROUND(100*(Índices!U62/Índices!U61-1),4)</f>
         <v>2.1619000000000002</v>
       </c>
       <c r="V62" s="15">
+        <f>ROUND(100*(Índices!V62/Índices!V61-1),4)</f>
         <v>3.1560999999999999</v>
       </c>
     </row>
@@ -13002,39 +13751,51 @@
         <v>3.4016000000000002</v>
       </c>
       <c r="K63" s="16">
+        <f>ROUND(100*(Índices!K63/Índices!K62-1),4)</f>
         <v>2.4578000000000002</v>
       </c>
       <c r="L63" s="16">
+        <f>ROUND(100*(Índices!L63/Índices!L62-1),4)</f>
         <v>4.5465999999999998</v>
       </c>
       <c r="M63" s="16">
+        <f>ROUND(100*(Índices!M63/Índices!M62-1),4)</f>
         <v>2.4965999999999999</v>
       </c>
       <c r="N63" s="16">
+        <f>ROUND(100*(Índices!N63/Índices!N62-1),4)</f>
         <v>2.7541000000000002</v>
       </c>
       <c r="O63" s="16">
+        <f>ROUND(100*(Índices!O63/Índices!O62-1),4)</f>
         <v>4.7195999999999998</v>
       </c>
       <c r="P63" s="16">
+        <f>ROUND(100*(Índices!P63/Índices!P62-1),4)</f>
         <v>3.0863999999999998</v>
       </c>
       <c r="Q63" s="16">
+        <f>ROUND(100*(Índices!Q63/Índices!Q62-1),4)</f>
         <v>1.9601</v>
       </c>
       <c r="R63" s="16">
+        <f>ROUND(100*(Índices!R63/Índices!R62-1),4)</f>
         <v>3.9950999999999999</v>
       </c>
       <c r="S63" s="16">
+        <f>ROUND(100*(Índices!S63/Índices!S62-1),4)</f>
         <v>3.2923</v>
       </c>
       <c r="T63" s="16">
+        <f>ROUND(100*(Índices!T63/Índices!T62-1),4)</f>
         <v>4.1920000000000002</v>
       </c>
       <c r="U63" s="17">
+        <f>ROUND(100*(Índices!U63/Índices!U62-1),4)</f>
         <v>3.3544999999999998</v>
       </c>
       <c r="V63" s="15">
+        <f>ROUND(100*(Índices!V63/Índices!V62-1),4)</f>
         <v>3.6219999999999999</v>
       </c>
     </row>
@@ -13075,39 +13836,51 @@
         <v>2.5701999999999998</v>
       </c>
       <c r="K64" s="16">
+        <f>ROUND(100*(Índices!K64/Índices!K63-1),4)</f>
         <v>0.27179999999999999</v>
       </c>
       <c r="L64" s="16">
+        <f>ROUND(100*(Índices!L64/Índices!L63-1),4)</f>
         <v>4.9260999999999999</v>
       </c>
       <c r="M64" s="16">
+        <f>ROUND(100*(Índices!M64/Índices!M63-1),4)</f>
         <v>2.2027999999999999</v>
       </c>
       <c r="N64" s="16">
+        <f>ROUND(100*(Índices!N64/Índices!N63-1),4)</f>
         <v>2.7023999999999999</v>
       </c>
       <c r="O64" s="16">
+        <f>ROUND(100*(Índices!O64/Índices!O63-1),4)</f>
         <v>2.4401999999999999</v>
       </c>
       <c r="P64" s="16">
+        <f>ROUND(100*(Índices!P64/Índices!P63-1),4)</f>
         <v>2.2120000000000002</v>
       </c>
       <c r="Q64" s="16">
+        <f>ROUND(100*(Índices!Q64/Índices!Q63-1),4)</f>
         <v>1.2748999999999999</v>
       </c>
       <c r="R64" s="16">
+        <f>ROUND(100*(Índices!R64/Índices!R63-1),4)</f>
         <v>1.4598</v>
       </c>
       <c r="S64" s="16">
+        <f>ROUND(100*(Índices!S64/Índices!S63-1),4)</f>
         <v>3.2494999999999998</v>
       </c>
       <c r="T64" s="16">
+        <f>ROUND(100*(Índices!T64/Índices!T63-1),4)</f>
         <v>5.0263999999999998</v>
       </c>
       <c r="U64" s="17">
+        <f>ROUND(100*(Índices!U64/Índices!U63-1),4)</f>
         <v>2.0405000000000002</v>
       </c>
       <c r="V64" s="15">
+        <f>ROUND(100*(Índices!V64/Índices!V63-1),4)</f>
         <v>3.0251999999999999</v>
       </c>
     </row>
@@ -13148,39 +13921,51 @@
         <v>3.2065000000000001</v>
       </c>
       <c r="K65" s="16">
+        <f>ROUND(100*(Índices!K65/Índices!K64-1),4)</f>
         <v>4.9733000000000001</v>
       </c>
       <c r="L65" s="16">
+        <f>ROUND(100*(Índices!L65/Índices!L64-1),4)</f>
         <v>5.1097000000000001</v>
       </c>
       <c r="M65" s="16">
+        <f>ROUND(100*(Índices!M65/Índices!M64-1),4)</f>
         <v>2.0897000000000001</v>
       </c>
       <c r="N65" s="16">
+        <f>ROUND(100*(Índices!N65/Índices!N64-1),4)</f>
         <v>3.3732000000000002</v>
       </c>
       <c r="O65" s="16">
+        <f>ROUND(100*(Índices!O65/Índices!O64-1),4)</f>
         <v>0.50060000000000004</v>
       </c>
       <c r="P65" s="16">
+        <f>ROUND(100*(Índices!P65/Índices!P64-1),4)</f>
         <v>4.8836000000000004</v>
       </c>
       <c r="Q65" s="16">
+        <f>ROUND(100*(Índices!Q65/Índices!Q64-1),4)</f>
         <v>1.2625</v>
       </c>
       <c r="R65" s="16">
+        <f>ROUND(100*(Índices!R65/Índices!R64-1),4)</f>
         <v>3.9565000000000001</v>
       </c>
       <c r="S65" s="16">
+        <f>ROUND(100*(Índices!S65/Índices!S64-1),4)</f>
         <v>3.9207000000000001</v>
       </c>
       <c r="T65" s="16">
+        <f>ROUND(100*(Índices!T65/Índices!T64-1),4)</f>
         <v>5.8059000000000003</v>
       </c>
       <c r="U65" s="17">
+        <f>ROUND(100*(Índices!U65/Índices!U64-1),4)</f>
         <v>3.1758999999999999</v>
       </c>
       <c r="V65" s="15">
+        <f>ROUND(100*(Índices!V65/Índices!V64-1),4)</f>
         <v>4.0164</v>
       </c>
     </row>
@@ -13221,39 +14006,51 @@
         <v>3.2206000000000001</v>
       </c>
       <c r="K66" s="16">
+        <f>ROUND(100*(Índices!K66/Índices!K65-1),4)</f>
         <v>0.37880000000000003</v>
       </c>
       <c r="L66" s="16">
+        <f>ROUND(100*(Índices!L66/Índices!L65-1),4)</f>
         <v>5.1616999999999997</v>
       </c>
       <c r="M66" s="16">
+        <f>ROUND(100*(Índices!M66/Índices!M65-1),4)</f>
         <v>1.7966</v>
       </c>
       <c r="N66" s="16">
+        <f>ROUND(100*(Índices!N66/Índices!N65-1),4)</f>
         <v>3.3207</v>
       </c>
       <c r="O66" s="16">
+        <f>ROUND(100*(Índices!O66/Índices!O65-1),4)</f>
         <v>4.1022999999999996</v>
       </c>
       <c r="P66" s="16">
+        <f>ROUND(100*(Índices!P66/Índices!P65-1),4)</f>
         <v>2.7768999999999999</v>
       </c>
       <c r="Q66" s="16">
+        <f>ROUND(100*(Índices!Q66/Índices!Q65-1),4)</f>
         <v>3.5226000000000002</v>
       </c>
       <c r="R66" s="16">
+        <f>ROUND(100*(Índices!R66/Índices!R65-1),4)</f>
         <v>4.2103000000000002</v>
       </c>
       <c r="S66" s="16">
+        <f>ROUND(100*(Índices!S66/Índices!S65-1),4)</f>
         <v>4.4619999999999997</v>
       </c>
       <c r="T66" s="16">
+        <f>ROUND(100*(Índices!T66/Índices!T65-1),4)</f>
         <v>5.5090000000000003</v>
       </c>
       <c r="U66" s="17">
+        <f>ROUND(100*(Índices!U66/Índices!U65-1),4)</f>
         <v>4.2999000000000001</v>
       </c>
       <c r="V66" s="15">
+        <f>ROUND(100*(Índices!V66/Índices!V65-1),4)</f>
         <v>3.8626999999999998</v>
       </c>
     </row>
@@ -13294,39 +14091,51 @@
         <v>6.1284000000000001</v>
       </c>
       <c r="K67" s="16">
+        <f>ROUND(100*(Índices!K67/Índices!K66-1),4)</f>
         <v>2.3815</v>
       </c>
       <c r="L67" s="16">
+        <f>ROUND(100*(Índices!L67/Índices!L66-1),4)</f>
         <v>5.0465</v>
       </c>
       <c r="M67" s="16">
+        <f>ROUND(100*(Índices!M67/Índices!M66-1),4)</f>
         <v>2.8513000000000002</v>
       </c>
       <c r="N67" s="16">
+        <f>ROUND(100*(Índices!N67/Índices!N66-1),4)</f>
         <v>4.4306000000000001</v>
       </c>
       <c r="O67" s="16">
+        <f>ROUND(100*(Índices!O67/Índices!O66-1),4)</f>
         <v>3.6457000000000002</v>
       </c>
       <c r="P67" s="16">
+        <f>ROUND(100*(Índices!P67/Índices!P66-1),4)</f>
         <v>4.9577</v>
       </c>
       <c r="Q67" s="16">
+        <f>ROUND(100*(Índices!Q67/Índices!Q66-1),4)</f>
         <v>-0.64039999999999997</v>
       </c>
       <c r="R67" s="16">
+        <f>ROUND(100*(Índices!R67/Índices!R66-1),4)</f>
         <v>2.2829000000000002</v>
       </c>
       <c r="S67" s="16">
+        <f>ROUND(100*(Índices!S67/Índices!S66-1),4)</f>
         <v>4.4351000000000003</v>
       </c>
       <c r="T67" s="16">
+        <f>ROUND(100*(Índices!T67/Índices!T66-1),4)</f>
         <v>4.2625999999999999</v>
       </c>
       <c r="U67" s="17">
+        <f>ROUND(100*(Índices!U67/Índices!U66-1),4)</f>
         <v>4.3357000000000001</v>
       </c>
       <c r="V67" s="15">
+        <f>ROUND(100*(Índices!V67/Índices!V66-1),4)</f>
         <v>4.8651</v>
       </c>
     </row>
@@ -13367,39 +14176,51 @@
         <v>5.9473000000000003</v>
       </c>
       <c r="K68" s="16">
+        <f>ROUND(100*(Índices!K68/Índices!K67-1),4)</f>
         <v>4.5007999999999999</v>
       </c>
       <c r="L68" s="16">
+        <f>ROUND(100*(Índices!L68/Índices!L67-1),4)</f>
         <v>7.0515999999999996</v>
       </c>
       <c r="M68" s="16">
+        <f>ROUND(100*(Índices!M68/Índices!M67-1),4)</f>
         <v>7.6234000000000002</v>
       </c>
       <c r="N68" s="16">
+        <f>ROUND(100*(Índices!N68/Índices!N67-1),4)</f>
         <v>4.3875000000000002</v>
       </c>
       <c r="O68" s="16">
+        <f>ROUND(100*(Índices!O68/Índices!O67-1),4)</f>
         <v>4.9451999999999998</v>
       </c>
       <c r="P68" s="16">
+        <f>ROUND(100*(Índices!P68/Índices!P67-1),4)</f>
         <v>5.4894999999999996</v>
       </c>
       <c r="Q68" s="16">
+        <f>ROUND(100*(Índices!Q68/Índices!Q67-1),4)</f>
         <v>3.7688000000000001</v>
       </c>
       <c r="R68" s="16">
+        <f>ROUND(100*(Índices!R68/Índices!R67-1),4)</f>
         <v>3.3292999999999999</v>
       </c>
       <c r="S68" s="16">
+        <f>ROUND(100*(Índices!S68/Índices!S67-1),4)</f>
         <v>2.4441000000000002</v>
       </c>
       <c r="T68" s="16">
+        <f>ROUND(100*(Índices!T68/Índices!T67-1),4)</f>
         <v>5.4066999999999998</v>
       </c>
       <c r="U68" s="17">
+        <f>ROUND(100*(Índices!U68/Índices!U67-1),4)</f>
         <v>5.5303000000000004</v>
       </c>
       <c r="V68" s="15">
+        <f>ROUND(100*(Índices!V68/Índices!V67-1),4)</f>
         <v>5.5946999999999996</v>
       </c>
     </row>
@@ -13440,39 +14261,51 @@
         <v>6.1672000000000002</v>
       </c>
       <c r="K69" s="16">
+        <f>ROUND(100*(Índices!K69/Índices!K68-1),4)</f>
         <v>4.7222999999999997</v>
       </c>
       <c r="L69" s="16">
+        <f>ROUND(100*(Índices!L69/Índices!L68-1),4)</f>
         <v>7.4466999999999999</v>
       </c>
       <c r="M69" s="16">
+        <f>ROUND(100*(Índices!M69/Índices!M68-1),4)</f>
         <v>4.5648999999999997</v>
       </c>
       <c r="N69" s="16">
+        <f>ROUND(100*(Índices!N69/Índices!N68-1),4)</f>
         <v>5.5004999999999997</v>
       </c>
       <c r="O69" s="16">
+        <f>ROUND(100*(Índices!O69/Índices!O68-1),4)</f>
         <v>6.3952</v>
       </c>
       <c r="P69" s="16">
+        <f>ROUND(100*(Índices!P69/Índices!P68-1),4)</f>
         <v>5.3140000000000001</v>
       </c>
       <c r="Q69" s="16">
+        <f>ROUND(100*(Índices!Q69/Índices!Q68-1),4)</f>
         <v>3.8351999999999999</v>
       </c>
       <c r="R69" s="16">
+        <f>ROUND(100*(Índices!R69/Índices!R68-1),4)</f>
         <v>5.2328999999999999</v>
       </c>
       <c r="S69" s="16">
+        <f>ROUND(100*(Índices!S69/Índices!S68-1),4)</f>
         <v>4.7762000000000002</v>
       </c>
       <c r="T69" s="16">
+        <f>ROUND(100*(Índices!T69/Índices!T68-1),4)</f>
         <v>7.3558000000000003</v>
       </c>
       <c r="U69" s="17">
+        <f>ROUND(100*(Índices!U69/Índices!U68-1),4)</f>
         <v>5.2587000000000002</v>
       </c>
       <c r="V69" s="15">
+        <f>ROUND(100*(Índices!V69/Índices!V68-1),4)</f>
         <v>6.2613000000000003</v>
       </c>
     </row>
@@ -13513,39 +14346,51 @@
         <v>5.7431999999999999</v>
       </c>
       <c r="K70" s="16">
+        <f>ROUND(100*(Índices!K70/Índices!K69-1),4)</f>
         <v>6.3570000000000002</v>
       </c>
       <c r="L70" s="16">
+        <f>ROUND(100*(Índices!L70/Índices!L69-1),4)</f>
         <v>6.6191000000000004</v>
       </c>
       <c r="M70" s="16">
+        <f>ROUND(100*(Índices!M70/Índices!M69-1),4)</f>
         <v>3.5882000000000001</v>
       </c>
       <c r="N70" s="16">
+        <f>ROUND(100*(Índices!N70/Índices!N69-1),4)</f>
         <v>5.3537999999999997</v>
       </c>
       <c r="O70" s="16">
+        <f>ROUND(100*(Índices!O70/Índices!O69-1),4)</f>
         <v>6.2127999999999997</v>
       </c>
       <c r="P70" s="16">
+        <f>ROUND(100*(Índices!P70/Índices!P69-1),4)</f>
         <v>6.1364000000000001</v>
       </c>
       <c r="Q70" s="16">
+        <f>ROUND(100*(Índices!Q70/Índices!Q69-1),4)</f>
         <v>3.9590000000000001</v>
       </c>
       <c r="R70" s="16">
+        <f>ROUND(100*(Índices!R70/Índices!R69-1),4)</f>
         <v>5.1947999999999999</v>
       </c>
       <c r="S70" s="16">
+        <f>ROUND(100*(Índices!S70/Índices!S69-1),4)</f>
         <v>4.3234000000000004</v>
       </c>
       <c r="T70" s="16">
+        <f>ROUND(100*(Índices!T70/Índices!T69-1),4)</f>
         <v>5.7504</v>
       </c>
       <c r="U70" s="17">
+        <f>ROUND(100*(Índices!U70/Índices!U69-1),4)</f>
         <v>4.5564999999999998</v>
       </c>
       <c r="V70" s="15">
+        <f>ROUND(100*(Índices!V70/Índices!V69-1),4)</f>
         <v>5.7534000000000001</v>
       </c>
     </row>
@@ -13586,39 +14431,51 @@
         <v>6.4846000000000004</v>
       </c>
       <c r="K71" s="16">
+        <f>ROUND(100*(Índices!K71/Índices!K70-1),4)</f>
         <v>8.1594999999999995</v>
       </c>
       <c r="L71" s="16">
+        <f>ROUND(100*(Índices!L71/Índices!L70-1),4)</f>
         <v>6.7850999999999999</v>
       </c>
       <c r="M71" s="16">
+        <f>ROUND(100*(Índices!M71/Índices!M70-1),4)</f>
         <v>6.7778999999999998</v>
       </c>
       <c r="N71" s="16">
+        <f>ROUND(100*(Índices!N71/Índices!N70-1),4)</f>
         <v>5.9897</v>
       </c>
       <c r="O71" s="16">
+        <f>ROUND(100*(Índices!O71/Índices!O70-1),4)</f>
         <v>7.4096000000000002</v>
       </c>
       <c r="P71" s="16">
+        <f>ROUND(100*(Índices!P71/Índices!P70-1),4)</f>
         <v>4.7755000000000001</v>
       </c>
       <c r="Q71" s="16">
+        <f>ROUND(100*(Índices!Q71/Índices!Q70-1),4)</f>
         <v>0.31969999999999998</v>
       </c>
       <c r="R71" s="16">
+        <f>ROUND(100*(Índices!R71/Índices!R70-1),4)</f>
         <v>4.3410000000000002</v>
       </c>
       <c r="S71" s="16">
+        <f>ROUND(100*(Índices!S71/Índices!S70-1),4)</f>
         <v>3.8536000000000001</v>
       </c>
       <c r="T71" s="16">
+        <f>ROUND(100*(Índices!T71/Índices!T70-1),4)</f>
         <v>6.2733999999999996</v>
       </c>
       <c r="U71" s="17">
+        <f>ROUND(100*(Índices!U71/Índices!U70-1),4)</f>
         <v>5.0303000000000004</v>
       </c>
       <c r="V71" s="15">
+        <f>ROUND(100*(Índices!V71/Índices!V70-1),4)</f>
         <v>6.2454999999999998</v>
       </c>
     </row>
@@ -13659,39 +14516,51 @@
         <v>7.7127999999999997</v>
       </c>
       <c r="K72" s="16">
+        <f>ROUND(100*(Índices!K72/Índices!K71-1),4)</f>
         <v>7.0674999999999999</v>
       </c>
       <c r="L72" s="16">
+        <f>ROUND(100*(Índices!L72/Índices!L71-1),4)</f>
         <v>11.203900000000001</v>
       </c>
       <c r="M72" s="16">
+        <f>ROUND(100*(Índices!M72/Índices!M71-1),4)</f>
         <v>4.5567000000000002</v>
       </c>
       <c r="N72" s="16">
+        <f>ROUND(100*(Índices!N72/Índices!N71-1),4)</f>
         <v>10.324199999999999</v>
       </c>
       <c r="O72" s="16">
+        <f>ROUND(100*(Índices!O72/Índices!O71-1),4)</f>
         <v>6.8418999999999999</v>
       </c>
       <c r="P72" s="16">
+        <f>ROUND(100*(Índices!P72/Índices!P71-1),4)</f>
         <v>5.5407000000000002</v>
       </c>
       <c r="Q72" s="16">
+        <f>ROUND(100*(Índices!Q72/Índices!Q71-1),4)</f>
         <v>6.8606999999999996</v>
       </c>
       <c r="R72" s="16">
+        <f>ROUND(100*(Índices!R72/Índices!R71-1),4)</f>
         <v>13.196400000000001</v>
       </c>
       <c r="S72" s="16">
+        <f>ROUND(100*(Índices!S72/Índices!S71-1),4)</f>
         <v>6.6818999999999997</v>
       </c>
       <c r="T72" s="16">
+        <f>ROUND(100*(Índices!T72/Índices!T71-1),4)</f>
         <v>9.7346000000000004</v>
       </c>
       <c r="U72" s="17">
+        <f>ROUND(100*(Índices!U72/Índices!U71-1),4)</f>
         <v>8.1035000000000004</v>
       </c>
       <c r="V72" s="15">
+        <f>ROUND(100*(Índices!V72/Índices!V71-1),4)</f>
         <v>9.3823000000000008</v>
       </c>
     </row>
@@ -13732,39 +14601,51 @@
         <v>7.1933999999999996</v>
       </c>
       <c r="K73" s="16">
+        <f>ROUND(100*(Índices!K73/Índices!K72-1),4)</f>
         <v>8.0449999999999999</v>
       </c>
       <c r="L73" s="16">
+        <f>ROUND(100*(Índices!L73/Índices!L72-1),4)</f>
         <v>9.8808000000000007</v>
       </c>
       <c r="M73" s="16">
+        <f>ROUND(100*(Índices!M73/Índices!M72-1),4)</f>
         <v>5.5495000000000001</v>
       </c>
       <c r="N73" s="16">
+        <f>ROUND(100*(Índices!N73/Índices!N72-1),4)</f>
         <v>8.4260999999999999</v>
       </c>
       <c r="O73" s="16">
+        <f>ROUND(100*(Índices!O73/Índices!O72-1),4)</f>
         <v>5.7171000000000003</v>
       </c>
       <c r="P73" s="16">
+        <f>ROUND(100*(Índices!P73/Índices!P72-1),4)</f>
         <v>6.7980999999999998</v>
       </c>
       <c r="Q73" s="16">
+        <f>ROUND(100*(Índices!Q73/Índices!Q72-1),4)</f>
         <v>6.5099</v>
       </c>
       <c r="R73" s="16">
+        <f>ROUND(100*(Índices!R73/Índices!R72-1),4)</f>
         <v>5.0244</v>
       </c>
       <c r="S73" s="16">
+        <f>ROUND(100*(Índices!S73/Índices!S72-1),4)</f>
         <v>5.1094999999999997</v>
       </c>
       <c r="T73" s="16">
+        <f>ROUND(100*(Índices!T73/Índices!T72-1),4)</f>
         <v>6.6879</v>
       </c>
       <c r="U73" s="17">
+        <f>ROUND(100*(Índices!U73/Índices!U72-1),4)</f>
         <v>8.6515000000000004</v>
       </c>
       <c r="V73" s="15">
+        <f>ROUND(100*(Índices!V73/Índices!V72-1),4)</f>
         <v>7.5420999999999996</v>
       </c>
     </row>
@@ -13805,39 +14686,51 @@
         <v>6.4233000000000002</v>
       </c>
       <c r="K74" s="16">
+        <f>ROUND(100*(Índices!K74/Índices!K73-1),4)</f>
         <v>8.2986000000000004</v>
       </c>
       <c r="L74" s="16">
+        <f>ROUND(100*(Índices!L74/Índices!L73-1),4)</f>
         <v>7.2717999999999998</v>
       </c>
       <c r="M74" s="16">
+        <f>ROUND(100*(Índices!M74/Índices!M73-1),4)</f>
         <v>3.1425000000000001</v>
       </c>
       <c r="N74" s="16">
+        <f>ROUND(100*(Índices!N74/Índices!N73-1),4)</f>
         <v>6.0476999999999999</v>
       </c>
       <c r="O74" s="16">
+        <f>ROUND(100*(Índices!O74/Índices!O73-1),4)</f>
         <v>4.3326000000000002</v>
       </c>
       <c r="P74" s="16">
+        <f>ROUND(100*(Índices!P74/Índices!P73-1),4)</f>
         <v>5.7956000000000003</v>
       </c>
       <c r="Q74" s="16">
+        <f>ROUND(100*(Índices!Q74/Índices!Q73-1),4)</f>
         <v>3.2492999999999999</v>
       </c>
       <c r="R74" s="16">
+        <f>ROUND(100*(Índices!R74/Índices!R73-1),4)</f>
         <v>5.2401</v>
       </c>
       <c r="S74" s="16">
+        <f>ROUND(100*(Índices!S74/Índices!S73-1),4)</f>
         <v>5.4345999999999997</v>
       </c>
       <c r="T74" s="16">
+        <f>ROUND(100*(Índices!T74/Índices!T73-1),4)</f>
         <v>4.9492000000000003</v>
       </c>
       <c r="U74" s="17">
+        <f>ROUND(100*(Índices!U74/Índices!U73-1),4)</f>
         <v>6.7948000000000004</v>
       </c>
       <c r="V74" s="15">
+        <f>ROUND(100*(Índices!V74/Índices!V73-1),4)</f>
         <v>6.2728999999999999</v>
       </c>
     </row>
@@ -13878,39 +14771,51 @@
         <v>6.1540999999999997</v>
       </c>
       <c r="K75" s="16">
+        <f>ROUND(100*(Índices!K75/Índices!K74-1),4)</f>
         <v>5.7168000000000001</v>
       </c>
       <c r="L75" s="16">
+        <f>ROUND(100*(Índices!L75/Índices!L74-1),4)</f>
         <v>6.3273999999999999</v>
       </c>
       <c r="M75" s="16">
+        <f>ROUND(100*(Índices!M75/Índices!M74-1),4)</f>
         <v>7.4356999999999998</v>
       </c>
       <c r="N75" s="16">
+        <f>ROUND(100*(Índices!N75/Índices!N74-1),4)</f>
         <v>4.9236000000000004</v>
       </c>
       <c r="O75" s="16">
+        <f>ROUND(100*(Índices!O75/Índices!O74-1),4)</f>
         <v>7.1135000000000002</v>
       </c>
       <c r="P75" s="16">
+        <f>ROUND(100*(Índices!P75/Índices!P74-1),4)</f>
         <v>4.4977999999999998</v>
       </c>
       <c r="Q75" s="16">
+        <f>ROUND(100*(Índices!Q75/Índices!Q74-1),4)</f>
         <v>12.863799999999999</v>
       </c>
       <c r="R75" s="16">
+        <f>ROUND(100*(Índices!R75/Índices!R74-1),4)</f>
         <v>5.6348000000000003</v>
       </c>
       <c r="S75" s="16">
+        <f>ROUND(100*(Índices!S75/Índices!S74-1),4)</f>
         <v>9.6046999999999993</v>
       </c>
       <c r="T75" s="16">
+        <f>ROUND(100*(Índices!T75/Índices!T74-1),4)</f>
         <v>7.4821999999999997</v>
       </c>
       <c r="U75" s="17">
+        <f>ROUND(100*(Índices!U75/Índices!U74-1),4)</f>
         <v>6.1540999999999997</v>
       </c>
       <c r="V75" s="15">
+        <f>ROUND(100*(Índices!V75/Índices!V74-1),4)</f>
         <v>6.1764000000000001</v>
       </c>
     </row>
@@ -13951,39 +14856,51 @@
         <v>3.9645999999999999</v>
       </c>
       <c r="K76" s="16">
+        <f>ROUND(100*(Índices!K76/Índices!K75-1),4)</f>
         <v>5.4661</v>
       </c>
       <c r="L76" s="16">
+        <f>ROUND(100*(Índices!L76/Índices!L75-1),4)</f>
         <v>5.4363999999999999</v>
       </c>
       <c r="M76" s="16">
+        <f>ROUND(100*(Índices!M76/Índices!M75-1),4)</f>
         <v>8.5505999999999993</v>
       </c>
       <c r="N76" s="16">
+        <f>ROUND(100*(Índices!N76/Índices!N75-1),4)</f>
         <v>5.4226999999999999</v>
       </c>
       <c r="O76" s="16">
+        <f>ROUND(100*(Índices!O76/Índices!O75-1),4)</f>
         <v>4.1056999999999997</v>
       </c>
       <c r="P76" s="16">
+        <f>ROUND(100*(Índices!P76/Índices!P75-1),4)</f>
         <v>6.0602</v>
       </c>
       <c r="Q76" s="16">
+        <f>ROUND(100*(Índices!Q76/Índices!Q75-1),4)</f>
         <v>6.8594999999999997</v>
       </c>
       <c r="R76" s="16">
+        <f>ROUND(100*(Índices!R76/Índices!R75-1),4)</f>
         <v>4.1597</v>
       </c>
       <c r="S76" s="16">
+        <f>ROUND(100*(Índices!S76/Índices!S75-1),4)</f>
         <v>6.5237999999999996</v>
       </c>
       <c r="T76" s="16">
+        <f>ROUND(100*(Índices!T76/Índices!T75-1),4)</f>
         <v>5.5529999999999999</v>
       </c>
       <c r="U76" s="17">
+        <f>ROUND(100*(Índices!U76/Índices!U75-1),4)</f>
         <v>5.8413000000000004</v>
       </c>
       <c r="V76" s="15">
+        <f>ROUND(100*(Índices!V76/Índices!V75-1),4)</f>
         <v>4.7290999999999999</v>
       </c>
     </row>
@@ -14024,39 +14941,51 @@
         <v>3.6168</v>
       </c>
       <c r="K77" s="16">
+        <f>ROUND(100*(Índices!K77/Índices!K76-1),4)</f>
         <v>6.7271999999999998</v>
       </c>
       <c r="L77" s="16">
+        <f>ROUND(100*(Índices!L77/Índices!L76-1),4)</f>
         <v>4.1062000000000003</v>
       </c>
       <c r="M77" s="16">
+        <f>ROUND(100*(Índices!M77/Índices!M76-1),4)</f>
         <v>4.1905000000000001</v>
       </c>
       <c r="N77" s="16">
+        <f>ROUND(100*(Índices!N77/Índices!N76-1),4)</f>
         <v>5.9387999999999996</v>
       </c>
       <c r="O77" s="16">
+        <f>ROUND(100*(Índices!O77/Índices!O76-1),4)</f>
         <v>5.6829999999999998</v>
       </c>
       <c r="P77" s="16">
+        <f>ROUND(100*(Índices!P77/Índices!P76-1),4)</f>
         <v>5.7976000000000001</v>
       </c>
       <c r="Q77" s="16">
+        <f>ROUND(100*(Índices!Q77/Índices!Q76-1),4)</f>
         <v>2.9906000000000001</v>
       </c>
       <c r="R77" s="16">
+        <f>ROUND(100*(Índices!R77/Índices!R76-1),4)</f>
         <v>4.6047000000000002</v>
       </c>
       <c r="S77" s="16">
+        <f>ROUND(100*(Índices!S77/Índices!S76-1),4)</f>
         <v>7.5102000000000002</v>
       </c>
       <c r="T77" s="16">
+        <f>ROUND(100*(Índices!T77/Índices!T76-1),4)</f>
         <v>7.0899000000000001</v>
       </c>
       <c r="U77" s="17">
+        <f>ROUND(100*(Índices!U77/Índices!U76-1),4)</f>
         <v>5.7485999999999997</v>
       </c>
       <c r="V77" s="15">
+        <f>ROUND(100*(Índices!V77/Índices!V76-1),4)</f>
         <v>4.6736000000000004</v>
       </c>
     </row>
@@ -14097,39 +15026,51 @@
         <v>5.0232999999999999</v>
       </c>
       <c r="K78" s="16">
+        <f>ROUND(100*(Índices!K78/Índices!K77-1),4)</f>
         <v>5.7912999999999997</v>
       </c>
       <c r="L78" s="16">
+        <f>ROUND(100*(Índices!L78/Índices!L77-1),4)</f>
         <v>4.5631000000000004</v>
       </c>
       <c r="M78" s="16">
+        <f>ROUND(100*(Índices!M78/Índices!M77-1),4)</f>
         <v>8.0393000000000008</v>
       </c>
       <c r="N78" s="16">
+        <f>ROUND(100*(Índices!N78/Índices!N77-1),4)</f>
         <v>5.4081999999999999</v>
       </c>
       <c r="O78" s="16">
+        <f>ROUND(100*(Índices!O78/Índices!O77-1),4)</f>
         <v>4.8879999999999999</v>
       </c>
       <c r="P78" s="16">
+        <f>ROUND(100*(Índices!P78/Índices!P77-1),4)</f>
         <v>5.9306999999999999</v>
       </c>
       <c r="Q78" s="16">
+        <f>ROUND(100*(Índices!Q78/Índices!Q77-1),4)</f>
         <v>3.6368</v>
       </c>
       <c r="R78" s="16">
+        <f>ROUND(100*(Índices!R78/Índices!R77-1),4)</f>
         <v>8.9690999999999992</v>
       </c>
       <c r="S78" s="16">
+        <f>ROUND(100*(Índices!S78/Índices!S77-1),4)</f>
         <v>5.4950999999999999</v>
       </c>
       <c r="T78" s="16">
+        <f>ROUND(100*(Índices!T78/Índices!T77-1),4)</f>
         <v>6.0357000000000003</v>
       </c>
       <c r="U78" s="17">
+        <f>ROUND(100*(Índices!U78/Índices!U77-1),4)</f>
         <v>6.8041999999999998</v>
       </c>
       <c r="V78" s="15">
+        <f>ROUND(100*(Índices!V78/Índices!V77-1),4)</f>
         <v>5.6157000000000004</v>
       </c>
     </row>
@@ -14170,39 +15111,51 @@
         <v>8.4095999999999993</v>
       </c>
       <c r="K79" s="16">
+        <f>ROUND(100*(Índices!K79/Índices!K78-1),4)</f>
         <v>4.9448999999999996</v>
       </c>
       <c r="L79" s="16">
+        <f>ROUND(100*(Índices!L79/Índices!L78-1),4)</f>
         <v>5.4911000000000003</v>
       </c>
       <c r="M79" s="16">
+        <f>ROUND(100*(Índices!M79/Índices!M78-1),4)</f>
         <v>4.8117999999999999</v>
       </c>
       <c r="N79" s="16">
+        <f>ROUND(100*(Índices!N79/Índices!N78-1),4)</f>
         <v>5.0514000000000001</v>
       </c>
       <c r="O79" s="16">
+        <f>ROUND(100*(Índices!O79/Índices!O78-1),4)</f>
         <v>5.3212000000000002</v>
       </c>
       <c r="P79" s="16">
+        <f>ROUND(100*(Índices!P79/Índices!P78-1),4)</f>
         <v>4.8672000000000004</v>
       </c>
       <c r="Q79" s="16">
+        <f>ROUND(100*(Índices!Q79/Índices!Q78-1),4)</f>
         <v>5.1454000000000004</v>
       </c>
       <c r="R79" s="16">
+        <f>ROUND(100*(Índices!R79/Índices!R78-1),4)</f>
         <v>6.1383000000000001</v>
       </c>
       <c r="S79" s="16">
+        <f>ROUND(100*(Índices!S79/Índices!S78-1),4)</f>
         <v>4.4001999999999999</v>
       </c>
       <c r="T79" s="16">
+        <f>ROUND(100*(Índices!T79/Índices!T78-1),4)</f>
         <v>7.4892000000000003</v>
       </c>
       <c r="U79" s="17">
+        <f>ROUND(100*(Índices!U79/Índices!U78-1),4)</f>
         <v>6.4878999999999998</v>
       </c>
       <c r="V79" s="15">
+        <f>ROUND(100*(Índices!V79/Índices!V78-1),4)</f>
         <v>6.9964000000000004</v>
       </c>
     </row>
@@ -14243,39 +15196,51 @@
         <v>8.0272000000000006</v>
       </c>
       <c r="K80" s="16">
+        <f>ROUND(100*(Índices!K80/Índices!K79-1),4)</f>
         <v>7.0099</v>
       </c>
       <c r="L80" s="16">
+        <f>ROUND(100*(Índices!L80/Índices!L79-1),4)</f>
         <v>5.6176000000000004</v>
       </c>
       <c r="M80" s="16">
+        <f>ROUND(100*(Índices!M80/Índices!M79-1),4)</f>
         <v>6.5286999999999997</v>
       </c>
       <c r="N80" s="16">
+        <f>ROUND(100*(Índices!N80/Índices!N79-1),4)</f>
         <v>5.8083</v>
       </c>
       <c r="O80" s="16">
+        <f>ROUND(100*(Índices!O80/Índices!O79-1),4)</f>
         <v>5.7218</v>
       </c>
       <c r="P80" s="16">
+        <f>ROUND(100*(Índices!P80/Índices!P79-1),4)</f>
         <v>5.2965999999999998</v>
       </c>
       <c r="Q80" s="16">
+        <f>ROUND(100*(Índices!Q80/Índices!Q79-1),4)</f>
         <v>2.2435999999999998</v>
       </c>
       <c r="R80" s="16">
+        <f>ROUND(100*(Índices!R80/Índices!R79-1),4)</f>
         <v>4.3699000000000003</v>
       </c>
       <c r="S80" s="16">
+        <f>ROUND(100*(Índices!S80/Índices!S79-1),4)</f>
         <v>5.3960999999999997</v>
       </c>
       <c r="T80" s="16">
+        <f>ROUND(100*(Índices!T80/Índices!T79-1),4)</f>
         <v>7.8384999999999998</v>
       </c>
       <c r="U80" s="17">
+        <f>ROUND(100*(Índices!U80/Índices!U79-1),4)</f>
         <v>6.3159999999999998</v>
       </c>
       <c r="V80" s="15">
+        <f>ROUND(100*(Índices!V80/Índices!V79-1),4)</f>
         <v>6.9038000000000004</v>
       </c>
     </row>
@@ -14316,39 +15281,51 @@
         <v>10.4635</v>
       </c>
       <c r="K81" s="16">
+        <f>ROUND(100*(Índices!K81/Índices!K80-1),4)</f>
         <v>5.1749000000000001</v>
       </c>
       <c r="L81" s="16">
+        <f>ROUND(100*(Índices!L81/Índices!L80-1),4)</f>
         <v>8.1166</v>
       </c>
       <c r="M81" s="16">
+        <f>ROUND(100*(Índices!M81/Índices!M80-1),4)</f>
         <v>5.5396999999999998</v>
       </c>
       <c r="N81" s="16">
+        <f>ROUND(100*(Índices!N81/Índices!N80-1),4)</f>
         <v>8.6427999999999994</v>
       </c>
       <c r="O81" s="16">
+        <f>ROUND(100*(Índices!O81/Índices!O80-1),4)</f>
         <v>6.5762999999999998</v>
       </c>
       <c r="P81" s="16">
+        <f>ROUND(100*(Índices!P81/Índices!P80-1),4)</f>
         <v>6.4295999999999998</v>
       </c>
       <c r="Q81" s="16">
+        <f>ROUND(100*(Índices!Q81/Índices!Q80-1),4)</f>
         <v>6.2846000000000002</v>
       </c>
       <c r="R81" s="16">
+        <f>ROUND(100*(Índices!R81/Índices!R80-1),4)</f>
         <v>7.5522</v>
       </c>
       <c r="S81" s="16">
+        <f>ROUND(100*(Índices!S81/Índices!S80-1),4)</f>
         <v>5.6021999999999998</v>
       </c>
       <c r="T81" s="16">
+        <f>ROUND(100*(Índices!T81/Índices!T80-1),4)</f>
         <v>9.8788</v>
       </c>
       <c r="U81" s="17">
+        <f>ROUND(100*(Índices!U81/Índices!U80-1),4)</f>
         <v>6.5972999999999997</v>
       </c>
       <c r="V81" s="15">
+        <f>ROUND(100*(Índices!V81/Índices!V80-1),4)</f>
         <v>9.1041000000000007</v>
       </c>
     </row>
@@ -14389,39 +15366,51 @@
         <v>7.1569000000000003</v>
       </c>
       <c r="K82" s="16">
+        <f>ROUND(100*(Índices!K82/Índices!K81-1),4)</f>
         <v>9.1568000000000005</v>
       </c>
       <c r="L82" s="16">
+        <f>ROUND(100*(Índices!L82/Índices!L81-1),4)</f>
         <v>8.4385999999999992</v>
       </c>
       <c r="M82" s="16">
+        <f>ROUND(100*(Índices!M82/Índices!M81-1),4)</f>
         <v>11.8596</v>
       </c>
       <c r="N82" s="16">
+        <f>ROUND(100*(Índices!N82/Índices!N81-1),4)</f>
         <v>8.7582000000000004</v>
       </c>
       <c r="O82" s="16">
+        <f>ROUND(100*(Índices!O82/Índices!O81-1),4)</f>
         <v>9.0589999999999993</v>
       </c>
       <c r="P82" s="16">
+        <f>ROUND(100*(Índices!P82/Índices!P81-1),4)</f>
         <v>8.1126000000000005</v>
       </c>
       <c r="Q82" s="16">
+        <f>ROUND(100*(Índices!Q82/Índices!Q81-1),4)</f>
         <v>7.5900999999999996</v>
       </c>
       <c r="R82" s="16">
+        <f>ROUND(100*(Índices!R82/Índices!R81-1),4)</f>
         <v>8.3775999999999993</v>
       </c>
       <c r="S82" s="16">
+        <f>ROUND(100*(Índices!S82/Índices!S81-1),4)</f>
         <v>5.6154999999999999</v>
       </c>
       <c r="T82" s="16">
+        <f>ROUND(100*(Índices!T82/Índices!T81-1),4)</f>
         <v>9.4174000000000007</v>
       </c>
       <c r="U82" s="17">
+        <f>ROUND(100*(Índices!U82/Índices!U81-1),4)</f>
         <v>7.0998000000000001</v>
       </c>
       <c r="V82" s="15">
+        <f>ROUND(100*(Índices!V82/Índices!V81-1),4)</f>
         <v>8.0434999999999999</v>
       </c>
     </row>
@@ -14462,39 +15451,51 @@
         <v>6.0064000000000002</v>
       </c>
       <c r="K83" s="16">
+        <f>ROUND(100*(Índices!K83/Índices!K82-1),4)</f>
         <v>5.9130000000000003</v>
       </c>
       <c r="L83" s="16">
+        <f>ROUND(100*(Índices!L83/Índices!L82-1),4)</f>
         <v>5.8930999999999996</v>
       </c>
       <c r="M83" s="16">
+        <f>ROUND(100*(Índices!M83/Índices!M82-1),4)</f>
         <v>8.1280000000000001</v>
       </c>
       <c r="N83" s="16">
+        <f>ROUND(100*(Índices!N83/Índices!N82-1),4)</f>
         <v>7.9974999999999996</v>
       </c>
       <c r="O83" s="16">
+        <f>ROUND(100*(Índices!O83/Índices!O82-1),4)</f>
         <v>8.6036000000000001</v>
       </c>
       <c r="P83" s="16">
+        <f>ROUND(100*(Índices!P83/Índices!P82-1),4)</f>
         <v>6.4973000000000001</v>
       </c>
       <c r="Q83" s="16">
+        <f>ROUND(100*(Índices!Q83/Índices!Q82-1),4)</f>
         <v>10.736000000000001</v>
       </c>
       <c r="R83" s="16">
+        <f>ROUND(100*(Índices!R83/Índices!R82-1),4)</f>
         <v>6.4600999999999997</v>
       </c>
       <c r="S83" s="16">
+        <f>ROUND(100*(Índices!S83/Índices!S82-1),4)</f>
         <v>8.3574000000000002</v>
       </c>
       <c r="T83" s="16">
+        <f>ROUND(100*(Índices!T83/Índices!T82-1),4)</f>
         <v>6.3658999999999999</v>
       </c>
       <c r="U83" s="17">
+        <f>ROUND(100*(Índices!U83/Índices!U82-1),4)</f>
         <v>6.5537000000000001</v>
       </c>
       <c r="V83" s="15">
+        <f>ROUND(100*(Índices!V83/Índices!V82-1),4)</f>
         <v>6.3170999999999999</v>
       </c>
     </row>
@@ -14535,39 +15536,51 @@
         <v>7.4528999999999996</v>
       </c>
       <c r="K84" s="16">
+        <f>ROUND(100*(Índices!K84/Índices!K83-1),4)</f>
         <v>9.6751000000000005</v>
       </c>
       <c r="L84" s="16">
+        <f>ROUND(100*(Índices!L84/Índices!L83-1),4)</f>
         <v>6.0027999999999997</v>
       </c>
       <c r="M84" s="16">
+        <f>ROUND(100*(Índices!M84/Índices!M83-1),4)</f>
         <v>4.0037000000000003</v>
       </c>
       <c r="N84" s="16">
+        <f>ROUND(100*(Índices!N84/Índices!N83-1),4)</f>
         <v>6.1509</v>
       </c>
       <c r="O84" s="16">
+        <f>ROUND(100*(Índices!O84/Índices!O83-1),4)</f>
         <v>9.0420999999999996</v>
       </c>
       <c r="P84" s="16">
+        <f>ROUND(100*(Índices!P84/Índices!P83-1),4)</f>
         <v>5.3342999999999998</v>
       </c>
       <c r="Q84" s="16">
+        <f>ROUND(100*(Índices!Q84/Índices!Q83-1),4)</f>
         <v>13.696099999999999</v>
       </c>
       <c r="R84" s="16">
+        <f>ROUND(100*(Índices!R84/Índices!R83-1),4)</f>
         <v>11.2011</v>
       </c>
       <c r="S84" s="16">
+        <f>ROUND(100*(Índices!S84/Índices!S83-1),4)</f>
         <v>7.4119000000000002</v>
       </c>
       <c r="T84" s="16">
+        <f>ROUND(100*(Índices!T84/Índices!T83-1),4)</f>
         <v>7.3982999999999999</v>
       </c>
       <c r="U84" s="17">
+        <f>ROUND(100*(Índices!U84/Índices!U83-1),4)</f>
         <v>6.3228999999999997</v>
       </c>
       <c r="V84" s="15">
+        <f>ROUND(100*(Índices!V84/Índices!V83-1),4)</f>
         <v>7.4741</v>
       </c>
     </row>
@@ -14608,39 +15621,51 @@
         <v>15.696999999999999</v>
       </c>
       <c r="K85" s="16">
+        <f>ROUND(100*(Índices!K85/Índices!K84-1),4)</f>
         <v>9.5191999999999997</v>
       </c>
       <c r="L85" s="16">
+        <f>ROUND(100*(Índices!L85/Índices!L84-1),4)</f>
         <v>9.5129000000000001</v>
       </c>
       <c r="M85" s="16">
+        <f>ROUND(100*(Índices!M85/Índices!M84-1),4)</f>
         <v>9.0033999999999992</v>
       </c>
       <c r="N85" s="16">
+        <f>ROUND(100*(Índices!N85/Índices!N84-1),4)</f>
         <v>14.0593</v>
       </c>
       <c r="O85" s="16">
+        <f>ROUND(100*(Índices!O85/Índices!O84-1),4)</f>
         <v>15.2477</v>
       </c>
       <c r="P85" s="16">
+        <f>ROUND(100*(Índices!P85/Índices!P84-1),4)</f>
         <v>10.4903</v>
       </c>
       <c r="Q85" s="16">
+        <f>ROUND(100*(Índices!Q85/Índices!Q84-1),4)</f>
         <v>7.1186999999999996</v>
       </c>
       <c r="R85" s="16">
+        <f>ROUND(100*(Índices!R85/Índices!R84-1),4)</f>
         <v>11.583299999999999</v>
       </c>
       <c r="S85" s="16">
+        <f>ROUND(100*(Índices!S85/Índices!S84-1),4)</f>
         <v>8.8645999999999994</v>
       </c>
       <c r="T85" s="16">
+        <f>ROUND(100*(Índices!T85/Índices!T84-1),4)</f>
         <v>12.483599999999999</v>
       </c>
       <c r="U85" s="17">
+        <f>ROUND(100*(Índices!U85/Índices!U84-1),4)</f>
         <v>9.36</v>
       </c>
       <c r="V85" s="15">
+        <f>ROUND(100*(Índices!V85/Índices!V84-1),4)</f>
         <v>13.183299999999999</v>
       </c>
     </row>
@@ -14681,39 +15706,51 @@
         <v>14.0038</v>
       </c>
       <c r="K86" s="16">
+        <f>ROUND(100*(Índices!K86/Índices!K85-1),4)</f>
         <v>10.401</v>
       </c>
       <c r="L86" s="16">
+        <f>ROUND(100*(Índices!L86/Índices!L85-1),4)</f>
         <v>11.9557</v>
       </c>
       <c r="M86" s="16">
+        <f>ROUND(100*(Índices!M86/Índices!M85-1),4)</f>
         <v>8.5284999999999993</v>
       </c>
       <c r="N86" s="16">
+        <f>ROUND(100*(Índices!N86/Índices!N85-1),4)</f>
         <v>12.648099999999999</v>
       </c>
       <c r="O86" s="16">
+        <f>ROUND(100*(Índices!O86/Índices!O85-1),4)</f>
         <v>9.5690000000000008</v>
       </c>
       <c r="P86" s="16">
+        <f>ROUND(100*(Índices!P86/Índices!P85-1),4)</f>
         <v>10.8613</v>
       </c>
       <c r="Q86" s="16">
+        <f>ROUND(100*(Índices!Q86/Índices!Q85-1),4)</f>
         <v>10.7159</v>
       </c>
       <c r="R86" s="16">
+        <f>ROUND(100*(Índices!R86/Índices!R85-1),4)</f>
         <v>15.1358</v>
       </c>
       <c r="S86" s="16">
+        <f>ROUND(100*(Índices!S86/Índices!S85-1),4)</f>
         <v>10.354100000000001</v>
       </c>
       <c r="T86" s="16">
+        <f>ROUND(100*(Índices!T86/Índices!T85-1),4)</f>
         <v>13.3858</v>
       </c>
       <c r="U86" s="17">
+        <f>ROUND(100*(Índices!U86/Índices!U85-1),4)</f>
         <v>11.68</v>
       </c>
       <c r="V86" s="15">
+        <f>ROUND(100*(Índices!V86/Índices!V85-1),4)</f>
         <v>13.3774</v>
       </c>
     </row>
@@ -14754,39 +15791,51 @@
         <v>7.6951000000000001</v>
       </c>
       <c r="K87" s="16">
+        <f>ROUND(100*(Índices!K87/Índices!K86-1),4)</f>
         <v>10.1191</v>
       </c>
       <c r="L87" s="16">
+        <f>ROUND(100*(Índices!L87/Índices!L86-1),4)</f>
         <v>10.5251</v>
       </c>
       <c r="M87" s="16">
+        <f>ROUND(100*(Índices!M87/Índices!M86-1),4)</f>
         <v>7.7514000000000003</v>
       </c>
       <c r="N87" s="16">
+        <f>ROUND(100*(Índices!N87/Índices!N86-1),4)</f>
         <v>10.698499999999999</v>
       </c>
       <c r="O87" s="16">
+        <f>ROUND(100*(Índices!O87/Índices!O86-1),4)</f>
         <v>5.1062000000000003</v>
       </c>
       <c r="P87" s="16">
+        <f>ROUND(100*(Índices!P87/Índices!P86-1),4)</f>
         <v>7.1205999999999996</v>
       </c>
       <c r="Q87" s="16">
+        <f>ROUND(100*(Índices!Q87/Índices!Q86-1),4)</f>
         <v>13.2967</v>
       </c>
       <c r="R87" s="16">
+        <f>ROUND(100*(Índices!R87/Índices!R86-1),4)</f>
         <v>9.2935999999999996</v>
       </c>
       <c r="S87" s="16">
+        <f>ROUND(100*(Índices!S87/Índices!S86-1),4)</f>
         <v>9.8818000000000001</v>
       </c>
       <c r="T87" s="16">
+        <f>ROUND(100*(Índices!T87/Índices!T86-1),4)</f>
         <v>8.8413000000000004</v>
       </c>
       <c r="U87" s="17">
+        <f>ROUND(100*(Índices!U87/Índices!U86-1),4)</f>
         <v>7.6627000000000001</v>
       </c>
       <c r="V87" s="15">
+        <f>ROUND(100*(Índices!V87/Índices!V86-1),4)</f>
         <v>8.7851999999999997</v>
       </c>
     </row>
@@ -14827,39 +15876,51 @@
         <v>16.177499999999998</v>
       </c>
       <c r="K88" s="16">
+        <f>ROUND(100*(Índices!K88/Índices!K87-1),4)</f>
         <v>10.8324</v>
       </c>
       <c r="L88" s="16">
+        <f>ROUND(100*(Índices!L88/Índices!L87-1),4)</f>
         <v>10.970599999999999</v>
       </c>
       <c r="M88" s="16">
+        <f>ROUND(100*(Índices!M88/Índices!M87-1),4)</f>
         <v>7.1440999999999999</v>
       </c>
       <c r="N88" s="16">
+        <f>ROUND(100*(Índices!N88/Índices!N87-1),4)</f>
         <v>12.4428</v>
       </c>
       <c r="O88" s="16">
+        <f>ROUND(100*(Índices!O88/Índices!O87-1),4)</f>
         <v>15.8459</v>
       </c>
       <c r="P88" s="16">
+        <f>ROUND(100*(Índices!P88/Índices!P87-1),4)</f>
         <v>10.409599999999999</v>
       </c>
       <c r="Q88" s="16">
+        <f>ROUND(100*(Índices!Q88/Índices!Q87-1),4)</f>
         <v>15.744199999999999</v>
       </c>
       <c r="R88" s="16">
+        <f>ROUND(100*(Índices!R88/Índices!R87-1),4)</f>
         <v>13.197100000000001</v>
       </c>
       <c r="S88" s="16">
+        <f>ROUND(100*(Índices!S88/Índices!S87-1),4)</f>
         <v>11.1882</v>
       </c>
       <c r="T88" s="16">
+        <f>ROUND(100*(Índices!T88/Índices!T87-1),4)</f>
         <v>12.0669</v>
       </c>
       <c r="U88" s="17">
+        <f>ROUND(100*(Índices!U88/Índices!U87-1),4)</f>
         <v>11.5144</v>
       </c>
       <c r="V88" s="15">
+        <f>ROUND(100*(Índices!V88/Índices!V87-1),4)</f>
         <v>13.7128</v>
       </c>
     </row>
@@ -14900,39 +15961,51 @@
         <v>28.386500000000002</v>
       </c>
       <c r="K89" s="16">
+        <f>ROUND(100*(Índices!K89/Índices!K88-1),4)</f>
         <v>19.7699</v>
       </c>
       <c r="L89" s="16">
+        <f>ROUND(100*(Índices!L89/Índices!L88-1),4)</f>
         <v>17.014199999999999</v>
       </c>
       <c r="M89" s="16">
+        <f>ROUND(100*(Índices!M89/Índices!M88-1),4)</f>
         <v>13.781599999999999</v>
       </c>
       <c r="N89" s="16">
+        <f>ROUND(100*(Índices!N89/Índices!N88-1),4)</f>
         <v>30.681899999999999</v>
       </c>
       <c r="O89" s="16">
+        <f>ROUND(100*(Índices!O89/Índices!O88-1),4)</f>
         <v>32.6252</v>
       </c>
       <c r="P89" s="16">
+        <f>ROUND(100*(Índices!P89/Índices!P88-1),4)</f>
         <v>31.6769</v>
       </c>
       <c r="Q89" s="16">
+        <f>ROUND(100*(Índices!Q89/Índices!Q88-1),4)</f>
         <v>15.1836</v>
       </c>
       <c r="R89" s="16">
+        <f>ROUND(100*(Índices!R89/Índices!R88-1),4)</f>
         <v>20.186900000000001</v>
       </c>
       <c r="S89" s="16">
+        <f>ROUND(100*(Índices!S89/Índices!S88-1),4)</f>
         <v>10.439500000000001</v>
       </c>
       <c r="T89" s="16">
+        <f>ROUND(100*(Índices!T89/Índices!T88-1),4)</f>
         <v>21.505400000000002</v>
       </c>
       <c r="U89" s="17">
+        <f>ROUND(100*(Índices!U89/Índices!U88-1),4)</f>
         <v>32.678800000000003</v>
       </c>
       <c r="V89" s="15">
+        <f>ROUND(100*(Índices!V89/Índices!V88-1),4)</f>
         <v>24.908100000000001</v>
       </c>
     </row>
@@ -14973,39 +16046,51 @@
         <v>18.4206</v>
       </c>
       <c r="K90" s="16">
+        <f>ROUND(100*(Índices!K90/Índices!K89-1),4)</f>
         <v>19.333300000000001</v>
       </c>
       <c r="L90" s="16">
+        <f>ROUND(100*(Índices!L90/Índices!L89-1),4)</f>
         <v>13.9252</v>
       </c>
       <c r="M90" s="16">
+        <f>ROUND(100*(Índices!M90/Índices!M89-1),4)</f>
         <v>14.2447</v>
       </c>
       <c r="N90" s="16">
+        <f>ROUND(100*(Índices!N90/Índices!N89-1),4)</f>
         <v>22.320900000000002</v>
       </c>
       <c r="O90" s="16">
+        <f>ROUND(100*(Índices!O90/Índices!O89-1),4)</f>
         <v>20.450700000000001</v>
       </c>
       <c r="P90" s="16">
+        <f>ROUND(100*(Índices!P90/Índices!P89-1),4)</f>
         <v>26.314499999999999</v>
       </c>
       <c r="Q90" s="16">
+        <f>ROUND(100*(Índices!Q90/Índices!Q89-1),4)</f>
         <v>19.771899999999999</v>
       </c>
       <c r="R90" s="16">
+        <f>ROUND(100*(Índices!R90/Índices!R89-1),4)</f>
         <v>24.017199999999999</v>
       </c>
       <c r="S90" s="16">
+        <f>ROUND(100*(Índices!S90/Índices!S89-1),4)</f>
         <v>5.6069000000000004</v>
       </c>
       <c r="T90" s="16">
+        <f>ROUND(100*(Índices!T90/Índices!T89-1),4)</f>
         <v>19.231100000000001</v>
       </c>
       <c r="U90" s="17">
+        <f>ROUND(100*(Índices!U90/Índices!U89-1),4)</f>
         <v>44.383099999999999</v>
       </c>
       <c r="V90" s="15">
+        <f>ROUND(100*(Índices!V90/Índices!V89-1),4)</f>
         <v>19.935099999999998</v>
       </c>
     </row>
@@ -15046,39 +16131,51 @@
         <v>10.5022</v>
       </c>
       <c r="K91" s="16">
+        <f>ROUND(100*(Índices!K91/Índices!K90-1),4)</f>
         <v>17.358000000000001</v>
       </c>
       <c r="L91" s="16">
+        <f>ROUND(100*(Índices!L91/Índices!L90-1),4)</f>
         <v>8.8325999999999993</v>
       </c>
       <c r="M91" s="16">
+        <f>ROUND(100*(Índices!M91/Índices!M90-1),4)</f>
         <v>20.098400000000002</v>
       </c>
       <c r="N91" s="16">
+        <f>ROUND(100*(Índices!N91/Índices!N90-1),4)</f>
         <v>10.3285</v>
       </c>
       <c r="O91" s="16">
+        <f>ROUND(100*(Índices!O91/Índices!O90-1),4)</f>
         <v>13.5549</v>
       </c>
       <c r="P91" s="16">
+        <f>ROUND(100*(Índices!P91/Índices!P90-1),4)</f>
         <v>21.3124</v>
       </c>
       <c r="Q91" s="16">
+        <f>ROUND(100*(Índices!Q91/Índices!Q90-1),4)</f>
         <v>21.319500000000001</v>
       </c>
       <c r="R91" s="16">
+        <f>ROUND(100*(Índices!R91/Índices!R90-1),4)</f>
         <v>8.5731000000000002</v>
       </c>
       <c r="S91" s="16">
+        <f>ROUND(100*(Índices!S91/Índices!S90-1),4)</f>
         <v>10.5665</v>
       </c>
       <c r="T91" s="16">
+        <f>ROUND(100*(Índices!T91/Índices!T90-1),4)</f>
         <v>11.0763</v>
       </c>
       <c r="U91" s="17">
+        <f>ROUND(100*(Índices!U91/Índices!U90-1),4)</f>
         <v>16.5928</v>
       </c>
       <c r="V91" s="15">
+        <f>ROUND(100*(Índices!V91/Índices!V90-1),4)</f>
         <v>10.6305</v>
       </c>
     </row>
@@ -15119,39 +16216,51 @@
         <v>9.2150999999999996</v>
       </c>
       <c r="K92" s="16">
+        <f>ROUND(100*(Índices!K92/Índices!K91-1),4)</f>
         <v>10.976800000000001</v>
       </c>
       <c r="L92" s="16">
+        <f>ROUND(100*(Índices!L92/Índices!L91-1),4)</f>
         <v>7.0989000000000004</v>
       </c>
       <c r="M92" s="16">
+        <f>ROUND(100*(Índices!M92/Índices!M91-1),4)</f>
         <v>13.2197</v>
       </c>
       <c r="N92" s="16">
+        <f>ROUND(100*(Índices!N92/Índices!N91-1),4)</f>
         <v>5.0319000000000003</v>
       </c>
       <c r="O92" s="16">
+        <f>ROUND(100*(Índices!O92/Índices!O91-1),4)</f>
         <v>12.206300000000001</v>
       </c>
       <c r="P92" s="16">
+        <f>ROUND(100*(Índices!P92/Índices!P91-1),4)</f>
         <v>12.997999999999999</v>
       </c>
       <c r="Q92" s="16">
+        <f>ROUND(100*(Índices!Q92/Índices!Q91-1),4)</f>
         <v>16.370699999999999</v>
       </c>
       <c r="R92" s="16">
+        <f>ROUND(100*(Índices!R92/Índices!R91-1),4)</f>
         <v>8.5126000000000008</v>
       </c>
       <c r="S92" s="16">
+        <f>ROUND(100*(Índices!S92/Índices!S91-1),4)</f>
         <v>23.4373</v>
       </c>
       <c r="T92" s="16">
+        <f>ROUND(100*(Índices!T92/Índices!T91-1),4)</f>
         <v>8.2866999999999997</v>
       </c>
       <c r="U92" s="17">
+        <f>ROUND(100*(Índices!U92/Índices!U91-1),4)</f>
         <v>9.5693999999999999</v>
       </c>
       <c r="V92" s="15">
+        <f>ROUND(100*(Índices!V92/Índices!V91-1),4)</f>
         <v>8.3788999999999998</v>
       </c>
     </row>
@@ -15192,39 +16301,51 @@
         <v>6.3246000000000002</v>
       </c>
       <c r="K93" s="16">
+        <f>ROUND(100*(Índices!K93/Índices!K92-1),4)</f>
         <v>6.8922999999999996</v>
       </c>
       <c r="L93" s="16">
+        <f>ROUND(100*(Índices!L93/Índices!L92-1),4)</f>
         <v>6.8451000000000004</v>
       </c>
       <c r="M93" s="16">
+        <f>ROUND(100*(Índices!M93/Índices!M92-1),4)</f>
         <v>35.386299999999999</v>
       </c>
       <c r="N93" s="16">
+        <f>ROUND(100*(Índices!N93/Índices!N92-1),4)</f>
         <v>6.4996999999999998</v>
       </c>
       <c r="O93" s="16">
+        <f>ROUND(100*(Índices!O93/Índices!O92-1),4)</f>
         <v>9.1286000000000005</v>
       </c>
       <c r="P93" s="16">
+        <f>ROUND(100*(Índices!P93/Índices!P92-1),4)</f>
         <v>6.2891000000000004</v>
       </c>
       <c r="Q93" s="16">
+        <f>ROUND(100*(Índices!Q93/Índices!Q92-1),4)</f>
         <v>13.994400000000001</v>
       </c>
       <c r="R93" s="16">
+        <f>ROUND(100*(Índices!R93/Índices!R92-1),4)</f>
         <v>7.1341999999999999</v>
       </c>
       <c r="S93" s="16">
+        <f>ROUND(100*(Índices!S93/Índices!S92-1),4)</f>
         <v>8.5754999999999999</v>
       </c>
       <c r="T93" s="16">
+        <f>ROUND(100*(Índices!T93/Índices!T92-1),4)</f>
         <v>7.3002000000000002</v>
       </c>
       <c r="U93" s="17">
+        <f>ROUND(100*(Índices!U93/Índices!U92-1),4)</f>
         <v>5.6855000000000002</v>
       </c>
       <c r="V93" s="15">
+        <f>ROUND(100*(Índices!V93/Índices!V92-1),4)</f>
         <v>6.6303000000000001</v>
       </c>
     </row>
@@ -15265,39 +16386,51 @@
         <v>6.1848999999999998</v>
       </c>
       <c r="K94" s="16">
+        <f>ROUND(100*(Índices!K94/Índices!K93-1),4)</f>
         <v>7.3925999999999998</v>
       </c>
       <c r="L94" s="16">
+        <f>ROUND(100*(Índices!L94/Índices!L93-1),4)</f>
         <v>4.2073</v>
       </c>
       <c r="M94" s="16">
+        <f>ROUND(100*(Índices!M94/Índices!M93-1),4)</f>
         <v>2.5518000000000001</v>
       </c>
       <c r="N94" s="16">
+        <f>ROUND(100*(Índices!N94/Índices!N93-1),4)</f>
         <v>3.2280000000000002</v>
       </c>
       <c r="O94" s="16">
+        <f>ROUND(100*(Índices!O94/Índices!O93-1),4)</f>
         <v>0.69520000000000004</v>
       </c>
       <c r="P94" s="16">
+        <f>ROUND(100*(Índices!P94/Índices!P93-1),4)</f>
         <v>3.9729000000000001</v>
       </c>
       <c r="Q94" s="16">
+        <f>ROUND(100*(Índices!Q94/Índices!Q93-1),4)</f>
         <v>9.0968</v>
       </c>
       <c r="R94" s="16">
+        <f>ROUND(100*(Índices!R94/Índices!R93-1),4)</f>
         <v>4.5640000000000001</v>
       </c>
       <c r="S94" s="16">
+        <f>ROUND(100*(Índices!S94/Índices!S93-1),4)</f>
         <v>8.1049000000000007</v>
       </c>
       <c r="T94" s="16">
+        <f>ROUND(100*(Índices!T94/Índices!T93-1),4)</f>
         <v>5.6345000000000001</v>
       </c>
       <c r="U94" s="17">
+        <f>ROUND(100*(Índices!U94/Índices!U93-1),4)</f>
         <v>4.3044000000000002</v>
       </c>
       <c r="V94" s="15">
+        <f>ROUND(100*(Índices!V94/Índices!V93-1),4)</f>
         <v>5.3617999999999997</v>
       </c>
     </row>
@@ -15338,39 +16471,51 @@
         <v>4.8456999999999999</v>
       </c>
       <c r="K95" s="16">
+        <f>ROUND(100*(Índices!K95/Índices!K94-1),4)</f>
         <v>3.4357000000000002</v>
       </c>
       <c r="L95" s="16">
+        <f>ROUND(100*(Índices!L95/Índices!L94-1),4)</f>
         <v>4.8103999999999996</v>
       </c>
       <c r="M95" s="16">
+        <f>ROUND(100*(Índices!M95/Índices!M94-1),4)</f>
         <v>14.4078</v>
       </c>
       <c r="N95" s="16">
+        <f>ROUND(100*(Índices!N95/Índices!N94-1),4)</f>
         <v>2.2847</v>
       </c>
       <c r="O95" s="16">
+        <f>ROUND(100*(Índices!O95/Índices!O94-1),4)</f>
         <v>4.7441000000000004</v>
       </c>
       <c r="P95" s="16">
+        <f>ROUND(100*(Índices!P95/Índices!P94-1),4)</f>
         <v>3.9338000000000002</v>
       </c>
       <c r="Q95" s="16">
+        <f>ROUND(100*(Índices!Q95/Índices!Q94-1),4)</f>
         <v>5.7211999999999996</v>
       </c>
       <c r="R95" s="16">
+        <f>ROUND(100*(Índices!R95/Índices!R94-1),4)</f>
         <v>5.6208</v>
       </c>
       <c r="S95" s="16">
+        <f>ROUND(100*(Índices!S95/Índices!S94-1),4)</f>
         <v>7.4158999999999997</v>
       </c>
       <c r="T95" s="16">
+        <f>ROUND(100*(Índices!T95/Índices!T94-1),4)</f>
         <v>6.3552</v>
       </c>
       <c r="U95" s="17">
+        <f>ROUND(100*(Índices!U95/Índices!U94-1),4)</f>
         <v>2.7610999999999999</v>
       </c>
       <c r="V95" s="15">
+        <f>ROUND(100*(Índices!V95/Índices!V94-1),4)</f>
         <v>4.7662000000000004</v>
       </c>
     </row>
@@ -15411,39 +16556,51 @@
         <v>4.8535000000000004</v>
       </c>
       <c r="K96" s="16">
+        <f>ROUND(100*(Índices!K96/Índices!K95-1),4)</f>
         <v>6.7329999999999997</v>
       </c>
       <c r="L96" s="16">
+        <f>ROUND(100*(Índices!L96/Índices!L95-1),4)</f>
         <v>4.7510000000000003</v>
       </c>
       <c r="M96" s="16">
+        <f>ROUND(100*(Índices!M96/Índices!M95-1),4)</f>
         <v>6.0595999999999997</v>
       </c>
       <c r="N96" s="16">
+        <f>ROUND(100*(Índices!N96/Índices!N95-1),4)</f>
         <v>3.4531999999999998</v>
       </c>
       <c r="O96" s="16">
+        <f>ROUND(100*(Índices!O96/Índices!O95-1),4)</f>
         <v>5.8482000000000003</v>
       </c>
       <c r="P96" s="16">
+        <f>ROUND(100*(Índices!P96/Índices!P95-1),4)</f>
         <v>2.6294</v>
       </c>
       <c r="Q96" s="16">
+        <f>ROUND(100*(Índices!Q96/Índices!Q95-1),4)</f>
         <v>5.0122999999999998</v>
       </c>
       <c r="R96" s="16">
+        <f>ROUND(100*(Índices!R96/Índices!R95-1),4)</f>
         <v>5.6676000000000002</v>
       </c>
       <c r="S96" s="16">
+        <f>ROUND(100*(Índices!S96/Índices!S95-1),4)</f>
         <v>6.1784999999999997</v>
       </c>
       <c r="T96" s="16">
+        <f>ROUND(100*(Índices!T96/Índices!T95-1),4)</f>
         <v>6.4307999999999996</v>
       </c>
       <c r="U96" s="17">
+        <f>ROUND(100*(Índices!U96/Índices!U95-1),4)</f>
         <v>3.4521000000000002</v>
       </c>
       <c r="V96" s="15">
+        <f>ROUND(100*(Índices!V96/Índices!V95-1),4)</f>
         <v>5.0087999999999999</v>
       </c>
     </row>
@@ -15484,39 +16641,51 @@
         <v>3.7239</v>
       </c>
       <c r="K97" s="16">
+        <f>ROUND(100*(Índices!K97/Índices!K96-1),4)</f>
         <v>4.0309999999999997</v>
       </c>
       <c r="L97" s="16">
+        <f>ROUND(100*(Índices!L97/Índices!L96-1),4)</f>
         <v>2.7345999999999999</v>
       </c>
       <c r="M97" s="16">
+        <f>ROUND(100*(Índices!M97/Índices!M96-1),4)</f>
         <v>7.0934999999999997</v>
       </c>
       <c r="N97" s="16">
+        <f>ROUND(100*(Índices!N97/Índices!N96-1),4)</f>
         <v>4.2632000000000003</v>
       </c>
       <c r="O97" s="16">
+        <f>ROUND(100*(Índices!O97/Índices!O96-1),4)</f>
         <v>4.1345000000000001</v>
       </c>
       <c r="P97" s="16">
+        <f>ROUND(100*(Índices!P97/Índices!P96-1),4)</f>
         <v>5.0505000000000004</v>
       </c>
       <c r="Q97" s="16">
+        <f>ROUND(100*(Índices!Q97/Índices!Q96-1),4)</f>
         <v>7.6725000000000003</v>
       </c>
       <c r="R97" s="16">
+        <f>ROUND(100*(Índices!R97/Índices!R96-1),4)</f>
         <v>3.6793</v>
       </c>
       <c r="S97" s="16">
+        <f>ROUND(100*(Índices!S97/Índices!S96-1),4)</f>
         <v>6.8845000000000001</v>
       </c>
       <c r="T97" s="16">
+        <f>ROUND(100*(Índices!T97/Índices!T96-1),4)</f>
         <v>4.8756000000000004</v>
       </c>
       <c r="U97" s="17">
+        <f>ROUND(100*(Índices!U97/Índices!U96-1),4)</f>
         <v>2.2768999999999999</v>
       </c>
       <c r="V97" s="15">
+        <f>ROUND(100*(Índices!V97/Índices!V96-1),4)</f>
         <v>3.7467000000000001</v>
       </c>
     </row>
@@ -15557,39 +16726,51 @@
         <v>1.9977</v>
       </c>
       <c r="K98" s="16">
+        <f>ROUND(100*(Índices!K98/Índices!K97-1),4)</f>
         <v>1.1489</v>
       </c>
       <c r="L98" s="16">
+        <f>ROUND(100*(Índices!L98/Índices!L97-1),4)</f>
         <v>2.5487000000000002</v>
       </c>
       <c r="M98" s="16">
+        <f>ROUND(100*(Índices!M98/Índices!M97-1),4)</f>
         <v>7.3296999999999999</v>
       </c>
       <c r="N98" s="16">
+        <f>ROUND(100*(Índices!N98/Índices!N97-1),4)</f>
         <v>2.6941999999999999</v>
       </c>
       <c r="O98" s="16">
+        <f>ROUND(100*(Índices!O98/Índices!O97-1),4)</f>
         <v>3.3355999999999999</v>
       </c>
       <c r="P98" s="16">
+        <f>ROUND(100*(Índices!P98/Índices!P97-1),4)</f>
         <v>3.3900999999999999</v>
       </c>
       <c r="Q98" s="16">
+        <f>ROUND(100*(Índices!Q98/Índices!Q97-1),4)</f>
         <v>4.1878000000000002</v>
       </c>
       <c r="R98" s="16">
+        <f>ROUND(100*(Índices!R98/Índices!R97-1),4)</f>
         <v>2.1261999999999999</v>
       </c>
       <c r="S98" s="16">
+        <f>ROUND(100*(Índices!S98/Índices!S97-1),4)</f>
         <v>6.8409000000000004</v>
       </c>
       <c r="T98" s="16">
+        <f>ROUND(100*(Índices!T98/Índices!T97-1),4)</f>
         <v>3.7934000000000001</v>
       </c>
       <c r="U98" s="17">
+        <f>ROUND(100*(Índices!U98/Índices!U97-1),4)</f>
         <v>3.3424</v>
       </c>
       <c r="V98" s="15">
+        <f>ROUND(100*(Índices!V98/Índices!V97-1),4)</f>
         <v>2.4476</v>
       </c>
     </row>
@@ -15630,39 +16811,51 @@
         <v>1.1819999999999999</v>
       </c>
       <c r="K99" s="16">
+        <f>ROUND(100*(Índices!K99/Índices!K98-1),4)</f>
         <v>3.2557999999999998</v>
       </c>
       <c r="L99" s="16">
+        <f>ROUND(100*(Índices!L99/Índices!L98-1),4)</f>
         <v>3.8195000000000001</v>
       </c>
       <c r="M99" s="16">
+        <f>ROUND(100*(Índices!M99/Índices!M98-1),4)</f>
         <v>5.4292999999999996</v>
       </c>
       <c r="N99" s="16">
+        <f>ROUND(100*(Índices!N99/Índices!N98-1),4)</f>
         <v>2.6139999999999999</v>
       </c>
       <c r="O99" s="16">
+        <f>ROUND(100*(Índices!O99/Índices!O98-1),4)</f>
         <v>3.5609000000000002</v>
       </c>
       <c r="P99" s="16">
+        <f>ROUND(100*(Índices!P99/Índices!P98-1),4)</f>
         <v>1.2087000000000001</v>
       </c>
       <c r="Q99" s="16">
+        <f>ROUND(100*(Índices!Q99/Índices!Q98-1),4)</f>
         <v>2.605</v>
       </c>
       <c r="R99" s="16">
+        <f>ROUND(100*(Índices!R99/Índices!R98-1),4)</f>
         <v>2.8637000000000001</v>
       </c>
       <c r="S99" s="16">
+        <f>ROUND(100*(Índices!S99/Índices!S98-1),4)</f>
         <v>7.2032999999999996</v>
       </c>
       <c r="T99" s="16">
+        <f>ROUND(100*(Índices!T99/Índices!T98-1),4)</f>
         <v>4.3139000000000003</v>
       </c>
       <c r="U99" s="17">
+        <f>ROUND(100*(Índices!U99/Índices!U98-1),4)</f>
         <v>2.8113000000000001</v>
       </c>
       <c r="V99" s="15">
+        <f>ROUND(100*(Índices!V99/Índices!V98-1),4)</f>
         <v>2.4329000000000001</v>
       </c>
     </row>
@@ -15703,39 +16896,51 @@
         <v>1.3479000000000001</v>
       </c>
       <c r="K100" s="16">
+        <f>ROUND(100*(Índices!K100/Índices!K99-1),4)</f>
         <v>3.1389999999999998</v>
       </c>
       <c r="L100" s="16">
+        <f>ROUND(100*(Índices!L100/Índices!L99-1),4)</f>
         <v>2.7793999999999999</v>
       </c>
       <c r="M100" s="16">
+        <f>ROUND(100*(Índices!M100/Índices!M99-1),4)</f>
         <v>4.4584000000000001</v>
       </c>
       <c r="N100" s="16">
+        <f>ROUND(100*(Índices!N100/Índices!N99-1),4)</f>
         <v>1.5077</v>
       </c>
       <c r="O100" s="16">
+        <f>ROUND(100*(Índices!O100/Índices!O99-1),4)</f>
         <v>2.9194</v>
       </c>
       <c r="P100" s="16">
+        <f>ROUND(100*(Índices!P100/Índices!P99-1),4)</f>
         <v>3.3864999999999998</v>
       </c>
       <c r="Q100" s="16">
+        <f>ROUND(100*(Índices!Q100/Índices!Q99-1),4)</f>
         <v>1.9329000000000001</v>
       </c>
       <c r="R100" s="16">
+        <f>ROUND(100*(Índices!R100/Índices!R99-1),4)</f>
         <v>3.0055999999999998</v>
       </c>
       <c r="S100" s="16">
+        <f>ROUND(100*(Índices!S100/Índices!S99-1),4)</f>
         <v>7.8918999999999997</v>
       </c>
       <c r="T100" s="16">
+        <f>ROUND(100*(Índices!T100/Índices!T99-1),4)</f>
         <v>3.6360999999999999</v>
       </c>
       <c r="U100" s="17">
+        <f>ROUND(100*(Índices!U100/Índices!U99-1),4)</f>
         <v>2.2850000000000001</v>
       </c>
       <c r="V100" s="15">
+        <f>ROUND(100*(Índices!V100/Índices!V99-1),4)</f>
         <v>2.1347</v>
       </c>
     </row>
@@ -15776,39 +16981,51 @@
         <v>1.1963999999999999</v>
       </c>
       <c r="K101" s="16">
+        <f>ROUND(100*(Índices!K101/Índices!K100-1),4)</f>
         <v>2.1141999999999999</v>
       </c>
       <c r="L101" s="16">
+        <f>ROUND(100*(Índices!L101/Índices!L100-1),4)</f>
         <v>1.1696</v>
       </c>
       <c r="M101" s="16">
+        <f>ROUND(100*(Índices!M101/Índices!M100-1),4)</f>
         <v>5.2697000000000003</v>
       </c>
       <c r="N101" s="16">
+        <f>ROUND(100*(Índices!N101/Índices!N100-1),4)</f>
         <v>0.94430000000000003</v>
       </c>
       <c r="O101" s="16">
+        <f>ROUND(100*(Índices!O101/Índices!O100-1),4)</f>
         <v>2.0994999999999999</v>
       </c>
       <c r="P101" s="16">
+        <f>ROUND(100*(Índices!P101/Índices!P100-1),4)</f>
         <v>2.2602000000000002</v>
       </c>
       <c r="Q101" s="16">
+        <f>ROUND(100*(Índices!Q101/Índices!Q100-1),4)</f>
         <v>4.7553999999999998</v>
       </c>
       <c r="R101" s="16">
+        <f>ROUND(100*(Índices!R101/Índices!R100-1),4)</f>
         <v>2.7968999999999999</v>
       </c>
       <c r="S101" s="16">
+        <f>ROUND(100*(Índices!S101/Índices!S100-1),4)</f>
         <v>6.5979000000000001</v>
       </c>
       <c r="T101" s="16">
+        <f>ROUND(100*(Índices!T101/Índices!T100-1),4)</f>
         <v>4.5021000000000004</v>
       </c>
       <c r="U101" s="17">
+        <f>ROUND(100*(Índices!U101/Índices!U100-1),4)</f>
         <v>2.1419999999999999</v>
       </c>
       <c r="V101" s="15">
+        <f>ROUND(100*(Índices!V101/Índices!V100-1),4)</f>
         <v>1.9220999999999999</v>
       </c>
     </row>
@@ -15849,39 +17066,51 @@
         <v>0.18099999999999999</v>
       </c>
       <c r="K102" s="16">
+        <f>ROUND(100*(Índices!K102/Índices!K101-1),4)</f>
         <v>0.99380000000000002</v>
       </c>
       <c r="L102" s="16">
+        <f>ROUND(100*(Índices!L102/Índices!L101-1),4)</f>
         <v>0.86770000000000003</v>
       </c>
       <c r="M102" s="16">
+        <f>ROUND(100*(Índices!M102/Índices!M101-1),4)</f>
         <v>4.1188000000000002</v>
       </c>
       <c r="N102" s="16">
+        <f>ROUND(100*(Índices!N102/Índices!N101-1),4)</f>
         <v>1.6161000000000001</v>
       </c>
       <c r="O102" s="16">
+        <f>ROUND(100*(Índices!O102/Índices!O101-1),4)</f>
         <v>2.3757999999999999</v>
       </c>
       <c r="P102" s="16">
+        <f>ROUND(100*(Índices!P102/Índices!P101-1),4)</f>
         <v>1.2430000000000001</v>
       </c>
       <c r="Q102" s="16">
+        <f>ROUND(100*(Índices!Q102/Índices!Q101-1),4)</f>
         <v>-2.1705999999999999</v>
       </c>
       <c r="R102" s="16">
+        <f>ROUND(100*(Índices!R102/Índices!R101-1),4)</f>
         <v>2.4620000000000002</v>
       </c>
       <c r="S102" s="16">
+        <f>ROUND(100*(Índices!S102/Índices!S101-1),4)</f>
         <v>5.3228</v>
       </c>
       <c r="T102" s="16">
+        <f>ROUND(100*(Índices!T102/Índices!T101-1),4)</f>
         <v>5.1494</v>
       </c>
       <c r="U102" s="17">
+        <f>ROUND(100*(Índices!U102/Índices!U101-1),4)</f>
         <v>2.4754</v>
       </c>
       <c r="V102" s="15">
+        <f>ROUND(100*(Índices!V102/Índices!V101-1),4)</f>
         <v>1.5645</v>
       </c>
     </row>
@@ -15922,39 +17151,51 @@
         <v>1.9495</v>
       </c>
       <c r="K103" s="16">
+        <f>ROUND(100*(Índices!K103/Índices!K102-1),4)</f>
         <v>1.0314000000000001</v>
       </c>
       <c r="L103" s="16">
+        <f>ROUND(100*(Índices!L103/Índices!L102-1),4)</f>
         <v>1.9166000000000001</v>
       </c>
       <c r="M103" s="16">
+        <f>ROUND(100*(Índices!M103/Índices!M102-1),4)</f>
         <v>3.7764000000000002</v>
       </c>
       <c r="N103" s="16">
+        <f>ROUND(100*(Índices!N103/Índices!N102-1),4)</f>
         <v>1.0124</v>
       </c>
       <c r="O103" s="16">
+        <f>ROUND(100*(Índices!O103/Índices!O102-1),4)</f>
         <v>2.0562</v>
       </c>
       <c r="P103" s="16">
+        <f>ROUND(100*(Índices!P103/Índices!P102-1),4)</f>
         <v>1.7322</v>
       </c>
       <c r="Q103" s="16">
+        <f>ROUND(100*(Índices!Q103/Índices!Q102-1),4)</f>
         <v>-0.62419999999999998</v>
       </c>
       <c r="R103" s="16">
+        <f>ROUND(100*(Índices!R103/Índices!R102-1),4)</f>
         <v>2.9359999999999999</v>
       </c>
       <c r="S103" s="16">
+        <f>ROUND(100*(Índices!S103/Índices!S102-1),4)</f>
         <v>2.6537999999999999</v>
       </c>
       <c r="T103" s="16">
+        <f>ROUND(100*(Índices!T103/Índices!T102-1),4)</f>
         <v>2.1930000000000001</v>
       </c>
       <c r="U103" s="17">
+        <f>ROUND(100*(Índices!U103/Índices!U102-1),4)</f>
         <v>2.9281999999999999</v>
       </c>
       <c r="V103" s="15">
+        <f>ROUND(100*(Índices!V103/Índices!V102-1),4)</f>
         <v>2.0148000000000001</v>
       </c>
     </row>
@@ -15995,39 +17236,51 @@
         <v>4.6249000000000002</v>
       </c>
       <c r="K104" s="16">
+        <f>ROUND(100*(Índices!K104/Índices!K103-1),4)</f>
         <v>-0.39829999999999999</v>
       </c>
       <c r="L104" s="16">
+        <f>ROUND(100*(Índices!L104/Índices!L103-1),4)</f>
         <v>1.0295000000000001</v>
       </c>
       <c r="M104" s="16">
+        <f>ROUND(100*(Índices!M104/Índices!M103-1),4)</f>
         <v>2.8586999999999998</v>
       </c>
       <c r="N104" s="16">
+        <f>ROUND(100*(Índices!N104/Índices!N103-1),4)</f>
         <v>1.4823999999999999</v>
       </c>
       <c r="O104" s="16">
+        <f>ROUND(100*(Índices!O104/Índices!O103-1),4)</f>
         <v>1.8416999999999999</v>
       </c>
       <c r="P104" s="16">
+        <f>ROUND(100*(Índices!P104/Índices!P103-1),4)</f>
         <v>1.7077</v>
       </c>
       <c r="Q104" s="16">
+        <f>ROUND(100*(Índices!Q104/Índices!Q103-1),4)</f>
         <v>2.8839000000000001</v>
       </c>
       <c r="R104" s="16">
+        <f>ROUND(100*(Índices!R104/Índices!R103-1),4)</f>
         <v>0.156</v>
       </c>
       <c r="S104" s="16">
+        <f>ROUND(100*(Índices!S104/Índices!S103-1),4)</f>
         <v>-2.4119000000000002</v>
       </c>
       <c r="T104" s="16">
+        <f>ROUND(100*(Índices!T104/Índices!T103-1),4)</f>
         <v>3.8717000000000001</v>
       </c>
       <c r="U104" s="17">
+        <f>ROUND(100*(Índices!U104/Índices!U103-1),4)</f>
         <v>3.1615000000000002</v>
       </c>
       <c r="V104" s="15">
+        <f>ROUND(100*(Índices!V104/Índices!V103-1),4)</f>
         <v>3.0316000000000001</v>
       </c>
     </row>
@@ -16068,39 +17321,51 @@
         <v>3.2475000000000001</v>
       </c>
       <c r="K105" s="16">
+        <f>ROUND(100*(Índices!K105/Índices!K104-1),4)</f>
         <v>4.2161</v>
       </c>
       <c r="L105" s="16">
+        <f>ROUND(100*(Índices!L105/Índices!L104-1),4)</f>
         <v>1.1894</v>
       </c>
       <c r="M105" s="16">
+        <f>ROUND(100*(Índices!M105/Índices!M104-1),4)</f>
         <v>1.8848</v>
       </c>
       <c r="N105" s="16">
+        <f>ROUND(100*(Índices!N105/Índices!N104-1),4)</f>
         <v>0.93579999999999997</v>
       </c>
       <c r="O105" s="16">
+        <f>ROUND(100*(Índices!O105/Índices!O104-1),4)</f>
         <v>2.4942000000000002</v>
       </c>
       <c r="P105" s="16">
+        <f>ROUND(100*(Índices!P105/Índices!P104-1),4)</f>
         <v>1.6681999999999999</v>
       </c>
       <c r="Q105" s="16">
+        <f>ROUND(100*(Índices!Q105/Índices!Q104-1),4)</f>
         <v>2.5556999999999999</v>
       </c>
       <c r="R105" s="16">
+        <f>ROUND(100*(Índices!R105/Índices!R104-1),4)</f>
         <v>3.9842</v>
       </c>
       <c r="S105" s="16">
+        <f>ROUND(100*(Índices!S105/Índices!S104-1),4)</f>
         <v>2.0528</v>
       </c>
       <c r="T105" s="16">
+        <f>ROUND(100*(Índices!T105/Índices!T104-1),4)</f>
         <v>4.1219000000000001</v>
       </c>
       <c r="U105" s="17">
+        <f>ROUND(100*(Índices!U105/Índices!U104-1),4)</f>
         <v>2.5432999999999999</v>
       </c>
       <c r="V105" s="15">
+        <f>ROUND(100*(Índices!V105/Índices!V104-1),4)</f>
         <v>2.9986000000000002</v>
       </c>
     </row>
@@ -16141,39 +17406,51 @@
         <v>1.7863</v>
       </c>
       <c r="K106" s="16">
+        <f>ROUND(100*(Índices!K106/Índices!K105-1),4)</f>
         <v>1.2527999999999999</v>
       </c>
       <c r="L106" s="16">
+        <f>ROUND(100*(Índices!L106/Índices!L105-1),4)</f>
         <v>1.4686999999999999</v>
       </c>
       <c r="M106" s="16">
+        <f>ROUND(100*(Índices!M106/Índices!M105-1),4)</f>
         <v>2.4238</v>
       </c>
       <c r="N106" s="16">
+        <f>ROUND(100*(Índices!N106/Índices!N105-1),4)</f>
         <v>1.3919999999999999</v>
       </c>
       <c r="O106" s="16">
+        <f>ROUND(100*(Índices!O106/Índices!O105-1),4)</f>
         <v>2.7444999999999999</v>
       </c>
       <c r="P106" s="16">
+        <f>ROUND(100*(Índices!P106/Índices!P105-1),4)</f>
         <v>0.35699999999999998</v>
       </c>
       <c r="Q106" s="16">
+        <f>ROUND(100*(Índices!Q106/Índices!Q105-1),4)</f>
         <v>4.9504000000000001</v>
       </c>
       <c r="R106" s="16">
+        <f>ROUND(100*(Índices!R106/Índices!R105-1),4)</f>
         <v>1.7065999999999999</v>
       </c>
       <c r="S106" s="16">
+        <f>ROUND(100*(Índices!S106/Índices!S105-1),4)</f>
         <v>2.1568999999999998</v>
       </c>
       <c r="T106" s="16">
+        <f>ROUND(100*(Índices!T106/Índices!T105-1),4)</f>
         <v>3.0951</v>
       </c>
       <c r="U106" s="17">
+        <f>ROUND(100*(Índices!U106/Índices!U105-1),4)</f>
         <v>2.5825</v>
       </c>
       <c r="V106" s="15">
+        <f>ROUND(100*(Índices!V106/Índices!V105-1),4)</f>
         <v>1.9458</v>
       </c>
     </row>
@@ -16214,39 +17491,51 @@
         <v>2.3601999999999999</v>
       </c>
       <c r="K107" s="16">
+        <f>ROUND(100*(Índices!K107/Índices!K106-1),4)</f>
         <v>4.1736000000000004</v>
       </c>
       <c r="L107" s="16">
+        <f>ROUND(100*(Índices!L107/Índices!L106-1),4)</f>
         <v>2.7155</v>
       </c>
       <c r="M107" s="16">
+        <f>ROUND(100*(Índices!M107/Índices!M106-1),4)</f>
         <v>3.4001000000000001</v>
       </c>
       <c r="N107" s="16">
+        <f>ROUND(100*(Índices!N107/Índices!N106-1),4)</f>
         <v>1.8982000000000001</v>
       </c>
       <c r="O107" s="16">
+        <f>ROUND(100*(Índices!O107/Índices!O106-1),4)</f>
         <v>2.1537000000000002</v>
       </c>
       <c r="P107" s="16">
+        <f>ROUND(100*(Índices!P107/Índices!P106-1),4)</f>
         <v>1.6028</v>
       </c>
       <c r="Q107" s="16">
+        <f>ROUND(100*(Índices!Q107/Índices!Q106-1),4)</f>
         <v>2.3384999999999998</v>
       </c>
       <c r="R107" s="16">
+        <f>ROUND(100*(Índices!R107/Índices!R106-1),4)</f>
         <v>2.472</v>
       </c>
       <c r="S107" s="16">
+        <f>ROUND(100*(Índices!S107/Índices!S106-1),4)</f>
         <v>5.33</v>
       </c>
       <c r="T107" s="16">
+        <f>ROUND(100*(Índices!T107/Índices!T106-1),4)</f>
         <v>2.1682999999999999</v>
       </c>
       <c r="U107" s="17">
+        <f>ROUND(100*(Índices!U107/Índices!U106-1),4)</f>
         <v>0.99550000000000005</v>
       </c>
       <c r="V107" s="15">
+        <f>ROUND(100*(Índices!V107/Índices!V106-1),4)</f>
         <v>2.3281999999999998</v>
       </c>
     </row>
@@ -16287,39 +17576,51 @@
         <v>3.5238999999999998</v>
       </c>
       <c r="K108" s="16">
+        <f>ROUND(100*(Índices!K108/Índices!K107-1),4)</f>
         <v>1.2192000000000001</v>
       </c>
       <c r="L108" s="16">
+        <f>ROUND(100*(Índices!L108/Índices!L107-1),4)</f>
         <v>2.2050999999999998</v>
       </c>
       <c r="M108" s="16">
+        <f>ROUND(100*(Índices!M108/Índices!M107-1),4)</f>
         <v>1.5389999999999999</v>
       </c>
       <c r="N108" s="16">
+        <f>ROUND(100*(Índices!N108/Índices!N107-1),4)</f>
         <v>1.54</v>
       </c>
       <c r="O108" s="16">
+        <f>ROUND(100*(Índices!O108/Índices!O107-1),4)</f>
         <v>1.1391</v>
       </c>
       <c r="P108" s="16">
+        <f>ROUND(100*(Índices!P108/Índices!P107-1),4)</f>
         <v>2.7711999999999999</v>
       </c>
       <c r="Q108" s="16">
+        <f>ROUND(100*(Índices!Q108/Índices!Q107-1),4)</f>
         <v>3.7555000000000001</v>
       </c>
       <c r="R108" s="16">
+        <f>ROUND(100*(Índices!R108/Índices!R107-1),4)</f>
         <v>4.8144</v>
       </c>
       <c r="S108" s="16">
+        <f>ROUND(100*(Índices!S108/Índices!S107-1),4)</f>
         <v>4.3624000000000001</v>
       </c>
       <c r="T108" s="16">
+        <f>ROUND(100*(Índices!T108/Índices!T107-1),4)</f>
         <v>2.7088999999999999</v>
       </c>
       <c r="U108" s="17">
+        <f>ROUND(100*(Índices!U108/Índices!U107-1),4)</f>
         <v>2.1472000000000002</v>
       </c>
       <c r="V108" s="15">
+        <f>ROUND(100*(Índices!V108/Índices!V107-1),4)</f>
         <v>3.0211999999999999</v>
       </c>
     </row>
@@ -16360,39 +17661,51 @@
         <v>1.4757</v>
       </c>
       <c r="K109" s="16">
+        <f>ROUND(100*(Índices!K109/Índices!K108-1),4)</f>
         <v>4.444</v>
       </c>
       <c r="L109" s="16">
+        <f>ROUND(100*(Índices!L109/Índices!L108-1),4)</f>
         <v>0.62190000000000001</v>
       </c>
       <c r="M109" s="16">
+        <f>ROUND(100*(Índices!M109/Índices!M108-1),4)</f>
         <v>2.6928000000000001</v>
       </c>
       <c r="N109" s="16">
+        <f>ROUND(100*(Índices!N109/Índices!N108-1),4)</f>
         <v>0.93520000000000003</v>
       </c>
       <c r="O109" s="16">
+        <f>ROUND(100*(Índices!O109/Índices!O108-1),4)</f>
         <v>1.7205999999999999</v>
       </c>
       <c r="P109" s="16">
+        <f>ROUND(100*(Índices!P109/Índices!P108-1),4)</f>
         <v>3.5581</v>
       </c>
       <c r="Q109" s="16">
+        <f>ROUND(100*(Índices!Q109/Índices!Q108-1),4)</f>
         <v>4.6970999999999998</v>
       </c>
       <c r="R109" s="16">
+        <f>ROUND(100*(Índices!R109/Índices!R108-1),4)</f>
         <v>0.53080000000000005</v>
       </c>
       <c r="S109" s="16">
+        <f>ROUND(100*(Índices!S109/Índices!S108-1),4)</f>
         <v>2.9026999999999998</v>
       </c>
       <c r="T109" s="16">
+        <f>ROUND(100*(Índices!T109/Índices!T108-1),4)</f>
         <v>3.4422000000000001</v>
       </c>
       <c r="U109" s="17">
+        <f>ROUND(100*(Índices!U109/Índices!U108-1),4)</f>
         <v>2.2492999999999999</v>
       </c>
       <c r="V109" s="15">
+        <f>ROUND(100*(Índices!V109/Índices!V108-1),4)</f>
         <v>1.6693</v>
       </c>
     </row>
@@ -16433,39 +17746,51 @@
         <v>1.5581</v>
       </c>
       <c r="K110" s="16">
+        <f>ROUND(100*(Índices!K110/Índices!K109-1),4)</f>
         <v>0.53410000000000002</v>
       </c>
       <c r="L110" s="16">
+        <f>ROUND(100*(Índices!L110/Índices!L109-1),4)</f>
         <v>-1.3429</v>
       </c>
       <c r="M110" s="16">
+        <f>ROUND(100*(Índices!M110/Índices!M109-1),4)</f>
         <v>3.1423999999999999</v>
       </c>
       <c r="N110" s="16">
+        <f>ROUND(100*(Índices!N110/Índices!N109-1),4)</f>
         <v>2.2124999999999999</v>
       </c>
       <c r="O110" s="16">
+        <f>ROUND(100*(Índices!O110/Índices!O109-1),4)</f>
         <v>2.2858999999999998</v>
       </c>
       <c r="P110" s="16">
+        <f>ROUND(100*(Índices!P110/Índices!P109-1),4)</f>
         <v>2.9731000000000001</v>
       </c>
       <c r="Q110" s="16">
+        <f>ROUND(100*(Índices!Q110/Índices!Q109-1),4)</f>
         <v>3.4643000000000002</v>
       </c>
       <c r="R110" s="16">
+        <f>ROUND(100*(Índices!R110/Índices!R109-1),4)</f>
         <v>1.3376999999999999</v>
       </c>
       <c r="S110" s="16">
+        <f>ROUND(100*(Índices!S110/Índices!S109-1),4)</f>
         <v>5.7842000000000002</v>
       </c>
       <c r="T110" s="16">
+        <f>ROUND(100*(Índices!T110/Índices!T109-1),4)</f>
         <v>1.2056</v>
       </c>
       <c r="U110" s="17">
+        <f>ROUND(100*(Índices!U110/Índices!U109-1),4)</f>
         <v>2.1455000000000002</v>
       </c>
       <c r="V110" s="15">
+        <f>ROUND(100*(Índices!V110/Índices!V109-1),4)</f>
         <v>1.1499999999999999</v>
       </c>
     </row>
@@ -16506,39 +17831,51 @@
         <v>2.2686999999999999</v>
       </c>
       <c r="K111" s="16">
+        <f>ROUND(100*(Índices!K111/Índices!K110-1),4)</f>
         <v>2.6392000000000002</v>
       </c>
       <c r="L111" s="16">
+        <f>ROUND(100*(Índices!L111/Índices!L110-1),4)</f>
         <v>1.7358</v>
       </c>
       <c r="M111" s="16">
+        <f>ROUND(100*(Índices!M111/Índices!M110-1),4)</f>
         <v>2.8279999999999998</v>
       </c>
       <c r="N111" s="16">
+        <f>ROUND(100*(Índices!N111/Índices!N110-1),4)</f>
         <v>1.6339999999999999</v>
       </c>
       <c r="O111" s="16">
+        <f>ROUND(100*(Índices!O111/Índices!O110-1),4)</f>
         <v>1.8307</v>
       </c>
       <c r="P111" s="16">
+        <f>ROUND(100*(Índices!P111/Índices!P110-1),4)</f>
         <v>3.4594999999999998</v>
       </c>
       <c r="Q111" s="16">
+        <f>ROUND(100*(Índices!Q111/Índices!Q110-1),4)</f>
         <v>2.7322000000000002</v>
       </c>
       <c r="R111" s="16">
+        <f>ROUND(100*(Índices!R111/Índices!R110-1),4)</f>
         <v>1.6108</v>
       </c>
       <c r="S111" s="16">
+        <f>ROUND(100*(Índices!S111/Índices!S110-1),4)</f>
         <v>5.7397999999999998</v>
       </c>
       <c r="T111" s="16">
+        <f>ROUND(100*(Índices!T111/Índices!T110-1),4)</f>
         <v>2.2783000000000002</v>
       </c>
       <c r="U111" s="17">
+        <f>ROUND(100*(Índices!U111/Índices!U110-1),4)</f>
         <v>2.4439000000000002</v>
       </c>
       <c r="V111" s="15">
+        <f>ROUND(100*(Índices!V111/Índices!V110-1),4)</f>
         <v>2.1185999999999998</v>
       </c>
     </row>
@@ -16579,39 +17916,51 @@
         <v>3.2688999999999999</v>
       </c>
       <c r="K112" s="16">
+        <f>ROUND(100*(Índices!K112/Índices!K111-1),4)</f>
         <v>0.33200000000000002</v>
       </c>
       <c r="L112" s="16">
+        <f>ROUND(100*(Índices!L112/Índices!L111-1),4)</f>
         <v>1.3657999999999999</v>
       </c>
       <c r="M112" s="16">
+        <f>ROUND(100*(Índices!M112/Índices!M111-1),4)</f>
         <v>3.4380000000000002</v>
       </c>
       <c r="N112" s="16">
+        <f>ROUND(100*(Índices!N112/Índices!N111-1),4)</f>
         <v>1.119</v>
       </c>
       <c r="O112" s="16">
+        <f>ROUND(100*(Índices!O112/Índices!O111-1),4)</f>
         <v>2.3965000000000001</v>
       </c>
       <c r="P112" s="16">
+        <f>ROUND(100*(Índices!P112/Índices!P111-1),4)</f>
         <v>3.0304000000000002</v>
       </c>
       <c r="Q112" s="16">
+        <f>ROUND(100*(Índices!Q112/Índices!Q111-1),4)</f>
         <v>3.0445000000000002</v>
       </c>
       <c r="R112" s="16">
+        <f>ROUND(100*(Índices!R112/Índices!R111-1),4)</f>
         <v>2.4485000000000001</v>
       </c>
       <c r="S112" s="16">
+        <f>ROUND(100*(Índices!S112/Índices!S111-1),4)</f>
         <v>4.8711000000000002</v>
       </c>
       <c r="T112" s="16">
+        <f>ROUND(100*(Índices!T112/Índices!T111-1),4)</f>
         <v>2.4801000000000002</v>
       </c>
       <c r="U112" s="17">
+        <f>ROUND(100*(Índices!U112/Índices!U111-1),4)</f>
         <v>2.5068000000000001</v>
       </c>
       <c r="V112" s="15">
+        <f>ROUND(100*(Índices!V112/Índices!V111-1),4)</f>
         <v>2.4952000000000001</v>
       </c>
     </row>
@@ -16652,39 +18001,51 @@
         <v>2.1086999999999998</v>
       </c>
       <c r="K113" s="16">
+        <f>ROUND(100*(Índices!K113/Índices!K112-1),4)</f>
         <v>2.4317000000000002</v>
       </c>
       <c r="L113" s="16">
+        <f>ROUND(100*(Índices!L113/Índices!L112-1),4)</f>
         <v>0.55920000000000003</v>
       </c>
       <c r="M113" s="16">
+        <f>ROUND(100*(Índices!M113/Índices!M112-1),4)</f>
         <v>3.3896000000000002</v>
       </c>
       <c r="N113" s="16">
+        <f>ROUND(100*(Índices!N113/Índices!N112-1),4)</f>
         <v>2.0001000000000002</v>
       </c>
       <c r="O113" s="16">
+        <f>ROUND(100*(Índices!O113/Índices!O112-1),4)</f>
         <v>2.0903999999999998</v>
       </c>
       <c r="P113" s="16">
+        <f>ROUND(100*(Índices!P113/Índices!P112-1),4)</f>
         <v>3.9982000000000002</v>
       </c>
       <c r="Q113" s="16">
+        <f>ROUND(100*(Índices!Q113/Índices!Q112-1),4)</f>
         <v>3.0379999999999998</v>
       </c>
       <c r="R113" s="16">
+        <f>ROUND(100*(Índices!R113/Índices!R112-1),4)</f>
         <v>2.5417000000000001</v>
       </c>
       <c r="S113" s="16">
+        <f>ROUND(100*(Índices!S113/Índices!S112-1),4)</f>
         <v>4.8147000000000002</v>
       </c>
       <c r="T113" s="16">
+        <f>ROUND(100*(Índices!T113/Índices!T112-1),4)</f>
         <v>3.0933000000000002</v>
       </c>
       <c r="U113" s="17">
+        <f>ROUND(100*(Índices!U113/Índices!U112-1),4)</f>
         <v>2.6438000000000001</v>
       </c>
       <c r="V113" s="15">
+        <f>ROUND(100*(Índices!V113/Índices!V112-1),4)</f>
         <v>2.1663999999999999</v>
       </c>
     </row>
@@ -16725,113 +18086,222 @@
         <v>2.9632000000000001</v>
       </c>
       <c r="K114" s="16">
+        <f>ROUND(100*(Índices!K114/Índices!K113-1),4)</f>
         <v>0.09</v>
       </c>
       <c r="L114" s="16">
+        <f>ROUND(100*(Índices!L114/Índices!L113-1),4)</f>
         <v>1.1326000000000001</v>
       </c>
       <c r="M114" s="16">
+        <f>ROUND(100*(Índices!M114/Índices!M113-1),4)</f>
         <v>3.0529000000000002</v>
       </c>
       <c r="N114" s="16">
+        <f>ROUND(100*(Índices!N114/Índices!N113-1),4)</f>
         <v>1.8302</v>
       </c>
       <c r="O114" s="16">
+        <f>ROUND(100*(Índices!O114/Índices!O113-1),4)</f>
         <v>2.3418000000000001</v>
       </c>
       <c r="P114" s="16">
+        <f>ROUND(100*(Índices!P114/Índices!P113-1),4)</f>
         <v>1.8548</v>
       </c>
       <c r="Q114" s="16">
+        <f>ROUND(100*(Índices!Q114/Índices!Q113-1),4)</f>
         <v>-1.0443</v>
       </c>
       <c r="R114" s="16">
+        <f>ROUND(100*(Índices!R114/Índices!R113-1),4)</f>
         <v>1.0244</v>
       </c>
       <c r="S114" s="16">
+        <f>ROUND(100*(Índices!S114/Índices!S113-1),4)</f>
         <v>5.1432000000000002</v>
       </c>
       <c r="T114" s="16">
+        <f>ROUND(100*(Índices!T114/Índices!T113-1),4)</f>
         <v>3.9603000000000002</v>
       </c>
       <c r="U114" s="17">
+        <f>ROUND(100*(Índices!U114/Índices!U113-1),4)</f>
         <v>2.7301000000000002</v>
       </c>
       <c r="V114" s="15">
+        <f>ROUND(100*(Índices!V114/Índices!V113-1),4)</f>
         <v>2.5274999999999999</v>
       </c>
     </row>
-    <row r="115" spans="2:22" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B115" s="48">
+    <row r="115" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B115" s="13">
         <v>46054</v>
       </c>
-      <c r="C115" s="18">
+      <c r="C115" s="15">
         <f>ROUND(100*(Índices!C115/Índices!C114-1),4)</f>
         <v>2.5402</v>
       </c>
-      <c r="D115" s="19">
+      <c r="D115" s="16">
         <f>ROUND(100*(Índices!D115/Índices!D114-1),4)</f>
         <v>2.2839999999999998</v>
       </c>
-      <c r="E115" s="19">
+      <c r="E115" s="16">
         <f>ROUND(100*(Índices!E115/Índices!E114-1),4)</f>
         <v>2.7242999999999999</v>
       </c>
-      <c r="F115" s="19">
+      <c r="F115" s="16">
         <f>ROUND(100*(Índices!F115/Índices!F114-1),4)</f>
         <v>3.0423</v>
       </c>
-      <c r="G115" s="19">
+      <c r="G115" s="16">
         <f>ROUND(100*(Índices!G115/Índices!G114-1),4)</f>
         <v>2.9007000000000001</v>
       </c>
-      <c r="H115" s="19">
+      <c r="H115" s="16">
         <f>ROUND(100*(Índices!H115/Índices!H114-1),4)</f>
         <v>2.9041999999999999</v>
       </c>
-      <c r="I115" s="20">
+      <c r="I115" s="17">
         <f>ROUND(100*(Índices!I115/Índices!I114-1),4)</f>
         <v>2.6263999999999998</v>
       </c>
-      <c r="J115" s="19">
+      <c r="J115" s="16">
         <f>ROUND(100*(Índices!J115/Índices!J114-1),4)</f>
         <v>2.0246</v>
       </c>
-      <c r="K115" s="19">
+      <c r="K115" s="16">
+        <f>ROUND(100*(Índices!K115/Índices!K114-1),4)</f>
         <v>0.35</v>
       </c>
-      <c r="L115" s="19">
+      <c r="L115" s="16">
+        <f>ROUND(100*(Índices!L115/Índices!L114-1),4)</f>
         <v>1.4723999999999999</v>
       </c>
-      <c r="M115" s="19">
+      <c r="M115" s="16">
+        <f>ROUND(100*(Índices!M115/Índices!M114-1),4)</f>
         <v>6.7877000000000001</v>
       </c>
-      <c r="N115" s="19">
+      <c r="N115" s="16">
+        <f>ROUND(100*(Índices!N115/Índices!N114-1),4)</f>
         <v>2.5644999999999998</v>
       </c>
-      <c r="O115" s="19">
+      <c r="O115" s="16">
+        <f>ROUND(100*(Índices!O115/Índices!O114-1),4)</f>
         <v>2.4708000000000001</v>
       </c>
-      <c r="P115" s="19">
+      <c r="P115" s="16">
+        <f>ROUND(100*(Índices!P115/Índices!P114-1),4)</f>
         <v>1.978</v>
       </c>
-      <c r="Q115" s="19">
+      <c r="Q115" s="16">
+        <f>ROUND(100*(Índices!Q115/Índices!Q114-1),4)</f>
         <v>-1.0564</v>
       </c>
-      <c r="R115" s="19">
+      <c r="R115" s="16">
+        <f>ROUND(100*(Índices!R115/Índices!R114-1),4)</f>
         <v>2.3454000000000002</v>
       </c>
-      <c r="S115" s="19">
+      <c r="S115" s="16">
+        <f>ROUND(100*(Índices!S115/Índices!S114-1),4)</f>
         <v>1.3282</v>
       </c>
-      <c r="T115" s="19">
+      <c r="T115" s="16">
+        <f>ROUND(100*(Índices!T115/Índices!T114-1),4)</f>
         <v>2.9319000000000002</v>
       </c>
-      <c r="U115" s="20">
+      <c r="U115" s="17">
+        <f>ROUND(100*(Índices!U115/Índices!U114-1),4)</f>
         <v>3.2768000000000002</v>
       </c>
-      <c r="V115" s="18">
+      <c r="V115" s="15">
+        <f>ROUND(100*(Índices!V115/Índices!V114-1),4)</f>
         <v>2.2141999999999999</v>
+      </c>
+    </row>
+    <row r="116" spans="2:22" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B116" s="48">
+        <v>46082</v>
+      </c>
+      <c r="C116" s="18">
+        <f>ROUND(100*(Índices!C116/Índices!C115-1),4)</f>
+        <v>2.2690999999999999</v>
+      </c>
+      <c r="D116" s="19">
+        <f>ROUND(100*(Índices!D116/Índices!D115-1),4)</f>
+        <v>2.0867</v>
+      </c>
+      <c r="E116" s="19">
+        <f>ROUND(100*(Índices!E116/Índices!E115-1),4)</f>
+        <v>2.3247</v>
+      </c>
+      <c r="F116" s="19">
+        <f>ROUND(100*(Índices!F116/Índices!F115-1),4)</f>
+        <v>2.9150999999999998</v>
+      </c>
+      <c r="G116" s="19">
+        <f>ROUND(100*(Índices!G116/Índices!G115-1),4)</f>
+        <v>3.7635000000000001</v>
+      </c>
+      <c r="H116" s="19">
+        <f>ROUND(100*(Índices!H116/Índices!H115-1),4)</f>
+        <v>2.3010999999999999</v>
+      </c>
+      <c r="I116" s="20">
+        <f>ROUND(100*(Índices!I116/Índices!I115-1),4)</f>
+        <v>1.6325000000000001</v>
+      </c>
+      <c r="J116" s="19">
+        <f>ROUND(100*(Índices!J116/Índices!J115-1),4)</f>
+        <v>2.1017999999999999</v>
+      </c>
+      <c r="K116" s="19">
+        <f>ROUND(100*(Índices!K116/Índices!K115-1),4)</f>
+        <v>0.92810000000000004</v>
+      </c>
+      <c r="L116" s="19">
+        <f>ROUND(100*(Índices!L116/Índices!L115-1),4)</f>
+        <v>-0.39910000000000001</v>
+      </c>
+      <c r="M116" s="19">
+        <f>ROUND(100*(Índices!M116/Índices!M115-1),4)</f>
+        <v>3.7198000000000002</v>
+      </c>
+      <c r="N116" s="19">
+        <f>ROUND(100*(Índices!N116/Índices!N115-1),4)</f>
+        <v>1.2919</v>
+      </c>
+      <c r="O116" s="19">
+        <f>ROUND(100*(Índices!O116/Índices!O115-1),4)</f>
+        <v>2.6438999999999999</v>
+      </c>
+      <c r="P116" s="19">
+        <f>ROUND(100*(Índices!P116/Índices!P115-1),4)</f>
+        <v>4.1078999999999999</v>
+      </c>
+      <c r="Q116" s="19">
+        <f>ROUND(100*(Índices!Q116/Índices!Q115-1),4)</f>
+        <v>3.3121</v>
+      </c>
+      <c r="R116" s="19">
+        <f>ROUND(100*(Índices!R116/Índices!R115-1),4)</f>
+        <v>3.5611999999999999</v>
+      </c>
+      <c r="S116" s="19">
+        <f>ROUND(100*(Índices!S116/Índices!S115-1),4)</f>
+        <v>-10.152900000000001</v>
+      </c>
+      <c r="T116" s="19">
+        <f>ROUND(100*(Índices!T116/Índices!T115-1),4)</f>
+        <v>3.4249000000000001</v>
+      </c>
+      <c r="U116" s="20">
+        <f>ROUND(100*(Índices!U116/Índices!U115-1),4)</f>
+        <v>1.6877</v>
+      </c>
+      <c r="V116" s="18">
+        <f>ROUND(100*(Índices!V116/Índices!V115-1),4)</f>
+        <v>2.0871</v>
       </c>
     </row>
   </sheetData>
@@ -16900,7 +18370,7 @@
       <c r="H4" s="70"/>
       <c r="I4" s="23" t="str">
         <f>+_xlfn.CONCAT(H5, " ", C4, "/", H5, " ", C4-1)</f>
-        <v>Feb. 2024/Feb. 2023</v>
+        <v>Mar. 2024/Mar. 2023</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.25">
@@ -16930,25 +18400,25 @@
         <v>18</v>
       </c>
       <c r="C6" s="27">
-        <v>1.8013999999999999</v>
+        <v>2.3969999999999998</v>
       </c>
       <c r="D6" s="27">
-        <v>2.3969999999999998</v>
+        <v>2.7004999999999999</v>
       </c>
       <c r="E6" s="27">
-        <v>2.7004999999999999</v>
+        <v>2.5646</v>
       </c>
       <c r="F6" s="27">
-        <v>2.5646</v>
+        <v>2.4319999999999999</v>
       </c>
       <c r="G6" s="27">
-        <v>2.4319999999999999</v>
+        <v>2.5402</v>
       </c>
       <c r="H6" s="27">
-        <v>2.5402</v>
+        <v>2.2690999999999999</v>
       </c>
       <c r="I6" s="28">
-        <v>33.051499999999997</v>
+        <v>32.6068</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -16968,25 +18438,25 @@
         <v>19</v>
       </c>
       <c r="C8" s="32">
-        <v>1.7339</v>
+        <v>2.4363999999999999</v>
       </c>
       <c r="D8" s="32">
-        <v>2.4363999999999999</v>
+        <v>2.8277000000000001</v>
       </c>
       <c r="E8" s="32">
-        <v>2.8277000000000001</v>
+        <v>2.6457000000000002</v>
       </c>
       <c r="F8" s="32">
-        <v>2.6457000000000002</v>
+        <v>2.3557000000000001</v>
       </c>
       <c r="G8" s="32">
-        <v>2.3557000000000001</v>
+        <v>2.2839999999999998</v>
       </c>
       <c r="H8" s="32">
-        <v>2.2839999999999998</v>
+        <v>2.0867</v>
       </c>
       <c r="I8" s="33">
-        <v>33.192500000000003</v>
+        <v>32.623699999999999</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.25">
@@ -16994,25 +18464,25 @@
         <v>2</v>
       </c>
       <c r="C9" s="32">
-        <v>1.7568999999999999</v>
+        <v>2.3344</v>
       </c>
       <c r="D9" s="32">
-        <v>2.3344</v>
+        <v>2.5508999999999999</v>
       </c>
       <c r="E9" s="32">
-        <v>2.5508999999999999</v>
+        <v>2.5547</v>
       </c>
       <c r="F9" s="32">
-        <v>2.5547</v>
+        <v>2.3969</v>
       </c>
       <c r="G9" s="32">
-        <v>2.3969</v>
+        <v>2.7242999999999999</v>
       </c>
       <c r="H9" s="32">
-        <v>2.7242999999999999</v>
+        <v>2.3247</v>
       </c>
       <c r="I9" s="33">
-        <v>32.850999999999999</v>
+        <v>32.4236</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.25">
@@ -17020,25 +18490,25 @@
         <v>3</v>
       </c>
       <c r="C10" s="32">
-        <v>2.0485000000000002</v>
+        <v>2.2738999999999998</v>
       </c>
       <c r="D10" s="32">
-        <v>2.2738999999999998</v>
+        <v>2.6806999999999999</v>
       </c>
       <c r="E10" s="32">
-        <v>2.6806999999999999</v>
+        <v>2.1278999999999999</v>
       </c>
       <c r="F10" s="32">
-        <v>2.1278999999999999</v>
+        <v>2.3860999999999999</v>
       </c>
       <c r="G10" s="32">
-        <v>2.3860999999999999</v>
+        <v>3.0423</v>
       </c>
       <c r="H10" s="32">
-        <v>3.0423</v>
+        <v>2.9150999999999998</v>
       </c>
       <c r="I10" s="33">
-        <v>33.005099999999999</v>
+        <v>32.524700000000003</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.25">
@@ -17046,25 +18516,25 @@
         <v>4</v>
       </c>
       <c r="C11" s="32">
-        <v>1.5421</v>
+        <v>2.1981999999999999</v>
       </c>
       <c r="D11" s="32">
-        <v>2.1981999999999999</v>
+        <v>2.5632000000000001</v>
       </c>
       <c r="E11" s="32">
-        <v>2.5632000000000001</v>
+        <v>2.4977</v>
       </c>
       <c r="F11" s="32">
-        <v>2.4977</v>
+        <v>3.3418999999999999</v>
       </c>
       <c r="G11" s="32">
-        <v>3.3418999999999999</v>
+        <v>2.9007000000000001</v>
       </c>
       <c r="H11" s="32">
-        <v>2.9007000000000001</v>
+        <v>3.7635000000000001</v>
       </c>
       <c r="I11" s="33">
-        <v>32.127299999999998</v>
+        <v>33.430399999999999</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.25">
@@ -17072,25 +18542,25 @@
         <v>5</v>
       </c>
       <c r="C12" s="32">
-        <v>2.0384000000000002</v>
+        <v>2.6499000000000001</v>
       </c>
       <c r="D12" s="32">
-        <v>2.6499000000000001</v>
+        <v>3.0586000000000002</v>
       </c>
       <c r="E12" s="32">
-        <v>3.0586000000000002</v>
+        <v>2.5573999999999999</v>
       </c>
       <c r="F12" s="32">
-        <v>2.5573999999999999</v>
+        <v>2.3765999999999998</v>
       </c>
       <c r="G12" s="32">
-        <v>2.3765999999999998</v>
+        <v>2.9041999999999999</v>
       </c>
       <c r="H12" s="32">
-        <v>2.9041999999999999</v>
+        <v>2.3010999999999999</v>
       </c>
       <c r="I12" s="33">
-        <v>33.9422</v>
+        <v>33.531700000000001</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.25">
@@ -17098,25 +18568,25 @@
         <v>6</v>
       </c>
       <c r="C13" s="32">
-        <v>2.2927</v>
+        <v>2.5768</v>
       </c>
       <c r="D13" s="32">
-        <v>2.5768</v>
+        <v>2.4605999999999999</v>
       </c>
       <c r="E13" s="32">
-        <v>2.4605999999999999</v>
+        <v>2.5169000000000001</v>
       </c>
       <c r="F13" s="32">
-        <v>2.5169000000000001</v>
+        <v>2.4904000000000002</v>
       </c>
       <c r="G13" s="32">
-        <v>2.4904000000000002</v>
+        <v>2.6263999999999998</v>
       </c>
       <c r="H13" s="32">
-        <v>2.6263999999999998</v>
+        <v>1.6325000000000001</v>
       </c>
       <c r="I13" s="33">
-        <v>33.123399999999997</v>
+        <v>32.054699999999997</v>
       </c>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.25">
@@ -17146,25 +18616,25 @@
         <v>20</v>
       </c>
       <c r="C16" s="32">
-        <v>1.5581</v>
+        <v>2.2686999999999999</v>
       </c>
       <c r="D16" s="32">
-        <v>2.2686999999999999</v>
+        <v>3.2688999999999999</v>
       </c>
       <c r="E16" s="32">
-        <v>3.2688999999999999</v>
+        <v>2.1086999999999998</v>
       </c>
       <c r="F16" s="32">
-        <v>2.1086999999999998</v>
+        <v>2.9632000000000001</v>
       </c>
       <c r="G16" s="32">
-        <v>2.9632000000000001</v>
+        <v>2.0246</v>
       </c>
       <c r="H16" s="32">
-        <v>2.0246</v>
+        <v>2.1017999999999999</v>
       </c>
       <c r="I16" s="33">
-        <v>36.017899999999997</v>
+        <v>32.740299999999998</v>
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.25">
@@ -17172,25 +18642,25 @@
         <v>21</v>
       </c>
       <c r="C17" s="32">
-        <v>0.53410000000000002</v>
+        <v>2.6392000000000002</v>
       </c>
       <c r="D17" s="32">
-        <v>2.6392000000000002</v>
+        <v>0.33200000000000002</v>
       </c>
       <c r="E17" s="32">
-        <v>0.33200000000000002</v>
+        <v>2.4317000000000002</v>
       </c>
       <c r="F17" s="32">
-        <v>2.4317000000000002</v>
+        <v>0.09</v>
       </c>
       <c r="G17" s="32">
-        <v>0.09</v>
+        <v>0.35</v>
       </c>
       <c r="H17" s="32">
-        <v>0.35</v>
+        <v>0.92810000000000004</v>
       </c>
       <c r="I17" s="33">
-        <v>23.2895</v>
+        <v>24.9312</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.25">
@@ -17198,25 +18668,25 @@
         <v>22</v>
       </c>
       <c r="C18" s="32">
-        <v>-1.3429</v>
+        <v>1.7358</v>
       </c>
       <c r="D18" s="32">
-        <v>1.7358</v>
+        <v>1.3657999999999999</v>
       </c>
       <c r="E18" s="32">
-        <v>1.3657999999999999</v>
+        <v>0.55920000000000003</v>
       </c>
       <c r="F18" s="32">
-        <v>0.55920000000000003</v>
+        <v>1.1326000000000001</v>
       </c>
       <c r="G18" s="32">
-        <v>1.1326000000000001</v>
+        <v>1.4723999999999999</v>
       </c>
       <c r="H18" s="32">
-        <v>1.4723999999999999</v>
+        <v>-0.39910000000000001</v>
       </c>
       <c r="I18" s="33">
-        <v>15.055400000000001</v>
+        <v>13.426</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.25">
@@ -17224,25 +18694,25 @@
         <v>23</v>
       </c>
       <c r="C19" s="32">
-        <v>3.1423999999999999</v>
+        <v>2.8279999999999998</v>
       </c>
       <c r="D19" s="32">
-        <v>2.8279999999999998</v>
+        <v>3.4380000000000002</v>
       </c>
       <c r="E19" s="32">
-        <v>3.4380000000000002</v>
+        <v>3.3896000000000002</v>
       </c>
       <c r="F19" s="32">
-        <v>3.3896000000000002</v>
+        <v>3.0529000000000002</v>
       </c>
       <c r="G19" s="32">
-        <v>3.0529000000000002</v>
+        <v>6.7877000000000001</v>
       </c>
       <c r="H19" s="32">
-        <v>6.7877000000000001</v>
+        <v>3.7198000000000002</v>
       </c>
       <c r="I19" s="33">
-        <v>44.299599999999998</v>
+        <v>45.481999999999999</v>
       </c>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.25">
@@ -17250,25 +18720,25 @@
         <v>24</v>
       </c>
       <c r="C20" s="32">
-        <v>2.2124999999999999</v>
+        <v>1.6339999999999999</v>
       </c>
       <c r="D20" s="32">
-        <v>1.6339999999999999</v>
+        <v>1.119</v>
       </c>
       <c r="E20" s="32">
-        <v>1.119</v>
+        <v>2.0001000000000002</v>
       </c>
       <c r="F20" s="32">
-        <v>2.0001000000000002</v>
+        <v>1.8302</v>
       </c>
       <c r="G20" s="32">
-        <v>1.8302</v>
+        <v>2.5644999999999998</v>
       </c>
       <c r="H20" s="32">
-        <v>2.5644999999999998</v>
+        <v>1.2919</v>
       </c>
       <c r="I20" s="33">
-        <v>21.360299999999999</v>
+        <v>21.1311</v>
       </c>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.25">
@@ -17276,25 +18746,25 @@
         <v>25</v>
       </c>
       <c r="C21" s="32">
-        <v>2.2858999999999998</v>
+        <v>1.8307</v>
       </c>
       <c r="D21" s="32">
-        <v>1.8307</v>
+        <v>2.3965000000000001</v>
       </c>
       <c r="E21" s="32">
-        <v>2.3965000000000001</v>
+        <v>2.0903999999999998</v>
       </c>
       <c r="F21" s="32">
-        <v>2.0903999999999998</v>
+        <v>2.3418000000000001</v>
       </c>
       <c r="G21" s="32">
-        <v>2.3418000000000001</v>
+        <v>2.4708000000000001</v>
       </c>
       <c r="H21" s="32">
-        <v>2.4708000000000001</v>
+        <v>2.6438999999999999</v>
       </c>
       <c r="I21" s="33">
-        <v>28.6935</v>
+        <v>29.7119</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.25">
@@ -17302,25 +18772,25 @@
         <v>26</v>
       </c>
       <c r="C22" s="32">
-        <v>2.9731000000000001</v>
+        <v>3.4594999999999998</v>
       </c>
       <c r="D22" s="32">
-        <v>3.4594999999999998</v>
+        <v>3.0304000000000002</v>
       </c>
       <c r="E22" s="32">
-        <v>3.0304000000000002</v>
+        <v>3.9982000000000002</v>
       </c>
       <c r="F22" s="32">
-        <v>3.9982000000000002</v>
+        <v>1.8548</v>
       </c>
       <c r="G22" s="32">
-        <v>1.8548</v>
+        <v>1.978</v>
       </c>
       <c r="H22" s="32">
-        <v>1.978</v>
+        <v>4.1078999999999999</v>
       </c>
       <c r="I22" s="33">
-        <v>33.074800000000003</v>
+        <v>36.241100000000003</v>
       </c>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.25">
@@ -17328,25 +18798,25 @@
         <v>27</v>
       </c>
       <c r="C23" s="32">
-        <v>3.4643000000000002</v>
+        <v>2.7322000000000002</v>
       </c>
       <c r="D23" s="32">
-        <v>2.7322000000000002</v>
+        <v>3.0445000000000002</v>
       </c>
       <c r="E23" s="32">
-        <v>3.0445000000000002</v>
+        <v>3.0379999999999998</v>
       </c>
       <c r="F23" s="32">
-        <v>3.0379999999999998</v>
+        <v>-1.0443</v>
       </c>
       <c r="G23" s="32">
-        <v>-1.0443</v>
+        <v>-1.0564</v>
       </c>
       <c r="H23" s="32">
-        <v>-1.0564</v>
+        <v>3.3121</v>
       </c>
       <c r="I23" s="33">
-        <v>36.066200000000002</v>
+        <v>36.613900000000001</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.25">
@@ -17354,25 +18824,25 @@
         <v>28</v>
       </c>
       <c r="C24" s="32">
-        <v>1.3376999999999999</v>
+        <v>1.6108</v>
       </c>
       <c r="D24" s="32">
-        <v>1.6108</v>
+        <v>2.4485000000000001</v>
       </c>
       <c r="E24" s="32">
-        <v>2.4485000000000001</v>
+        <v>2.5417000000000001</v>
       </c>
       <c r="F24" s="32">
-        <v>2.5417000000000001</v>
+        <v>1.0244</v>
       </c>
       <c r="G24" s="32">
-        <v>1.0244</v>
+        <v>2.3454000000000002</v>
       </c>
       <c r="H24" s="32">
-        <v>2.3454000000000002</v>
+        <v>3.5611999999999999</v>
       </c>
       <c r="I24" s="33">
-        <v>27.917100000000001</v>
+        <v>32.256799999999998</v>
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.25">
@@ -17380,25 +18850,25 @@
         <v>29</v>
       </c>
       <c r="C25" s="32">
-        <v>5.7842000000000002</v>
+        <v>5.7397999999999998</v>
       </c>
       <c r="D25" s="32">
-        <v>5.7397999999999998</v>
+        <v>4.8711000000000002</v>
       </c>
       <c r="E25" s="32">
-        <v>4.8711000000000002</v>
+        <v>4.8147000000000002</v>
       </c>
       <c r="F25" s="32">
-        <v>4.8147000000000002</v>
+        <v>5.1432000000000002</v>
       </c>
       <c r="G25" s="32">
-        <v>5.1432000000000002</v>
+        <v>1.3282</v>
       </c>
       <c r="H25" s="32">
-        <v>1.3282</v>
+        <v>-10.152900000000001</v>
       </c>
       <c r="I25" s="33">
-        <v>50.653799999999997</v>
+        <v>38.868400000000001</v>
       </c>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.25">
@@ -17406,25 +18876,25 @@
         <v>30</v>
       </c>
       <c r="C26" s="32">
-        <v>1.2056</v>
+        <v>2.2783000000000002</v>
       </c>
       <c r="D26" s="32">
-        <v>2.2783000000000002</v>
+        <v>2.4801000000000002</v>
       </c>
       <c r="E26" s="32">
-        <v>2.4801000000000002</v>
+        <v>3.0933000000000002</v>
       </c>
       <c r="F26" s="32">
-        <v>3.0933000000000002</v>
+        <v>3.9603000000000002</v>
       </c>
       <c r="G26" s="32">
-        <v>3.9603000000000002</v>
+        <v>2.9319000000000002</v>
       </c>
       <c r="H26" s="32">
-        <v>2.9319000000000002</v>
+        <v>3.4249000000000001</v>
       </c>
       <c r="I26" s="33">
-        <v>41.646900000000002</v>
+        <v>41.042299999999997</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.25">
@@ -17432,25 +18902,25 @@
         <v>31</v>
       </c>
       <c r="C27" s="32">
-        <v>2.1455000000000002</v>
+        <v>2.4439000000000002</v>
       </c>
       <c r="D27" s="32">
-        <v>2.4439000000000002</v>
+        <v>2.5068000000000001</v>
       </c>
       <c r="E27" s="32">
-        <v>2.5068000000000001</v>
+        <v>2.6438000000000001</v>
       </c>
       <c r="F27" s="32">
-        <v>2.6438000000000001</v>
+        <v>2.7301000000000002</v>
       </c>
       <c r="G27" s="32">
-        <v>2.7301000000000002</v>
+        <v>3.2768000000000002</v>
       </c>
       <c r="H27" s="32">
-        <v>3.2768000000000002</v>
+        <v>1.6877</v>
       </c>
       <c r="I27" s="33">
-        <v>33.683700000000002</v>
+        <v>31.781300000000002</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.25">
@@ -17480,25 +18950,25 @@
         <v>33</v>
       </c>
       <c r="C30" s="32">
-        <v>1.1499999999999999</v>
+        <v>2.1185999999999998</v>
       </c>
       <c r="D30" s="32">
-        <v>2.1185999999999998</v>
+        <v>2.4952000000000001</v>
       </c>
       <c r="E30" s="32">
-        <v>2.4952000000000001</v>
+        <v>2.1663999999999999</v>
       </c>
       <c r="F30" s="32">
-        <v>2.1663999999999999</v>
+        <v>2.5274999999999999</v>
       </c>
       <c r="G30" s="32">
-        <v>2.5274999999999999</v>
+        <v>2.2141999999999999</v>
       </c>
       <c r="H30" s="32">
-        <v>2.2141999999999999</v>
+        <v>2.0871</v>
       </c>
       <c r="I30" s="33">
-        <v>31.275099999999998</v>
+        <v>30.024000000000001</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.25">
@@ -17506,25 +18976,25 @@
         <v>19</v>
       </c>
       <c r="C31" s="32">
-        <v>1.0967</v>
+        <v>2.2909999999999999</v>
       </c>
       <c r="D31" s="32">
-        <v>2.2909999999999999</v>
+        <v>2.6549999999999998</v>
       </c>
       <c r="E31" s="32">
-        <v>2.6549999999999998</v>
+        <v>2.1663999999999999</v>
       </c>
       <c r="F31" s="32">
-        <v>2.1663999999999999</v>
+        <v>2.7825000000000002</v>
       </c>
       <c r="G31" s="32">
-        <v>2.7825000000000002</v>
+        <v>1.8584000000000001</v>
       </c>
       <c r="H31" s="32">
-        <v>1.8584000000000001</v>
+        <v>1.7617</v>
       </c>
       <c r="I31" s="33">
-        <v>32.087800000000001</v>
+        <v>30.437000000000001</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.25">
@@ -17532,25 +19002,25 @@
         <v>2</v>
       </c>
       <c r="C32" s="32">
-        <v>1.1006</v>
+        <v>1.9105000000000001</v>
       </c>
       <c r="D32" s="32">
-        <v>1.9105000000000001</v>
+        <v>2.3687999999999998</v>
       </c>
       <c r="E32" s="32">
-        <v>2.3687999999999998</v>
+        <v>2.2696999999999998</v>
       </c>
       <c r="F32" s="32">
-        <v>2.2696999999999998</v>
+        <v>2.3115999999999999</v>
       </c>
       <c r="G32" s="32">
-        <v>2.3115999999999999</v>
+        <v>2.6072000000000002</v>
       </c>
       <c r="H32" s="32">
-        <v>2.6072000000000002</v>
+        <v>2.2222</v>
       </c>
       <c r="I32" s="33">
-        <v>31.500299999999999</v>
+        <v>30.499300000000002</v>
       </c>
     </row>
     <row r="33" spans="2:9" x14ac:dyDescent="0.25">
@@ -17558,25 +19028,25 @@
         <v>3</v>
       </c>
       <c r="C33" s="32">
-        <v>1.4411</v>
+        <v>2.2098</v>
       </c>
       <c r="D33" s="32">
-        <v>2.2098</v>
+        <v>2.5064000000000002</v>
       </c>
       <c r="E33" s="32">
-        <v>2.5064000000000002</v>
+        <v>1.6786000000000001</v>
       </c>
       <c r="F33" s="32">
-        <v>1.6786000000000001</v>
+        <v>2.3090000000000002</v>
       </c>
       <c r="G33" s="32">
-        <v>2.3090000000000002</v>
+        <v>2.4470000000000001</v>
       </c>
       <c r="H33" s="32">
-        <v>2.4470000000000001</v>
+        <v>3.0299</v>
       </c>
       <c r="I33" s="33">
-        <v>31.083100000000002</v>
+        <v>29.862400000000001</v>
       </c>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.25">
@@ -17584,25 +19054,25 @@
         <v>4</v>
       </c>
       <c r="C34" s="32">
-        <v>1.0519000000000001</v>
+        <v>1.9383999999999999</v>
       </c>
       <c r="D34" s="32">
-        <v>1.9383999999999999</v>
+        <v>2.4870000000000001</v>
       </c>
       <c r="E34" s="32">
-        <v>2.4870000000000001</v>
+        <v>2.2094</v>
       </c>
       <c r="F34" s="32">
-        <v>2.2094</v>
+        <v>2.9220999999999999</v>
       </c>
       <c r="G34" s="32">
-        <v>2.9220999999999999</v>
+        <v>3.2063000000000001</v>
       </c>
       <c r="H34" s="32">
-        <v>3.2063000000000001</v>
+        <v>3.2139000000000002</v>
       </c>
       <c r="I34" s="33">
-        <v>31.628699999999998</v>
+        <v>31.495799999999999</v>
       </c>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.25">
@@ -17610,25 +19080,25 @@
         <v>5</v>
       </c>
       <c r="C35" s="32">
-        <v>1.5072000000000001</v>
+        <v>2.2623000000000002</v>
       </c>
       <c r="D35" s="32">
-        <v>2.2623000000000002</v>
+        <v>2.6513</v>
       </c>
       <c r="E35" s="32">
-        <v>2.6513</v>
+        <v>2.3127</v>
       </c>
       <c r="F35" s="32">
-        <v>2.3127</v>
+        <v>2.0385</v>
       </c>
       <c r="G35" s="32">
-        <v>2.0385</v>
+        <v>2.1634000000000002</v>
       </c>
       <c r="H35" s="32">
-        <v>2.1634000000000002</v>
+        <v>2.2298</v>
       </c>
       <c r="I35" s="33">
-        <v>27.292000000000002</v>
+        <v>26.6602</v>
       </c>
     </row>
     <row r="36" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -17636,25 +19106,25 @@
         <v>6</v>
       </c>
       <c r="C36" s="35">
-        <v>1.3167</v>
+        <v>1.8217000000000001</v>
       </c>
       <c r="D36" s="35">
-        <v>1.8217000000000001</v>
+        <v>1.6400999999999999</v>
       </c>
       <c r="E36" s="35">
-        <v>1.6400999999999999</v>
+        <v>1.9037999999999999</v>
       </c>
       <c r="F36" s="35">
-        <v>1.9037999999999999</v>
+        <v>2.0792000000000002</v>
       </c>
       <c r="G36" s="35">
-        <v>2.0792000000000002</v>
+        <v>1.623</v>
       </c>
       <c r="H36" s="35">
-        <v>1.623</v>
+        <v>1.7052</v>
       </c>
       <c r="I36" s="36">
-        <v>25.946999999999999</v>
+        <v>24.9451</v>
       </c>
     </row>
     <row r="37" spans="2:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -17768,25 +19238,25 @@
         <v>37</v>
       </c>
       <c r="C5" s="41">
-        <v>2.2839999999999998</v>
+        <v>2.0867</v>
       </c>
       <c r="D5" s="41">
-        <v>2.7242999999999999</v>
+        <v>2.3247</v>
       </c>
       <c r="E5" s="41">
-        <v>3.0423</v>
+        <v>2.9150999999999998</v>
       </c>
       <c r="F5" s="41">
-        <v>2.9007000000000001</v>
+        <v>3.7635000000000001</v>
       </c>
       <c r="G5" s="41">
-        <v>2.9041999999999999</v>
+        <v>2.3010999999999999</v>
       </c>
       <c r="H5" s="41">
-        <v>2.6263999999999998</v>
+        <v>1.6325000000000001</v>
       </c>
       <c r="I5" s="42">
-        <v>2.5402</v>
+        <v>2.2690999999999999</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.25">
@@ -17794,25 +19264,25 @@
         <v>20</v>
       </c>
       <c r="C6" s="32">
-        <v>0.36120000000000002</v>
+        <v>0.42859999999999998</v>
       </c>
       <c r="D6" s="32">
-        <v>0.73899999999999999</v>
+        <v>0.63529999999999998</v>
       </c>
       <c r="E6" s="32">
-        <v>0.96399999999999997</v>
+        <v>1.1867000000000001</v>
       </c>
       <c r="F6" s="32">
-        <v>1.4200999999999999</v>
+        <v>1.4597</v>
       </c>
       <c r="G6" s="32">
-        <v>0.85929999999999995</v>
+        <v>0.77529999999999999</v>
       </c>
       <c r="H6" s="32">
-        <v>0.44009999999999999</v>
+        <v>0.62239999999999995</v>
       </c>
       <c r="I6" s="33">
-        <v>0.60899999999999999</v>
+        <v>0.62470000000000003</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.25">
@@ -17820,25 +19290,25 @@
         <v>21</v>
       </c>
       <c r="C7" s="32">
-        <v>2.9999999999999997E-4</v>
+        <v>1.8200000000000001E-2</v>
       </c>
       <c r="D7" s="32">
-        <v>1.8599999999999998E-2</v>
+        <v>2.6200000000000001E-2</v>
       </c>
       <c r="E7" s="32">
-        <v>-4.0000000000000002E-4</v>
+        <v>2.8799999999999999E-2</v>
       </c>
       <c r="F7" s="32">
-        <v>4.1799999999999997E-2</v>
+        <v>5.16E-2</v>
       </c>
       <c r="G7" s="32">
-        <v>1.44E-2</v>
+        <v>1.37E-2</v>
       </c>
       <c r="H7" s="32">
-        <v>7.6E-3</v>
+        <v>1.8200000000000001E-2</v>
       </c>
       <c r="I7" s="33">
-        <v>9.4000000000000004E-3</v>
+        <v>2.3E-2</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.25">
@@ -17846,25 +19316,25 @@
         <v>22</v>
       </c>
       <c r="C8" s="32">
-        <v>9.1499999999999998E-2</v>
+        <v>-0.1191</v>
       </c>
       <c r="D8" s="32">
-        <v>0.1258</v>
+        <v>1.5699999999999999E-2</v>
       </c>
       <c r="E8" s="32">
-        <v>0.14330000000000001</v>
+        <v>0.1777</v>
       </c>
       <c r="F8" s="32">
-        <v>0.1598</v>
+        <v>0.20269999999999999</v>
       </c>
       <c r="G8" s="32">
-        <v>7.9500000000000001E-2</v>
+        <v>0.1174</v>
       </c>
       <c r="H8" s="32">
-        <v>0.1305</v>
+        <v>0.11600000000000001</v>
       </c>
       <c r="I8" s="33">
-        <v>0.1111</v>
+        <v>-1.5100000000000001E-2</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.25">
@@ -17872,25 +19342,25 @@
         <v>23</v>
       </c>
       <c r="C9" s="32">
-        <v>0.60470000000000002</v>
+        <v>0.375</v>
       </c>
       <c r="D9" s="32">
-        <v>0.57650000000000001</v>
+        <v>0.28899999999999998</v>
       </c>
       <c r="E9" s="32">
-        <v>0.85260000000000002</v>
+        <v>0.39960000000000001</v>
       </c>
       <c r="F9" s="32">
-        <v>0.37269999999999998</v>
+        <v>1.0591999999999999</v>
       </c>
       <c r="G9" s="32">
-        <v>1.115</v>
+        <v>0.3528</v>
       </c>
       <c r="H9" s="32">
-        <v>1.2051000000000001</v>
+        <v>0.28660000000000002</v>
       </c>
       <c r="I9" s="33">
-        <v>0.65549999999999997</v>
+        <v>0.373</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.25">
@@ -17898,25 +19368,25 @@
         <v>24</v>
       </c>
       <c r="C10" s="32">
-        <v>0.15890000000000001</v>
+        <v>6.8099999999999994E-2</v>
       </c>
       <c r="D10" s="32">
-        <v>0.1061</v>
+        <v>7.7899999999999997E-2</v>
       </c>
       <c r="E10" s="32">
-        <v>0.1293</v>
+        <v>6.08E-2</v>
       </c>
       <c r="F10" s="32">
-        <v>0.1696</v>
+        <v>5.5E-2</v>
       </c>
       <c r="G10" s="32">
-        <v>0.10349999999999999</v>
+        <v>6.7699999999999996E-2</v>
       </c>
       <c r="H10" s="32">
-        <v>0.1145</v>
+        <v>5.4999999999999997E-3</v>
       </c>
       <c r="I10" s="33">
-        <v>0.13439999999999999</v>
+        <v>6.7500000000000004E-2</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.25">
@@ -17924,25 +19394,25 @@
         <v>25</v>
       </c>
       <c r="C11" s="32">
-        <v>0.2099</v>
+        <v>0.28050000000000003</v>
       </c>
       <c r="D11" s="32">
-        <v>0.248</v>
+        <v>0.23019999999999999</v>
       </c>
       <c r="E11" s="32">
-        <v>0.1686</v>
+        <v>0.16969999999999999</v>
       </c>
       <c r="F11" s="32">
-        <v>0.1464</v>
+        <v>0.1215</v>
       </c>
       <c r="G11" s="32">
-        <v>0.21640000000000001</v>
+        <v>0.18740000000000001</v>
       </c>
       <c r="H11" s="32">
-        <v>0.2009</v>
+        <v>0.14460000000000001</v>
       </c>
       <c r="I11" s="33">
-        <v>0.2172</v>
+        <v>0.23749999999999999</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.25">
@@ -17950,25 +19420,25 @@
         <v>26</v>
       </c>
       <c r="C12" s="32">
-        <v>0.2261</v>
+        <v>0.54369999999999996</v>
       </c>
       <c r="D12" s="32">
-        <v>0.21579999999999999</v>
+        <v>0.40110000000000001</v>
       </c>
       <c r="E12" s="32">
-        <v>0.31030000000000002</v>
+        <v>0.44340000000000002</v>
       </c>
       <c r="F12" s="32">
-        <v>0.28060000000000002</v>
+        <v>0.2792</v>
       </c>
       <c r="G12" s="32">
-        <v>0.10829999999999999</v>
+        <v>0.4975</v>
       </c>
       <c r="H12" s="32">
-        <v>0.18340000000000001</v>
+        <v>0.47270000000000001</v>
       </c>
       <c r="I12" s="33">
-        <v>0.2228</v>
+        <v>0.47049999999999997</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.25">
@@ -17976,25 +19446,25 @@
         <v>27</v>
       </c>
       <c r="C13" s="32">
-        <v>-2.93E-2</v>
+        <v>0.10059999999999999</v>
       </c>
       <c r="D13" s="32">
-        <v>-3.7100000000000001E-2</v>
+        <v>6.9599999999999995E-2</v>
       </c>
       <c r="E13" s="32">
-        <v>1.2800000000000001E-2</v>
+        <v>6.3299999999999995E-2</v>
       </c>
       <c r="F13" s="32">
-        <v>-2.4299999999999999E-2</v>
+        <v>6.6400000000000001E-2</v>
       </c>
       <c r="G13" s="32">
-        <v>-2.4400000000000002E-2</v>
+        <v>5.3400000000000003E-2</v>
       </c>
       <c r="H13" s="32">
-        <v>-2.3E-3</v>
+        <v>7.5899999999999995E-2</v>
       </c>
       <c r="I13" s="33">
-        <v>-2.7400000000000001E-2</v>
+        <v>8.2299999999999998E-2</v>
       </c>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.25">
@@ -18002,25 +19472,25 @@
         <v>28</v>
       </c>
       <c r="C14" s="32">
-        <v>9.1700000000000004E-2</v>
+        <v>0.21640000000000001</v>
       </c>
       <c r="D14" s="32">
-        <v>0.27800000000000002</v>
+        <v>0.28720000000000001</v>
       </c>
       <c r="E14" s="32">
-        <v>1.4800000000000001E-2</v>
+        <v>0.2349</v>
       </c>
       <c r="F14" s="32">
-        <v>0.18029999999999999</v>
+        <v>6.5199999999999994E-2</v>
       </c>
       <c r="G14" s="32">
-        <v>6.3799999999999996E-2</v>
+        <v>0.16950000000000001</v>
       </c>
       <c r="H14" s="32">
-        <v>7.6899999999999996E-2</v>
+        <v>0.11509999999999999</v>
       </c>
       <c r="I14" s="33">
-        <v>0.152</v>
+        <v>0.22800000000000001</v>
       </c>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.25">
@@ -18028,25 +19498,25 @@
         <v>29</v>
       </c>
       <c r="C15" s="32">
-        <v>9.5699999999999993E-2</v>
+        <v>-0.32400000000000001</v>
       </c>
       <c r="D15" s="32">
-        <v>-1.24E-2</v>
+        <v>-0.1411</v>
       </c>
       <c r="E15" s="32">
-        <v>-9.1999999999999998E-3</v>
+        <v>-0.26279999999999998</v>
       </c>
       <c r="F15" s="32">
-        <v>-5.2699999999999997E-2</v>
+        <v>4.7600000000000003E-2</v>
       </c>
       <c r="G15" s="32">
-        <v>0.10979999999999999</v>
+        <v>-0.20100000000000001</v>
       </c>
       <c r="H15" s="32">
-        <v>4.2599999999999999E-2</v>
+        <v>-0.38429999999999997</v>
       </c>
       <c r="I15" s="33">
-        <v>4.3099999999999999E-2</v>
+        <v>-0.2369</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.25">
@@ -18054,25 +19524,25 @@
         <v>30</v>
       </c>
       <c r="C16" s="32">
-        <v>0.34939999999999999</v>
+        <v>0.43540000000000001</v>
       </c>
       <c r="D16" s="32">
-        <v>0.35289999999999999</v>
+        <v>0.37959999999999999</v>
       </c>
       <c r="E16" s="32">
-        <v>0.37030000000000002</v>
+        <v>0.35389999999999999</v>
       </c>
       <c r="F16" s="32">
-        <v>0.1295</v>
+        <v>0.2908</v>
       </c>
       <c r="G16" s="32">
-        <v>0.14829999999999999</v>
+        <v>0.2165</v>
       </c>
       <c r="H16" s="32">
-        <v>0.14760000000000001</v>
+        <v>0.11600000000000001</v>
       </c>
       <c r="I16" s="33">
-        <v>0.32250000000000001</v>
+        <v>0.37830000000000003</v>
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.25">
@@ -18080,22 +19550,22 @@
         <v>31</v>
       </c>
       <c r="C17" s="32">
-        <v>0.12379999999999999</v>
+        <v>6.3299999999999995E-2</v>
       </c>
       <c r="D17" s="32">
-        <v>0.113</v>
+        <v>5.3900000000000003E-2</v>
       </c>
       <c r="E17" s="32">
-        <v>8.5999999999999993E-2</v>
+        <v>5.8799999999999998E-2</v>
       </c>
       <c r="F17" s="32">
-        <v>7.6899999999999996E-2</v>
+        <v>6.4500000000000002E-2</v>
       </c>
       <c r="G17" s="32">
-        <v>0.1103</v>
+        <v>5.11E-2</v>
       </c>
       <c r="H17" s="32">
-        <v>7.9600000000000004E-2</v>
+        <v>4.3999999999999997E-2</v>
       </c>
       <c r="I17" s="33">
         <v>0.08</v>
@@ -18128,25 +19598,25 @@
         <v>37</v>
       </c>
       <c r="C20" s="41">
-        <v>33.192500000000003</v>
+        <v>32.623699999999999</v>
       </c>
       <c r="D20" s="41">
-        <v>32.850999999999999</v>
+        <v>32.4236</v>
       </c>
       <c r="E20" s="41">
-        <v>33.005099999999999</v>
+        <v>32.524700000000003</v>
       </c>
       <c r="F20" s="41">
-        <v>32.127299999999998</v>
+        <v>33.430399999999999</v>
       </c>
       <c r="G20" s="41">
-        <v>33.9422</v>
+        <v>33.531700000000001</v>
       </c>
       <c r="H20" s="41">
-        <v>33.123399999999997</v>
+        <v>32.054699999999997</v>
       </c>
       <c r="I20" s="42">
-        <v>33.051499999999997</v>
+        <v>32.6068</v>
       </c>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.25">
@@ -18154,25 +19624,25 @@
         <v>20</v>
       </c>
       <c r="C21" s="32">
-        <v>9.2178000000000004</v>
+        <v>8.3094000000000001</v>
       </c>
       <c r="D21" s="32">
-        <v>10.8096</v>
+        <v>10.1304</v>
       </c>
       <c r="E21" s="32">
-        <v>12.9297</v>
+        <v>12.3735</v>
       </c>
       <c r="F21" s="32">
-        <v>13.858599999999999</v>
+        <v>13.6159</v>
       </c>
       <c r="G21" s="32">
-        <v>11.466200000000001</v>
+        <v>11.0108</v>
       </c>
       <c r="H21" s="32">
-        <v>8.0873000000000008</v>
+        <v>8.1262000000000008</v>
       </c>
       <c r="I21" s="33">
-        <v>10.291499999999999</v>
+        <v>9.5824999999999996</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.25">
@@ -18180,25 +19650,25 @@
         <v>21</v>
       </c>
       <c r="C22" s="32">
-        <v>0.60070000000000001</v>
+        <v>0.61670000000000003</v>
       </c>
       <c r="D22" s="32">
-        <v>0.68010000000000004</v>
+        <v>0.7127</v>
       </c>
       <c r="E22" s="32">
-        <v>0.51039999999999996</v>
+        <v>0.54459999999999997</v>
       </c>
       <c r="F22" s="32">
-        <v>0.5958</v>
+        <v>0.6603</v>
       </c>
       <c r="G22" s="32">
-        <v>0.60289999999999999</v>
+        <v>0.62870000000000004</v>
       </c>
       <c r="H22" s="32">
-        <v>0.69750000000000001</v>
+        <v>0.71089999999999998</v>
       </c>
       <c r="I22" s="33">
-        <v>0.62590000000000001</v>
+        <v>0.65149999999999997</v>
       </c>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.25">
@@ -18206,25 +19676,25 @@
         <v>22</v>
       </c>
       <c r="C23" s="32">
-        <v>1.1172</v>
+        <v>1.024</v>
       </c>
       <c r="D23" s="32">
-        <v>1.2209000000000001</v>
+        <v>1.0668</v>
       </c>
       <c r="E23" s="32">
-        <v>1.6615</v>
+        <v>1.4822</v>
       </c>
       <c r="F23" s="32">
-        <v>1.3461000000000001</v>
+        <v>1.4692000000000001</v>
       </c>
       <c r="G23" s="32">
-        <v>1.4410000000000001</v>
+        <v>1.1684000000000001</v>
       </c>
       <c r="H23" s="32">
-        <v>2.04</v>
+        <v>1.7209000000000001</v>
       </c>
       <c r="I23" s="33">
-        <v>1.2594000000000001</v>
+        <v>1.1295999999999999</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.25">
@@ -18232,25 +19702,25 @@
         <v>23</v>
       </c>
       <c r="C24" s="32">
-        <v>4.0495000000000001</v>
+        <v>4.0890000000000004</v>
       </c>
       <c r="D24" s="32">
-        <v>3.8138999999999998</v>
+        <v>3.8477000000000001</v>
       </c>
       <c r="E24" s="32">
-        <v>3.875</v>
+        <v>4.0088999999999997</v>
       </c>
       <c r="F24" s="32">
-        <v>4.3304</v>
+        <v>5.3650000000000002</v>
       </c>
       <c r="G24" s="32">
-        <v>4.7001999999999997</v>
+        <v>4.6951000000000001</v>
       </c>
       <c r="H24" s="32">
-        <v>7.0789999999999997</v>
+        <v>6.7061999999999999</v>
       </c>
       <c r="I24" s="33">
-        <v>4.1417999999999999</v>
+        <v>4.2095000000000002</v>
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.25">
@@ -18258,25 +19728,25 @@
         <v>24</v>
       </c>
       <c r="C25" s="32">
-        <v>1.2996000000000001</v>
+        <v>1.2656000000000001</v>
       </c>
       <c r="D25" s="32">
-        <v>1.1700999999999999</v>
+        <v>1.1332</v>
       </c>
       <c r="E25" s="32">
-        <v>1.0939000000000001</v>
+        <v>1.0403</v>
       </c>
       <c r="F25" s="32">
-        <v>1.0307999999999999</v>
+        <v>1.0331999999999999</v>
       </c>
       <c r="G25" s="32">
-        <v>1.2005999999999999</v>
+        <v>1.1798999999999999</v>
       </c>
       <c r="H25" s="32">
-        <v>1.2750999999999999</v>
+        <v>1.1292</v>
       </c>
       <c r="I25" s="33">
-        <v>1.2228000000000001</v>
+        <v>1.1836</v>
       </c>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.25">
@@ -18284,25 +19754,25 @@
         <v>25</v>
       </c>
       <c r="C26" s="32">
-        <v>2.7320000000000002</v>
+        <v>2.8123999999999998</v>
       </c>
       <c r="D26" s="32">
-        <v>2.8292000000000002</v>
+        <v>2.8803000000000001</v>
       </c>
       <c r="E26" s="32">
-        <v>2.1701000000000001</v>
+        <v>2.1252</v>
       </c>
       <c r="F26" s="32">
-        <v>1.7154</v>
+        <v>1.6876</v>
       </c>
       <c r="G26" s="32">
-        <v>2.4068000000000001</v>
+        <v>2.4323999999999999</v>
       </c>
       <c r="H26" s="32">
-        <v>1.8359000000000001</v>
+        <v>1.8143</v>
       </c>
       <c r="I26" s="33">
-        <v>2.6230000000000002</v>
+        <v>2.6722999999999999</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.25">
@@ -18310,25 +19780,25 @@
         <v>26</v>
       </c>
       <c r="C27" s="32">
-        <v>3.8978999999999999</v>
+        <v>4.2662000000000004</v>
       </c>
       <c r="D27" s="32">
-        <v>3.5384000000000002</v>
+        <v>3.7082000000000002</v>
       </c>
       <c r="E27" s="32">
-        <v>2.9449999999999998</v>
+        <v>3.2280000000000002</v>
       </c>
       <c r="F27" s="32">
-        <v>3.1053999999999999</v>
+        <v>3.3071000000000002</v>
       </c>
       <c r="G27" s="32">
-        <v>4.5557999999999996</v>
+        <v>4.9108999999999998</v>
       </c>
       <c r="H27" s="32">
-        <v>5.5776000000000003</v>
+        <v>5.8080999999999996</v>
       </c>
       <c r="I27" s="33">
-        <v>3.7845</v>
+        <v>4.0646000000000004</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.25">
@@ -18336,25 +19806,25 @@
         <v>27</v>
       </c>
       <c r="C28" s="32">
-        <v>0.98660000000000003</v>
+        <v>0.97589999999999999</v>
       </c>
       <c r="D28" s="32">
-        <v>0.86939999999999995</v>
+        <v>0.88260000000000005</v>
       </c>
       <c r="E28" s="32">
-        <v>0.80010000000000003</v>
+        <v>0.82350000000000001</v>
       </c>
       <c r="F28" s="32">
-        <v>0.81510000000000005</v>
+        <v>0.83440000000000003</v>
       </c>
       <c r="G28" s="32">
-        <v>0.69920000000000004</v>
+        <v>0.71589999999999998</v>
       </c>
       <c r="H28" s="32">
-        <v>0.87590000000000001</v>
+        <v>0.86639999999999995</v>
       </c>
       <c r="I28" s="33">
-        <v>0.90600000000000003</v>
+        <v>0.90869999999999995</v>
       </c>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.25">
@@ -18362,25 +19832,25 @@
         <v>28</v>
       </c>
       <c r="C29" s="32">
-        <v>1.8306</v>
+        <v>2.0594999999999999</v>
       </c>
       <c r="D29" s="32">
-        <v>2.1438000000000001</v>
+        <v>2.4260999999999999</v>
       </c>
       <c r="E29" s="32">
-        <v>1.3217000000000001</v>
+        <v>1.5224</v>
       </c>
       <c r="F29" s="32">
-        <v>1.4739</v>
+        <v>1.4556</v>
       </c>
       <c r="G29" s="32">
-        <v>1.5828</v>
+        <v>1.6882999999999999</v>
       </c>
       <c r="H29" s="32">
-        <v>1.4729000000000001</v>
+        <v>1.4552</v>
       </c>
       <c r="I29" s="33">
-        <v>1.8573999999999999</v>
+        <v>2.0737999999999999</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.25">
@@ -18388,25 +19858,25 @@
         <v>29</v>
       </c>
       <c r="C30" s="32">
-        <v>1.038</v>
+        <v>0.9778</v>
       </c>
       <c r="D30" s="32">
-        <v>0.58940000000000003</v>
+        <v>0.49109999999999998</v>
       </c>
       <c r="E30" s="32">
-        <v>1.2060999999999999</v>
+        <v>1.1527000000000001</v>
       </c>
       <c r="F30" s="32">
-        <v>0.439</v>
+        <v>0.50629999999999997</v>
       </c>
       <c r="G30" s="32">
-        <v>0.84040000000000004</v>
+        <v>0.68020000000000003</v>
       </c>
       <c r="H30" s="32">
-        <v>0.97819999999999996</v>
+        <v>0.77849999999999997</v>
       </c>
       <c r="I30" s="33">
-        <v>0.85619999999999996</v>
+        <v>0.77769999999999995</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.25">
@@ -18414,25 +19884,25 @@
         <v>30</v>
       </c>
       <c r="C31" s="32">
-        <v>5.1292</v>
+        <v>5.0423</v>
       </c>
       <c r="D31" s="32">
-        <v>4.0964999999999998</v>
+        <v>4.0976999999999997</v>
       </c>
       <c r="E31" s="32">
-        <v>3.6065999999999998</v>
+        <v>3.3650000000000002</v>
       </c>
       <c r="F31" s="32">
-        <v>2.4902000000000002</v>
+        <v>2.6092</v>
       </c>
       <c r="G31" s="32">
-        <v>3.2376999999999998</v>
+        <v>3.2732999999999999</v>
       </c>
       <c r="H31" s="32">
-        <v>2.2553999999999998</v>
+        <v>2.0331000000000001</v>
       </c>
       <c r="I31" s="33">
-        <v>4.3230000000000004</v>
+        <v>4.2651000000000003</v>
       </c>
     </row>
     <row r="32" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -18440,25 +19910,25 @@
         <v>31</v>
       </c>
       <c r="C32" s="35">
-        <v>1.2925</v>
+        <v>1.1840999999999999</v>
       </c>
       <c r="D32" s="35">
-        <v>1.0886</v>
+        <v>1.0455000000000001</v>
       </c>
       <c r="E32" s="35">
-        <v>0.8851</v>
+        <v>0.85870000000000002</v>
       </c>
       <c r="F32" s="35">
-        <v>0.92589999999999995</v>
+        <v>0.88600000000000001</v>
       </c>
       <c r="G32" s="35">
-        <v>1.2087000000000001</v>
+        <v>1.1476999999999999</v>
       </c>
       <c r="H32" s="35">
-        <v>0.95069999999999999</v>
+        <v>0.90749999999999997</v>
       </c>
       <c r="I32" s="36">
-        <v>1.1583000000000001</v>
+        <v>1.0864</v>
       </c>
     </row>
     <row r="33" spans="2:9" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">

--- a/assets/excel/IPCse - Series históricas.xlsx
+++ b/assets/excel/IPCse - Series históricas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iaral\Dropbox\IPC seasonal adjustment\IPCse\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{42D2DCA1-30D2-40BC-8862-5E464150D88B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA9F21C6-3C3F-42FD-8ED9-9E080968B9FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{A81B6F3A-9175-42CA-B78F-287A4E3C6249}"/>
   </bookViews>
@@ -203,9 +203,6 @@
 Tasa de Inflación Mensual por Quintiles</t>
   </si>
   <si>
-    <t>Oct.</t>
-  </si>
-  <si>
     <t>Nov.</t>
   </si>
   <si>
@@ -219,6 +216,9 @@
   </si>
   <si>
     <t>Mar.</t>
+  </si>
+  <si>
+    <t>Abr.</t>
   </si>
 </sst>
 </file>
@@ -991,9 +991,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1031,7 +1031,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1137,7 +1137,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1279,7 +1279,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1287,7 +1287,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA821952-0137-4F39-844C-15CA99AC928E}">
-  <dimension ref="B1:V116"/>
+  <dimension ref="B1:V117"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="15.5703125" defaultRowHeight="18" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="4" customWidth="1"/>
@@ -8634,69 +8634,134 @@
         <v>10427.577499999999</v>
       </c>
     </row>
-    <row r="116" spans="2:22" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B116" s="14">
+    <row r="116" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B116" s="13">
         <v>46082</v>
       </c>
-      <c r="C116" s="18">
+      <c r="C116" s="15">
         <v>10956.1021</v>
       </c>
-      <c r="D116" s="19">
+      <c r="D116" s="16">
         <v>10887.980100000001</v>
       </c>
-      <c r="E116" s="19">
+      <c r="E116" s="16">
         <v>10925.5167</v>
       </c>
-      <c r="F116" s="19">
+      <c r="F116" s="16">
         <v>11076.978800000001</v>
       </c>
-      <c r="G116" s="19">
+      <c r="G116" s="16">
         <v>10996.589400000001</v>
       </c>
-      <c r="H116" s="19">
+      <c r="H116" s="16">
         <v>11122.317300000001</v>
       </c>
-      <c r="I116" s="20">
+      <c r="I116" s="17">
         <v>11026.3896</v>
       </c>
-      <c r="J116" s="19">
+      <c r="J116" s="16">
         <v>11648.402700000001</v>
       </c>
-      <c r="K116" s="19">
+      <c r="K116" s="16">
         <v>7618.9602000000004</v>
       </c>
-      <c r="L116" s="19">
+      <c r="L116" s="16">
         <v>8000.4431000000004</v>
       </c>
-      <c r="M116" s="19">
+      <c r="M116" s="16">
         <v>12092.325999999999</v>
       </c>
-      <c r="N116" s="19">
+      <c r="N116" s="16">
         <v>8925.5949999999993</v>
       </c>
-      <c r="O116" s="19">
+      <c r="O116" s="16">
         <v>12210.1445</v>
       </c>
-      <c r="P116" s="19">
+      <c r="P116" s="16">
         <v>11598.991900000001</v>
       </c>
-      <c r="Q116" s="19">
+      <c r="Q116" s="16">
         <v>9747.6638000000003</v>
       </c>
-      <c r="R116" s="19">
+      <c r="R116" s="16">
         <v>9766.2255999999998</v>
       </c>
-      <c r="S116" s="19">
+      <c r="S116" s="16">
         <v>9304.0820999999996</v>
       </c>
-      <c r="T116" s="19">
+      <c r="T116" s="16">
         <v>13663.4095</v>
       </c>
-      <c r="U116" s="20">
+      <c r="U116" s="17">
         <v>10656.376200000001</v>
       </c>
-      <c r="V116" s="18">
+      <c r="V116" s="15">
         <v>10645.208000000001</v>
+      </c>
+    </row>
+    <row r="117" spans="2:22" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B117" s="14">
+        <v>46113</v>
+      </c>
+      <c r="C117" s="18">
+        <v>11228.8565</v>
+      </c>
+      <c r="D117" s="19">
+        <v>11176.9575</v>
+      </c>
+      <c r="E117" s="19">
+        <v>11184.360699999999</v>
+      </c>
+      <c r="F117" s="19">
+        <v>11325.324500000001</v>
+      </c>
+      <c r="G117" s="19">
+        <v>11285.165800000001</v>
+      </c>
+      <c r="H117" s="19">
+        <v>11361.1214</v>
+      </c>
+      <c r="I117" s="20">
+        <v>11331.750400000001</v>
+      </c>
+      <c r="J117" s="19">
+        <v>11856.9944</v>
+      </c>
+      <c r="K117" s="19">
+        <v>7865.2641999999996</v>
+      </c>
+      <c r="L117" s="19">
+        <v>8046.4912999999997</v>
+      </c>
+      <c r="M117" s="19">
+        <v>12513.106</v>
+      </c>
+      <c r="N117" s="19">
+        <v>9183.4130999999998</v>
+      </c>
+      <c r="O117" s="19">
+        <v>12517.199500000001</v>
+      </c>
+      <c r="P117" s="19">
+        <v>12109.456</v>
+      </c>
+      <c r="Q117" s="19">
+        <v>10119.8717</v>
+      </c>
+      <c r="R117" s="19">
+        <v>9863.0329999999994</v>
+      </c>
+      <c r="S117" s="19">
+        <v>9654.8444</v>
+      </c>
+      <c r="T117" s="19">
+        <v>14019.0486</v>
+      </c>
+      <c r="U117" s="20">
+        <v>10916.9899</v>
+      </c>
+      <c r="V117" s="18">
+        <v>10847.252200000001</v>
       </c>
     </row>
   </sheetData>
@@ -8712,7 +8777,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED968B30-91AE-4BCD-9838-818BA334E48C}">
-  <dimension ref="B1:V116"/>
+  <dimension ref="B1:V117"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="15.5703125" defaultRowHeight="18" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="4" customWidth="1"/>
@@ -18219,89 +18284,174 @@
         <v>2.2141999999999999</v>
       </c>
     </row>
-    <row r="116" spans="2:22" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B116" s="48">
+    <row r="116" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B116" s="13">
         <v>46082</v>
       </c>
-      <c r="C116" s="18">
+      <c r="C116" s="15">
         <f>ROUND(100*(Índices!C116/Índices!C115-1),4)</f>
         <v>2.2690999999999999</v>
       </c>
-      <c r="D116" s="19">
+      <c r="D116" s="16">
         <f>ROUND(100*(Índices!D116/Índices!D115-1),4)</f>
         <v>2.0867</v>
       </c>
-      <c r="E116" s="19">
+      <c r="E116" s="16">
         <f>ROUND(100*(Índices!E116/Índices!E115-1),4)</f>
         <v>2.3247</v>
       </c>
-      <c r="F116" s="19">
+      <c r="F116" s="16">
         <f>ROUND(100*(Índices!F116/Índices!F115-1),4)</f>
         <v>2.9150999999999998</v>
       </c>
-      <c r="G116" s="19">
+      <c r="G116" s="16">
         <f>ROUND(100*(Índices!G116/Índices!G115-1),4)</f>
         <v>3.7635000000000001</v>
       </c>
-      <c r="H116" s="19">
+      <c r="H116" s="16">
         <f>ROUND(100*(Índices!H116/Índices!H115-1),4)</f>
         <v>2.3010999999999999</v>
       </c>
-      <c r="I116" s="20">
+      <c r="I116" s="17">
         <f>ROUND(100*(Índices!I116/Índices!I115-1),4)</f>
         <v>1.6325000000000001</v>
       </c>
-      <c r="J116" s="19">
+      <c r="J116" s="16">
         <f>ROUND(100*(Índices!J116/Índices!J115-1),4)</f>
         <v>2.1017999999999999</v>
       </c>
-      <c r="K116" s="19">
+      <c r="K116" s="16">
         <f>ROUND(100*(Índices!K116/Índices!K115-1),4)</f>
         <v>0.92810000000000004</v>
       </c>
-      <c r="L116" s="19">
+      <c r="L116" s="16">
         <f>ROUND(100*(Índices!L116/Índices!L115-1),4)</f>
         <v>-0.39910000000000001</v>
       </c>
-      <c r="M116" s="19">
+      <c r="M116" s="16">
         <f>ROUND(100*(Índices!M116/Índices!M115-1),4)</f>
         <v>3.7198000000000002</v>
       </c>
-      <c r="N116" s="19">
+      <c r="N116" s="16">
         <f>ROUND(100*(Índices!N116/Índices!N115-1),4)</f>
         <v>1.2919</v>
       </c>
-      <c r="O116" s="19">
+      <c r="O116" s="16">
         <f>ROUND(100*(Índices!O116/Índices!O115-1),4)</f>
         <v>2.6438999999999999</v>
       </c>
-      <c r="P116" s="19">
+      <c r="P116" s="16">
         <f>ROUND(100*(Índices!P116/Índices!P115-1),4)</f>
         <v>4.1078999999999999</v>
       </c>
-      <c r="Q116" s="19">
+      <c r="Q116" s="16">
         <f>ROUND(100*(Índices!Q116/Índices!Q115-1),4)</f>
         <v>3.3121</v>
       </c>
-      <c r="R116" s="19">
+      <c r="R116" s="16">
         <f>ROUND(100*(Índices!R116/Índices!R115-1),4)</f>
         <v>3.5611999999999999</v>
       </c>
-      <c r="S116" s="19">
+      <c r="S116" s="16">
         <f>ROUND(100*(Índices!S116/Índices!S115-1),4)</f>
         <v>-10.152900000000001</v>
       </c>
-      <c r="T116" s="19">
+      <c r="T116" s="16">
         <f>ROUND(100*(Índices!T116/Índices!T115-1),4)</f>
         <v>3.4249000000000001</v>
       </c>
-      <c r="U116" s="20">
+      <c r="U116" s="17">
         <f>ROUND(100*(Índices!U116/Índices!U115-1),4)</f>
         <v>1.6877</v>
       </c>
-      <c r="V116" s="18">
+      <c r="V116" s="15">
         <f>ROUND(100*(Índices!V116/Índices!V115-1),4)</f>
         <v>2.0871</v>
+      </c>
+    </row>
+    <row r="117" spans="2:22" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B117" s="48">
+        <v>46113</v>
+      </c>
+      <c r="C117" s="18">
+        <f>ROUND(100*(Índices!C117/Índices!C116-1),4)</f>
+        <v>2.4895</v>
+      </c>
+      <c r="D117" s="19">
+        <f>ROUND(100*(Índices!D117/Índices!D116-1),4)</f>
+        <v>2.6541000000000001</v>
+      </c>
+      <c r="E117" s="19">
+        <f>ROUND(100*(Índices!E117/Índices!E116-1),4)</f>
+        <v>2.3692000000000002</v>
+      </c>
+      <c r="F117" s="19">
+        <f>ROUND(100*(Índices!F117/Índices!F116-1),4)</f>
+        <v>2.242</v>
+      </c>
+      <c r="G117" s="19">
+        <f>ROUND(100*(Índices!G117/Índices!G116-1),4)</f>
+        <v>2.6242000000000001</v>
+      </c>
+      <c r="H117" s="19">
+        <f>ROUND(100*(Índices!H117/Índices!H116-1),4)</f>
+        <v>2.1471</v>
+      </c>
+      <c r="I117" s="20">
+        <f>ROUND(100*(Índices!I117/Índices!I116-1),4)</f>
+        <v>2.7694000000000001</v>
+      </c>
+      <c r="J117" s="19">
+        <f>ROUND(100*(Índices!J117/Índices!J116-1),4)</f>
+        <v>1.7907</v>
+      </c>
+      <c r="K117" s="19">
+        <f>ROUND(100*(Índices!K117/Índices!K116-1),4)</f>
+        <v>3.2328000000000001</v>
+      </c>
+      <c r="L117" s="19">
+        <f>ROUND(100*(Índices!L117/Índices!L116-1),4)</f>
+        <v>0.5756</v>
+      </c>
+      <c r="M117" s="19">
+        <f>ROUND(100*(Índices!M117/Índices!M116-1),4)</f>
+        <v>3.4796999999999998</v>
+      </c>
+      <c r="N117" s="19">
+        <f>ROUND(100*(Índices!N117/Índices!N116-1),4)</f>
+        <v>2.8885000000000001</v>
+      </c>
+      <c r="O117" s="19">
+        <f>ROUND(100*(Índices!O117/Índices!O116-1),4)</f>
+        <v>2.5148000000000001</v>
+      </c>
+      <c r="P117" s="19">
+        <f>ROUND(100*(Índices!P117/Índices!P116-1),4)</f>
+        <v>4.4009</v>
+      </c>
+      <c r="Q117" s="19">
+        <f>ROUND(100*(Índices!Q117/Índices!Q116-1),4)</f>
+        <v>3.8184</v>
+      </c>
+      <c r="R117" s="19">
+        <f>ROUND(100*(Índices!R117/Índices!R116-1),4)</f>
+        <v>0.99119999999999997</v>
+      </c>
+      <c r="S117" s="19">
+        <f>ROUND(100*(Índices!S117/Índices!S116-1),4)</f>
+        <v>3.77</v>
+      </c>
+      <c r="T117" s="19">
+        <f>ROUND(100*(Índices!T117/Índices!T116-1),4)</f>
+        <v>2.6029</v>
+      </c>
+      <c r="U117" s="20">
+        <f>ROUND(100*(Índices!U117/Índices!U116-1),4)</f>
+        <v>2.4456000000000002</v>
+      </c>
+      <c r="V117" s="18">
+        <f>ROUND(100*(Índices!V117/Índices!V116-1),4)</f>
+        <v>1.8979999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -18370,7 +18520,7 @@
       <c r="H4" s="70"/>
       <c r="I4" s="23" t="str">
         <f>+_xlfn.CONCAT(H5, " ", C4, "/", H5, " ", C4-1)</f>
-        <v>Mar. 2024/Mar. 2023</v>
+        <v>Abr. 2024/Abr. 2023</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.25">
@@ -18400,25 +18550,25 @@
         <v>18</v>
       </c>
       <c r="C6" s="27">
-        <v>2.3969999999999998</v>
+        <v>2.7004999999999999</v>
       </c>
       <c r="D6" s="27">
-        <v>2.7004999999999999</v>
+        <v>2.5646</v>
       </c>
       <c r="E6" s="27">
-        <v>2.5646</v>
+        <v>2.4319999999999999</v>
       </c>
       <c r="F6" s="27">
-        <v>2.4319999999999999</v>
+        <v>2.5402</v>
       </c>
       <c r="G6" s="27">
-        <v>2.5402</v>
+        <v>2.2690999999999999</v>
       </c>
       <c r="H6" s="27">
-        <v>2.2690999999999999</v>
+        <v>2.4895</v>
       </c>
       <c r="I6" s="28">
-        <v>32.6068</v>
+        <v>32.3504</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -18438,25 +18588,25 @@
         <v>19</v>
       </c>
       <c r="C8" s="32">
-        <v>2.4363999999999999</v>
+        <v>2.8277000000000001</v>
       </c>
       <c r="D8" s="32">
-        <v>2.8277000000000001</v>
+        <v>2.6457000000000002</v>
       </c>
       <c r="E8" s="32">
-        <v>2.6457000000000002</v>
+        <v>2.3557000000000001</v>
       </c>
       <c r="F8" s="32">
-        <v>2.3557000000000001</v>
+        <v>2.2839999999999998</v>
       </c>
       <c r="G8" s="32">
-        <v>2.2839999999999998</v>
+        <v>2.0867</v>
       </c>
       <c r="H8" s="32">
-        <v>2.0867</v>
+        <v>2.6541000000000001</v>
       </c>
       <c r="I8" s="33">
-        <v>32.623699999999999</v>
+        <v>32.633000000000003</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.25">
@@ -18464,25 +18614,25 @@
         <v>2</v>
       </c>
       <c r="C9" s="32">
-        <v>2.3344</v>
+        <v>2.5508999999999999</v>
       </c>
       <c r="D9" s="32">
-        <v>2.5508999999999999</v>
+        <v>2.5547</v>
       </c>
       <c r="E9" s="32">
-        <v>2.5547</v>
+        <v>2.3969</v>
       </c>
       <c r="F9" s="32">
-        <v>2.3969</v>
+        <v>2.7242999999999999</v>
       </c>
       <c r="G9" s="32">
-        <v>2.7242999999999999</v>
+        <v>2.3247</v>
       </c>
       <c r="H9" s="32">
-        <v>2.3247</v>
+        <v>2.3692000000000002</v>
       </c>
       <c r="I9" s="33">
-        <v>32.4236</v>
+        <v>31.882200000000001</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.25">
@@ -18490,25 +18640,25 @@
         <v>3</v>
       </c>
       <c r="C10" s="32">
-        <v>2.2738999999999998</v>
+        <v>2.6806999999999999</v>
       </c>
       <c r="D10" s="32">
-        <v>2.6806999999999999</v>
+        <v>2.1278999999999999</v>
       </c>
       <c r="E10" s="32">
-        <v>2.1278999999999999</v>
+        <v>2.3860999999999999</v>
       </c>
       <c r="F10" s="32">
-        <v>2.3860999999999999</v>
+        <v>3.0423</v>
       </c>
       <c r="G10" s="32">
-        <v>3.0423</v>
+        <v>2.9150999999999998</v>
       </c>
       <c r="H10" s="32">
-        <v>2.9150999999999998</v>
+        <v>2.242</v>
       </c>
       <c r="I10" s="33">
-        <v>32.524700000000003</v>
+        <v>32.1021</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.25">
@@ -18516,25 +18666,25 @@
         <v>4</v>
       </c>
       <c r="C11" s="32">
-        <v>2.1981999999999999</v>
+        <v>2.5632000000000001</v>
       </c>
       <c r="D11" s="32">
-        <v>2.5632000000000001</v>
+        <v>2.4977</v>
       </c>
       <c r="E11" s="32">
-        <v>2.4977</v>
+        <v>3.3418999999999999</v>
       </c>
       <c r="F11" s="32">
-        <v>3.3418999999999999</v>
+        <v>2.9007000000000001</v>
       </c>
       <c r="G11" s="32">
-        <v>2.9007000000000001</v>
+        <v>3.7635000000000001</v>
       </c>
       <c r="H11" s="32">
-        <v>3.7635000000000001</v>
+        <v>2.6242000000000001</v>
       </c>
       <c r="I11" s="33">
-        <v>33.430399999999999</v>
+        <v>33.523099999999999</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.25">
@@ -18542,25 +18692,25 @@
         <v>5</v>
       </c>
       <c r="C12" s="32">
-        <v>2.6499000000000001</v>
+        <v>3.0586000000000002</v>
       </c>
       <c r="D12" s="32">
-        <v>3.0586000000000002</v>
+        <v>2.5573999999999999</v>
       </c>
       <c r="E12" s="32">
-        <v>2.5573999999999999</v>
+        <v>2.3765999999999998</v>
       </c>
       <c r="F12" s="32">
-        <v>2.3765999999999998</v>
+        <v>2.9041999999999999</v>
       </c>
       <c r="G12" s="32">
-        <v>2.9041999999999999</v>
+        <v>2.3010999999999999</v>
       </c>
       <c r="H12" s="32">
-        <v>2.3010999999999999</v>
+        <v>2.1471</v>
       </c>
       <c r="I12" s="33">
-        <v>33.531700000000001</v>
+        <v>32.582700000000003</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.25">
@@ -18568,25 +18718,25 @@
         <v>6</v>
       </c>
       <c r="C13" s="32">
-        <v>2.5768</v>
+        <v>2.4605999999999999</v>
       </c>
       <c r="D13" s="32">
-        <v>2.4605999999999999</v>
+        <v>2.5169000000000001</v>
       </c>
       <c r="E13" s="32">
-        <v>2.5169000000000001</v>
+        <v>2.4904000000000002</v>
       </c>
       <c r="F13" s="32">
-        <v>2.4904000000000002</v>
+        <v>2.6263999999999998</v>
       </c>
       <c r="G13" s="32">
-        <v>2.6263999999999998</v>
+        <v>1.6325000000000001</v>
       </c>
       <c r="H13" s="32">
-        <v>1.6325000000000001</v>
+        <v>2.7694000000000001</v>
       </c>
       <c r="I13" s="33">
-        <v>32.054699999999997</v>
+        <v>31.9907</v>
       </c>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.25">
@@ -18616,25 +18766,25 @@
         <v>20</v>
       </c>
       <c r="C16" s="32">
-        <v>2.2686999999999999</v>
+        <v>3.2688999999999999</v>
       </c>
       <c r="D16" s="32">
-        <v>3.2688999999999999</v>
+        <v>2.1086999999999998</v>
       </c>
       <c r="E16" s="32">
-        <v>2.1086999999999998</v>
+        <v>2.9632000000000001</v>
       </c>
       <c r="F16" s="32">
-        <v>2.9632000000000001</v>
+        <v>2.0246</v>
       </c>
       <c r="G16" s="32">
-        <v>2.0246</v>
+        <v>2.1017999999999999</v>
       </c>
       <c r="H16" s="32">
-        <v>2.1017999999999999</v>
+        <v>1.7907</v>
       </c>
       <c r="I16" s="33">
-        <v>32.740299999999998</v>
+        <v>30.871500000000001</v>
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.25">
@@ -18642,25 +18792,25 @@
         <v>21</v>
       </c>
       <c r="C17" s="32">
-        <v>2.6392000000000002</v>
+        <v>0.33200000000000002</v>
       </c>
       <c r="D17" s="32">
-        <v>0.33200000000000002</v>
+        <v>2.4317000000000002</v>
       </c>
       <c r="E17" s="32">
-        <v>2.4317000000000002</v>
+        <v>0.09</v>
       </c>
       <c r="F17" s="32">
-        <v>0.09</v>
+        <v>0.35</v>
       </c>
       <c r="G17" s="32">
-        <v>0.35</v>
+        <v>0.92810000000000004</v>
       </c>
       <c r="H17" s="32">
-        <v>0.92810000000000004</v>
+        <v>3.2328000000000001</v>
       </c>
       <c r="I17" s="33">
-        <v>24.9312</v>
+        <v>23.752600000000001</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.25">
@@ -18668,25 +18818,25 @@
         <v>22</v>
       </c>
       <c r="C18" s="32">
-        <v>1.7358</v>
+        <v>1.3657999999999999</v>
       </c>
       <c r="D18" s="32">
-        <v>1.3657999999999999</v>
+        <v>0.55920000000000003</v>
       </c>
       <c r="E18" s="32">
-        <v>0.55920000000000003</v>
+        <v>1.1326000000000001</v>
       </c>
       <c r="F18" s="32">
-        <v>1.1326000000000001</v>
+        <v>1.4723999999999999</v>
       </c>
       <c r="G18" s="32">
-        <v>1.4723999999999999</v>
+        <v>-0.39910000000000001</v>
       </c>
       <c r="H18" s="32">
-        <v>-0.39910000000000001</v>
+        <v>0.5756</v>
       </c>
       <c r="I18" s="33">
-        <v>13.426</v>
+        <v>12.7448</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.25">
@@ -18694,25 +18844,25 @@
         <v>23</v>
       </c>
       <c r="C19" s="32">
-        <v>2.8279999999999998</v>
+        <v>3.4380000000000002</v>
       </c>
       <c r="D19" s="32">
-        <v>3.4380000000000002</v>
+        <v>3.3896000000000002</v>
       </c>
       <c r="E19" s="32">
-        <v>3.3896000000000002</v>
+        <v>3.0529000000000002</v>
       </c>
       <c r="F19" s="32">
-        <v>3.0529000000000002</v>
+        <v>6.7877000000000001</v>
       </c>
       <c r="G19" s="32">
-        <v>6.7877000000000001</v>
+        <v>3.7198000000000002</v>
       </c>
       <c r="H19" s="32">
-        <v>3.7198000000000002</v>
+        <v>3.4796999999999998</v>
       </c>
       <c r="I19" s="33">
-        <v>45.481999999999999</v>
+        <v>47.842799999999997</v>
       </c>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.25">
@@ -18720,25 +18870,25 @@
         <v>24</v>
       </c>
       <c r="C20" s="32">
-        <v>1.6339999999999999</v>
+        <v>1.119</v>
       </c>
       <c r="D20" s="32">
-        <v>1.119</v>
+        <v>2.0001000000000002</v>
       </c>
       <c r="E20" s="32">
-        <v>2.0001000000000002</v>
+        <v>1.8302</v>
       </c>
       <c r="F20" s="32">
-        <v>1.8302</v>
+        <v>2.5644999999999998</v>
       </c>
       <c r="G20" s="32">
-        <v>2.5644999999999998</v>
+        <v>1.2919</v>
       </c>
       <c r="H20" s="32">
-        <v>1.2919</v>
+        <v>2.8885000000000001</v>
       </c>
       <c r="I20" s="33">
-        <v>21.1311</v>
+        <v>23.472799999999999</v>
       </c>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.25">
@@ -18746,25 +18896,25 @@
         <v>25</v>
       </c>
       <c r="C21" s="32">
-        <v>1.8307</v>
+        <v>2.3965000000000001</v>
       </c>
       <c r="D21" s="32">
-        <v>2.3965000000000001</v>
+        <v>2.0903999999999998</v>
       </c>
       <c r="E21" s="32">
-        <v>2.0903999999999998</v>
+        <v>2.3418000000000001</v>
       </c>
       <c r="F21" s="32">
-        <v>2.3418000000000001</v>
+        <v>2.4708000000000001</v>
       </c>
       <c r="G21" s="32">
-        <v>2.4708000000000001</v>
+        <v>2.6438999999999999</v>
       </c>
       <c r="H21" s="32">
-        <v>2.6438999999999999</v>
+        <v>2.5148000000000001</v>
       </c>
       <c r="I21" s="33">
-        <v>29.7119</v>
+        <v>29.733499999999999</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.25">
@@ -18772,25 +18922,25 @@
         <v>26</v>
       </c>
       <c r="C22" s="32">
-        <v>3.4594999999999998</v>
+        <v>3.0304000000000002</v>
       </c>
       <c r="D22" s="32">
-        <v>3.0304000000000002</v>
+        <v>3.9982000000000002</v>
       </c>
       <c r="E22" s="32">
-        <v>3.9982000000000002</v>
+        <v>1.8548</v>
       </c>
       <c r="F22" s="32">
-        <v>1.8548</v>
+        <v>1.978</v>
       </c>
       <c r="G22" s="32">
-        <v>1.978</v>
+        <v>4.1078999999999999</v>
       </c>
       <c r="H22" s="32">
-        <v>4.1078999999999999</v>
+        <v>4.4009</v>
       </c>
       <c r="I22" s="33">
-        <v>36.241100000000003</v>
+        <v>39.8752</v>
       </c>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.25">
@@ -18798,25 +18948,25 @@
         <v>27</v>
       </c>
       <c r="C23" s="32">
-        <v>2.7322000000000002</v>
+        <v>3.0445000000000002</v>
       </c>
       <c r="D23" s="32">
-        <v>3.0445000000000002</v>
+        <v>3.0379999999999998</v>
       </c>
       <c r="E23" s="32">
-        <v>3.0379999999999998</v>
+        <v>-1.0443</v>
       </c>
       <c r="F23" s="32">
-        <v>-1.0443</v>
+        <v>-1.0564</v>
       </c>
       <c r="G23" s="32">
-        <v>-1.0564</v>
+        <v>3.3121</v>
       </c>
       <c r="H23" s="32">
-        <v>3.3121</v>
+        <v>3.8184</v>
       </c>
       <c r="I23" s="33">
-        <v>36.613900000000001</v>
+        <v>38.295200000000001</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.25">
@@ -18824,25 +18974,25 @@
         <v>28</v>
       </c>
       <c r="C24" s="32">
-        <v>1.6108</v>
+        <v>2.4485000000000001</v>
       </c>
       <c r="D24" s="32">
-        <v>2.4485000000000001</v>
+        <v>2.5417000000000001</v>
       </c>
       <c r="E24" s="32">
-        <v>2.5417000000000001</v>
+        <v>1.0244</v>
       </c>
       <c r="F24" s="32">
-        <v>1.0244</v>
+        <v>2.3454000000000002</v>
       </c>
       <c r="G24" s="32">
-        <v>2.3454000000000002</v>
+        <v>3.5611999999999999</v>
       </c>
       <c r="H24" s="32">
-        <v>3.5611999999999999</v>
+        <v>0.99119999999999997</v>
       </c>
       <c r="I24" s="33">
-        <v>32.256799999999998</v>
+        <v>28.452500000000001</v>
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.25">
@@ -18850,25 +19000,25 @@
         <v>29</v>
       </c>
       <c r="C25" s="32">
-        <v>5.7397999999999998</v>
+        <v>4.8711000000000002</v>
       </c>
       <c r="D25" s="32">
-        <v>4.8711000000000002</v>
+        <v>4.8147000000000002</v>
       </c>
       <c r="E25" s="32">
-        <v>4.8147000000000002</v>
+        <v>5.1432000000000002</v>
       </c>
       <c r="F25" s="32">
-        <v>5.1432000000000002</v>
+        <v>1.3282</v>
       </c>
       <c r="G25" s="32">
-        <v>1.3282</v>
+        <v>-10.152900000000001</v>
       </c>
       <c r="H25" s="32">
-        <v>-10.152900000000001</v>
+        <v>3.77</v>
       </c>
       <c r="I25" s="33">
-        <v>38.868400000000001</v>
+        <v>41.260199999999998</v>
       </c>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.25">
@@ -18876,25 +19026,25 @@
         <v>30</v>
       </c>
       <c r="C26" s="32">
-        <v>2.2783000000000002</v>
+        <v>2.4801000000000002</v>
       </c>
       <c r="D26" s="32">
-        <v>2.4801000000000002</v>
+        <v>3.0933000000000002</v>
       </c>
       <c r="E26" s="32">
-        <v>3.0933000000000002</v>
+        <v>3.9603000000000002</v>
       </c>
       <c r="F26" s="32">
-        <v>3.9603000000000002</v>
+        <v>2.9319000000000002</v>
       </c>
       <c r="G26" s="32">
-        <v>2.9319000000000002</v>
+        <v>3.4249000000000001</v>
       </c>
       <c r="H26" s="32">
-        <v>3.4249000000000001</v>
+        <v>2.6029</v>
       </c>
       <c r="I26" s="33">
-        <v>41.042299999999997</v>
+        <v>38.991199999999999</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.25">
@@ -18902,25 +19052,25 @@
         <v>31</v>
       </c>
       <c r="C27" s="32">
-        <v>2.4439000000000002</v>
+        <v>2.5068000000000001</v>
       </c>
       <c r="D27" s="32">
-        <v>2.5068000000000001</v>
+        <v>2.6438000000000001</v>
       </c>
       <c r="E27" s="32">
-        <v>2.6438000000000001</v>
+        <v>2.7301000000000002</v>
       </c>
       <c r="F27" s="32">
-        <v>2.7301000000000002</v>
+        <v>3.2768000000000002</v>
       </c>
       <c r="G27" s="32">
-        <v>3.2768000000000002</v>
+        <v>1.6877</v>
       </c>
       <c r="H27" s="32">
-        <v>1.6877</v>
+        <v>2.4456000000000002</v>
       </c>
       <c r="I27" s="33">
-        <v>31.781300000000002</v>
+        <v>31.6508</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.25">
@@ -18950,25 +19100,25 @@
         <v>33</v>
       </c>
       <c r="C30" s="32">
-        <v>2.1185999999999998</v>
+        <v>2.4952000000000001</v>
       </c>
       <c r="D30" s="32">
-        <v>2.4952000000000001</v>
+        <v>2.1663999999999999</v>
       </c>
       <c r="E30" s="32">
-        <v>2.1663999999999999</v>
+        <v>2.5274999999999999</v>
       </c>
       <c r="F30" s="32">
-        <v>2.5274999999999999</v>
+        <v>2.2141999999999999</v>
       </c>
       <c r="G30" s="32">
-        <v>2.2141999999999999</v>
+        <v>2.0871</v>
       </c>
       <c r="H30" s="32">
-        <v>2.0871</v>
+        <v>1.8979999999999999</v>
       </c>
       <c r="I30" s="33">
-        <v>30.024000000000001</v>
+        <v>28.622699999999998</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.25">
@@ -18976,25 +19126,25 @@
         <v>19</v>
       </c>
       <c r="C31" s="32">
-        <v>2.2909999999999999</v>
+        <v>2.6549999999999998</v>
       </c>
       <c r="D31" s="32">
-        <v>2.6549999999999998</v>
+        <v>2.1663999999999999</v>
       </c>
       <c r="E31" s="32">
-        <v>2.1663999999999999</v>
+        <v>2.7825000000000002</v>
       </c>
       <c r="F31" s="32">
-        <v>2.7825000000000002</v>
+        <v>1.8584000000000001</v>
       </c>
       <c r="G31" s="32">
-        <v>1.8584000000000001</v>
+        <v>1.7617</v>
       </c>
       <c r="H31" s="32">
-        <v>1.7617</v>
+        <v>1.9493</v>
       </c>
       <c r="I31" s="33">
-        <v>30.437000000000001</v>
+        <v>29.1403</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.25">
@@ -19002,25 +19152,25 @@
         <v>2</v>
       </c>
       <c r="C32" s="32">
-        <v>1.9105000000000001</v>
+        <v>2.3687999999999998</v>
       </c>
       <c r="D32" s="32">
-        <v>2.3687999999999998</v>
+        <v>2.2696999999999998</v>
       </c>
       <c r="E32" s="32">
-        <v>2.2696999999999998</v>
+        <v>2.3115999999999999</v>
       </c>
       <c r="F32" s="32">
-        <v>2.3115999999999999</v>
+        <v>2.6072000000000002</v>
       </c>
       <c r="G32" s="32">
-        <v>2.6072000000000002</v>
+        <v>2.2222</v>
       </c>
       <c r="H32" s="32">
-        <v>2.2222</v>
+        <v>1.8652</v>
       </c>
       <c r="I32" s="33">
-        <v>30.499300000000002</v>
+        <v>28.886399999999998</v>
       </c>
     </row>
     <row r="33" spans="2:9" x14ac:dyDescent="0.25">
@@ -19028,25 +19178,25 @@
         <v>3</v>
       </c>
       <c r="C33" s="32">
-        <v>2.2098</v>
+        <v>2.5064000000000002</v>
       </c>
       <c r="D33" s="32">
-        <v>2.5064000000000002</v>
+        <v>1.6786000000000001</v>
       </c>
       <c r="E33" s="32">
-        <v>1.6786000000000001</v>
+        <v>2.3090000000000002</v>
       </c>
       <c r="F33" s="32">
-        <v>2.3090000000000002</v>
+        <v>2.4470000000000001</v>
       </c>
       <c r="G33" s="32">
-        <v>2.4470000000000001</v>
+        <v>3.0299</v>
       </c>
       <c r="H33" s="32">
-        <v>3.0299</v>
+        <v>1.7193000000000001</v>
       </c>
       <c r="I33" s="33">
-        <v>29.862400000000001</v>
+        <v>28.328199999999999</v>
       </c>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.25">
@@ -19054,25 +19204,25 @@
         <v>4</v>
       </c>
       <c r="C34" s="32">
-        <v>1.9383999999999999</v>
+        <v>2.4870000000000001</v>
       </c>
       <c r="D34" s="32">
-        <v>2.4870000000000001</v>
+        <v>2.2094</v>
       </c>
       <c r="E34" s="32">
-        <v>2.2094</v>
+        <v>2.9220999999999999</v>
       </c>
       <c r="F34" s="32">
-        <v>2.9220999999999999</v>
+        <v>3.2063000000000001</v>
       </c>
       <c r="G34" s="32">
-        <v>3.2063000000000001</v>
+        <v>3.2139000000000002</v>
       </c>
       <c r="H34" s="32">
-        <v>3.2139000000000002</v>
+        <v>2.0484</v>
       </c>
       <c r="I34" s="33">
-        <v>31.495799999999999</v>
+        <v>30.439900000000002</v>
       </c>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.25">
@@ -19080,25 +19230,25 @@
         <v>5</v>
       </c>
       <c r="C35" s="32">
-        <v>2.2623000000000002</v>
+        <v>2.6513</v>
       </c>
       <c r="D35" s="32">
-        <v>2.6513</v>
+        <v>2.3127</v>
       </c>
       <c r="E35" s="32">
-        <v>2.3127</v>
+        <v>2.0385</v>
       </c>
       <c r="F35" s="32">
-        <v>2.0385</v>
+        <v>2.1634000000000002</v>
       </c>
       <c r="G35" s="32">
-        <v>2.1634000000000002</v>
+        <v>2.2298</v>
       </c>
       <c r="H35" s="32">
-        <v>2.2298</v>
+        <v>1.4777</v>
       </c>
       <c r="I35" s="33">
-        <v>26.6602</v>
+        <v>25.343900000000001</v>
       </c>
     </row>
     <row r="36" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -19106,25 +19256,25 @@
         <v>6</v>
       </c>
       <c r="C36" s="35">
-        <v>1.8217000000000001</v>
+        <v>1.6400999999999999</v>
       </c>
       <c r="D36" s="35">
-        <v>1.6400999999999999</v>
+        <v>1.9037999999999999</v>
       </c>
       <c r="E36" s="35">
-        <v>1.9037999999999999</v>
+        <v>2.0792000000000002</v>
       </c>
       <c r="F36" s="35">
-        <v>2.0792000000000002</v>
+        <v>1.623</v>
       </c>
       <c r="G36" s="35">
-        <v>1.623</v>
+        <v>1.7052</v>
       </c>
       <c r="H36" s="35">
-        <v>1.7052</v>
+        <v>2.2423000000000002</v>
       </c>
       <c r="I36" s="36">
-        <v>24.9451</v>
+        <v>23.854700000000001</v>
       </c>
     </row>
     <row r="37" spans="2:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -19238,25 +19388,25 @@
         <v>37</v>
       </c>
       <c r="C5" s="41">
-        <v>2.0867</v>
+        <v>2.6541000000000001</v>
       </c>
       <c r="D5" s="41">
-        <v>2.3247</v>
+        <v>2.3692000000000002</v>
       </c>
       <c r="E5" s="41">
-        <v>2.9150999999999998</v>
+        <v>2.242</v>
       </c>
       <c r="F5" s="41">
-        <v>3.7635000000000001</v>
+        <v>2.6242000000000001</v>
       </c>
       <c r="G5" s="41">
-        <v>2.3010999999999999</v>
+        <v>2.1471</v>
       </c>
       <c r="H5" s="41">
-        <v>1.6325000000000001</v>
+        <v>2.7694000000000001</v>
       </c>
       <c r="I5" s="42">
-        <v>2.2690999999999999</v>
+        <v>2.4895</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.25">
@@ -19264,25 +19414,25 @@
         <v>20</v>
       </c>
       <c r="C6" s="32">
-        <v>0.42859999999999998</v>
+        <v>0.37580000000000002</v>
       </c>
       <c r="D6" s="32">
-        <v>0.63529999999999998</v>
+        <v>0.67889999999999995</v>
       </c>
       <c r="E6" s="32">
-        <v>1.1867000000000001</v>
+        <v>0.55559999999999998</v>
       </c>
       <c r="F6" s="32">
-        <v>1.4597</v>
+        <v>0.96660000000000001</v>
       </c>
       <c r="G6" s="32">
-        <v>0.77529999999999999</v>
+        <v>0.23960000000000001</v>
       </c>
       <c r="H6" s="32">
-        <v>0.62239999999999995</v>
+        <v>0.62319999999999998</v>
       </c>
       <c r="I6" s="33">
-        <v>0.62470000000000003</v>
+        <v>0.52270000000000005</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.25">
@@ -19290,25 +19440,25 @@
         <v>21</v>
       </c>
       <c r="C7" s="32">
-        <v>1.8200000000000001E-2</v>
+        <v>7.9399999999999998E-2</v>
       </c>
       <c r="D7" s="32">
-        <v>2.6200000000000001E-2</v>
+        <v>7.6100000000000001E-2</v>
       </c>
       <c r="E7" s="32">
-        <v>2.8799999999999999E-2</v>
+        <v>6.7100000000000007E-2</v>
       </c>
       <c r="F7" s="32">
-        <v>5.16E-2</v>
+        <v>7.2700000000000001E-2</v>
       </c>
       <c r="G7" s="32">
-        <v>1.37E-2</v>
+        <v>8.3500000000000005E-2</v>
       </c>
       <c r="H7" s="32">
-        <v>1.8200000000000001E-2</v>
+        <v>9.5600000000000004E-2</v>
       </c>
       <c r="I7" s="33">
-        <v>2.3E-2</v>
+        <v>7.8E-2</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.25">
@@ -19316,25 +19466,25 @@
         <v>22</v>
       </c>
       <c r="C8" s="32">
-        <v>-0.1191</v>
+        <v>7.6399999999999996E-2</v>
       </c>
       <c r="D8" s="32">
-        <v>1.5699999999999999E-2</v>
+        <v>-9.4999999999999998E-3</v>
       </c>
       <c r="E8" s="32">
-        <v>0.1777</v>
+        <v>-7.2499999999999995E-2</v>
       </c>
       <c r="F8" s="32">
-        <v>0.20269999999999999</v>
+        <v>-1.7100000000000001E-2</v>
       </c>
       <c r="G8" s="32">
-        <v>0.1174</v>
+        <v>9.3600000000000003E-2</v>
       </c>
       <c r="H8" s="32">
-        <v>0.11600000000000001</v>
+        <v>0.15620000000000001</v>
       </c>
       <c r="I8" s="33">
-        <v>-1.5100000000000001E-2</v>
+        <v>3.7100000000000001E-2</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.25">
@@ -19342,25 +19492,25 @@
         <v>23</v>
       </c>
       <c r="C9" s="32">
-        <v>0.375</v>
+        <v>0.49440000000000001</v>
       </c>
       <c r="D9" s="32">
-        <v>0.28899999999999998</v>
+        <v>0.22140000000000001</v>
       </c>
       <c r="E9" s="32">
-        <v>0.39960000000000001</v>
+        <v>0.36799999999999999</v>
       </c>
       <c r="F9" s="32">
-        <v>1.0591999999999999</v>
+        <v>0.38329999999999997</v>
       </c>
       <c r="G9" s="32">
-        <v>0.3528</v>
+        <v>0.1452</v>
       </c>
       <c r="H9" s="32">
-        <v>0.28660000000000002</v>
+        <v>0.45050000000000001</v>
       </c>
       <c r="I9" s="33">
-        <v>0.373</v>
+        <v>0.36730000000000002</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.25">
@@ -19368,25 +19518,25 @@
         <v>24</v>
       </c>
       <c r="C10" s="32">
-        <v>6.8099999999999994E-2</v>
+        <v>0.15870000000000001</v>
       </c>
       <c r="D10" s="32">
-        <v>7.7899999999999997E-2</v>
+        <v>0.1517</v>
       </c>
       <c r="E10" s="32">
-        <v>6.08E-2</v>
+        <v>0.1042</v>
       </c>
       <c r="F10" s="32">
-        <v>5.5E-2</v>
+        <v>0.1043</v>
       </c>
       <c r="G10" s="32">
-        <v>6.7699999999999996E-2</v>
+        <v>0.1295</v>
       </c>
       <c r="H10" s="32">
-        <v>5.4999999999999997E-3</v>
+        <v>0.1792</v>
       </c>
       <c r="I10" s="33">
-        <v>6.7500000000000004E-2</v>
+        <v>0.14960000000000001</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.25">
@@ -19394,25 +19544,25 @@
         <v>25</v>
       </c>
       <c r="C11" s="32">
-        <v>0.28050000000000003</v>
+        <v>0.2492</v>
       </c>
       <c r="D11" s="32">
-        <v>0.23019999999999999</v>
+        <v>0.2341</v>
       </c>
       <c r="E11" s="32">
-        <v>0.16969999999999999</v>
+        <v>0.14899999999999999</v>
       </c>
       <c r="F11" s="32">
-        <v>0.1215</v>
+        <v>0.15</v>
       </c>
       <c r="G11" s="32">
-        <v>0.18740000000000001</v>
+        <v>0.21479999999999999</v>
       </c>
       <c r="H11" s="32">
-        <v>0.14460000000000001</v>
+        <v>0.13100000000000001</v>
       </c>
       <c r="I11" s="33">
-        <v>0.23749999999999999</v>
+        <v>0.22550000000000001</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.25">
@@ -19420,25 +19570,25 @@
         <v>26</v>
       </c>
       <c r="C12" s="32">
-        <v>0.54369999999999996</v>
+        <v>0.43919999999999998</v>
       </c>
       <c r="D12" s="32">
-        <v>0.40110000000000001</v>
+        <v>0.5343</v>
       </c>
       <c r="E12" s="32">
-        <v>0.44340000000000002</v>
+        <v>0.47199999999999998</v>
       </c>
       <c r="F12" s="32">
-        <v>0.2792</v>
+        <v>0.61029999999999995</v>
       </c>
       <c r="G12" s="32">
-        <v>0.4975</v>
+        <v>0.69289999999999996</v>
       </c>
       <c r="H12" s="32">
-        <v>0.47270000000000001</v>
+        <v>0.72499999999999998</v>
       </c>
       <c r="I12" s="33">
-        <v>0.47049999999999997</v>
+        <v>0.50790000000000002</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.25">
@@ -19446,25 +19596,25 @@
         <v>27</v>
       </c>
       <c r="C13" s="32">
-        <v>0.10059999999999999</v>
+        <v>0.10009999999999999</v>
       </c>
       <c r="D13" s="32">
-        <v>6.9599999999999995E-2</v>
+        <v>0.10249999999999999</v>
       </c>
       <c r="E13" s="32">
-        <v>6.3299999999999995E-2</v>
+        <v>6.6299999999999998E-2</v>
       </c>
       <c r="F13" s="32">
-        <v>6.6400000000000001E-2</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="G13" s="32">
-        <v>5.3400000000000003E-2</v>
+        <v>8.3699999999999997E-2</v>
       </c>
       <c r="H13" s="32">
-        <v>7.5899999999999995E-2</v>
+        <v>6.2399999999999997E-2</v>
       </c>
       <c r="I13" s="33">
-        <v>8.2299999999999998E-2</v>
+        <v>9.5799999999999996E-2</v>
       </c>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.25">
@@ -19472,25 +19622,25 @@
         <v>28</v>
       </c>
       <c r="C14" s="32">
-        <v>0.21640000000000001</v>
+        <v>0.1032</v>
       </c>
       <c r="D14" s="32">
-        <v>0.28720000000000001</v>
+        <v>9.2999999999999992E-3</v>
       </c>
       <c r="E14" s="32">
-        <v>0.2349</v>
+        <v>6.8699999999999997E-2</v>
       </c>
       <c r="F14" s="32">
-        <v>6.5199999999999994E-2</v>
+        <v>9.8599999999999993E-2</v>
       </c>
       <c r="G14" s="32">
-        <v>0.16950000000000001</v>
+        <v>4.2900000000000001E-2</v>
       </c>
       <c r="H14" s="32">
-        <v>0.11509999999999999</v>
+        <v>6.93E-2</v>
       </c>
       <c r="I14" s="33">
-        <v>0.22800000000000001</v>
+        <v>6.3899999999999998E-2</v>
       </c>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.25">
@@ -19498,25 +19648,25 @@
         <v>29</v>
       </c>
       <c r="C15" s="32">
-        <v>-0.32400000000000001</v>
+        <v>0.1459</v>
       </c>
       <c r="D15" s="32">
-        <v>-0.1411</v>
+        <v>3.9300000000000002E-2</v>
       </c>
       <c r="E15" s="32">
-        <v>-0.26279999999999998</v>
+        <v>-7.1999999999999998E-3</v>
       </c>
       <c r="F15" s="32">
-        <v>4.7600000000000003E-2</v>
+        <v>-2.3999999999999998E-3</v>
       </c>
       <c r="G15" s="32">
-        <v>-0.20100000000000001</v>
+        <v>7.5999999999999998E-2</v>
       </c>
       <c r="H15" s="32">
-        <v>-0.38429999999999997</v>
+        <v>3.5900000000000001E-2</v>
       </c>
       <c r="I15" s="33">
-        <v>-0.2369</v>
+        <v>8.3599999999999994E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.25">
@@ -19524,25 +19674,25 @@
         <v>30</v>
       </c>
       <c r="C16" s="32">
-        <v>0.43540000000000001</v>
+        <v>0.32950000000000002</v>
       </c>
       <c r="D16" s="32">
-        <v>0.37959999999999999</v>
+        <v>0.26500000000000001</v>
       </c>
       <c r="E16" s="32">
-        <v>0.35389999999999999</v>
+        <v>0.41849999999999998</v>
       </c>
       <c r="F16" s="32">
-        <v>0.2908</v>
+        <v>9.4200000000000006E-2</v>
       </c>
       <c r="G16" s="32">
-        <v>0.2165</v>
+        <v>0.23350000000000001</v>
       </c>
       <c r="H16" s="32">
-        <v>0.11600000000000001</v>
+        <v>0.16750000000000001</v>
       </c>
       <c r="I16" s="33">
-        <v>0.37830000000000003</v>
+        <v>0.29060000000000002</v>
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.25">
@@ -19550,22 +19700,22 @@
         <v>31</v>
       </c>
       <c r="C17" s="32">
-        <v>6.3299999999999995E-2</v>
+        <v>0.1022</v>
       </c>
       <c r="D17" s="32">
-        <v>5.3900000000000003E-2</v>
+        <v>6.6000000000000003E-2</v>
       </c>
       <c r="E17" s="32">
-        <v>5.8799999999999998E-2</v>
+        <v>5.2299999999999999E-2</v>
       </c>
       <c r="F17" s="32">
-        <v>6.4500000000000002E-2</v>
+        <v>6.88E-2</v>
       </c>
       <c r="G17" s="32">
-        <v>5.11E-2</v>
+        <v>0.112</v>
       </c>
       <c r="H17" s="32">
-        <v>4.3999999999999997E-2</v>
+        <v>7.3599999999999999E-2</v>
       </c>
       <c r="I17" s="33">
         <v>0.08</v>
@@ -19598,25 +19748,25 @@
         <v>37</v>
       </c>
       <c r="C20" s="41">
-        <v>32.623699999999999</v>
+        <v>32.633000000000003</v>
       </c>
       <c r="D20" s="41">
-        <v>32.4236</v>
+        <v>31.882200000000001</v>
       </c>
       <c r="E20" s="41">
-        <v>32.524700000000003</v>
+        <v>32.1021</v>
       </c>
       <c r="F20" s="41">
-        <v>33.430399999999999</v>
+        <v>33.523099999999999</v>
       </c>
       <c r="G20" s="41">
-        <v>33.531700000000001</v>
+        <v>32.582700000000003</v>
       </c>
       <c r="H20" s="41">
-        <v>32.054699999999997</v>
+        <v>31.9907</v>
       </c>
       <c r="I20" s="42">
-        <v>32.6068</v>
+        <v>32.3504</v>
       </c>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.25">
@@ -19624,25 +19774,25 @@
         <v>20</v>
       </c>
       <c r="C21" s="32">
-        <v>8.3094000000000001</v>
+        <v>7.7969999999999997</v>
       </c>
       <c r="D21" s="32">
-        <v>10.1304</v>
+        <v>9.7025000000000006</v>
       </c>
       <c r="E21" s="32">
-        <v>12.3735</v>
+        <v>11.5844</v>
       </c>
       <c r="F21" s="32">
-        <v>13.6159</v>
+        <v>13.3118</v>
       </c>
       <c r="G21" s="32">
-        <v>11.0108</v>
+        <v>9.8314000000000004</v>
       </c>
       <c r="H21" s="32">
-        <v>8.1262000000000008</v>
+        <v>7.6722000000000001</v>
       </c>
       <c r="I21" s="33">
-        <v>9.5824999999999996</v>
+        <v>9.0574999999999992</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.25">
@@ -19650,25 +19800,25 @@
         <v>21</v>
       </c>
       <c r="C22" s="32">
-        <v>0.61670000000000003</v>
+        <v>0.58720000000000006</v>
       </c>
       <c r="D22" s="32">
-        <v>0.7127</v>
+        <v>0.67300000000000004</v>
       </c>
       <c r="E22" s="32">
-        <v>0.54459999999999997</v>
+        <v>0.52590000000000003</v>
       </c>
       <c r="F22" s="32">
-        <v>0.6603</v>
+        <v>0.63670000000000004</v>
       </c>
       <c r="G22" s="32">
-        <v>0.62870000000000004</v>
+        <v>0.61739999999999995</v>
       </c>
       <c r="H22" s="32">
-        <v>0.71089999999999998</v>
+        <v>0.69020000000000004</v>
       </c>
       <c r="I22" s="33">
-        <v>0.65149999999999997</v>
+        <v>0.62080000000000002</v>
       </c>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.25">
@@ -19676,25 +19826,25 @@
         <v>22</v>
       </c>
       <c r="C23" s="32">
-        <v>1.024</v>
+        <v>1.0163</v>
       </c>
       <c r="D23" s="32">
-        <v>1.0668</v>
+        <v>0.99329999999999996</v>
       </c>
       <c r="E23" s="32">
-        <v>1.4822</v>
+        <v>1.3383</v>
       </c>
       <c r="F23" s="32">
-        <v>1.4692000000000001</v>
+        <v>1.3859999999999999</v>
       </c>
       <c r="G23" s="32">
-        <v>1.1684000000000001</v>
+        <v>1.1303000000000001</v>
       </c>
       <c r="H23" s="32">
-        <v>1.7209000000000001</v>
+        <v>1.5585</v>
       </c>
       <c r="I23" s="33">
-        <v>1.1295999999999999</v>
+        <v>1.0780000000000001</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.25">
@@ -19702,25 +19852,25 @@
         <v>23</v>
       </c>
       <c r="C24" s="32">
-        <v>4.0890000000000004</v>
+        <v>4.4427000000000003</v>
       </c>
       <c r="D24" s="32">
-        <v>3.8477000000000001</v>
+        <v>3.8567</v>
       </c>
       <c r="E24" s="32">
-        <v>4.0088999999999997</v>
+        <v>4.2366999999999999</v>
       </c>
       <c r="F24" s="32">
-        <v>5.3650000000000002</v>
+        <v>5.5472999999999999</v>
       </c>
       <c r="G24" s="32">
-        <v>4.6951000000000001</v>
+        <v>4.6064999999999996</v>
       </c>
       <c r="H24" s="32">
-        <v>6.7061999999999999</v>
+        <v>6.7845000000000004</v>
       </c>
       <c r="I24" s="33">
-        <v>4.2095000000000002</v>
+        <v>4.3935000000000004</v>
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.25">
@@ -19728,25 +19878,25 @@
         <v>24</v>
       </c>
       <c r="C25" s="32">
-        <v>1.2656000000000001</v>
+        <v>1.3720000000000001</v>
       </c>
       <c r="D25" s="32">
-        <v>1.1332</v>
+        <v>1.2545999999999999</v>
       </c>
       <c r="E25" s="32">
-        <v>1.0403</v>
+        <v>1.1106</v>
       </c>
       <c r="F25" s="32">
-        <v>1.0331999999999999</v>
+        <v>1.1025</v>
       </c>
       <c r="G25" s="32">
-        <v>1.1798999999999999</v>
+        <v>1.2753000000000001</v>
       </c>
       <c r="H25" s="32">
-        <v>1.1292</v>
+        <v>1.2503</v>
       </c>
       <c r="I25" s="33">
-        <v>1.1836</v>
+        <v>1.2910999999999999</v>
       </c>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.25">
@@ -19754,25 +19904,25 @@
         <v>25</v>
       </c>
       <c r="C26" s="32">
-        <v>2.8123999999999998</v>
+        <v>2.7852999999999999</v>
       </c>
       <c r="D26" s="32">
-        <v>2.8803000000000001</v>
+        <v>2.9005999999999998</v>
       </c>
       <c r="E26" s="32">
-        <v>2.1252</v>
+        <v>2.0956000000000001</v>
       </c>
       <c r="F26" s="32">
-        <v>1.6876</v>
+        <v>1.7076</v>
       </c>
       <c r="G26" s="32">
-        <v>2.4323999999999999</v>
+        <v>2.4592000000000001</v>
       </c>
       <c r="H26" s="32">
-        <v>1.8143</v>
+        <v>1.7969999999999999</v>
       </c>
       <c r="I26" s="33">
-        <v>2.6722999999999999</v>
+        <v>2.6665999999999999</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.25">
@@ -19780,25 +19930,25 @@
         <v>26</v>
       </c>
       <c r="C27" s="32">
-        <v>4.2662000000000004</v>
+        <v>4.5265000000000004</v>
       </c>
       <c r="D27" s="32">
-        <v>3.7082000000000002</v>
+        <v>4.1113999999999997</v>
       </c>
       <c r="E27" s="32">
-        <v>3.2280000000000002</v>
+        <v>3.6343000000000001</v>
       </c>
       <c r="F27" s="32">
-        <v>3.3071000000000002</v>
+        <v>3.8460000000000001</v>
       </c>
       <c r="G27" s="32">
-        <v>4.9108999999999998</v>
+        <v>5.3554000000000004</v>
       </c>
       <c r="H27" s="32">
-        <v>5.8080999999999996</v>
+        <v>6.3529999999999998</v>
       </c>
       <c r="I27" s="33">
-        <v>4.0646000000000004</v>
+        <v>4.4188999999999998</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.25">
@@ -19806,25 +19956,25 @@
         <v>27</v>
       </c>
       <c r="C28" s="32">
-        <v>0.97589999999999999</v>
+        <v>1.0308999999999999</v>
       </c>
       <c r="D28" s="32">
-        <v>0.88260000000000005</v>
+        <v>0.91990000000000005</v>
       </c>
       <c r="E28" s="32">
-        <v>0.82350000000000001</v>
+        <v>0.81950000000000001</v>
       </c>
       <c r="F28" s="32">
-        <v>0.83440000000000003</v>
+        <v>0.88290000000000002</v>
       </c>
       <c r="G28" s="32">
-        <v>0.71589999999999998</v>
+        <v>0.75880000000000003</v>
       </c>
       <c r="H28" s="32">
-        <v>0.86639999999999995</v>
+        <v>0.87709999999999999</v>
       </c>
       <c r="I28" s="33">
-        <v>0.90869999999999995</v>
+        <v>0.9506</v>
       </c>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.25">
@@ -19832,25 +19982,25 @@
         <v>28</v>
       </c>
       <c r="C29" s="32">
-        <v>2.0594999999999999</v>
+        <v>1.9572000000000001</v>
       </c>
       <c r="D29" s="32">
-        <v>2.4260999999999999</v>
+        <v>1.9738</v>
       </c>
       <c r="E29" s="32">
-        <v>1.5224</v>
+        <v>1.3489</v>
       </c>
       <c r="F29" s="32">
-        <v>1.4556</v>
+        <v>1.3778999999999999</v>
       </c>
       <c r="G29" s="32">
-        <v>1.6882999999999999</v>
+        <v>1.5793999999999999</v>
       </c>
       <c r="H29" s="32">
-        <v>1.4552</v>
+        <v>1.4157</v>
       </c>
       <c r="I29" s="33">
-        <v>2.0737999999999999</v>
+        <v>1.8506</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.25">
@@ -19858,25 +20008,25 @@
         <v>29</v>
       </c>
       <c r="C30" s="32">
-        <v>0.9778</v>
+        <v>1.1063000000000001</v>
       </c>
       <c r="D30" s="32">
-        <v>0.49109999999999998</v>
+        <v>0.50349999999999995</v>
       </c>
       <c r="E30" s="32">
-        <v>1.1527000000000001</v>
+        <v>1.1384000000000001</v>
       </c>
       <c r="F30" s="32">
-        <v>0.50629999999999997</v>
+        <v>0.46989999999999998</v>
       </c>
       <c r="G30" s="32">
-        <v>0.68020000000000003</v>
+        <v>0.67500000000000004</v>
       </c>
       <c r="H30" s="32">
-        <v>0.77849999999999997</v>
+        <v>0.77290000000000003</v>
       </c>
       <c r="I30" s="33">
-        <v>0.77769999999999995</v>
+        <v>0.83609999999999995</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.25">
@@ -19884,25 +20034,25 @@
         <v>30</v>
       </c>
       <c r="C31" s="32">
-        <v>5.0423</v>
+        <v>4.8150000000000004</v>
       </c>
       <c r="D31" s="32">
-        <v>4.0976999999999997</v>
+        <v>3.9683999999999999</v>
       </c>
       <c r="E31" s="32">
-        <v>3.3650000000000002</v>
+        <v>3.4462000000000002</v>
       </c>
       <c r="F31" s="32">
-        <v>2.6092</v>
+        <v>2.3851</v>
       </c>
       <c r="G31" s="32">
-        <v>3.2732999999999999</v>
+        <v>3.1718999999999999</v>
       </c>
       <c r="H31" s="32">
-        <v>2.0331000000000001</v>
+        <v>1.911</v>
       </c>
       <c r="I31" s="33">
-        <v>4.2651000000000003</v>
+        <v>4.1040000000000001</v>
       </c>
     </row>
     <row r="32" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -19910,25 +20060,25 @@
         <v>31</v>
       </c>
       <c r="C32" s="35">
-        <v>1.1840999999999999</v>
+        <v>1.1960999999999999</v>
       </c>
       <c r="D32" s="35">
-        <v>1.0455000000000001</v>
+        <v>1.0232000000000001</v>
       </c>
       <c r="E32" s="35">
-        <v>0.85870000000000002</v>
+        <v>0.82350000000000001</v>
       </c>
       <c r="F32" s="35">
-        <v>0.88600000000000001</v>
+        <v>0.86899999999999999</v>
       </c>
       <c r="G32" s="35">
-        <v>1.1476999999999999</v>
+        <v>1.1217999999999999</v>
       </c>
       <c r="H32" s="35">
-        <v>0.90749999999999997</v>
+        <v>0.90990000000000004</v>
       </c>
       <c r="I32" s="36">
-        <v>1.0864</v>
+        <v>1.0797000000000001</v>
       </c>
     </row>
     <row r="33" spans="2:9" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
